--- a/docs/programs/NAS_NOTE_STUDIO_SPEC.xlsx
+++ b/docs/programs/NAS_NOTE_STUDIO_SPEC.xlsx
@@ -2,38 +2,39 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="R0324c94d997d44cc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Product_Vision" sheetId="2" r:id="Rc07f9176c0ad4e3d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decisions" sheetId="3" r:id="R5071ea3c623d47f8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Competitors" sheetId="4" r:id="Re24597d3ba624d69"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open_Source" sheetId="5" r:id="R0c07b83189634070"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source_Index" sheetId="6" r:id="R4d9f248d0c1246ab"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Information_Architecture" sheetId="7" r:id="Re65cb88cfb0f460b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI_Layout" sheetId="8" r:id="R9dc49f6773294719"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="User_Flows" sheetId="9" r:id="R61778d02b14241da"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Note_Types" sheetId="10" r:id="R74881458c0314521"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Block_Catalog" sheetId="11" r:id="Re1087b97f69f4cde"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Slash_Commands" sheetId="12" r:id="R8e7622df51654d55"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Context_Menus" sheetId="13" r:id="R8009858dcde94743"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Keyboard_Shortcuts" sheetId="14" r:id="Re05a6cd0c7134ac9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Database_Views" sheetId="15" r:id="R1a7b4d985e504701"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Code_Text_Mode" sheetId="16" r:id="R4d3cbe745a7f4c77"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Python_Notebook" sheetId="17" r:id="R11ead72f7da4438c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Collaboration" sheetId="18" r:id="Rb06694264f4447e2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Offline_Desktop" sheetId="19" r:id="Rd1011def1da144bc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data_Model" sheetId="20" r:id="R5113eca3957e465b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Storage_Interop" sheetId="21" r:id="Ra0be81ed444f4227"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Security" sheetId="22" r:id="R405f3553a0314029"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="API_Contracts" sheetId="23" r:id="R2f1b75b62b0b48a9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="State_Machines" sheetId="24" r:id="R2b67b37897ef4a4d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Error_Recovery" sheetId="25" r:id="R7639d29db8d043e8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cross_App_Relations" sheetId="26" r:id="Rb67c79d8e1bd4024"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Performance" sheetId="27" r:id="R2f6c74d2c254472c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Accessibility" sheetId="28" r:id="R28f86ac989224061"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test_Matrix" sheetId="29" r:id="R72b95b5610ea4bab"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="30" r:id="R795b108ff4724668"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open_Questions" sheetId="31" r:id="R46593580723b4291"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Change_Log" sheetId="32" r:id="R98994e1ed40f4f2b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="Rfbddb88f7f5e4e74"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Product_Vision" sheetId="2" r:id="R50e1cbed2d084d33"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decisions" sheetId="3" r:id="Ra53f84f98962423a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Competitors" sheetId="4" r:id="R3d44f46081c7453f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open_Source" sheetId="5" r:id="R641b7ddf5d5a4b22"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source_Index" sheetId="6" r:id="R203d03662f144da7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Information_Architecture" sheetId="7" r:id="R319f473c9eb84204"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI_Layout" sheetId="8" r:id="Re7423932c0184521"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="User_Flows" sheetId="9" r:id="R5d6aedf015d744c6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Note_Types" sheetId="10" r:id="Rf7defec3400f414e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Block_Catalog" sheetId="11" r:id="Rbbf9155b05b74b31"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Slash_Commands" sheetId="12" r:id="R0f548b6721194a02"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Context_Menus" sheetId="13" r:id="R2d31545797de4ace"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Keyboard_Shortcuts" sheetId="14" r:id="Rae6fb967e0f64dab"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Database_Views" sheetId="15" r:id="R2e7d2ea17ecb4be9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Code_Text_Mode" sheetId="16" r:id="R2dd7a10f4782458a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Python_Notebook" sheetId="17" r:id="R603f0f3544ec4bc4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Collaboration" sheetId="18" r:id="R98a73a42ef3c477d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Offline_Desktop" sheetId="19" r:id="Rec4be0a0813e453d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data_Model" sheetId="20" r:id="Rdb79cea11f2a4446"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Storage_Interop" sheetId="21" r:id="R7f152be831cd4e78"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Security" sheetId="22" r:id="R61d6e465f3b047db"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="API_Contracts" sheetId="23" r:id="Rbe9b11c2e16040c8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="State_Machines" sheetId="24" r:id="Rc9519dd155cc4590"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Error_Recovery" sheetId="25" r:id="R23daa2d9a7ff449c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cross_App_Relations" sheetId="26" r:id="R626ad29e11a742e9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Performance" sheetId="27" r:id="Rea79373fda6844e0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Accessibility" sheetId="28" r:id="R5244652229a84bc9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test_Matrix" sheetId="29" r:id="R88e9fdd90a6148a9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="30" r:id="Ra90ce207c84345f6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open_Questions" sheetId="31" r:id="Rf49da71d87f94ad1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Change_Log" sheetId="32" r:id="R6cd7325725944479"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Implementation_Status" sheetId="33" r:id="Ra87e55e6c9034d20"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -44,7 +45,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fonts count="3">
+  <x:fonts count="4">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -60,8 +61,14 @@
       <x:color rgb="FF0F172A"/>
       <x:name val="Aptos"/>
     </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="Carlito"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="4">
+  <x:fills count="5">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -78,8 +85,13 @@
         <x:fgColor rgb="FFF8FAFC"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF25233A"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
-  <x:borders count="3">
+  <x:borders count="4">
     <x:border/>
     <x:border>
       <x:left style="thin">
@@ -109,11 +121,25 @@
         <x:color rgb="FFCBD5E1"/>
       </x:bottom>
     </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFD8D5E5"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color rgb="FFD8D5E5"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FFD8D5E5"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFD8D5E5"/>
+      </x:bottom>
+    </x:border>
   </x:borders>
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="12">
+  <x:cellXfs count="21">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -136,6 +162,29 @@
       <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
@@ -879,7 +928,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc5de7483b89d4e68"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re69fa58db8a24c2d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1182,7 +1231,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdd0c2fa261444086"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R26476fa0c3bd4a80"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1525,7 +1574,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R31e741452f104af1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4862f791334f4b6d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1848,7 +1897,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R122c431584cd433d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8f1a3a806562471a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2193,7 +2242,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R38a0064b74584012"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R28abdabd2b374975"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2691,7 +2740,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf27118bad0124e17"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra0088dc171b84b83"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2951,7 +3000,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R476a657aa3484569"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R807e8535b10744df"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3143,7 +3192,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re3ea512e7e5e41ba"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb9bae51867a84721"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3403,7 +3452,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R729e87c954b2429b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5f66f9ab67034335"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3595,7 +3644,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb9512f8bbfa94665"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb282cd0fc88f4e43"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3787,7 +3836,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rafd19c90ca2741e3"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb4925c0fe13a4310"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3920,7 +3969,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6dcc9c1b5c5f49e3"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0e181cfd1a494e02"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4197,7 +4246,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbdbb7ed610be4b1e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2cbfe16b8def4574"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4372,7 +4421,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1590c09de1054b82"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2e065a50d4a449c1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4615,7 +4664,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb580ab12ceff465b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R447639966c3248e4"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4977,7 +5026,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd169574fc7354c50"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Reabd2e085c624d70"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5288,7 +5337,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0e1d2c7b96d24cef"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R85a27bccf18d4a8a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5514,7 +5563,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R74cb0a78a17646fc"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re8520498c8a24519"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5774,7 +5823,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9958230ce7d4465f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdaa795ba711e4cb1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5966,7 +6015,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3d95e58fc2a34545"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R662c15b1f65248d0"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6127,7 +6176,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rba31e5886eed4013"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf7a59795c8ff4f49"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6530,7 +6579,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R547860f61dde4ea2"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0f5ca955b6bf4181"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6739,7 +6788,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd663710fef3a403c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra39996ed02644d6d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6797,16 +6846,16 @@
         <x:v>M1 Core Notes</x:v>
       </x:c>
       <x:c r="B3" s="10" t="str">
-        <x:v>첫 구현</x:v>
+        <x:v>1차 핵심 기반 구현·운영 E2E 전</x:v>
       </x:c>
       <x:c r="C3" s="10" t="str">
-        <x:v>노트 shell, tree/search, block/Markdown/TXT/code, autosave, version, trash, NAS file picker/attachment, import/export 기본</x:v>
+        <x:v>개인 저장소, 앱 shell, 검색, block/Markdown/TXT/code, autosave/Ctrl+S, revision 충돌, version, trash, NAS 첨부, import/export 기본</x:v>
       </x:c>
       <x:c r="D3" s="10" t="str">
-        <x:v>계정 경계·IME·단축키·오프라인 queue·권한 E2E</x:v>
+        <x:v>자동 service·quota 회귀와 production build 통과. 다음 gate는 NAS 배포, 실제 입력·재로딩·충돌·첨부·휴지통 E2E</x:v>
       </x:c>
       <x:c r="E3" s="10" t="str">
-        <x:v>실시간 다중 편집, Python, database</x:v>
+        <x:v>실시간 다중 편집, Python, database, 고급 offline queue</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="84" customHeight="1">
@@ -6880,7 +6929,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Raca3a9cee9a3467a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R510111704d534e26"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7089,7 +7138,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R14cd1f692bf2413b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R372fe4966287440d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7149,11 +7198,228 @@
         <x:v>Codex</x:v>
       </x:c>
     </x:row>
+    <x:row r="3">
+      <x:c r="A3" s="13" t="str">
+        <x:v>2026-09-06</x:v>
+      </x:c>
+      <x:c r="B3" s="13" t="str">
+        <x:v>0.2-m1-core</x:v>
+      </x:c>
+      <x:c r="C3" s="13" t="str">
+        <x:v>M1 핵심 기반 구현·운영 E2E 전</x:v>
+      </x:c>
+      <x:c r="D3" s="13" t="str">
+        <x:v>계정별 원자 저장 API, Tiptap/Monaco 편집 UI, autosave/Ctrl+S, 충돌·버전·휴지통·검색, NAS 첨부, import/export와 플랫폼 앱 등록.</x:v>
+      </x:c>
+      <x:c r="E3" s="13" t="str">
+        <x:v>backend 11 tests 및 syntax, frontend production build 통과. 운영·브라우저 검증은 배포 직후 수행.</x:v>
+      </x:c>
+      <x:c r="F3" s="13" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1c70d77b73e741a3"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R397365aeb68a4d4a"/>
   </x:tableParts>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="12" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="25" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="42" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="42" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="42" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="15" hidden="0" customHeight="1">
+      <x:c r="A1" s="19" t="str">
+        <x:v>단계</x:v>
+      </x:c>
+      <x:c r="B1" s="19" t="str">
+        <x:v>기능 묶음</x:v>
+      </x:c>
+      <x:c r="C1" s="19" t="str">
+        <x:v>상태</x:v>
+      </x:c>
+      <x:c r="D1" s="19" t="str">
+        <x:v>구현 근거</x:v>
+      </x:c>
+      <x:c r="E1" s="19" t="str">
+        <x:v>검증</x:v>
+      </x:c>
+      <x:c r="F1" s="19" t="str">
+        <x:v>다음 게이트</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" ht="15" hidden="0" customHeight="1">
+      <x:c r="A2" s="20" t="str">
+        <x:v>M1-A</x:v>
+      </x:c>
+      <x:c r="B2" s="20" t="str">
+        <x:v>계정별 저장·권한</x:v>
+      </x:c>
+      <x:c r="C2" s="20" t="str">
+        <x:v>구현 완료</x:v>
+      </x:c>
+      <x:c r="D2" s="20" t="str">
+        <x:v>personal root/.note_studio, atomic JSON, 5MB 제한</x:v>
+      </x:c>
+      <x:c r="E2" s="20" t="str">
+        <x:v>격리·크기·원자 저장 service test</x:v>
+      </x:c>
+      <x:c r="F2" s="20" t="str">
+        <x:v>NAS 실계정 A/B 경계 E2E</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" ht="15" hidden="0" customHeight="1">
+      <x:c r="A3" s="20" t="str">
+        <x:v>M1-A</x:v>
+      </x:c>
+      <x:c r="B3" s="20" t="str">
+        <x:v>revision·버전·복구</x:v>
+      </x:c>
+      <x:c r="C3" s="20" t="str">
+        <x:v>구현 완료</x:v>
+      </x:c>
+      <x:c r="D3" s="20" t="str">
+        <x:v>expectedRevision 409, save 전 snapshot, 100개 보존</x:v>
+      </x:c>
+      <x:c r="E3" s="20" t="str">
+        <x:v>충돌·복원·retention test</x:v>
+      </x:c>
+      <x:c r="F3" s="20" t="str">
+        <x:v>두 브라우저 실제 충돌 E2E</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="15" hidden="0" customHeight="1">
+      <x:c r="A4" s="20" t="str">
+        <x:v>M1-B</x:v>
+      </x:c>
+      <x:c r="B4" s="20" t="str">
+        <x:v>앱 shell·4종 편집기</x:v>
+      </x:c>
+      <x:c r="C4" s="20" t="str">
+        <x:v>구현 완료</x:v>
+      </x:c>
+      <x:c r="D4" s="20" t="str">
+        <x:v>React/MUI, Tiptap block, Monaco md/txt/code</x:v>
+      </x:c>
+      <x:c r="E4" s="20" t="str">
+        <x:v>production build</x:v>
+      </x:c>
+      <x:c r="F4" s="20" t="str">
+        <x:v>한글 IME·커서·반응형 실화면</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A5" s="20" t="str">
+        <x:v>M1-B</x:v>
+      </x:c>
+      <x:c r="B5" s="20" t="str">
+        <x:v>자동/수동 저장</x:v>
+      </x:c>
+      <x:c r="C5" s="20" t="str">
+        <x:v>구현 완료</x:v>
+      </x:c>
+      <x:c r="D5" s="20" t="str">
+        <x:v>850ms debounce, Ctrl/Cmd+S, 저장 중 추가 입력 재저장</x:v>
+      </x:c>
+      <x:c r="E5" s="20" t="str">
+        <x:v>production build·코드 검토</x:v>
+      </x:c>
+      <x:c r="F5" s="20" t="str">
+        <x:v>네트워크 단절/복귀 E2E</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="15" hidden="0" customHeight="1">
+      <x:c r="A6" s="20" t="str">
+        <x:v>M1-C</x:v>
+      </x:c>
+      <x:c r="B6" s="20" t="str">
+        <x:v>검색·휴지통</x:v>
+      </x:c>
+      <x:c r="C6" s="20" t="str">
+        <x:v>구현 완료</x:v>
+      </x:c>
+      <x:c r="D6" s="20" t="str">
+        <x:v>제목/내용 검색, soft delete, restore, permanent delete</x:v>
+      </x:c>
+      <x:c r="E6" s="20" t="str">
+        <x:v>service test</x:v>
+      </x:c>
+      <x:c r="F6" s="20" t="str">
+        <x:v>브라우저 전 기능 E2E</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A7" s="20" t="str">
+        <x:v>M1-C</x:v>
+      </x:c>
+      <x:c r="B7" s="20" t="str">
+        <x:v>NAS 첨부·import/export</x:v>
+      </x:c>
+      <x:c r="C7" s="20" t="str">
+        <x:v>기본 구현 완료</x:v>
+      </x:c>
+      <x:c r="D7" s="20" t="str">
+        <x:v>서버 검증 상대경로 참조, 5MB UTF-8 import, 형식별 export</x:v>
+      </x:c>
+      <x:c r="E7" s="20" t="str">
+        <x:v>service attachment test·build</x:v>
+      </x:c>
+      <x:c r="F7" s="20" t="str">
+        <x:v>첨부 권한회수·이동/삭제 UX 보강</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A8" s="20" t="str">
+        <x:v>M1-D</x:v>
+      </x:c>
+      <x:c r="B8" s="20" t="str">
+        <x:v>계층 트리·slash/context menu</x:v>
+      </x:c>
+      <x:c r="C8" s="20" t="str">
+        <x:v>다음 구현</x:v>
+      </x:c>
+      <x:c r="D8" s="20" t="str">
+        <x:v>parentId 기반은 있으나 UI/순환 검사·명령 registry 미구현</x:v>
+      </x:c>
+      <x:c r="E8" s="20" t="str">
+        <x:v>미실시</x:v>
+      </x:c>
+      <x:c r="F8" s="20" t="str">
+        <x:v>M1 core 운영 E2E 통과 뒤 시작</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A9" s="20" t="str">
+        <x:v>M1-E</x:v>
+      </x:c>
+      <x:c r="B9" s="20" t="str">
+        <x:v>오프라인 queue</x:v>
+      </x:c>
+      <x:c r="C9" s="20" t="str">
+        <x:v>다음 구현</x:v>
+      </x:c>
+      <x:c r="D9" s="20" t="str">
+        <x:v>설계만 완료</x:v>
+      </x:c>
+      <x:c r="E9" s="20" t="str">
+        <x:v>미실시</x:v>
+      </x:c>
+      <x:c r="F9" s="20" t="str">
+        <x:v>IndexedDB/Yjs spike와 계정 로그아웃 cache purge gate</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
 </file>
 
@@ -7361,7 +7627,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc71d167f59ec46df"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb754d4f92bd841ee"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7644,7 +7910,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R876768797aa44ca1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re1d1b66d0db040d7"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8040,7 +8306,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc3058e29617749a6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbe5cb4a0fccc47b5"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8283,7 +8549,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdfddd28d65e24b5a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Raee7feb426e14437"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8458,7 +8724,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9353fed0645e4d35"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0436e964506b4c4d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8667,7 +8933,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf1ed4193d64943fa"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7c2fb8b6ed624b34"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/programs/NAS_NOTE_STUDIO_SPEC.xlsx
+++ b/docs/programs/NAS_NOTE_STUDIO_SPEC.xlsx
@@ -2,39 +2,39 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="Rfbddb88f7f5e4e74"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Product_Vision" sheetId="2" r:id="R50e1cbed2d084d33"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decisions" sheetId="3" r:id="Ra53f84f98962423a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Competitors" sheetId="4" r:id="R3d44f46081c7453f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open_Source" sheetId="5" r:id="R641b7ddf5d5a4b22"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source_Index" sheetId="6" r:id="R203d03662f144da7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Information_Architecture" sheetId="7" r:id="R319f473c9eb84204"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI_Layout" sheetId="8" r:id="Re7423932c0184521"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="User_Flows" sheetId="9" r:id="R5d6aedf015d744c6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Note_Types" sheetId="10" r:id="Rf7defec3400f414e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Block_Catalog" sheetId="11" r:id="Rbbf9155b05b74b31"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Slash_Commands" sheetId="12" r:id="R0f548b6721194a02"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Context_Menus" sheetId="13" r:id="R2d31545797de4ace"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Keyboard_Shortcuts" sheetId="14" r:id="Rae6fb967e0f64dab"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Database_Views" sheetId="15" r:id="R2e7d2ea17ecb4be9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Code_Text_Mode" sheetId="16" r:id="R2dd7a10f4782458a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Python_Notebook" sheetId="17" r:id="R603f0f3544ec4bc4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Collaboration" sheetId="18" r:id="R98a73a42ef3c477d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Offline_Desktop" sheetId="19" r:id="Rec4be0a0813e453d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data_Model" sheetId="20" r:id="Rdb79cea11f2a4446"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Storage_Interop" sheetId="21" r:id="R7f152be831cd4e78"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Security" sheetId="22" r:id="R61d6e465f3b047db"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="API_Contracts" sheetId="23" r:id="Rbe9b11c2e16040c8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="State_Machines" sheetId="24" r:id="Rc9519dd155cc4590"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Error_Recovery" sheetId="25" r:id="R23daa2d9a7ff449c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cross_App_Relations" sheetId="26" r:id="R626ad29e11a742e9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Performance" sheetId="27" r:id="Rea79373fda6844e0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Accessibility" sheetId="28" r:id="R5244652229a84bc9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test_Matrix" sheetId="29" r:id="R88e9fdd90a6148a9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="30" r:id="Ra90ce207c84345f6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open_Questions" sheetId="31" r:id="Rf49da71d87f94ad1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Change_Log" sheetId="32" r:id="R6cd7325725944479"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Implementation_Status" sheetId="33" r:id="Ra87e55e6c9034d20"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="R3388cf09d1e942ba"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Product_Vision" sheetId="2" r:id="R26ffcef568ed4792"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decisions" sheetId="3" r:id="R44eb0abe5b4b4bb6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Competitors" sheetId="4" r:id="Re2a40e29bfc44851"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open_Source" sheetId="5" r:id="Rca1765fe2287467d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source_Index" sheetId="6" r:id="Ra45ac2b129884309"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Information_Architecture" sheetId="7" r:id="Rbb10397d187545ff"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI_Layout" sheetId="8" r:id="Rdf860caca00642c7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="User_Flows" sheetId="9" r:id="R5173c69287b04acb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Note_Types" sheetId="10" r:id="R76a2af0bef8d4fdc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Block_Catalog" sheetId="11" r:id="Rebd7ac0e26bc4157"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Slash_Commands" sheetId="12" r:id="R87c74cfc05f443cf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Context_Menus" sheetId="13" r:id="R72dce82cb4a84814"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Keyboard_Shortcuts" sheetId="14" r:id="Ra96a082470954de1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Database_Views" sheetId="15" r:id="R6da85b3c185b4bab"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Code_Text_Mode" sheetId="16" r:id="Rdd320d7f09164493"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Python_Notebook" sheetId="17" r:id="R0a540fb89d04457f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Collaboration" sheetId="18" r:id="R5370090a194949f9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Offline_Desktop" sheetId="19" r:id="Re7243f026f6d45d9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data_Model" sheetId="20" r:id="R45957834f4944971"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Storage_Interop" sheetId="21" r:id="R75339221ac454a00"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Security" sheetId="22" r:id="Rd7ebcbee625440e1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="API_Contracts" sheetId="23" r:id="Rd18c38163dd142da"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="State_Machines" sheetId="24" r:id="Rcaa1c12c87c34223"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Error_Recovery" sheetId="25" r:id="R89346f0bc5594802"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cross_App_Relations" sheetId="26" r:id="R99f51ca7ecb44f4b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Performance" sheetId="27" r:id="R513edfe67f3e471f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Accessibility" sheetId="28" r:id="R8383051cce9c48b6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test_Matrix" sheetId="29" r:id="R4c63447f5f5f4331"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="30" r:id="R955e981af43d47bb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open_Questions" sheetId="31" r:id="R1bb968c8f2e9465d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Change_Log" sheetId="32" r:id="R9e8e0fa636c64744"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Implementation_Status" sheetId="33" r:id="Rc84b1c3708de4250"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -928,7 +928,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re69fa58db8a24c2d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R00a75e50ee454cc8"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1231,7 +1231,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R26476fa0c3bd4a80"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8c41107bb9784ae3"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1574,7 +1574,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4862f791334f4b6d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5aa118ca9fe54220"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1897,7 +1897,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8f1a3a806562471a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfa2fa22540ca4f60"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2242,7 +2242,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R28abdabd2b374975"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6425a691914e431f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2740,7 +2740,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra0088dc171b84b83"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9a1f361589284422"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3000,7 +3000,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R807e8535b10744df"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfd67ea5eb1bf4afa"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3192,7 +3192,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb9bae51867a84721"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc1f9d21b0a0c4983"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3452,7 +3452,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5f66f9ab67034335"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0d0cbcc5d7974516"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3644,7 +3644,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb282cd0fc88f4e43"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R15955edaf1924004"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3836,7 +3836,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb4925c0fe13a4310"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R70ebd467784849fb"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3969,7 +3969,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0e181cfd1a494e02"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rea1605fce42d4041"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4246,7 +4246,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2cbfe16b8def4574"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbc877bc8bd014761"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4421,7 +4421,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2e065a50d4a449c1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf83ced5d1fc04ad4"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4664,7 +4664,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R447639966c3248e4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4905f2478f1c42b5"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5026,7 +5026,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Reabd2e085c624d70"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9eff4ce2167d4e10"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5337,7 +5337,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R85a27bccf18d4a8a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7028df63f3c94892"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5563,7 +5563,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re8520498c8a24519"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5eab074d33ec414e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5823,7 +5823,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdaa795ba711e4cb1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R60199911edff4315"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6015,7 +6015,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R662c15b1f65248d0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R49fb586c42da414f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6176,7 +6176,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf7a59795c8ff4f49"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R28232aa870f342f2"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6579,7 +6579,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0f5ca955b6bf4181"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7a3d974e18e4406f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6788,7 +6788,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra39996ed02644d6d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Reca45b06e0654748"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6929,7 +6929,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R510111704d534e26"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf67b5be2a5c14d57"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7138,7 +7138,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R372fe4966287440d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R129b550b6549442a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7206,13 +7206,13 @@
         <x:v>0.2-m1-core</x:v>
       </x:c>
       <x:c r="C3" s="13" t="str">
-        <x:v>M1 핵심 기반 구현·운영 E2E 전</x:v>
+        <x:v>M1 핵심 기반 운영 배포·HTTP E2E 완료 / 로그인 실화면 E2E 전</x:v>
       </x:c>
       <x:c r="D3" s="13" t="str">
-        <x:v>계정별 원자 저장 API, Tiptap/Monaco 편집 UI, autosave/Ctrl+S, 충돌·버전·휴지통·검색, NAS 첨부, import/export와 플랫폼 앱 등록.</x:v>
+        <x:v>계정별 원자 저장 API, lazy-loaded Tiptap/Monaco 편집 UI, autosave/Ctrl+S, 충돌·버전·휴지통·검색, NAS 첨부, import/export와 플랫폼 앱 등록.</x:v>
       </x:c>
       <x:c r="E3" s="13" t="str">
-        <x:v>backend 11 tests 및 syntax, frontend production build 통과. 운영·브라우저 검증은 배포 직후 수행.</x:v>
+        <x:v>로컬·NAS 11 tests, production/PDF.js, 운영 API 전 흐름, 서비스 active, 내부·공개 200. 로그인 화면이라 사용자 인증 UI E2E는 남김.</x:v>
       </x:c>
       <x:c r="F3" s="13" t="str">
         <x:v>Codex</x:v>
@@ -7221,7 +7221,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R397365aeb68a4d4a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R27fe919ee6f64fa4"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7266,16 +7266,16 @@
         <x:v>계정별 저장·권한</x:v>
       </x:c>
       <x:c r="C2" s="20" t="str">
-        <x:v>구현 완료</x:v>
+        <x:v>운영 배포·HTTP E2E 완료</x:v>
       </x:c>
       <x:c r="D2" s="20" t="str">
         <x:v>personal root/.note_studio, atomic JSON, 5MB 제한</x:v>
       </x:c>
       <x:c r="E2" s="20" t="str">
-        <x:v>격리·크기·원자 저장 service test</x:v>
+        <x:v>격리·크기·원자 저장 service + 운영 API</x:v>
       </x:c>
       <x:c r="F2" s="20" t="str">
-        <x:v>NAS 실계정 A/B 경계 E2E</x:v>
+        <x:v>로그인 실계정 A/B 경계 E2E</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="15" hidden="0" customHeight="1">
@@ -7286,19 +7286,19 @@
         <x:v>revision·버전·복구</x:v>
       </x:c>
       <x:c r="C3" s="20" t="str">
-        <x:v>구현 완료</x:v>
+        <x:v>운영 배포·HTTP E2E 완료</x:v>
       </x:c>
       <x:c r="D3" s="20" t="str">
         <x:v>expectedRevision 409, save 전 snapshot, 100개 보존</x:v>
       </x:c>
       <x:c r="E3" s="20" t="str">
-        <x:v>충돌·복원·retention test</x:v>
+        <x:v>충돌·복원·retention + 운영 409</x:v>
       </x:c>
       <x:c r="F3" s="20" t="str">
-        <x:v>두 브라우저 실제 충돌 E2E</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" ht="15" hidden="0" customHeight="1">
+        <x:v>두 브라우저 실제 충돌 육안 E2E</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A4" s="20" t="str">
         <x:v>M1-B</x:v>
       </x:c>
@@ -7306,13 +7306,13 @@
         <x:v>앱 shell·4종 편집기</x:v>
       </x:c>
       <x:c r="C4" s="20" t="str">
-        <x:v>구현 완료</x:v>
+        <x:v>운영 배포·build 완료</x:v>
       </x:c>
       <x:c r="D4" s="20" t="str">
-        <x:v>React/MUI, Tiptap block, Monaco md/txt/code</x:v>
+        <x:v>React/MUI, Tiptap block, Monaco md/txt/code, lazy chunk</x:v>
       </x:c>
       <x:c r="E4" s="20" t="str">
-        <x:v>production build</x:v>
+        <x:v>local/NAS production build</x:v>
       </x:c>
       <x:c r="F4" s="20" t="str">
         <x:v>한글 IME·커서·반응형 실화면</x:v>
@@ -7326,13 +7326,13 @@
         <x:v>자동/수동 저장</x:v>
       </x:c>
       <x:c r="C5" s="20" t="str">
-        <x:v>구현 완료</x:v>
+        <x:v>운영 배포·HTTP E2E 완료</x:v>
       </x:c>
       <x:c r="D5" s="20" t="str">
         <x:v>850ms debounce, Ctrl/Cmd+S, 저장 중 추가 입력 재저장</x:v>
       </x:c>
       <x:c r="E5" s="20" t="str">
-        <x:v>production build·코드 검토</x:v>
+        <x:v>production build·운영 save/read</x:v>
       </x:c>
       <x:c r="F5" s="20" t="str">
         <x:v>네트워크 단절/복귀 E2E</x:v>
@@ -7346,16 +7346,16 @@
         <x:v>검색·휴지통</x:v>
       </x:c>
       <x:c r="C6" s="20" t="str">
-        <x:v>구현 완료</x:v>
+        <x:v>운영 배포·HTTP E2E 완료</x:v>
       </x:c>
       <x:c r="D6" s="20" t="str">
         <x:v>제목/내용 검색, soft delete, restore, permanent delete</x:v>
       </x:c>
       <x:c r="E6" s="20" t="str">
-        <x:v>service test</x:v>
+        <x:v>service + 운영 trash/restore/cleanup</x:v>
       </x:c>
       <x:c r="F6" s="20" t="str">
-        <x:v>브라우저 전 기능 E2E</x:v>
+        <x:v>로그인 브라우저 전 기능 E2E</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -7366,13 +7366,13 @@
         <x:v>NAS 첨부·import/export</x:v>
       </x:c>
       <x:c r="C7" s="20" t="str">
-        <x:v>기본 구현 완료</x:v>
+        <x:v>기본 운영 배포·HTTP E2E 완료</x:v>
       </x:c>
       <x:c r="D7" s="20" t="str">
         <x:v>서버 검증 상대경로 참조, 5MB UTF-8 import, 형식별 export</x:v>
       </x:c>
       <x:c r="E7" s="20" t="str">
-        <x:v>service attachment test·build</x:v>
+        <x:v>attachment service + 운영 import/export</x:v>
       </x:c>
       <x:c r="F7" s="20" t="str">
         <x:v>첨부 권한회수·이동/삭제 UX 보강</x:v>
@@ -7627,7 +7627,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb754d4f92bd841ee"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R99de5a15aeca4817"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7910,7 +7910,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re1d1b66d0db040d7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R144ae156eb8f4f33"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8306,7 +8306,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbe5cb4a0fccc47b5"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd99ea1a178f74504"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8549,7 +8549,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Raee7feb426e14437"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb34467b46ea24340"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8724,7 +8724,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0436e964506b4c4d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdce055e5ddcf4eb6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8933,7 +8933,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7c2fb8b6ed624b34"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R901d01c8d72649ce"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/programs/NAS_NOTE_STUDIO_SPEC.xlsx
+++ b/docs/programs/NAS_NOTE_STUDIO_SPEC.xlsx
@@ -2,39 +2,39 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="R3388cf09d1e942ba"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Product_Vision" sheetId="2" r:id="R26ffcef568ed4792"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decisions" sheetId="3" r:id="R44eb0abe5b4b4bb6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Competitors" sheetId="4" r:id="Re2a40e29bfc44851"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open_Source" sheetId="5" r:id="Rca1765fe2287467d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source_Index" sheetId="6" r:id="Ra45ac2b129884309"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Information_Architecture" sheetId="7" r:id="Rbb10397d187545ff"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI_Layout" sheetId="8" r:id="Rdf860caca00642c7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="User_Flows" sheetId="9" r:id="R5173c69287b04acb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Note_Types" sheetId="10" r:id="R76a2af0bef8d4fdc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Block_Catalog" sheetId="11" r:id="Rebd7ac0e26bc4157"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Slash_Commands" sheetId="12" r:id="R87c74cfc05f443cf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Context_Menus" sheetId="13" r:id="R72dce82cb4a84814"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Keyboard_Shortcuts" sheetId="14" r:id="Ra96a082470954de1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Database_Views" sheetId="15" r:id="R6da85b3c185b4bab"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Code_Text_Mode" sheetId="16" r:id="Rdd320d7f09164493"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Python_Notebook" sheetId="17" r:id="R0a540fb89d04457f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Collaboration" sheetId="18" r:id="R5370090a194949f9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Offline_Desktop" sheetId="19" r:id="Re7243f026f6d45d9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data_Model" sheetId="20" r:id="R45957834f4944971"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Storage_Interop" sheetId="21" r:id="R75339221ac454a00"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Security" sheetId="22" r:id="Rd7ebcbee625440e1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="API_Contracts" sheetId="23" r:id="Rd18c38163dd142da"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="State_Machines" sheetId="24" r:id="Rcaa1c12c87c34223"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Error_Recovery" sheetId="25" r:id="R89346f0bc5594802"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cross_App_Relations" sheetId="26" r:id="R99f51ca7ecb44f4b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Performance" sheetId="27" r:id="R513edfe67f3e471f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Accessibility" sheetId="28" r:id="R8383051cce9c48b6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test_Matrix" sheetId="29" r:id="R4c63447f5f5f4331"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="30" r:id="R955e981af43d47bb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open_Questions" sheetId="31" r:id="R1bb968c8f2e9465d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Change_Log" sheetId="32" r:id="R9e8e0fa636c64744"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Implementation_Status" sheetId="33" r:id="Rc84b1c3708de4250"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="Rc4dfc8d7546a4658"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Product_Vision" sheetId="2" r:id="R9319c56a305845fe"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decisions" sheetId="3" r:id="R4cccfc8035b94f9b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Competitors" sheetId="4" r:id="R7731c85736194d6d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open_Source" sheetId="5" r:id="R11ce828fe36a41e3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source_Index" sheetId="6" r:id="R5928ff8a1feb429d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Information_Architecture" sheetId="7" r:id="R818428598e1d405e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI_Layout" sheetId="8" r:id="Rbcdb69b13391430e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="User_Flows" sheetId="9" r:id="Rb2629f2c94604c60"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Note_Types" sheetId="10" r:id="R845bc8808a774428"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Block_Catalog" sheetId="11" r:id="Re38785f2f47d4c58"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Slash_Commands" sheetId="12" r:id="Re6facc325b1e4e6a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Context_Menus" sheetId="13" r:id="R62d5f8e4bc0c4e8d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Keyboard_Shortcuts" sheetId="14" r:id="Rbbd93eb902a242f8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Database_Views" sheetId="15" r:id="Ra9970e912d6c410b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Code_Text_Mode" sheetId="16" r:id="R4999d7f6d9f14834"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Python_Notebook" sheetId="17" r:id="R5d52463e58d44c72"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Collaboration" sheetId="18" r:id="R6a6ee02551364ef6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Offline_Desktop" sheetId="19" r:id="R8ff92f314fdc43d9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data_Model" sheetId="20" r:id="R7e76047504664151"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Storage_Interop" sheetId="21" r:id="R6fce6d512b9a450e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Security" sheetId="22" r:id="R14db1637e24e4203"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="API_Contracts" sheetId="23" r:id="Rce5e5eed026241b0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="State_Machines" sheetId="24" r:id="R2091b724beb9471e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Error_Recovery" sheetId="25" r:id="R4e3c20712ef14264"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cross_App_Relations" sheetId="26" r:id="Rbd24dc9c07774902"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Performance" sheetId="27" r:id="R9380c95eb8fa4c3f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Accessibility" sheetId="28" r:id="R1e5bdb800bf84270"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test_Matrix" sheetId="29" r:id="R0ad9a96180894fbe"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="30" r:id="R72cc5c2584824129"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open_Questions" sheetId="31" r:id="R1fea3d182cec43ea"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Change_Log" sheetId="32" r:id="Rc350a4a4a27a42bc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Implementation_Status" sheetId="33" r:id="R35b094599ad04e4c"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -928,7 +928,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R00a75e50ee454cc8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3962727bd5a04ecf"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1231,7 +1231,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8c41107bb9784ae3"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R24d3aeb6900b4613"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1574,7 +1574,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5aa118ca9fe54220"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R435ad9aee534484b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1897,7 +1897,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfa2fa22540ca4f60"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1dff5b8dda864e6c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2242,7 +2242,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6425a691914e431f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R010c32d7d7864552"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2740,7 +2740,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9a1f361589284422"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5c18efef569e4d88"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3000,7 +3000,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfd67ea5eb1bf4afa"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7bdbb59fcb7c4394"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3192,7 +3192,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc1f9d21b0a0c4983"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdc057b16c5594405"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3452,7 +3452,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0d0cbcc5d7974516"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re139a1ef4b87489b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3644,7 +3644,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R15955edaf1924004"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0e2e09daa22e4a47"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3836,7 +3836,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R70ebd467784849fb"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R29cf16042cad4c2c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3969,7 +3969,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rea1605fce42d4041"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R10f1d873168d4a46"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4246,7 +4246,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbc877bc8bd014761"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3d720b561f2440a9"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4421,7 +4421,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf83ced5d1fc04ad4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R93363e475695415b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4664,7 +4664,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4905f2478f1c42b5"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R73d6cc2230ba4a68"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5026,7 +5026,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9eff4ce2167d4e10"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf1e1d0f308ae43a0"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5337,7 +5337,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7028df63f3c94892"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re8702292413b4937"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5563,7 +5563,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5eab074d33ec414e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R95d8660f3eff4a30"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5823,7 +5823,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R60199911edff4315"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0688e22aa2774590"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6015,7 +6015,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R49fb586c42da414f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R58d5317df6ea4b0c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6176,7 +6176,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R28232aa870f342f2"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R615799c30e274511"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6579,7 +6579,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7a3d974e18e4406f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R397f9e0ff8c24c84"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6788,7 +6788,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Reca45b06e0654748"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8773ac60bc1b48cd"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6929,7 +6929,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf67b5be2a5c14d57"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R74a8e6009caa46ce"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7138,7 +7138,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R129b550b6549442a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3896267bff614a49"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7218,10 +7218,30 @@
         <x:v>Codex</x:v>
       </x:c>
     </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="13" t="str">
+        <x:v>2026-09-06</x:v>
+      </x:c>
+      <x:c r="B4" s="13" t="str">
+        <x:v>0.3-m1-tree-command</x:v>
+      </x:c>
+      <x:c r="C4" s="13" t="str">
+        <x:v>구현·자동 검증 / 운영 E2E 전</x:v>
+      </x:c>
+      <x:c r="D4" s="13" t="str">
+        <x:v>계층형 노트 표시, 하위 노트 생성, 최상위 이동, 서버 자손 순환 차단, /·Ctrl+K 블록 명령 registry.</x:v>
+      </x:c>
+      <x:c r="E4" s="13" t="str">
+        <x:v>backend note 8/8, frontend command/tree 3/3, production build.</x:v>
+      </x:c>
+      <x:c r="F4" s="13" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R27fe919ee6f64fa4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc94920e359bc45a0"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7386,16 +7406,16 @@
         <x:v>계층 트리·slash/context menu</x:v>
       </x:c>
       <x:c r="C8" s="20" t="str">
-        <x:v>다음 구현</x:v>
+        <x:v>구현·자동 검증 완료 / 운영 E2E 전</x:v>
       </x:c>
       <x:c r="D8" s="20" t="str">
-        <x:v>parentId 기반은 있으나 UI/순환 검사·명령 registry 미구현</x:v>
+        <x:v>parentId tree, 우클릭 하위 생성/최상위 이동, 자손 cycle 차단, /·Ctrl+K registry</x:v>
       </x:c>
       <x:c r="E8" s="20" t="str">
-        <x:v>미실시</x:v>
+        <x:v>backend cycle 1 + frontend registry/tree 3 tests, production build</x:v>
       </x:c>
       <x:c r="F8" s="20" t="str">
-        <x:v>M1 core 운영 E2E 통과 뒤 시작</x:v>
+        <x:v>NAS 배포와 로그인 실화면 우클릭·IME·slash E2E</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -7627,7 +7647,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R99de5a15aeca4817"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R57a60188fbaa427f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7910,7 +7930,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R144ae156eb8f4f33"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rab13ec6d237049a7"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8306,7 +8326,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd99ea1a178f74504"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc7261dcc6b134ef7"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8549,7 +8569,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb34467b46ea24340"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2d4fa0b6eef8498b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8724,7 +8744,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdce055e5ddcf4eb6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra1242bd7865141af"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8933,7 +8953,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R901d01c8d72649ce"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R37b959eae69747c0"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/programs/NAS_NOTE_STUDIO_SPEC.xlsx
+++ b/docs/programs/NAS_NOTE_STUDIO_SPEC.xlsx
@@ -2,39 +2,39 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="Rc4dfc8d7546a4658"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Product_Vision" sheetId="2" r:id="R9319c56a305845fe"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decisions" sheetId="3" r:id="R4cccfc8035b94f9b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Competitors" sheetId="4" r:id="R7731c85736194d6d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open_Source" sheetId="5" r:id="R11ce828fe36a41e3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source_Index" sheetId="6" r:id="R5928ff8a1feb429d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Information_Architecture" sheetId="7" r:id="R818428598e1d405e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI_Layout" sheetId="8" r:id="Rbcdb69b13391430e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="User_Flows" sheetId="9" r:id="Rb2629f2c94604c60"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Note_Types" sheetId="10" r:id="R845bc8808a774428"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Block_Catalog" sheetId="11" r:id="Re38785f2f47d4c58"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Slash_Commands" sheetId="12" r:id="Re6facc325b1e4e6a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Context_Menus" sheetId="13" r:id="R62d5f8e4bc0c4e8d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Keyboard_Shortcuts" sheetId="14" r:id="Rbbd93eb902a242f8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Database_Views" sheetId="15" r:id="Ra9970e912d6c410b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Code_Text_Mode" sheetId="16" r:id="R4999d7f6d9f14834"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Python_Notebook" sheetId="17" r:id="R5d52463e58d44c72"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Collaboration" sheetId="18" r:id="R6a6ee02551364ef6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Offline_Desktop" sheetId="19" r:id="R8ff92f314fdc43d9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data_Model" sheetId="20" r:id="R7e76047504664151"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Storage_Interop" sheetId="21" r:id="R6fce6d512b9a450e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Security" sheetId="22" r:id="R14db1637e24e4203"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="API_Contracts" sheetId="23" r:id="Rce5e5eed026241b0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="State_Machines" sheetId="24" r:id="R2091b724beb9471e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Error_Recovery" sheetId="25" r:id="R4e3c20712ef14264"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cross_App_Relations" sheetId="26" r:id="Rbd24dc9c07774902"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Performance" sheetId="27" r:id="R9380c95eb8fa4c3f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Accessibility" sheetId="28" r:id="R1e5bdb800bf84270"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test_Matrix" sheetId="29" r:id="R0ad9a96180894fbe"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="30" r:id="R72cc5c2584824129"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open_Questions" sheetId="31" r:id="R1fea3d182cec43ea"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Change_Log" sheetId="32" r:id="Rc350a4a4a27a42bc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Implementation_Status" sheetId="33" r:id="R35b094599ad04e4c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="R6eb9562bd73347cc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Product_Vision" sheetId="2" r:id="Rc330c3c8bff6484b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decisions" sheetId="3" r:id="Re3dbab34dbd845f8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Competitors" sheetId="4" r:id="R07214adc71b04621"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open_Source" sheetId="5" r:id="Rb5e5b6e489a2495b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source_Index" sheetId="6" r:id="R9898689c65fb4fe8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Information_Architecture" sheetId="7" r:id="R37143fb679d34166"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI_Layout" sheetId="8" r:id="Rc581f4ff979047a6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="User_Flows" sheetId="9" r:id="R99f2ec4db0b943a3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Note_Types" sheetId="10" r:id="Rb913225d6e714a37"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Block_Catalog" sheetId="11" r:id="R0a7ef228309a4d44"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Slash_Commands" sheetId="12" r:id="R77baacb8b22d4f69"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Context_Menus" sheetId="13" r:id="R47e5083b9248485c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Keyboard_Shortcuts" sheetId="14" r:id="Rdbd2bfeb347d4ef0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Database_Views" sheetId="15" r:id="R38047d44febd4700"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Code_Text_Mode" sheetId="16" r:id="Ra0ecd9ce3c274194"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Python_Notebook" sheetId="17" r:id="R8d2ba8f1f2584e66"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Collaboration" sheetId="18" r:id="R857815610de946f9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Offline_Desktop" sheetId="19" r:id="R816e29109cb04a8b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data_Model" sheetId="20" r:id="R0368505a3bf7440b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Storage_Interop" sheetId="21" r:id="R632a10277d1b4934"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Security" sheetId="22" r:id="R5cab643f232542d9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="API_Contracts" sheetId="23" r:id="Rfab52d5351404976"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="State_Machines" sheetId="24" r:id="R58231673952f4755"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Error_Recovery" sheetId="25" r:id="R95645907a75f4bc8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cross_App_Relations" sheetId="26" r:id="Rd7e9f1d3be03458d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Performance" sheetId="27" r:id="R4c138d69bb8d474a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Accessibility" sheetId="28" r:id="Rf8d9dbaf56994bdf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test_Matrix" sheetId="29" r:id="R88e9ae293c9e46ab"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="30" r:id="Rc76b38112fed49aa"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open_Questions" sheetId="31" r:id="R387c0f40ea554af0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Change_Log" sheetId="32" r:id="Rfda4fa5dd3444472"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Implementation_Status" sheetId="33" r:id="R797d2953039f4439"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -928,7 +928,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3962727bd5a04ecf"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2d03bbbbf8ec4e6e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1231,7 +1231,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R24d3aeb6900b4613"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3e2e1e9c7e9748bc"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1574,7 +1574,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R435ad9aee534484b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R46460ecb1a4e4a9d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1897,7 +1897,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1dff5b8dda864e6c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5f833838b4734d98"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2242,7 +2242,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R010c32d7d7864552"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rab5ccac86a3848d2"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2740,7 +2740,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5c18efef569e4d88"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf4842afea2bc43f0"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3000,7 +3000,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7bdbb59fcb7c4394"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8f2d23d8dd6a4631"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3192,7 +3192,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdc057b16c5594405"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4b74bee02a7f4399"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3452,7 +3452,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re139a1ef4b87489b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf0e1f34abeea4106"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3644,7 +3644,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0e2e09daa22e4a47"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5493f4fe73194ada"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3836,7 +3836,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R29cf16042cad4c2c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1e59bcd9e60b43dd"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3969,7 +3969,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R10f1d873168d4a46"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R85281a390ece445a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4246,7 +4246,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3d720b561f2440a9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb972bc0a30d349e0"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4421,7 +4421,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R93363e475695415b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R49a43bc93831467d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4664,7 +4664,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R73d6cc2230ba4a68"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re80d3ed524f74eb8"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5026,7 +5026,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf1e1d0f308ae43a0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8ceb9b1bdaca47aa"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5337,7 +5337,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re8702292413b4937"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R151174993b6c49a7"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5563,7 +5563,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R95d8660f3eff4a30"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R739e7f1623a3418d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5823,7 +5823,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0688e22aa2774590"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R824b3d2194894eca"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6015,7 +6015,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R58d5317df6ea4b0c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5fd4e69cfdba47d1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6176,7 +6176,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R615799c30e274511"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7dc33a4070d64f13"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6579,7 +6579,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R397f9e0ff8c24c84"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9f6784964ff343df"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6788,7 +6788,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8773ac60bc1b48cd"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd6adeabb1b1f4aa3"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6929,7 +6929,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R74a8e6009caa46ce"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5b8909fa322f4025"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7138,7 +7138,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3896267bff614a49"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R28c11dbc8cc54e77"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7226,13 +7226,13 @@
         <x:v>0.3-m1-tree-command</x:v>
       </x:c>
       <x:c r="C4" s="13" t="str">
-        <x:v>구현·자동 검증 / 운영 E2E 전</x:v>
+        <x:v>운영 배포·자동 검증 완료 / 로그인 실화면 전</x:v>
       </x:c>
       <x:c r="D4" s="13" t="str">
         <x:v>계층형 노트 표시, 하위 노트 생성, 최상위 이동, 서버 자손 순환 차단, /·Ctrl+K 블록 명령 registry.</x:v>
       </x:c>
       <x:c r="E4" s="13" t="str">
-        <x:v>backend note 8/8, frontend command/tree 3/3, production build.</x:v>
+        <x:v>commit 7e8caaa, NAS note 8/8, UI 3/3, production/PDF.js, live main.4dc2a7ae.js, HTTP/service 정상.</x:v>
       </x:c>
       <x:c r="F4" s="13" t="str">
         <x:v>Codex</x:v>
@@ -7241,7 +7241,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc94920e359bc45a0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R081ec9f8de494055"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7406,16 +7406,16 @@
         <x:v>계층 트리·slash/context menu</x:v>
       </x:c>
       <x:c r="C8" s="20" t="str">
-        <x:v>구현·자동 검증 완료 / 운영 E2E 전</x:v>
+        <x:v>운영 배포·자동 검증 완료 / 실화면 전</x:v>
       </x:c>
       <x:c r="D8" s="20" t="str">
         <x:v>parentId tree, 우클릭 하위 생성/최상위 이동, 자손 cycle 차단, /·Ctrl+K registry</x:v>
       </x:c>
       <x:c r="E8" s="20" t="str">
-        <x:v>backend cycle 1 + frontend registry/tree 3 tests, production build</x:v>
+        <x:v>NAS backend 8/8 + frontend 3/3 + build + HTTP/service</x:v>
       </x:c>
       <x:c r="F8" s="20" t="str">
-        <x:v>NAS 배포와 로그인 실화면 우클릭·IME·slash E2E</x:v>
+        <x:v>로그인 실화면 우클릭·IME·slash E2E</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -7647,7 +7647,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R57a60188fbaa427f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R02a4050f64f7483d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7930,7 +7930,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rab13ec6d237049a7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8bfcaa8197a745bb"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8326,7 +8326,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc7261dcc6b134ef7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4c3f4580832d4e87"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8569,7 +8569,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2d4fa0b6eef8498b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra56b5799f0ea49f2"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8744,7 +8744,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra1242bd7865141af"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R73e27692fb5b4828"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8953,7 +8953,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R37b959eae69747c0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re4d1e967b9b74a17"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/programs/NAS_NOTE_STUDIO_SPEC.xlsx
+++ b/docs/programs/NAS_NOTE_STUDIO_SPEC.xlsx
@@ -2,39 +2,39 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="R6eb9562bd73347cc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Product_Vision" sheetId="2" r:id="Rc330c3c8bff6484b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decisions" sheetId="3" r:id="Re3dbab34dbd845f8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Competitors" sheetId="4" r:id="R07214adc71b04621"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open_Source" sheetId="5" r:id="Rb5e5b6e489a2495b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source_Index" sheetId="6" r:id="R9898689c65fb4fe8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Information_Architecture" sheetId="7" r:id="R37143fb679d34166"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI_Layout" sheetId="8" r:id="Rc581f4ff979047a6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="User_Flows" sheetId="9" r:id="R99f2ec4db0b943a3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Note_Types" sheetId="10" r:id="Rb913225d6e714a37"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Block_Catalog" sheetId="11" r:id="R0a7ef228309a4d44"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Slash_Commands" sheetId="12" r:id="R77baacb8b22d4f69"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Context_Menus" sheetId="13" r:id="R47e5083b9248485c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Keyboard_Shortcuts" sheetId="14" r:id="Rdbd2bfeb347d4ef0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Database_Views" sheetId="15" r:id="R38047d44febd4700"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Code_Text_Mode" sheetId="16" r:id="Ra0ecd9ce3c274194"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Python_Notebook" sheetId="17" r:id="R8d2ba8f1f2584e66"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Collaboration" sheetId="18" r:id="R857815610de946f9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Offline_Desktop" sheetId="19" r:id="R816e29109cb04a8b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data_Model" sheetId="20" r:id="R0368505a3bf7440b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Storage_Interop" sheetId="21" r:id="R632a10277d1b4934"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Security" sheetId="22" r:id="R5cab643f232542d9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="API_Contracts" sheetId="23" r:id="Rfab52d5351404976"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="State_Machines" sheetId="24" r:id="R58231673952f4755"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Error_Recovery" sheetId="25" r:id="R95645907a75f4bc8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cross_App_Relations" sheetId="26" r:id="Rd7e9f1d3be03458d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Performance" sheetId="27" r:id="R4c138d69bb8d474a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Accessibility" sheetId="28" r:id="Rf8d9dbaf56994bdf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test_Matrix" sheetId="29" r:id="R88e9ae293c9e46ab"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="30" r:id="Rc76b38112fed49aa"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open_Questions" sheetId="31" r:id="R387c0f40ea554af0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Change_Log" sheetId="32" r:id="Rfda4fa5dd3444472"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Implementation_Status" sheetId="33" r:id="R797d2953039f4439"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="R33e105af35254e26"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Product_Vision" sheetId="2" r:id="Rbff19c2ac483427a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decisions" sheetId="3" r:id="Radf2fad0283842bb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Competitors" sheetId="4" r:id="R1121be17aeb542c1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open_Source" sheetId="5" r:id="Raac83768e7fe45a7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source_Index" sheetId="6" r:id="Rc870cd1eed094d14"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Information_Architecture" sheetId="7" r:id="R7a80a97d14ce471a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI_Layout" sheetId="8" r:id="R79405ef728dd4b9f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="User_Flows" sheetId="9" r:id="R7923f8063aa34fa7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Note_Types" sheetId="10" r:id="R39a4b8b6a4fa4b41"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Block_Catalog" sheetId="11" r:id="R3fabb14ac30c448c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Slash_Commands" sheetId="12" r:id="R57abd8c952a447ae"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Context_Menus" sheetId="13" r:id="Rd9a239a87d254b98"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Keyboard_Shortcuts" sheetId="14" r:id="R654dcb37a5a64281"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Database_Views" sheetId="15" r:id="R84f7d5a8d3754a58"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Code_Text_Mode" sheetId="16" r:id="R8628dc79dc9e48bb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Python_Notebook" sheetId="17" r:id="Rf492ada1743d4f19"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Collaboration" sheetId="18" r:id="R757a3e35bb484ec6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Offline_Desktop" sheetId="19" r:id="Rc8102fcef9604dc9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data_Model" sheetId="20" r:id="Rd562f07847ec42ab"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Storage_Interop" sheetId="21" r:id="Rbe8a0d902e864a3b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Security" sheetId="22" r:id="Ree6e6f88c1554c70"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="API_Contracts" sheetId="23" r:id="Ra95ffcfad5914e1d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="State_Machines" sheetId="24" r:id="R8dd9a86f87cf4d32"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Error_Recovery" sheetId="25" r:id="Rbac6869efdbb4422"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cross_App_Relations" sheetId="26" r:id="R968beef32bdf4912"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Performance" sheetId="27" r:id="R6b76cbf2ca884b6f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Accessibility" sheetId="28" r:id="R5cd7c64750e64886"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test_Matrix" sheetId="29" r:id="Rbf78a13943e3411e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="30" r:id="R81c9f4429595416f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open_Questions" sheetId="31" r:id="Rf5654a5927524968"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Change_Log" sheetId="32" r:id="Rda03175fda5d4556"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Implementation_Status" sheetId="33" r:id="R920fb7b5b5db4b92"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -928,7 +928,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2d03bbbbf8ec4e6e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R12d4df722e2444b5"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1228,10 +1228,50 @@
         <x:v>M2</x:v>
       </x:c>
     </x:row>
+    <x:row r="15">
+      <x:c r="A15" s="13" t="str">
+        <x:v>python-page</x:v>
+      </x:c>
+      <x:c r="B15" s="13" t="str">
+        <x:v>Python 실행 페이지</x:v>
+      </x:c>
+      <x:c r="C15" s="13" t="str">
+        <x:v>텍스트·제목·목록·파일·하위 페이지·Office 문서 reference와 실행 Python 셀을 섞는 rich page</x:v>
+      </x:c>
+      <x:c r="D15" s="13" t="str">
+        <x:v>Block canvas + cell editor + NAS kernel</x:v>
+      </x:c>
+      <x:c r="E15" s="13" t="str">
+        <x:v>MSP page/IPYNB/분리 PY+MD projection</x:v>
+      </x:c>
+      <x:c r="F15" s="13" t="str">
+        <x:v>M2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" s="13" t="str">
+        <x:v>notebook-root</x:v>
+      </x:c>
+      <x:c r="B16" s="13" t="str">
+        <x:v>노트북 작업공간</x:v>
+      </x:c>
+      <x:c r="C16" s="13" t="str">
+        <x:v>페이지 트리, 일반 파일, src/data/notebooks/references, 환경 선언을 담는 사용자 루트 폴더</x:v>
+      </x:c>
+      <x:c r="D16" s="13" t="str">
+        <x:v>Tree + file/page adapters</x:v>
+      </x:c>
+      <x:c r="E16" s="13" t="str">
+        <x:v>일반 폴더 bundle/manifest</x:v>
+      </x:c>
+      <x:c r="F16" s="13" t="str">
+        <x:v>M1 확장</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3e2e1e9c7e9748bc"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdec4f685a2ed41a1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1571,10 +1611,70 @@
         <x:v>M3</x:v>
       </x:c>
     </x:row>
+    <x:row r="17">
+      <x:c r="A17" s="13" t="str">
+        <x:v>Structure</x:v>
+      </x:c>
+      <x:c r="B17" s="13" t="str">
+        <x:v>Office document reference</x:v>
+      </x:c>
+      <x:c r="C17" s="13" t="str">
+        <x:v>/document 또는 우클릭 삽입 &gt; 문서 만들기</x:v>
+      </x:c>
+      <x:c r="D17" s="13" t="str">
+        <x:v>DOCX/XLSX/PPTX/HWP/HWPX 생성, stable document ID, 현재 경로·저장 상태, 클릭 전면 열기</x:v>
+      </x:c>
+      <x:c r="E17" s="13" t="str">
+        <x:v>Markdown fallback link + manifest</x:v>
+      </x:c>
+      <x:c r="F17" s="13" t="str">
+        <x:v>M1 확장</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" s="13" t="str">
+        <x:v>Collaboration</x:v>
+      </x:c>
+      <x:c r="B18" s="13" t="str">
+        <x:v>Comment anchor</x:v>
+      </x:c>
+      <x:c r="C18" s="13" t="str">
+        <x:v>선택 후 댓글 또는 Ctrl+Shift+M</x:v>
+      </x:c>
+      <x:c r="D18" s="13" t="str">
+        <x:v>페이지·block·inline·code range thread, 답글, mention, resolve/reopen</x:v>
+      </x:c>
+      <x:c r="E18" s="13" t="str">
+        <x:v>본문 export에서 기본 제외, 별도 comment archive 선택</x:v>
+      </x:c>
+      <x:c r="F18" s="13" t="str">
+        <x:v>M1.5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19" s="13" t="str">
+        <x:v>Code</x:v>
+      </x:c>
+      <x:c r="B19" s="13" t="str">
+        <x:v>Rich Python page blocks</x:v>
+      </x:c>
+      <x:c r="C19" s="13" t="str">
+        <x:v>/python-cell과 일반 block 혼합</x:v>
+      </x:c>
+      <x:c r="D19" s="13" t="str">
+        <x:v>실행기는 Python cell만 순서대로 실행하고 문서·링크·버튼 block은 실행하지 않음</x:v>
+      </x:c>
+      <x:c r="E19" s="13" t="str">
+        <x:v>IPYNB 또는 PY+MD+manifest</x:v>
+      </x:c>
+      <x:c r="F19" s="13" t="str">
+        <x:v>M2</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R46460ecb1a4e4a9d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfb31bd394658453b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1894,10 +1994,70 @@
         <x:v>M3</x:v>
       </x:c>
     </x:row>
+    <x:row r="16">
+      <x:c r="A16" s="13" t="str">
+        <x:v>파일·문서</x:v>
+      </x:c>
+      <x:c r="B16" s="13" t="str">
+        <x:v>/document</x:v>
+      </x:c>
+      <x:c r="C16" s="13" t="str">
+        <x:v>문서 만들기</x:v>
+      </x:c>
+      <x:c r="D16" s="13" t="str">
+        <x:v>현재 caret/block 또는 선택 폴더</x:v>
+      </x:c>
+      <x:c r="E16" s="13" t="str">
+        <x:v>DOCX/XLSX/PPTX/HWP/HWPX 선택 후 draft 생성</x:v>
+      </x:c>
+      <x:c r="F16" s="13" t="str">
+        <x:v>M1 확장</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" s="13" t="str">
+        <x:v>파일·문서</x:v>
+      </x:c>
+      <x:c r="B17" s="13" t="str">
+        <x:v>/link-document</x:v>
+      </x:c>
+      <x:c r="C17" s="13" t="str">
+        <x:v>기존 NAS 문서 연결</x:v>
+      </x:c>
+      <x:c r="D17" s="13" t="str">
+        <x:v>note edit + file read 권한</x:v>
+      </x:c>
+      <x:c r="E17" s="13" t="str">
+        <x:v>stable document reference block 삽입</x:v>
+      </x:c>
+      <x:c r="F17" s="13" t="str">
+        <x:v>M1 확장</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" s="13" t="str">
+        <x:v>협업</x:v>
+      </x:c>
+      <x:c r="B18" s="13" t="str">
+        <x:v>/comment</x:v>
+      </x:c>
+      <x:c r="C18" s="13" t="str">
+        <x:v>선택 영역에 댓글</x:v>
+      </x:c>
+      <x:c r="D18" s="13" t="str">
+        <x:v>comment 권한과 selection</x:v>
+      </x:c>
+      <x:c r="E18" s="13" t="str">
+        <x:v>anchor thread 열기</x:v>
+      </x:c>
+      <x:c r="F18" s="13" t="str">
+        <x:v>M1.5</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5f833838b4734d98"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdb4cf5bb05014f0f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2239,10 +2399,78 @@
         <x:v>삭제된 파일은 broken reference와 복구 경로</x:v>
       </x:c>
     </x:row>
+    <x:row r="20">
+      <x:c r="A20" s="13" t="str">
+        <x:v>노트북 폴더/파일 영역</x:v>
+      </x:c>
+      <x:c r="B20" s="13" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C20" s="13" t="str">
+        <x:v>새 페이지 / 새 폴더 / 문서 만들기</x:v>
+      </x:c>
+      <x:c r="D20" s="13" t="str">
+        <x:v>생성 권한</x:v>
+      </x:c>
+      <x:c r="E20" s="13" t="str">
+        <x:v>우클릭한 invocation directory를 draft 기본 저장 위치로 기억</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21">
+      <x:c r="A21" s="13" t="str">
+        <x:v>블록 핸들/본문 caret</x:v>
+      </x:c>
+      <x:c r="B21" s="13" t="str">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C21" s="13" t="str">
+        <x:v>하위 페이지 / Office 문서 / 기존 NAS 문서 연결</x:v>
+      </x:c>
+      <x:c r="D21" s="13" t="str">
+        <x:v>note edit + target create/read 권한</x:v>
+      </x:c>
+      <x:c r="E21" s="13" t="str">
+        <x:v>현재 위치에 page 또는 document reference block 삽입</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22">
+      <x:c r="A22" s="13" t="str">
+        <x:v>문서 reference</x:v>
+      </x:c>
+      <x:c r="B22" s="13" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C22" s="13" t="str">
+        <x:v>열기 / NAS에서 보기 / 위치 복사 / 다시 연결</x:v>
+      </x:c>
+      <x:c r="D22" s="13" t="str">
+        <x:v>대상 read 권한</x:v>
+      </x:c>
+      <x:c r="E22" s="13" t="str">
+        <x:v>지원 편집기를 전면 열고 stable ID를 서버에서 재해석</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23">
+      <x:c r="A23" s="13" t="str">
+        <x:v>문서 reference</x:v>
+      </x:c>
+      <x:c r="B23" s="13" t="str">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C23" s="13" t="str">
+        <x:v>링크 제거 / 링크와 파일 함께 삭제</x:v>
+      </x:c>
+      <x:c r="D23" s="13" t="str">
+        <x:v>note edit; 실제 삭제는 file delete 권한</x:v>
+      </x:c>
+      <x:c r="E23" s="13" t="str">
+        <x:v>기본은 링크만 제거. 함께 삭제는 확인 후 휴지통</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rab5ccac86a3848d2"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf599bc839e914f09"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2740,7 +2968,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf4842afea2bc43f0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc1c0ea63ec7f49e0"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3000,7 +3228,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8f2d23d8dd6a4631"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R60e20feff95e4feb"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3192,7 +3420,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4b74bee02a7f4399"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0c29b0107ef041e5"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3449,10 +3677,78 @@
         <x:v>M2</x:v>
       </x:c>
     </x:row>
+    <x:row r="15">
+      <x:c r="A15" s="13" t="str">
+        <x:v>혼합 페이지</x:v>
+      </x:c>
+      <x:c r="B15" s="13" t="str">
+        <x:v>일반 block + Python cell</x:v>
+      </x:c>
+      <x:c r="C15" s="13" t="str">
+        <x:v>페이지 링크·텍스트·이미지·Office reference와 code cell을 한 페이지에 배치하고 실행기는 code cell만 처리.</x:v>
+      </x:c>
+      <x:c r="D15" s="13" t="str">
+        <x:v>숨겨진 실행 상태와 block action이 코드로 섞이지 않음.</x:v>
+      </x:c>
+      <x:c r="E15" s="13" t="str">
+        <x:v>M2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" s="13" t="str">
+        <x:v>원격 실행</x:v>
+      </x:c>
+      <x:c r="B16" s="13" t="str">
+        <x:v>NAS workspace 실행</x:v>
+      </x:c>
+      <x:c r="C16" s="13" t="str">
+        <x:v>NAS 경로는 그대로 유지하고 PC는 편집·요청·stdout/stderr/rich output stream만 담당.</x:v>
+      </x:c>
+      <x:c r="D16" s="13" t="str">
+        <x:v>임의 로컬 앱 실행을 원격으로 가장하지 않고 공식 VS Code/Driver/Studio 관문만 지원.</x:v>
+      </x:c>
+      <x:c r="E16" s="13" t="str">
+        <x:v>M2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" s="13" t="str">
+        <x:v>자원 감지</x:v>
+      </x:c>
+      <x:c r="B17" s="13" t="str">
+        <x:v>동적 admission</x:v>
+      </x:c>
+      <x:c r="C17" s="13" t="str">
+        <x:v>매 배정 시 MemAvailable, CPU load, swap pressure, disk reserve, 온도, active/reserved 작업을 재측정.</x:v>
+      </x:c>
+      <x:c r="D17" s="13" t="str">
+        <x:v>현재 초기 전역 1·계정당 1. 증설은 OS 인식 후 계산하되 GPU capability는 MASTER 승인 전 차단.</x:v>
+      </x:c>
+      <x:c r="E17" s="13" t="str">
+        <x:v>M2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" s="13" t="str">
+        <x:v>로컬 투영</x:v>
+      </x:c>
+      <x:c r="B18" s="13" t="str">
+        <x:v>PY+MD+assets+manifest</x:v>
+      </x:c>
+      <x:c r="C18" s="13" t="str">
+        <x:v>stable block/cell marker, revision/hash/base snapshot으로 round-trip.</x:v>
+      </x:c>
+      <x:c r="D18" s="13" t="str">
+        <x:v>동시 수정은 자동 덮어쓰기 금지. rich-only block은 manifest 보존.</x:v>
+      </x:c>
+      <x:c r="E18" s="13" t="str">
+        <x:v>M2</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf0e1f34abeea4106"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb1dca47cee9a4be0"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3641,10 +3937,78 @@
         <x:v>unknown nodes round-trip 보존</x:v>
       </x:c>
     </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="13" t="str">
+        <x:v>댓글 범위</x:v>
+      </x:c>
+      <x:c r="B11" s="13" t="str">
+        <x:v>page discussion, block, inline text, Python cell/code range</x:v>
+      </x:c>
+      <x:c r="C11" s="13" t="str">
+        <x:v>NoteComment thread와 stable block/cell ID, 선택 anchor/context를 저장한다.</x:v>
+      </x:c>
+      <x:c r="D11" s="13" t="str">
+        <x:v>다른 계정·권한 회수 시 본문이나 댓글 preview를 노출하지 않는다.</x:v>
+      </x:c>
+      <x:c r="E11" s="13" t="str">
+        <x:v>M1.5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="13" t="str">
+        <x:v>댓글 수명</x:v>
+      </x:c>
+      <x:c r="B12" s="13" t="str">
+        <x:v>답글·mention·알림·resolve/reopen·수정·삭제</x:v>
+      </x:c>
+      <x:c r="C12" s="13" t="str">
+        <x:v>작성자·시간·권한·감사를 보존하고 해결된 thread도 조회 가능하게 한다.</x:v>
+      </x:c>
+      <x:c r="D12" s="13" t="str">
+        <x:v>삭제 사용자 표시와 알림 중복 정책을 고정한다.</x:v>
+      </x:c>
+      <x:c r="E12" s="13" t="str">
+        <x:v>M1.5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" s="13" t="str">
+        <x:v>anchor 복구</x:v>
+      </x:c>
+      <x:c r="B13" s="13" t="str">
+        <x:v>본문 또는 코드 변경 뒤 위치 추적</x:v>
+      </x:c>
+      <x:c r="C13" s="13" t="str">
+        <x:v>block ID와 앞뒤 문맥을 사용하고 확신할 수 없으면 위치 변경됨으로 표시한다.</x:v>
+      </x:c>
+      <x:c r="D13" s="13" t="str">
+        <x:v>비슷한 문장이 있어도 추측 재부착하지 않는다.</x:v>
+      </x:c>
+      <x:c r="E13" s="13" t="str">
+        <x:v>M1.5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" s="13" t="str">
+        <x:v>실제 소스 주석</x:v>
+      </x:c>
+      <x:c r="B14" s="13" t="str">
+        <x:v>.py # 등 언어 문법</x:v>
+      </x:c>
+      <x:c r="C14" s="13" t="str">
+        <x:v>review thread와 분리해 로컬 파일 round-trip에 포함한다.</x:v>
+      </x:c>
+      <x:c r="D14" s="13" t="str">
+        <x:v>검토 댓글을 source text로 자동 삽입하지 않는다.</x:v>
+      </x:c>
+      <x:c r="E14" s="13" t="str">
+        <x:v>M2</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5493f4fe73194ada"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra68c384b88a64abf"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3836,7 +4200,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1e59bcd9e60b43dd"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf067d158fbca4abd"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3969,7 +4333,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R85281a390ece445a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2a117e9de74040dd"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4243,10 +4607,112 @@
         <x:v>높음</x:v>
       </x:c>
     </x:row>
+    <x:row r="16">
+      <x:c r="A16" s="13" t="str">
+        <x:v>NotebookWorkspace</x:v>
+      </x:c>
+      <x:c r="B16" s="13" t="str">
+        <x:v>id, ownerUid, title, rootDirectoryId, schemaVersion, executionPolicy, timestamps</x:v>
+      </x:c>
+      <x:c r="C16" s="13" t="str">
+        <x:v>사용자 personal root 안의 stable directory identity와 연결</x:v>
+      </x:c>
+      <x:c r="D16" s="13" t="str">
+        <x:v>owner+rootDirectoryId</x:v>
+      </x:c>
+      <x:c r="E16" s="13" t="str">
+        <x:v>높음</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" s="13" t="str">
+        <x:v>PageProjection</x:v>
+      </x:c>
+      <x:c r="B17" s="13" t="str">
+        <x:v>pageId, clientId, serverRevision, baseHash, pyPath, mdPath, manifestPath, status</x:v>
+      </x:c>
+      <x:c r="C17" s="13" t="str">
+        <x:v>서버 rich page가 기준이며 로컬 두 파일을 독립 원본으로 취급하지 않음</x:v>
+      </x:c>
+      <x:c r="D17" s="13" t="str">
+        <x:v>page+client+revision</x:v>
+      </x:c>
+      <x:c r="E17" s="13" t="str">
+        <x:v>높음</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" s="13" t="str">
+        <x:v>DocumentIdentity</x:v>
+      </x:c>
+      <x:c r="B18" s="13" t="str">
+        <x:v>documentId, ownerUid, fileId, currentPath, revision, state</x:v>
+      </x:c>
+      <x:c r="C18" s="13" t="str">
+        <x:v>이동·이름 변경 후에도 같은 실제 파일을 가리킴</x:v>
+      </x:c>
+      <x:c r="D18" s="13" t="str">
+        <x:v>fileId/path 역색인</x:v>
+      </x:c>
+      <x:c r="E18" s="13" t="str">
+        <x:v>높음</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19" s="13" t="str">
+        <x:v>DocumentReferenceBlock</x:v>
+      </x:c>
+      <x:c r="B19" s="13" t="str">
+        <x:v>blockId, noteId, documentId, displayName, lastKnownPath</x:v>
+      </x:c>
+      <x:c r="C19" s="13" t="str">
+        <x:v>대상 권한을 상속하거나 파일을 복제하지 않음</x:v>
+      </x:c>
+      <x:c r="D19" s="13" t="str">
+        <x:v>document backlink</x:v>
+      </x:c>
+      <x:c r="E19" s="13" t="str">
+        <x:v>높음</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20" s="13" t="str">
+        <x:v>CommentAnchor</x:v>
+      </x:c>
+      <x:c r="B20" s="13" t="str">
+        <x:v>threadId, blockId, cellId, from/to, quote, prefix, suffix, anchorState</x:v>
+      </x:c>
+      <x:c r="C20" s="13" t="str">
+        <x:v>불확실한 재부착 금지</x:v>
+      </x:c>
+      <x:c r="D20" s="13" t="str">
+        <x:v>thread+block/cell</x:v>
+      </x:c>
+      <x:c r="E20" s="13" t="str">
+        <x:v>높음</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21">
+      <x:c r="A21" s="13" t="str">
+        <x:v>ExecutionCapability</x:v>
+      </x:c>
+      <x:c r="B21" s="13" t="str">
+        <x:v>subjectId, capability, grantedByMaster, limits, expiresAt, revokedAt</x:v>
+      </x:c>
+      <x:c r="C21" s="13" t="str">
+        <x:v>GPU/CUDA/high-load 권한은 MASTER만 부여·회수</x:v>
+      </x:c>
+      <x:c r="D21" s="13" t="str">
+        <x:v>subject+capability</x:v>
+      </x:c>
+      <x:c r="E21" s="13" t="str">
+        <x:v>매우 높음</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb972bc0a30d349e0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R934c0cfb873142b3"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4418,10 +4884,78 @@
         <x:v>STORAGE-CAPACITY-ALLOCATION</x:v>
       </x:c>
     </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="13" t="str">
+        <x:v>노트북 물리 루트</x:v>
+      </x:c>
+      <x:c r="B10" s="13" t="str">
+        <x:v>NOTE MANAGER/&lt;노트북 이름&gt;</x:v>
+      </x:c>
+      <x:c r="C10" s="13" t="str">
+        <x:v>페이지 marker가 있는 폴더와 일반 src/data/reference/env 파일을 함께 허용</x:v>
+      </x:c>
+      <x:c r="D10" s="13" t="str">
+        <x:v>노트북 밖 상대경로 이탈은 명시 연결 없이는 금지</x:v>
+      </x:c>
+      <x:c r="E10" s="13" t="str">
+        <x:v>M1 확장</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="13" t="str">
+        <x:v>Python 페이지 로컬 투영</x:v>
+      </x:c>
+      <x:c r="B11" s="13" t="str">
+        <x:v>&lt;페이지&gt;/&lt;페이지&gt;.py + .md + assets + .msp-page.json</x:v>
+      </x:c>
+      <x:c r="C11" s="13" t="str">
+        <x:v>PY에는 코드만, MD에는 표준 문서 block, 고급 block은 manifest</x:v>
+      </x:c>
+      <x:c r="D11" s="13" t="str">
+        <x:v>atomic write, hash, revision, base snapshot, conflict copy</x:v>
+      </x:c>
+      <x:c r="E11" s="13" t="str">
+        <x:v>M2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="13" t="str">
+        <x:v>환경 파일</x:v>
+      </x:c>
+      <x:c r="B12" s="13" t="str">
+        <x:v>.env.example 동기화, 실제 secret은 장치/서버 비밀 저장소</x:v>
+      </x:c>
+      <x:c r="C12" s="13" t="str">
+        <x:v>실행 때 환경변수로 주입하고 공유·Git·일반 동기화에서 제외</x:v>
+      </x:c>
+      <x:c r="D12" s="13" t="str">
+        <x:v>secret 포함 .env 자동 공유 금지</x:v>
+      </x:c>
+      <x:c r="E12" s="13" t="str">
+        <x:v>M2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" s="13" t="str">
+        <x:v>Office 문서 연결</x:v>
+      </x:c>
+      <x:c r="B13" s="13" t="str">
+        <x:v>호출 폴더 또는 사용자가 고른 계정 내 NAS 경로</x:v>
+      </x:c>
+      <x:c r="C13" s="13" t="str">
+        <x:v>실제 파일 하나와 stable document reference 사용</x:v>
+      </x:c>
+      <x:c r="D13" s="13" t="str">
+        <x:v>복제 금지, 이동·이름 변경 registry 갱신</x:v>
+      </x:c>
+      <x:c r="E13" s="13" t="str">
+        <x:v>M1 확장</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R49a43bc93831467d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R42a7fa329dc54920"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4661,10 +5195,78 @@
         <x:v>P0</x:v>
       </x:c>
     </x:row>
+    <x:row r="14">
+      <x:c r="A14" s="13" t="str">
+        <x:v>SEC-13</x:v>
+      </x:c>
+      <x:c r="B14" s="13" t="str">
+        <x:v>동적 실행 자원 고갈과 서비스 starvation</x:v>
+      </x:c>
+      <x:c r="C14" s="13" t="str">
+        <x:v>실제 cgroup/OS 지표 기반 예약 admission, 공정 대기열, 일반 서비스 reserve, timeout/OOM/출력 제한.</x:v>
+      </x:c>
+      <x:c r="D14" s="13" t="str">
+        <x:v>동시 사용자, swap 압박, disk full, 온도, worker crash 부하 테스트</x:v>
+      </x:c>
+      <x:c r="E14" s="13" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" s="13" t="str">
+        <x:v>SEC-14</x:v>
+      </x:c>
+      <x:c r="B15" s="13" t="str">
+        <x:v>GPU/CUDA·고부하 capability 오남용</x:v>
+      </x:c>
+      <x:c r="C15" s="13" t="str">
+        <x:v>기본 차단. MANAGER도 부여 불가, MASTER만 self-test·limit·만료를 포함해 계정별 허용.</x:v>
+      </x:c>
+      <x:c r="D15" s="13" t="str">
+        <x:v>권한 상승·만료·회수·감사 회귀</x:v>
+      </x:c>
+      <x:c r="E15" s="13" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" s="13" t="str">
+        <x:v>SEC-15</x:v>
+      </x:c>
+      <x:c r="B16" s="13" t="str">
+        <x:v>local projection이 서버/다른 변경을 덮어씀</x:v>
+      </x:c>
+      <x:c r="C16" s="13" t="str">
+        <x:v>base revision/hash 3-way merge, 원자 교체, 충돌 복사본, rich-only block 보존.</x:v>
+      </x:c>
+      <x:c r="D16" s="13" t="str">
+        <x:v>동시 NAS/PC 편집과 중단·재시작</x:v>
+      </x:c>
+      <x:c r="E16" s="13" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" s="13" t="str">
+        <x:v>SEC-16</x:v>
+      </x:c>
+      <x:c r="B17" s="13" t="str">
+        <x:v>Office draft가 다른 경로나 계정에 저장됨</x:v>
+      </x:c>
+      <x:c r="C17" s="13" t="str">
+        <x:v>invocation directory stable ID, first-save realpath/symlink/quota 재검증, 실패 시 위치 재선택.</x:v>
+      </x:c>
+      <x:c r="D17" s="13" t="str">
+        <x:v>폴더 이동·삭제·권한 회수·이름 충돌</x:v>
+      </x:c>
+      <x:c r="E17" s="13" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re80d3ed524f74eb8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8b80ddd6b52e4bb6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5023,10 +5625,112 @@
         <x:v>file read + note edit + quota</x:v>
       </x:c>
     </x:row>
+    <x:row r="21">
+      <x:c r="A21" s="13" t="str">
+        <x:v>Notebook</x:v>
+      </x:c>
+      <x:c r="B21" s="13" t="str">
+        <x:v>POST /api/notebooks/:id/projections</x:v>
+      </x:c>
+      <x:c r="C21" s="13" t="str">
+        <x:v>clientId, serverRevision, formats, idempotencyKey</x:v>
+      </x:c>
+      <x:c r="D21" s="13" t="str">
+        <x:v>projection descriptor/job</x:v>
+      </x:c>
+      <x:c r="E21" s="13" t="str">
+        <x:v>read/edit 권한, revision precondition</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22">
+      <x:c r="A22" s="13" t="str">
+        <x:v>Notebook</x:v>
+      </x:c>
+      <x:c r="B22" s="13" t="str">
+        <x:v>POST /api/notebooks/:id/execution-admission</x:v>
+      </x:c>
+      <x:c r="C22" s="13" t="str">
+        <x:v>environment, requestedResources, capability</x:v>
+      </x:c>
+      <x:c r="D22" s="13" t="str">
+        <x:v>queued/reserved/denied와 이유</x:v>
+      </x:c>
+      <x:c r="E22" s="13" t="str">
+        <x:v>execute 권한, MASTER capability, request dedupe</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23">
+      <x:c r="A23" s="13" t="str">
+        <x:v>Documents</x:v>
+      </x:c>
+      <x:c r="B23" s="13" t="str">
+        <x:v>POST /api/notes/:id/documents</x:v>
+      </x:c>
+      <x:c r="C23" s="13" t="str">
+        <x:v>format, invocationDirectoryId, caret/block anchor, draftId, idempotencyKey</x:v>
+      </x:c>
+      <x:c r="D23" s="13" t="str">
+        <x:v>draft/document reference descriptor</x:v>
+      </x:c>
+      <x:c r="E23" s="13" t="str">
+        <x:v>note edit + directory create + quota, 원자 생성/연결</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24">
+      <x:c r="A24" s="13" t="str">
+        <x:v>Documents</x:v>
+      </x:c>
+      <x:c r="B24" s="13" t="str">
+        <x:v>POST /api/note-document-drafts/:id/publish</x:v>
+      </x:c>
+      <x:c r="C24" s="13" t="str">
+        <x:v>name, targetDirectoryId, expectedPageRevision</x:v>
+      </x:c>
+      <x:c r="D24" s="13" t="str">
+        <x:v>documentId, currentPath, reference block</x:v>
+      </x:c>
+      <x:c r="E24" s="13" t="str">
+        <x:v>realpath/quota/extension, 반복 publish 안전</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25">
+      <x:c r="A25" s="13" t="str">
+        <x:v>Documents</x:v>
+      </x:c>
+      <x:c r="B25" s="13" t="str">
+        <x:v>GET /api/documents/:documentId/resolve</x:v>
+      </x:c>
+      <x:c r="C25" s="13" t="str">
+        <x:v>knownRevision</x:v>
+      </x:c>
+      <x:c r="D25" s="13" t="str">
+        <x:v>현재 path/state/editor kind</x:v>
+      </x:c>
+      <x:c r="E25" s="13" t="str">
+        <x:v>document read 권한, 경로 정보 최소화</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26">
+      <x:c r="A26" s="13" t="str">
+        <x:v>Comments</x:v>
+      </x:c>
+      <x:c r="B26" s="13" t="str">
+        <x:v>PATCH /api/note-comments/:threadId</x:v>
+      </x:c>
+      <x:c r="C26" s="13" t="str">
+        <x:v>body/resolve/reopen/anchor repair</x:v>
+      </x:c>
+      <x:c r="D26" s="13" t="str">
+        <x:v>thread revision</x:v>
+      </x:c>
+      <x:c r="E26" s="13" t="str">
+        <x:v>author/comment 권한, If-Match</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8ceb9b1bdaca47aa"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5fb3a66fdd5541f7"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5337,7 +6041,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R151174993b6c49a7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcddab77635e8401b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5560,10 +6264,95 @@
         <x:v>웹/WS/worker health</x:v>
       </x:c>
     </x:row>
+    <x:row r="13">
+      <x:c r="A13" s="13" t="str">
+        <x:v>투영 중 NAS·PC 동시 수정</x:v>
+      </x:c>
+      <x:c r="B13" s="13" t="str">
+        <x:v>base snapshot 기준 코드·문서별 3-way diff</x:v>
+      </x:c>
+      <x:c r="C13" s="13" t="str">
+        <x:v>내 사본/서버 사본/수동 병합</x:v>
+      </x:c>
+      <x:c r="D13" s="13" t="str">
+        <x:v>양쪽과 rich-only manifest 보존</x:v>
+      </x:c>
+      <x:c r="E13" s="13" t="str">
+        <x:v>새 revision으로 명시 확정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" s="13" t="str">
+        <x:v>Office 첫 저장 전 호출 폴더 이동·삭제</x:v>
+      </x:c>
+      <x:c r="B14" s="13" t="str">
+        <x:v>stable directory ID 재해석</x:v>
+      </x:c>
+      <x:c r="C14" s="13" t="str">
+        <x:v>새 NAS 위치 선택/초안 계속/취소</x:v>
+      </x:c>
+      <x:c r="D14" s="13" t="str">
+        <x:v>draft와 노트 본문 보존</x:v>
+      </x:c>
+      <x:c r="E14" s="13" t="str">
+        <x:v>원자 publish와 reference 생성</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" s="13" t="str">
+        <x:v>Office 파일 이동·이름 변경</x:v>
+      </x:c>
+      <x:c r="B15" s="13" t="str">
+        <x:v>document registry currentPath 갱신</x:v>
+      </x:c>
+      <x:c r="C15" s="13" t="str">
+        <x:v>NAS에서 보기/다시 연결</x:v>
+      </x:c>
+      <x:c r="D15" s="13" t="str">
+        <x:v>reference block과 backlink 유지</x:v>
+      </x:c>
+      <x:c r="E15" s="13" t="str">
+        <x:v>documentId resolve 성공</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" s="13" t="str">
+        <x:v>실행 admission 자원 부족</x:v>
+      </x:c>
+      <x:c r="B16" s="13" t="str">
+        <x:v>공정 queue와 지수 backoff 재평가</x:v>
+      </x:c>
+      <x:c r="C16" s="13" t="str">
+        <x:v>대기 취소/낮은 한도로 재요청</x:v>
+      </x:c>
+      <x:c r="D16" s="13" t="str">
+        <x:v>코드·문서·요청 metadata 보존</x:v>
+      </x:c>
+      <x:c r="E16" s="13" t="str">
+        <x:v>예약 후 시작 또는 명시 취소</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" s="13" t="str">
+        <x:v>장치 업그레이드·제거</x:v>
+      </x:c>
+      <x:c r="B17" s="13" t="str">
+        <x:v>metrics 즉시 갱신, 매 admission 실제 capacity 재계산</x:v>
+      </x:c>
+      <x:c r="C17" s="13" t="str">
+        <x:v>MASTER capability self-test/활성화</x:v>
+      </x:c>
+      <x:c r="D17" s="13" t="str">
+        <x:v>고부하 권한은 자동 확대하지 않음</x:v>
+      </x:c>
+      <x:c r="E17" s="13" t="str">
+        <x:v>OS 인식+검증 뒤 새 한도 적용</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R739e7f1623a3418d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5f36de33024a4c40"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5820,10 +6609,78 @@
         <x:v>채팅 지연이 편집 socket에 영향</x:v>
       </x:c>
     </x:row>
+    <x:row r="15">
+      <x:c r="A15" s="13" t="str">
+        <x:v>DOCUMENT-WORKSPACE</x:v>
+      </x:c>
+      <x:c r="B15" s="13" t="str">
+        <x:v>reuses</x:v>
+      </x:c>
+      <x:c r="C15" s="13" t="str">
+        <x:v>빈 DOCX/XLSX/PPTX/HWP/HWPX 생성, quota, 원자 저장, OnlyOffice/RHWP 전면 열기</x:v>
+      </x:c>
+      <x:c r="D15" s="13" t="str">
+        <x:v>draft context와 note reference transaction, stable document ID</x:v>
+      </x:c>
+      <x:c r="E15" s="13" t="str">
+        <x:v>별도 생성 로직 분기로 형식·저장 오류 재발</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" s="13" t="str">
+        <x:v>DOCUMENT-STUDIO</x:v>
+      </x:c>
+      <x:c r="B16" s="13" t="str">
+        <x:v>integrates</x:v>
+      </x:c>
+      <x:c r="C16" s="13" t="str">
+        <x:v>노트/페이지/선택 내용의 변환·내보내기 job과 결과 열기</x:v>
+      </x:c>
+      <x:c r="D16" s="13" t="str">
+        <x:v>원본 block과 결과 file reference 관계</x:v>
+      </x:c>
+      <x:c r="E16" s="13" t="str">
+        <x:v>문서 변환과 문서 편집 앱 명칭 혼동</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" s="13" t="str">
+        <x:v>PC-LINK/DRIVE</x:v>
+      </x:c>
+      <x:c r="B17" s="13" t="str">
+        <x:v>projects</x:v>
+      </x:c>
+      <x:c r="C17" s="13" t="str">
+        <x:v>노트북 폴더 placeholder/hydration, local PY+MD projection, 변경 watcher</x:v>
+      </x:c>
+      <x:c r="D17" s="13" t="str">
+        <x:v>stable cell marker와 3-way merge, machine-local env 제외</x:v>
+      </x:c>
+      <x:c r="E17" s="13" t="str">
+        <x:v>생성 파일이 사용자 편집을 덮어씀</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" s="13" t="str">
+        <x:v>ADMIN-SERVER-MONITORING</x:v>
+      </x:c>
+      <x:c r="B18" s="13" t="str">
+        <x:v>feeds</x:v>
+      </x:c>
+      <x:c r="C18" s="13" t="str">
+        <x:v>CPU/RAM/swap/disk/temperature/장치 지표</x:v>
+      </x:c>
+      <x:c r="D18" s="13" t="str">
+        <x:v>실행 admission용 예약·압력·capability 상태</x:v>
+      </x:c>
+      <x:c r="E18" s="13" t="str">
+        <x:v>표시 지표와 실제 scheduler 판단 불일치</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R824b3d2194894eca"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd9488069b7054ed4"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6012,10 +6869,61 @@
         <x:v>Tauri/Electron 비교</x:v>
       </x:c>
     </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="13" t="str">
+        <x:v>PERF-10</x:v>
+      </x:c>
+      <x:c r="B11" s="13" t="str">
+        <x:v>동적 Python scheduler</x:v>
+      </x:c>
+      <x:c r="C11" s="13" t="str">
+        <x:v>현재 장비는 global active 1, user active 1부터 시작</x:v>
+      </x:c>
+      <x:c r="D11" s="13" t="str">
+        <x:v>여러 계정 queue + MemAvailable 3GiB대 + swap pressure</x:v>
+      </x:c>
+      <x:c r="E11" s="13" t="str">
+        <x:v>자원 예약, fair queue, 일반 서비스 reserve, 측정 후 경량 2개</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="13" t="str">
+        <x:v>PERF-11</x:v>
+      </x:c>
+      <x:c r="B12" s="13" t="str">
+        <x:v>장치 재감지</x:v>
+      </x:c>
+      <x:c r="C12" s="13" t="str">
+        <x:v>UI 5초 갱신, admission마다 실제 capacity 재계산</x:v>
+      </x:c>
+      <x:c r="D12" s="13" t="str">
+        <x:v>RAM/디스크 변화와 GPU 추가 mock/실장비</x:v>
+      </x:c>
+      <x:c r="E12" s="13" t="str">
+        <x:v>감소 즉시 보수화, GPU는 MASTER self-test 전 비활성</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" s="13" t="str">
+        <x:v>PERF-12</x:v>
+      </x:c>
+      <x:c r="B13" s="13" t="str">
+        <x:v>페이지 로컬 투영</x:v>
+      </x:c>
+      <x:c r="C13" s="13" t="str">
+        <x:v>변경된 block/cell만 재생성하고 5,000 block에서도 UI/동기화 정지 없음</x:v>
+      </x:c>
+      <x:c r="D13" s="13" t="str">
+        <x:v>NAS/PC 동시 편집, 대형 MD·PY·assets</x:v>
+      </x:c>
+      <x:c r="E13" s="13" t="str">
+        <x:v>incremental projection, hash cache, background merge</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5fd4e69cfdba47d1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Reb04ff36ac1a4f0d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6176,7 +7084,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7dc33a4070d64f13"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R800dea6f13634c7e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6576,10 +7484,130 @@
         <x:v>M3</x:v>
       </x:c>
     </x:row>
+    <x:row r="20">
+      <x:c r="A20" s="13" t="str">
+        <x:v>T-019</x:v>
+      </x:c>
+      <x:c r="B20" s="13" t="str">
+        <x:v>혼합 Python 페이지</x:v>
+      </x:c>
+      <x:c r="C20" s="13" t="str">
+        <x:v>텍스트·링크·Office block 사이 code cell 실행/all/restart</x:v>
+      </x:c>
+      <x:c r="D20" s="13" t="str">
+        <x:v>code cell만 정확한 순서로 실행하고 문서 block은 실행되지 않음</x:v>
+      </x:c>
+      <x:c r="E20" s="13" t="str">
+        <x:v>integration+E2E</x:v>
+      </x:c>
+      <x:c r="F20" s="13" t="str">
+        <x:v>M2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21">
+      <x:c r="A21" s="13" t="str">
+        <x:v>T-020</x:v>
+      </x:c>
+      <x:c r="B21" s="13" t="str">
+        <x:v>로컬 투영</x:v>
+      </x:c>
+      <x:c r="C21" s="13" t="str">
+        <x:v>서버 page와 PC의 .py/.md를 동시에 수정 후 sync</x:v>
+      </x:c>
+      <x:c r="D21" s="13" t="str">
+        <x:v>사용자 변경을 덮어쓰지 않고 block별 diff/충돌 복사본, rich metadata 보존</x:v>
+      </x:c>
+      <x:c r="E21" s="13" t="str">
+        <x:v>round-trip+E2E</x:v>
+      </x:c>
+      <x:c r="F21" s="13" t="str">
+        <x:v>M2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22">
+      <x:c r="A22" s="13" t="str">
+        <x:v>T-021</x:v>
+      </x:c>
+      <x:c r="B22" s="13" t="str">
+        <x:v>댓글</x:v>
+      </x:c>
+      <x:c r="C22" s="13" t="str">
+        <x:v>inline/code range 댓글 뒤 본문 삽입·삭제·이동·resolve/reopen</x:v>
+      </x:c>
+      <x:c r="D22" s="13" t="str">
+        <x:v>anchor 복구 또는 위치 변경됨, 잘못된 재부착 없음</x:v>
+      </x:c>
+      <x:c r="E22" s="13" t="str">
+        <x:v>unit+E2E</x:v>
+      </x:c>
+      <x:c r="F22" s="13" t="str">
+        <x:v>M1.5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23">
+      <x:c r="A23" s="13" t="str">
+        <x:v>T-022</x:v>
+      </x:c>
+      <x:c r="B23" s="13" t="str">
+        <x:v>Office 생성</x:v>
+      </x:c>
+      <x:c r="C23" s="13" t="str">
+        <x:v>본문 caret·폴더 우클릭에서 5개 형식 생성, 다른 위치 첫 저장</x:v>
+      </x:c>
+      <x:c r="D23" s="13" t="str">
+        <x:v>호출 위치 기본값, 실제 파일 1개, reference block, 편집기 전면 열기</x:v>
+      </x:c>
+      <x:c r="E23" s="13" t="str">
+        <x:v>integration+E2E</x:v>
+      </x:c>
+      <x:c r="F23" s="13" t="str">
+        <x:v>M1 확장</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24">
+      <x:c r="A24" s="13" t="str">
+        <x:v>T-023</x:v>
+      </x:c>
+      <x:c r="B24" s="13" t="str">
+        <x:v>Office 저장 경계</x:v>
+      </x:c>
+      <x:c r="C24" s="13" t="str">
+        <x:v>호출 폴더 이동·삭제·권한 회수·quota full·이름 충돌</x:v>
+      </x:c>
+      <x:c r="D24" s="13" t="str">
+        <x:v>임의 fallback/덮어쓰기 없음, draft 보존, 위치 재선택·복구 가능</x:v>
+      </x:c>
+      <x:c r="E24" s="13" t="str">
+        <x:v>security+E2E</x:v>
+      </x:c>
+      <x:c r="F24" s="13" t="str">
+        <x:v>M1 확장</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25">
+      <x:c r="A25" s="13" t="str">
+        <x:v>T-024</x:v>
+      </x:c>
+      <x:c r="B25" s="13" t="str">
+        <x:v>동적 자원</x:v>
+      </x:c>
+      <x:c r="C25" s="13" t="str">
+        <x:v>동시 Python, swap pressure, OOM, 장치 용량 증감</x:v>
+      </x:c>
+      <x:c r="D25" s="13" t="str">
+        <x:v>일반 서비스 정상, 작업 queue/kill/retry, 새 OS capacity 반영, GPU 권한 자동 개방 없음</x:v>
+      </x:c>
+      <x:c r="E25" s="13" t="str">
+        <x:v>security+load</x:v>
+      </x:c>
+      <x:c r="F25" s="13" t="str">
+        <x:v>M2</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9f6784964ff343df"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3db7627c174c40f7"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6785,10 +7813,146 @@
         <x:v>PWA 오프라인 프로토타입 및 파일시스템·딥링크·업데이트 요구 확정 후</x:v>
       </x:c>
     </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="13" t="str">
+        <x:v>DEC-011</x:v>
+      </x:c>
+      <x:c r="B12" s="13" t="str">
+        <x:v>채택</x:v>
+      </x:c>
+      <x:c r="C12" s="13" t="str">
+        <x:v>노트북은 사용자 계정 루트의 휴대 가능한 작업공간이며 모든 페이지 유형이 하위 페이지와 일반 파일을 함께 가질 수 있다.</x:v>
+      </x:c>
+      <x:c r="D12" s="13" t="str">
+        <x:v>Notion식 계층과 Python·Markdown·환경·참고 파일을 한 프로젝트 경계에서 다루기 위해서다.</x:v>
+      </x:c>
+      <x:c r="E12" s="13" t="str">
+        <x:v>파일 관리자와 노트 트리의 물리·논리 경계 spike에서 충돌할 때</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" s="13" t="str">
+        <x:v>DEC-012</x:v>
+      </x:c>
+      <x:c r="B13" s="13" t="str">
+        <x:v>채택</x:v>
+      </x:c>
+      <x:c r="C13" s="13" t="str">
+        <x:v>Python 실행 페이지는 문서 블록과 실행 코드 셀을 섞되 raw .py 파일은 순수 소스로 유지한다.</x:v>
+      </x:c>
+      <x:c r="D13" s="13" t="str">
+        <x:v>텍스트·링크·Office 문서 블록이 코드 실행을 오염시키지 않고 외부 Python 도구 호환성을 지킨다.</x:v>
+      </x:c>
+      <x:c r="E13" s="13" t="str">
+        <x:v>Jupyter round-trip에서 block metadata를 보존할 수 없을 때</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" s="13" t="str">
+        <x:v>DEC-013</x:v>
+      </x:c>
+      <x:c r="B14" s="13" t="str">
+        <x:v>채택</x:v>
+      </x:c>
+      <x:c r="C14" s="13" t="str">
+        <x:v>NAS의 rich block 페이지를 기준 원본으로 하고 로컬에는 .py·.md·assets·숨김 manifest 작업 폴더를 투영한다.</x:v>
+      </x:c>
+      <x:c r="D14" s="13" t="str">
+        <x:v>NAS에서는 한 페이지 UX를 유지하면서 로컬 VS Code·터미널·Markdown 앱에서 실제 파일로 작업한다.</x:v>
+      </x:c>
+      <x:c r="E14" s="13" t="str">
+        <x:v>양방향 병합이 안정적으로 구현되지 못할 때 읽기 전용 export로 축소</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" s="13" t="str">
+        <x:v>DEC-014</x:v>
+      </x:c>
+      <x:c r="B15" s="13" t="str">
+        <x:v>채택</x:v>
+      </x:c>
+      <x:c r="C15" s="13" t="str">
+        <x:v>표준 Markdown 기능은 양방향 보존하고 글꼴·버튼·database·실행 output 등 고급 블록은 manifest와 rich schema에 보존한다.</x:v>
+      </x:c>
+      <x:c r="D15" s="13" t="str">
+        <x:v>MDX/raw HTML에 임의 기능을 넣으면 외부 편집기 호환성과 XSS 경계가 깨진다.</x:v>
+      </x:c>
+      <x:c r="E15" s="13" t="str">
+        <x:v>안전하고 공개된 확장 문법을 채택할 때</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" s="13" t="str">
+        <x:v>DEC-015</x:v>
+      </x:c>
+      <x:c r="B16" s="13" t="str">
+        <x:v>채택</x:v>
+      </x:c>
+      <x:c r="C16" s="13" t="str">
+        <x:v>Python 원격 실행은 실제 OS/cgroup 자원 기반 admission queue와 격리 worker를 통과해야 한다.</x:v>
+      </x:c>
+      <x:c r="D16" s="13" t="str">
+        <x:v>저사양 NAS에서 동시 실행이 일반 파일·노트 서비스를 중단시키지 않아야 한다.</x:v>
+      </x:c>
+      <x:c r="E16" s="13" t="str">
+        <x:v>예외 없음</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" s="13" t="str">
+        <x:v>DEC-016</x:v>
+      </x:c>
+      <x:c r="B17" s="13" t="str">
+        <x:v>채택</x:v>
+      </x:c>
+      <x:c r="C17" s="13" t="str">
+        <x:v>문서·블록·선택 텍스트·코드 줄 검토 댓글과 실제 소스 주석을 서로 다른 모델로 저장한다.</x:v>
+      </x:c>
+      <x:c r="D17" s="13" t="str">
+        <x:v>검토 대화가 .py/.md 본문을 바꾸지 않고 편집 후에도 안전하게 anchor를 추적해야 한다.</x:v>
+      </x:c>
+      <x:c r="E17" s="13" t="str">
+        <x:v>예외 없음</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" s="13" t="str">
+        <x:v>DEC-017</x:v>
+      </x:c>
+      <x:c r="B18" s="13" t="str">
+        <x:v>채택</x:v>
+      </x:c>
+      <x:c r="C18" s="13" t="str">
+        <x:v>노트 본문과 트리의 문서 만들기는 기존 문서 스튜디오 생성·편집 서비스를 재사용한다.</x:v>
+      </x:c>
+      <x:c r="D18" s="13" t="str">
+        <x:v>별도 빈 Office 파일 생성기를 만들지 않고 계정 경계·quota·원자 저장·OnlyOffice/RHWP 검증을 공유한다.</x:v>
+      </x:c>
+      <x:c r="E18" s="13" t="str">
+        <x:v>문서 스튜디오 API 계약이 교체될 때</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19" s="13" t="str">
+        <x:v>DEC-018</x:v>
+      </x:c>
+      <x:c r="B19" s="13" t="str">
+        <x:v>채택</x:v>
+      </x:c>
+      <x:c r="C19" s="13" t="str">
+        <x:v>Office 문서 최초 저장 기본 위치는 명령이 발생한 노트북 내부 폴더이며 다른 NAS 위치 저장 후에도 stable document ID 링크를 유지한다.</x:v>
+      </x:c>
+      <x:c r="D19" s="13" t="str">
+        <x:v>Notion 하위 페이지 링크와 같은 본문 UX를 실제 NAS 파일에 적용하고 이동·이름 변경으로 링크가 깨지지 않게 한다.</x:v>
+      </x:c>
+      <x:c r="E19" s="13" t="str">
+        <x:v>stable file/document identity 저장소 설계 변경 시</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd6adeabb1b1f4aa3"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf3c863aa22b740fa"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6929,7 +8093,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5b8909fa322f4025"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R304c5770598843e8"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7138,7 +8302,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R28c11dbc8cc54e77"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0d1a53911fd54c43"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7238,10 +8402,30 @@
         <x:v>Codex</x:v>
       </x:c>
     </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="13" t="str">
+        <x:v>2026-09-06</x:v>
+      </x:c>
+      <x:c r="B5" s="13" t="str">
+        <x:v>0.4-design-memory-sync</x:v>
+      </x:c>
+      <x:c r="C5" s="13" t="str">
+        <x:v>추가 요구 설계 동기화·구현 전</x:v>
+      </x:c>
+      <x:c r="D5" s="13" t="str">
+        <x:v>노트북 물리 계층, 혼합 Python 실행 페이지, NAS 원격 실행, PY/MD 로컬 투영, Markdown 표현 경계, 동적 자원 admission, 댓글/주석, 문서 스튜디오 Office 생성·첫 저장 위치·본문 reference UX를 관련 시트에 연결했다.</x:v>
+      </x:c>
+      <x:c r="E5" s="13" t="str">
+        <x:v>사용자 확인 9건과 릴레이 commits 12e28c3~f27bd79 대조. 실제 기능 구현·E2E는 아직 진행하지 않음.</x:v>
+      </x:c>
+      <x:c r="F5" s="13" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R081ec9f8de494055"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3c8dd16b0fcc49df"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7436,6 +8620,106 @@
       </x:c>
       <x:c r="F9" s="20" t="str">
         <x:v>IndexedDB/Yjs spike와 계정 로그아웃 cache purge gate</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="13" t="str">
+        <x:v>M1-F</x:v>
+      </x:c>
+      <x:c r="B10" s="13" t="str">
+        <x:v>노트북 물리 구조·페이지/일반 파일 계층</x:v>
+      </x:c>
+      <x:c r="C10" s="13" t="str">
+        <x:v>설계 확정·구현 전</x:v>
+      </x:c>
+      <x:c r="D10" s="13" t="str">
+        <x:v>NOTE MANAGER/노트북과 page marker, 하위 페이지·일반 파일 공존</x:v>
+      </x:c>
+      <x:c r="E10" s="13" t="str">
+        <x:v>미실시</x:v>
+      </x:c>
+      <x:c r="F10" s="13" t="str">
+        <x:v>현재 .note_studio 저장소와 파일 관리자 마이그레이션/호환 spike</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="13" t="str">
+        <x:v>M1-G</x:v>
+      </x:c>
+      <x:c r="B11" s="13" t="str">
+        <x:v>노트 본문 Office 생성·첫 저장·reference</x:v>
+      </x:c>
+      <x:c r="C11" s="13" t="str">
+        <x:v>설계 확정·구현 전</x:v>
+      </x:c>
+      <x:c r="D11" s="13" t="str">
+        <x:v>문서 스튜디오 재사용, invocation directory, stable document ID</x:v>
+      </x:c>
+      <x:c r="E11" s="13" t="str">
+        <x:v>미실시</x:v>
+      </x:c>
+      <x:c r="F11" s="13" t="str">
+        <x:v>공통 blank service 추출과 5개 형식 transaction/E2E</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="13" t="str">
+        <x:v>M1.5-A</x:v>
+      </x:c>
+      <x:c r="B12" s="13" t="str">
+        <x:v>페이지·블록·inline·코드 검토 댓글</x:v>
+      </x:c>
+      <x:c r="C12" s="13" t="str">
+        <x:v>설계 확정·구현 전</x:v>
+      </x:c>
+      <x:c r="D12" s="13" t="str">
+        <x:v>thread/anchor/mention/resolve 모델</x:v>
+      </x:c>
+      <x:c r="E12" s="13" t="str">
+        <x:v>미실시</x:v>
+      </x:c>
+      <x:c r="F12" s="13" t="str">
+        <x:v>Yjs/일반 revision 양쪽 anchor 이동 spike</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" s="13" t="str">
+        <x:v>M2-A</x:v>
+      </x:c>
+      <x:c r="B13" s="13" t="str">
+        <x:v>혼합 Python 실행 페이지·로컬 투영</x:v>
+      </x:c>
+      <x:c r="C13" s="13" t="str">
+        <x:v>설계 확정·구현 전</x:v>
+      </x:c>
+      <x:c r="D13" s="13" t="str">
+        <x:v>rich page + executable cells, PY+MD+manifest projection</x:v>
+      </x:c>
+      <x:c r="E13" s="13" t="str">
+        <x:v>미실시</x:v>
+      </x:c>
+      <x:c r="F13" s="13" t="str">
+        <x:v>nbformat/분리 파일 round-trip과 충돌 테스트</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" s="13" t="str">
+        <x:v>M2-B</x:v>
+      </x:c>
+      <x:c r="B14" s="13" t="str">
+        <x:v>NAS 원격 실행·동적 자원 scheduler</x:v>
+      </x:c>
+      <x:c r="C14" s="13" t="str">
+        <x:v>실장비 기준 확인·구현 전</x:v>
+      </x:c>
+      <x:c r="D14" s="13" t="str">
+        <x:v>cgroup v2, 전역/계정 active 1 초안, MASTER 고부하 capability</x:v>
+      </x:c>
+      <x:c r="E14" s="13" t="str">
+        <x:v>CPU/RAM/swap/disk/GPU 읽기 전용 확인</x:v>
+      </x:c>
+      <x:c r="F14" s="13" t="str">
+        <x:v>격리 worker·fair queue·부하/OOM/재감지 gate</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -7647,7 +8931,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R02a4050f64f7483d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6d1b13a347e54b6a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7930,7 +9214,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8bfcaa8197a745bb"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc65f6620f3044e8a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8326,7 +9610,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4c3f4580832d4e87"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb43ba7264eae4d2d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8569,7 +9853,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra56b5799f0ea49f2"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R63f98197dcc14041"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8744,7 +10028,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R73e27692fb5b4828"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rec22f17b39c84136"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8950,10 +10234,61 @@
         <x:v>다른 계정 링크면 자동 전환 금지, 사용자 선택. 앱 없으면 웹 fallback.</x:v>
       </x:c>
     </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="13" t="str">
+        <x:v>FLOW-PY-PROJECTION</x:v>
+      </x:c>
+      <x:c r="B12" s="13" t="str">
+        <x:v>NAS Drive에서 Python 실행 페이지 동기화</x:v>
+      </x:c>
+      <x:c r="C12" s="13" t="str">
+        <x:v>서버 page revision 확인 → .py/.md/assets/manifest 생성 또는 3-way 병합 → hash 기록</x:v>
+      </x:c>
+      <x:c r="D12" s="13" t="str">
+        <x:v>로컬 도구에서 순수 파일로 열고 수정 내용을 대응 block/cell에 역반영</x:v>
+      </x:c>
+      <x:c r="E12" s="13" t="str">
+        <x:v>서버·로컬 동시 수정은 덮어쓰지 않고 코드/문서별 충돌 비교와 복구본 제공</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" s="13" t="str">
+        <x:v>FLOW-PY-REMOTE</x:v>
+      </x:c>
+      <x:c r="B13" s="13" t="str">
+        <x:v>VS Code·터미널·노트에서 NAS 실행</x:v>
+      </x:c>
+      <x:c r="C13" s="13" t="str">
+        <x:v>사용자·workspace·capability 확인 → 자원 예약/admission → 격리 worker → 출력 stream → artifact publish</x:v>
+      </x:c>
+      <x:c r="D13" s="13" t="str">
+        <x:v>NAS 경로를 유지한 채 결과·오류·생성 파일을 PC에 표시</x:v>
+      </x:c>
+      <x:c r="E13" s="13" t="str">
+        <x:v>자원 부족은 실패가 아니라 대기. timeout/OOM은 worker만 종료하고 편집 내용 보존</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" s="13" t="str">
+        <x:v>FLOW-OFFICE-INLINE</x:v>
+      </x:c>
+      <x:c r="B14" s="13" t="str">
+        <x:v>노트 본문 caret 또는 노트북 폴더 우클릭</x:v>
+      </x:c>
+      <x:c r="C14" s="13" t="str">
+        <x:v>형식 선택 → invocation directory를 가진 draft → 작성 → 첫 저장 위치 선택 → 원자 publish → reference block 삽입 → 편집 창 전면 열기</x:v>
+      </x:c>
+      <x:c r="D14" s="13" t="str">
+        <x:v>기본 위치는 명령 발생 폴더이며 다른 NAS 위치를 골라도 원래 위치의 링크가 같은 문서를 연다.</x:v>
+      </x:c>
+      <x:c r="E14" s="13" t="str">
+        <x:v>원래 폴더 이동은 stable ID로 재해석. 삭제·권한 상실이면 위치를 다시 요구하고 임의 fallback 금지</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re4d1e967b9b74a17"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Raf4e88a2adb24ce1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/programs/NAS_NOTE_STUDIO_SPEC.xlsx
+++ b/docs/programs/NAS_NOTE_STUDIO_SPEC.xlsx
@@ -2,39 +2,39 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="R33e105af35254e26"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Product_Vision" sheetId="2" r:id="Rbff19c2ac483427a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decisions" sheetId="3" r:id="Radf2fad0283842bb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Competitors" sheetId="4" r:id="R1121be17aeb542c1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open_Source" sheetId="5" r:id="Raac83768e7fe45a7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source_Index" sheetId="6" r:id="Rc870cd1eed094d14"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Information_Architecture" sheetId="7" r:id="R7a80a97d14ce471a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI_Layout" sheetId="8" r:id="R79405ef728dd4b9f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="User_Flows" sheetId="9" r:id="R7923f8063aa34fa7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Note_Types" sheetId="10" r:id="R39a4b8b6a4fa4b41"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Block_Catalog" sheetId="11" r:id="R3fabb14ac30c448c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Slash_Commands" sheetId="12" r:id="R57abd8c952a447ae"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Context_Menus" sheetId="13" r:id="Rd9a239a87d254b98"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Keyboard_Shortcuts" sheetId="14" r:id="R654dcb37a5a64281"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Database_Views" sheetId="15" r:id="R84f7d5a8d3754a58"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Code_Text_Mode" sheetId="16" r:id="R8628dc79dc9e48bb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Python_Notebook" sheetId="17" r:id="Rf492ada1743d4f19"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Collaboration" sheetId="18" r:id="R757a3e35bb484ec6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Offline_Desktop" sheetId="19" r:id="Rc8102fcef9604dc9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data_Model" sheetId="20" r:id="Rd562f07847ec42ab"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Storage_Interop" sheetId="21" r:id="Rbe8a0d902e864a3b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Security" sheetId="22" r:id="Ree6e6f88c1554c70"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="API_Contracts" sheetId="23" r:id="Ra95ffcfad5914e1d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="State_Machines" sheetId="24" r:id="R8dd9a86f87cf4d32"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Error_Recovery" sheetId="25" r:id="Rbac6869efdbb4422"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cross_App_Relations" sheetId="26" r:id="R968beef32bdf4912"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Performance" sheetId="27" r:id="R6b76cbf2ca884b6f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Accessibility" sheetId="28" r:id="R5cd7c64750e64886"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test_Matrix" sheetId="29" r:id="Rbf78a13943e3411e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="30" r:id="R81c9f4429595416f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open_Questions" sheetId="31" r:id="Rf5654a5927524968"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Change_Log" sheetId="32" r:id="Rda03175fda5d4556"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Implementation_Status" sheetId="33" r:id="R920fb7b5b5db4b92"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="R617e6bdc9de84046"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Product_Vision" sheetId="2" r:id="Rbc1ea163a07d4d84"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decisions" sheetId="3" r:id="Re9477e72c9664c51"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Competitors" sheetId="4" r:id="R2232dae2691145ef"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open_Source" sheetId="5" r:id="R4fa348a26ef246ec"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source_Index" sheetId="6" r:id="R97bbfa5246224314"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Information_Architecture" sheetId="7" r:id="R5e4c9994e74d480c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI_Layout" sheetId="8" r:id="R1c18bcf66fcf4244"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="User_Flows" sheetId="9" r:id="Rb88f678aa11e4405"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Note_Types" sheetId="10" r:id="Raec31d627e85444d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Block_Catalog" sheetId="11" r:id="Rfad4da1bb7484cf8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Slash_Commands" sheetId="12" r:id="Rc7476a61e77545d8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Context_Menus" sheetId="13" r:id="R8bac605e5c544368"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Keyboard_Shortcuts" sheetId="14" r:id="Re8b828cab26842e6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Database_Views" sheetId="15" r:id="R16ff6f6bff704541"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Code_Text_Mode" sheetId="16" r:id="Rf37623cc53064f25"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Python_Notebook" sheetId="17" r:id="R0ae549aa4bf44e9b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Collaboration" sheetId="18" r:id="Rcc97b92152374407"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Offline_Desktop" sheetId="19" r:id="R14e240dec7414bdd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data_Model" sheetId="20" r:id="R920886e614a5432e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Storage_Interop" sheetId="21" r:id="R74ea42b3b16644c1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Security" sheetId="22" r:id="Rbe4bad5cdd194740"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="API_Contracts" sheetId="23" r:id="Rc6e805917d4c4c30"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="State_Machines" sheetId="24" r:id="R38b53b6e861e4249"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Error_Recovery" sheetId="25" r:id="Rb8574e4c56a3426d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cross_App_Relations" sheetId="26" r:id="R90a616b50809473f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Performance" sheetId="27" r:id="R7fefa445e1e64f47"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Accessibility" sheetId="28" r:id="R5fdc276ff1fd44a4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test_Matrix" sheetId="29" r:id="Rd09529bf9a9d43ec"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="30" r:id="R0db9a4b69ade4296"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open_Questions" sheetId="31" r:id="R67198c4614b74638"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Change_Log" sheetId="32" r:id="Reb2befac0dcd4521"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Implementation_Status" sheetId="33" r:id="R085df3a3a5c14d66"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -928,7 +928,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R12d4df722e2444b5"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R72483e57fe584eef"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1271,7 +1271,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdec4f685a2ed41a1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0652fa4e961a4a7a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1674,7 +1674,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfb31bd394658453b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rda06a8e59cf54f56"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2057,7 +2057,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdb4cf5bb05014f0f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc8267eca814c4156"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2470,7 +2470,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf599bc839e914f09"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1447d0354349494c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2968,7 +2968,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc1c0ea63ec7f49e0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Raf8f10fbb3bb4662"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3228,7 +3228,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R60e20feff95e4feb"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R74377a0c72f44ba6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3420,7 +3420,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0c29b0107ef041e5"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rba75b766dd8740bb"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3748,7 +3748,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb1dca47cee9a4be0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbe65752e8f2e441d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4008,7 +4008,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra68c384b88a64abf"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd5062d47f143446d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4200,7 +4200,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf067d158fbca4abd"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re9d3d8d8d2284ade"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4333,7 +4333,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2a117e9de74040dd"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R498a0277326d437e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4712,7 +4712,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R934c0cfb873142b3"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3f0bd3f7a4e649c9"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4955,7 +4955,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R42a7fa329dc54920"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb8554359b3c8499f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5266,7 +5266,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8b80ddd6b52e4bb6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Raabb35fdaaf1414e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5730,7 +5730,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5fb3a66fdd5541f7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdc8388a9b44e4ce0"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6041,7 +6041,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcddab77635e8401b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R00c907ddca464a2b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6352,7 +6352,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5f36de33024a4c40"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R26fe827f24f24ad9"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6680,7 +6680,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd9488069b7054ed4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R76efb3a9466a4329"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6923,7 +6923,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Reb04ff36ac1a4f0d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra83ee4a436184168"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7084,7 +7084,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R800dea6f13634c7e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R01617cb608914354"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7604,10 +7604,70 @@
         <x:v>M2</x:v>
       </x:c>
     </x:row>
+    <x:row r="26">
+      <x:c r="A26" s="13" t="str">
+        <x:v>T-025</x:v>
+      </x:c>
+      <x:c r="B26" s="13" t="str">
+        <x:v>노트북 물리 경계</x:v>
+      </x:c>
+      <x:c r="C26" s="13" t="str">
+        <x:v>계정별 NOTE MANAGER에서 노트북·페이지·하위 페이지 생성과 같은 이름 반복</x:v>
+      </x:c>
+      <x:c r="D26" s="13" t="str">
+        <x:v>개인 root 밖으로 나가지 않고 충돌 이름은 (2)로 분리되며 기존 노트는 이동되지 않음</x:v>
+      </x:c>
+      <x:c r="E26" s="13" t="str">
+        <x:v>unit+filesystem</x:v>
+      </x:c>
+      <x:c r="F26" s="13" t="str">
+        <x:v>M1-F</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27">
+      <x:c r="A27" s="13" t="str">
+        <x:v>T-026</x:v>
+      </x:c>
+      <x:c r="B27" s="13" t="str">
+        <x:v>노트북 계정 격리</x:v>
+      </x:c>
+      <x:c r="C27" s="13" t="str">
+        <x:v>A/B가 같은 노트북 이름을 만들고 다른 notebookId·parentId를 조합</x:v>
+      </x:c>
+      <x:c r="D27" s="13" t="str">
+        <x:v>레지스트리와 실제 경로가 계정별로 분리되고 노트북 경계 위반은 409</x:v>
+      </x:c>
+      <x:c r="E27" s="13" t="str">
+        <x:v>security+unit</x:v>
+      </x:c>
+      <x:c r="F27" s="13" t="str">
+        <x:v>M1-F</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28">
+      <x:c r="A28" s="13" t="str">
+        <x:v>T-027</x:v>
+      </x:c>
+      <x:c r="B28" s="13" t="str">
+        <x:v>노트북 경로 수명</x:v>
+      </x:c>
+      <x:c r="C28" s="13" t="str">
+        <x:v>title autosave, 명시 rename/move, trash/restore/permanent delete, 일반 파일 포함 페이지</x:v>
+      </x:c>
+      <x:c r="D28" s="13" t="str">
+        <x:v>자동 타이핑은 경로를 흔들지 않고 명시 작업만 원자 변경하며 사용자 파일을 암묵 삭제하지 않음</x:v>
+      </x:c>
+      <x:c r="E28" s="13" t="str">
+        <x:v>integration+E2E</x:v>
+      </x:c>
+      <x:c r="F28" s="13" t="str">
+        <x:v>M1-F 다음 gate</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3db7627c174c40f7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R320adbb9afbe4ed1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7952,7 +8012,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf3c863aa22b740fa"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd73c7877bfbb4252"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8093,7 +8153,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R304c5770598843e8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R71a924f783474505"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8302,7 +8362,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0d1a53911fd54c43"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf2c836517f484139"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8422,10 +8482,30 @@
         <x:v>Codex</x:v>
       </x:c>
     </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="13" t="str">
+        <x:v>2026-09-06</x:v>
+      </x:c>
+      <x:c r="B6" s="13" t="str">
+        <x:v>0.5-m1f-foundation</x:v>
+      </x:c>
+      <x:c r="C6" s="13" t="str">
+        <x:v>1차 기반 구현·로컬 검증 / 운영 배포 전</x:v>
+      </x:c>
+      <x:c r="D6" s="13" t="str">
+        <x:v>NOTE MANAGER 자동 생성, 노트북 registry/API/UI, 실제 노트북·페이지·하위 페이지 폴더, 안전 이름·충돌 분리·계정/노트북 경계, 기존 노트 병행 표시를 구현했다.</x:v>
+      </x:c>
+      <x:c r="E6" s="13" t="str">
+        <x:v>backend 전체 37 pass·2 환경 조건부 skip, note 15/15, frontend 기능 34 pass, production build. 외부 경로 소실과 활성 하위 페이지 삭제 경계를 추가 검증했다. 명시 rename/move·삭제 수명·projection·quota·실화면은 다음 gap으로 유지.</x:v>
+      </x:c>
+      <x:c r="F6" s="13" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3c8dd16b0fcc49df"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2a7c5746576c46ca"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8630,16 +8710,16 @@
         <x:v>노트북 물리 구조·페이지/일반 파일 계층</x:v>
       </x:c>
       <x:c r="C10" s="13" t="str">
-        <x:v>설계 확정·구현 전</x:v>
+        <x:v>1차 기반 구현·로컬 자동 검증 완료 / 운영 배포 전</x:v>
       </x:c>
       <x:c r="D10" s="13" t="str">
-        <x:v>NOTE MANAGER/노트북과 page marker, 하위 페이지·일반 파일 공존</x:v>
+        <x:v>계정 personal root의 NOTE MANAGER, hidden notebooks registry, 노트북·페이지·하위 페이지 실제 폴더, 기존 .note_studio 병행 호환, 단색 type 아이콘 트리</x:v>
       </x:c>
       <x:c r="E10" s="13" t="str">
-        <x:v>미실시</x:v>
+        <x:v>note service 15/15, backend 전체 37 pass·2 조건부 skip, frontend 기능 34 pass, production build</x:v>
       </x:c>
       <x:c r="F10" s="13" t="str">
-        <x:v>현재 .note_studio 저장소와 파일 관리자 마이그레이션/호환 spike</x:v>
+        <x:v>운영 배포/API smoke 뒤 명시적 rename·move transaction, 비어 있지 않은 page 삭제 정책, marker/local projection, quota gate, 로그인 실화면 E2E; 외부 경로 소실 409 상태와 활성 하위 페이지 부모 삭제 차단 포함</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
@@ -8931,7 +9011,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6d1b13a347e54b6a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc6479fb179b54723"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9214,7 +9294,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc65f6620f3044e8a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9cf8afad3ac54d4b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9610,7 +9690,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb43ba7264eae4d2d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7b32d93e723b4fa4"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9853,7 +9933,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R63f98197dcc14041"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rceadcf46b6bf4e93"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10028,7 +10108,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rec22f17b39c84136"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6632e90709264392"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10288,7 +10368,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Raf4e88a2adb24ce1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8b486d54e5754aba"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/programs/NAS_NOTE_STUDIO_SPEC.xlsx
+++ b/docs/programs/NAS_NOTE_STUDIO_SPEC.xlsx
@@ -2,39 +2,39 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="R617e6bdc9de84046"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Product_Vision" sheetId="2" r:id="Rbc1ea163a07d4d84"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decisions" sheetId="3" r:id="Re9477e72c9664c51"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Competitors" sheetId="4" r:id="R2232dae2691145ef"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open_Source" sheetId="5" r:id="R4fa348a26ef246ec"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source_Index" sheetId="6" r:id="R97bbfa5246224314"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Information_Architecture" sheetId="7" r:id="R5e4c9994e74d480c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI_Layout" sheetId="8" r:id="R1c18bcf66fcf4244"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="User_Flows" sheetId="9" r:id="Rb88f678aa11e4405"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Note_Types" sheetId="10" r:id="Raec31d627e85444d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Block_Catalog" sheetId="11" r:id="Rfad4da1bb7484cf8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Slash_Commands" sheetId="12" r:id="Rc7476a61e77545d8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Context_Menus" sheetId="13" r:id="R8bac605e5c544368"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Keyboard_Shortcuts" sheetId="14" r:id="Re8b828cab26842e6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Database_Views" sheetId="15" r:id="R16ff6f6bff704541"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Code_Text_Mode" sheetId="16" r:id="Rf37623cc53064f25"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Python_Notebook" sheetId="17" r:id="R0ae549aa4bf44e9b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Collaboration" sheetId="18" r:id="Rcc97b92152374407"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Offline_Desktop" sheetId="19" r:id="R14e240dec7414bdd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data_Model" sheetId="20" r:id="R920886e614a5432e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Storage_Interop" sheetId="21" r:id="R74ea42b3b16644c1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Security" sheetId="22" r:id="Rbe4bad5cdd194740"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="API_Contracts" sheetId="23" r:id="Rc6e805917d4c4c30"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="State_Machines" sheetId="24" r:id="R38b53b6e861e4249"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Error_Recovery" sheetId="25" r:id="Rb8574e4c56a3426d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cross_App_Relations" sheetId="26" r:id="R90a616b50809473f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Performance" sheetId="27" r:id="R7fefa445e1e64f47"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Accessibility" sheetId="28" r:id="R5fdc276ff1fd44a4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test_Matrix" sheetId="29" r:id="Rd09529bf9a9d43ec"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="30" r:id="R0db9a4b69ade4296"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open_Questions" sheetId="31" r:id="R67198c4614b74638"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Change_Log" sheetId="32" r:id="Reb2befac0dcd4521"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Implementation_Status" sheetId="33" r:id="R085df3a3a5c14d66"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="Rc5437cdb27f04f38"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Product_Vision" sheetId="2" r:id="R07d7e333ab3f4f50"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decisions" sheetId="3" r:id="R3d1af7e26b8b4825"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Competitors" sheetId="4" r:id="R0776e7c2e7e44373"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open_Source" sheetId="5" r:id="R02cc1baa67a04164"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source_Index" sheetId="6" r:id="R0fe5619bd37540ac"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Information_Architecture" sheetId="7" r:id="R654b2b9234b24e8e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI_Layout" sheetId="8" r:id="R545aeef68f804c81"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="User_Flows" sheetId="9" r:id="R1a706e2feaeb4006"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Note_Types" sheetId="10" r:id="R1c3076f63eaf4bcb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Block_Catalog" sheetId="11" r:id="Rcb2f564d0f3b4b7e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Slash_Commands" sheetId="12" r:id="Rc56061a6456042ae"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Context_Menus" sheetId="13" r:id="Rdf479176b992480b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Keyboard_Shortcuts" sheetId="14" r:id="R853925784cc046dc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Database_Views" sheetId="15" r:id="R670094c0a9c54922"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Code_Text_Mode" sheetId="16" r:id="R3fa3bdb0872f4f34"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Python_Notebook" sheetId="17" r:id="Rbbb3a5da3b774105"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Collaboration" sheetId="18" r:id="R1bda6f09d7ae40aa"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Offline_Desktop" sheetId="19" r:id="Rc8ceae5fc8194d5c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data_Model" sheetId="20" r:id="Rdd22685913474f76"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Storage_Interop" sheetId="21" r:id="R60b52d8800a54e5f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Security" sheetId="22" r:id="Re758d9b0aeef4088"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="API_Contracts" sheetId="23" r:id="Rd43a020b73ca42d6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="State_Machines" sheetId="24" r:id="R0bb4eb3753a94332"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Error_Recovery" sheetId="25" r:id="R0c98da6bc0e84375"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cross_App_Relations" sheetId="26" r:id="Ra7227c176870443f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Performance" sheetId="27" r:id="Ra3968fd32a03443b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Accessibility" sheetId="28" r:id="R3e20121406d546ce"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test_Matrix" sheetId="29" r:id="R0eeeb439e6764e93"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="30" r:id="R9dd3e0cd2113491f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open_Questions" sheetId="31" r:id="R640db6ece08940b4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Change_Log" sheetId="32" r:id="R3f7a57eaaaeb4dd0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Implementation_Status" sheetId="33" r:id="R74d117f60c2d4064"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -928,7 +928,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R72483e57fe584eef"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfde03ff7fcf24140"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1271,7 +1271,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0652fa4e961a4a7a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra506ae6636094fb4"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1674,7 +1674,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rda06a8e59cf54f56"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R936d0305f77a4a09"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2057,7 +2057,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc8267eca814c4156"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4ce96a6855ac4e95"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2470,7 +2470,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1447d0354349494c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf50d99dd097c4dbf"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2968,7 +2968,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Raf8f10fbb3bb4662"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd87e8877ea3a4eb5"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3228,7 +3228,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R74377a0c72f44ba6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbf6887ce0c834685"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3420,7 +3420,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rba75b766dd8740bb"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re167c1377ae24610"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3748,7 +3748,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbe65752e8f2e441d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0f5ae766d4d44b36"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4008,7 +4008,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd5062d47f143446d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1cf71d1afe2c4685"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4200,7 +4200,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re9d3d8d8d2284ade"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R846988d845b04646"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4333,7 +4333,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R498a0277326d437e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R70ae720b46984933"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4712,7 +4712,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3f0bd3f7a4e649c9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4c7fe2d9d6474e6f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4955,7 +4955,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb8554359b3c8499f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb3582e465c414774"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5266,7 +5266,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Raabb35fdaaf1414e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9d79ff55264b434f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5730,7 +5730,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdc8388a9b44e4ce0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ref29acba4a654900"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6041,7 +6041,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R00c907ddca464a2b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R634430ec18fb4363"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6352,7 +6352,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R26fe827f24f24ad9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R527a9fdb88af4739"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6680,7 +6680,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R76efb3a9466a4329"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7f139b34c8fb46bd"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6923,7 +6923,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra83ee4a436184168"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8c036884e34c4853"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7084,7 +7084,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R01617cb608914354"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdd2f08cc041b49a2"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7667,7 +7667,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R320adbb9afbe4ed1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb04ec025ebae45d2"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8012,7 +8012,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd73c7877bfbb4252"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rba6b038183ca4643"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8153,7 +8153,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R71a924f783474505"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9a09d5e4e84447d0"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8362,7 +8362,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf2c836517f484139"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc1f3cd6785d14b11"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8490,13 +8490,13 @@
         <x:v>0.5-m1f-foundation</x:v>
       </x:c>
       <x:c r="C6" s="13" t="str">
-        <x:v>1차 기반 구현·로컬 검증 / 운영 배포 전</x:v>
+        <x:v>1차 기반 운영 배포·Linux 전체 검증 / 2차 transaction 전</x:v>
       </x:c>
       <x:c r="D6" s="13" t="str">
         <x:v>NOTE MANAGER 자동 생성, 노트북 registry/API/UI, 실제 노트북·페이지·하위 페이지 폴더, 안전 이름·충돌 분리·계정/노트북 경계, 기존 노트 병행 표시를 구현했다.</x:v>
       </x:c>
       <x:c r="E6" s="13" t="str">
-        <x:v>backend 전체 37 pass·2 환경 조건부 skip, note 15/15, frontend 기능 34 pass, production build. 외부 경로 소실과 활성 하위 페이지 삭제 경계를 추가 검증했다. 명시 rename/move·삭제 수명·projection·quota·실화면은 다음 gap으로 유지.</x:v>
+        <x:v>commit 5160dfb. NAS backend 39/39, frontend build/PDF.js 4.8.69, live main.3a1e3abc.js, internal/public 200, auth gate 401, services active. 로그인 실화면과 2차 gap은 남김.</x:v>
       </x:c>
       <x:c r="F6" s="13" t="str">
         <x:v>Codex</x:v>
@@ -8505,7 +8505,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2a7c5746576c46ca"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf1c9ad92823c4502"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8710,13 +8710,13 @@
         <x:v>노트북 물리 구조·페이지/일반 파일 계층</x:v>
       </x:c>
       <x:c r="C10" s="13" t="str">
-        <x:v>1차 기반 구현·로컬 자동 검증 완료 / 운영 배포 전</x:v>
+        <x:v>1차 기반 운영 배포·Linux 전체 검증 완료 / 2차 transaction 전</x:v>
       </x:c>
       <x:c r="D10" s="13" t="str">
         <x:v>계정 personal root의 NOTE MANAGER, hidden notebooks registry, 노트북·페이지·하위 페이지 실제 폴더, 기존 .note_studio 병행 호환, 단색 type 아이콘 트리</x:v>
       </x:c>
       <x:c r="E10" s="13" t="str">
-        <x:v>note service 15/15, backend 전체 37 pass·2 조건부 skip, frontend 기능 34 pass, production build</x:v>
+        <x:v>local note 15/15·backend 37+2 skip·frontend 34·build; NAS backend 39/39·build/PDF.js·HTTP/service</x:v>
       </x:c>
       <x:c r="F10" s="13" t="str">
         <x:v>운영 배포/API smoke 뒤 명시적 rename·move transaction, 비어 있지 않은 page 삭제 정책, marker/local projection, quota gate, 로그인 실화면 E2E; 외부 경로 소실 409 상태와 활성 하위 페이지 부모 삭제 차단 포함</x:v>
@@ -9011,7 +9011,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc6479fb179b54723"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R351e6b55c286488e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9294,7 +9294,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9cf8afad3ac54d4b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2d12c7f166374d90"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9690,7 +9690,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7b32d93e723b4fa4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8aea3eaceef24f08"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9933,7 +9933,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rceadcf46b6bf4e93"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7cb53c37fd074d01"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10108,7 +10108,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6632e90709264392"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re62337da67034b10"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10368,7 +10368,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8b486d54e5754aba"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb54d284a74d84903"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/programs/NAS_NOTE_STUDIO_SPEC.xlsx
+++ b/docs/programs/NAS_NOTE_STUDIO_SPEC.xlsx
@@ -2,39 +2,39 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="Rc5437cdb27f04f38"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Product_Vision" sheetId="2" r:id="R07d7e333ab3f4f50"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decisions" sheetId="3" r:id="R3d1af7e26b8b4825"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Competitors" sheetId="4" r:id="R0776e7c2e7e44373"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open_Source" sheetId="5" r:id="R02cc1baa67a04164"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source_Index" sheetId="6" r:id="R0fe5619bd37540ac"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Information_Architecture" sheetId="7" r:id="R654b2b9234b24e8e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI_Layout" sheetId="8" r:id="R545aeef68f804c81"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="User_Flows" sheetId="9" r:id="R1a706e2feaeb4006"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Note_Types" sheetId="10" r:id="R1c3076f63eaf4bcb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Block_Catalog" sheetId="11" r:id="Rcb2f564d0f3b4b7e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Slash_Commands" sheetId="12" r:id="Rc56061a6456042ae"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Context_Menus" sheetId="13" r:id="Rdf479176b992480b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Keyboard_Shortcuts" sheetId="14" r:id="R853925784cc046dc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Database_Views" sheetId="15" r:id="R670094c0a9c54922"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Code_Text_Mode" sheetId="16" r:id="R3fa3bdb0872f4f34"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Python_Notebook" sheetId="17" r:id="Rbbb3a5da3b774105"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Collaboration" sheetId="18" r:id="R1bda6f09d7ae40aa"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Offline_Desktop" sheetId="19" r:id="Rc8ceae5fc8194d5c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data_Model" sheetId="20" r:id="Rdd22685913474f76"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Storage_Interop" sheetId="21" r:id="R60b52d8800a54e5f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Security" sheetId="22" r:id="Re758d9b0aeef4088"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="API_Contracts" sheetId="23" r:id="Rd43a020b73ca42d6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="State_Machines" sheetId="24" r:id="R0bb4eb3753a94332"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Error_Recovery" sheetId="25" r:id="R0c98da6bc0e84375"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cross_App_Relations" sheetId="26" r:id="Ra7227c176870443f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Performance" sheetId="27" r:id="Ra3968fd32a03443b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Accessibility" sheetId="28" r:id="R3e20121406d546ce"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test_Matrix" sheetId="29" r:id="R0eeeb439e6764e93"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="30" r:id="R9dd3e0cd2113491f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open_Questions" sheetId="31" r:id="R640db6ece08940b4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Change_Log" sheetId="32" r:id="R3f7a57eaaaeb4dd0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Implementation_Status" sheetId="33" r:id="R74d117f60c2d4064"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="R88008cd0850f4e14"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Product_Vision" sheetId="2" r:id="Ra501753b327b4ebc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decisions" sheetId="3" r:id="R0ceb798270954d37"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Competitors" sheetId="4" r:id="R57873ee093cc44c8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open_Source" sheetId="5" r:id="Re9101f3ee9e14170"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source_Index" sheetId="6" r:id="R659f0cec87bc422a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Information_Architecture" sheetId="7" r:id="R4175522060e04a1c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI_Layout" sheetId="8" r:id="Rac918d4c860e494a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="User_Flows" sheetId="9" r:id="R4a6ee37a6c594932"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Note_Types" sheetId="10" r:id="Re4ebda6b5de44de4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Block_Catalog" sheetId="11" r:id="R7e187ed83ece4f1d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Slash_Commands" sheetId="12" r:id="R0244fdaf49e847b6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Context_Menus" sheetId="13" r:id="Rd14a1648fc924ebe"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Keyboard_Shortcuts" sheetId="14" r:id="R4ea5c7b0516b485a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Database_Views" sheetId="15" r:id="Racb1f9a0ac44419d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Code_Text_Mode" sheetId="16" r:id="Rc31acca65fe8421b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Python_Notebook" sheetId="17" r:id="Re3e3c28ee5624630"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Collaboration" sheetId="18" r:id="Ra2a2b851496545aa"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Offline_Desktop" sheetId="19" r:id="R4701f2d34eb64805"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data_Model" sheetId="20" r:id="R7ef7d1345bbc4ebc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Storage_Interop" sheetId="21" r:id="Rb933c305d4f7470e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Security" sheetId="22" r:id="R981c8d328c864d56"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="API_Contracts" sheetId="23" r:id="Reb22e8a83a2a429d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="State_Machines" sheetId="24" r:id="R6a5a09feb0b1467f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Error_Recovery" sheetId="25" r:id="Rc8865528409b495b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cross_App_Relations" sheetId="26" r:id="Ra345e50048544b1b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Performance" sheetId="27" r:id="Rdf20ec1e230d4bfa"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Accessibility" sheetId="28" r:id="Rb9858d62b6714972"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test_Matrix" sheetId="29" r:id="R51dc9b333b6342be"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="30" r:id="Re4034a6fe1524276"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open_Questions" sheetId="31" r:id="R69fc854729dc476b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Change_Log" sheetId="32" r:id="Rbc9a773cc4ce4d7b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Implementation_Status" sheetId="33" r:id="R722978725e4b4041"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -928,7 +928,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfde03ff7fcf24140"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re7dbb9b6911a42c8"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1271,7 +1271,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra506ae6636094fb4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R15971f26e26949ed"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1674,7 +1674,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R936d0305f77a4a09"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1a46ec7f87d04d60"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2057,7 +2057,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4ce96a6855ac4e95"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R47d87b2c3fe346cb"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2470,7 +2470,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf50d99dd097c4dbf"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6aea1f5f9eb24fb9"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2968,7 +2968,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd87e8877ea3a4eb5"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfa63eda388424182"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3228,7 +3228,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbf6887ce0c834685"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6b9eaf2dc3364387"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3420,7 +3420,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re167c1377ae24610"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R565d183ad6ed4f77"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3748,7 +3748,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0f5ae766d4d44b36"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rab03f804eed24330"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4008,7 +4008,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1cf71d1afe2c4685"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R46f08e51a6d04b50"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4200,7 +4200,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R846988d845b04646"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ree357a84a59140aa"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4333,7 +4333,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R70ae720b46984933"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R344fca5a6ed74361"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4712,7 +4712,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4c7fe2d9d6474e6f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R44b4080cb9274db6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4955,7 +4955,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb3582e465c414774"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7bc9a6cd40504632"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5263,10 +5263,27 @@
         <x:v>P0</x:v>
       </x:c>
     </x:row>
+    <x:row r="18">
+      <x:c r="A18" s="13" t="str">
+        <x:v>SEC-17</x:v>
+      </x:c>
+      <x:c r="B18" s="13" t="str">
+        <x:v>실행 자원 격리</x:v>
+      </x:c>
+      <x:c r="C18" s="13" t="str">
+        <x:v>일반 웹 요청 CPU/RAM을 사용자별로 추정하지 않고 관리 job만 userUid/jobId로 귀속한다.</x:v>
+      </x:c>
+      <x:c r="D18" s="13" t="str">
+        <x:v>Python 실행은 non-root cgroup v2, CPU/RAM/PID/time/disk/output 제한, 기본 network none을 모두 적용하기 전 공개하지 않는다.</x:v>
+      </x:c>
+      <x:c r="E18" s="13" t="str">
+        <x:v>M2 worker gate</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9d79ff55264b434f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9c759652c9d549df"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5727,10 +5744,27 @@
         <x:v>author/comment 권한, If-Match</x:v>
       </x:c>
     </x:row>
+    <x:row r="27">
+      <x:c r="A27" s="13" t="str">
+        <x:v>API-27</x:v>
+      </x:c>
+      <x:c r="B27" s="13" t="str">
+        <x:v>공통 자원 예약 계약</x:v>
+      </x:c>
+      <x:c r="C27" s="13" t="str">
+        <x:v>관리 작업 시작 전 userUid, jobId, 요청 CPU·RAM으로 reserve하고 available만 실행한다.</x:v>
+      </x:c>
+      <x:c r="D27" s="13" t="str">
+        <x:v>queued는 안전 회복 뒤 재평가, blocked는 이유 코드 표시, 모든 종료 경로는 release한다.</x:v>
+      </x:c>
+      <x:c r="E27" s="13" t="str">
+        <x:v>backend/resourceControlService.js</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ref29acba4a654900"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R95e6e5456d994ff7"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6041,7 +6075,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R634430ec18fb4363"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R168eece0bba54ccb"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6352,7 +6386,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R527a9fdb88af4739"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ree8cb3b484ad4f78"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6680,7 +6714,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7f139b34c8fb46bd"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R716964b315db436c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6920,10 +6954,27 @@
         <x:v>incremental projection, hash cache, background merge</x:v>
       </x:c>
     </x:row>
+    <x:row r="14">
+      <x:c r="A14" s="13" t="str">
+        <x:v>PERF-13</x:v>
+      </x:c>
+      <x:c r="B14" s="13" t="str">
+        <x:v>서버 자원 admission</x:v>
+      </x:c>
+      <x:c r="C14" s="13" t="str">
+        <x:v>Python/AI/문서 변환은 공통 자원 정책의 사용자 CPU·RAM·동시 작업 예약과 시스템 soft 대기/hard 차단을 통과해야 한다.</x:v>
+      </x:c>
+      <x:c r="D14" s="13" t="str">
+        <x:v>자동 기준은 논리 CPU·RAM·NAS 여유를 매 수집 시 재계산하고 관리자 override를 지원한다.</x:v>
+      </x:c>
+      <x:c r="E14" s="13" t="str">
+        <x:v>M2 worker gate</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8c036884e34c4853"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R934b710b5e454ae8"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7084,7 +7135,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdd2f08cc041b49a2"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R96b226bab20642a8"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7664,10 +7715,30 @@
         <x:v>M1-F 다음 gate</x:v>
       </x:c>
     </x:row>
+    <x:row r="29">
+      <x:c r="A29" s="13" t="str">
+        <x:v>T-028</x:v>
+      </x:c>
+      <x:c r="B29" s="13" t="str">
+        <x:v>자원 정책 자동/수동·사용자 한도</x:v>
+      </x:c>
+      <x:c r="C29" s="13" t="str">
+        <x:v>CPU/RAM/스왑/온도/디스크 soft·hard와 사용자 CPU/RAM/동시 작업 초과</x:v>
+      </x:c>
+      <x:c r="D29" s="13" t="str">
+        <x:v>soft queued, hard/user blocked, monitor-only available, 정책 저장 후 재로드 일치</x:v>
+      </x:c>
+      <x:c r="E29" s="13" t="str">
+        <x:v>unit+API+E2E</x:v>
+      </x:c>
+      <x:c r="F29" s="13" t="str">
+        <x:v>M2 resource gate</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb04ec025ebae45d2"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R96f88786fb454585"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8012,7 +8083,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rba6b038183ca4643"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R88e0ef0ec4d94071"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8153,7 +8224,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9a09d5e4e84447d0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0d003bbe8be6425d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8362,7 +8433,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc1f3cd6785d14b11"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3299631d57aa4d30"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8502,10 +8573,30 @@
         <x:v>Codex</x:v>
       </x:c>
     </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="13" t="str">
+        <x:v>2026-09-06</x:v>
+      </x:c>
+      <x:c r="B7" s="13" t="str">
+        <x:v>0.6-resource-control-foundation</x:v>
+      </x:c>
+      <x:c r="C7" s="13" t="str">
+        <x:v>1차 구현·로컬 검증 / 운영 배포 전</x:v>
+      </x:c>
+      <x:c r="D7" s="13" t="str">
+        <x:v>노트 Python·AI 실행보다 먼저 공통 자원 정책·이력·사용자 한도와 문서 변환 admission을 구현했다.</x:v>
+      </x:c>
+      <x:c r="E7" s="13" t="str">
+        <x:v>공유 Node 요청은 사용자별 CPU/RAM으로 표시하지 않으며 실제 worker cgroup은 M2 gate로 유지한다.</x:v>
+      </x:c>
+      <x:c r="F7" s="13" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf1c9ad92823c4502"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re666425b9e634c57"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8800,6 +8891,26 @@
       </x:c>
       <x:c r="F14" s="13" t="str">
         <x:v>격리 worker·fair queue·부하/OOM/재감지 gate</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" s="13" t="str">
+        <x:v>M2-R</x:v>
+      </x:c>
+      <x:c r="B15" s="13" t="str">
+        <x:v>공통 자원 보호 선행 기반</x:v>
+      </x:c>
+      <x:c r="C15" s="13" t="str">
+        <x:v>정책·이력·문서 변환 admission 1차 구현 / NAS 배포 전</x:v>
+      </x:c>
+      <x:c r="D15" s="13" t="str">
+        <x:v>auto/manual 기준, 사용자별 storage와 관리 job 예약, 30초 이력, 관리자 UI</x:v>
+      </x:c>
+      <x:c r="E15" s="13" t="str">
+        <x:v>resource control unit 포함 backend 전체 45 tests·frontend build</x:v>
+      </x:c>
+      <x:c r="F15" s="13" t="str">
+        <x:v>남음: NAS 실측/E2E, Python·AI non-root cgroup worker 실제 계측</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -9011,7 +9122,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R351e6b55c286488e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R37ea4eed6ac7438d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9294,7 +9405,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2d12c7f166374d90"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb07395930733466a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9690,7 +9801,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8aea3eaceef24f08"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R69a229243e184128"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9933,7 +10044,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7cb53c37fd074d01"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1710fc8064854d08"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10108,7 +10219,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re62337da67034b10"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R701b38d4fad3459c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10368,7 +10479,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb54d284a74d84903"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc3bba632d88c436e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/programs/NAS_NOTE_STUDIO_SPEC.xlsx
+++ b/docs/programs/NAS_NOTE_STUDIO_SPEC.xlsx
@@ -2,39 +2,39 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="R88008cd0850f4e14"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Product_Vision" sheetId="2" r:id="Ra501753b327b4ebc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decisions" sheetId="3" r:id="R0ceb798270954d37"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Competitors" sheetId="4" r:id="R57873ee093cc44c8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open_Source" sheetId="5" r:id="Re9101f3ee9e14170"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source_Index" sheetId="6" r:id="R659f0cec87bc422a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Information_Architecture" sheetId="7" r:id="R4175522060e04a1c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI_Layout" sheetId="8" r:id="Rac918d4c860e494a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="User_Flows" sheetId="9" r:id="R4a6ee37a6c594932"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Note_Types" sheetId="10" r:id="Re4ebda6b5de44de4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Block_Catalog" sheetId="11" r:id="R7e187ed83ece4f1d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Slash_Commands" sheetId="12" r:id="R0244fdaf49e847b6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Context_Menus" sheetId="13" r:id="Rd14a1648fc924ebe"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Keyboard_Shortcuts" sheetId="14" r:id="R4ea5c7b0516b485a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Database_Views" sheetId="15" r:id="Racb1f9a0ac44419d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Code_Text_Mode" sheetId="16" r:id="Rc31acca65fe8421b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Python_Notebook" sheetId="17" r:id="Re3e3c28ee5624630"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Collaboration" sheetId="18" r:id="Ra2a2b851496545aa"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Offline_Desktop" sheetId="19" r:id="R4701f2d34eb64805"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data_Model" sheetId="20" r:id="R7ef7d1345bbc4ebc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Storage_Interop" sheetId="21" r:id="Rb933c305d4f7470e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Security" sheetId="22" r:id="R981c8d328c864d56"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="API_Contracts" sheetId="23" r:id="Reb22e8a83a2a429d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="State_Machines" sheetId="24" r:id="R6a5a09feb0b1467f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Error_Recovery" sheetId="25" r:id="Rc8865528409b495b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cross_App_Relations" sheetId="26" r:id="Ra345e50048544b1b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Performance" sheetId="27" r:id="Rdf20ec1e230d4bfa"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Accessibility" sheetId="28" r:id="Rb9858d62b6714972"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test_Matrix" sheetId="29" r:id="R51dc9b333b6342be"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="30" r:id="Re4034a6fe1524276"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open_Questions" sheetId="31" r:id="R69fc854729dc476b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Change_Log" sheetId="32" r:id="Rbc9a773cc4ce4d7b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Implementation_Status" sheetId="33" r:id="R722978725e4b4041"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="R53cf500ed7ab474e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Product_Vision" sheetId="2" r:id="Rfb3e242d8da94f20"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decisions" sheetId="3" r:id="Rc03a4cf7ff784820"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Competitors" sheetId="4" r:id="Recfc4974dc5746f7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open_Source" sheetId="5" r:id="R7c5fe94c4fd54b3d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source_Index" sheetId="6" r:id="R9e55173ba796483d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Information_Architecture" sheetId="7" r:id="Rb1d5e63bce344578"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI_Layout" sheetId="8" r:id="Raae64536dd984b5b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="User_Flows" sheetId="9" r:id="R0a430da740a14343"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Note_Types" sheetId="10" r:id="R71b54a2f937643ba"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Block_Catalog" sheetId="11" r:id="R7e81e26fb3d645ff"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Slash_Commands" sheetId="12" r:id="R3a7883984f15493e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Context_Menus" sheetId="13" r:id="Ra9418c80d0e44c6d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Keyboard_Shortcuts" sheetId="14" r:id="R7617ba48930b487c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Database_Views" sheetId="15" r:id="R4daf9daad30c4d8b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Code_Text_Mode" sheetId="16" r:id="R8021bb22e7d54ad6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Python_Notebook" sheetId="17" r:id="Rb5f3693451c14e1c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Collaboration" sheetId="18" r:id="R7a1ac9053db747ea"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Offline_Desktop" sheetId="19" r:id="R9c4942fdec9146d9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data_Model" sheetId="20" r:id="R2911bcb6280e40e4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Storage_Interop" sheetId="21" r:id="R3b23f3b3637e468b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Security" sheetId="22" r:id="Rd35f667898764871"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="API_Contracts" sheetId="23" r:id="R6e46227a055c4419"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="State_Machines" sheetId="24" r:id="R1ae466d16e2b4220"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Error_Recovery" sheetId="25" r:id="Rad79dc923c124b86"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cross_App_Relations" sheetId="26" r:id="R98e8648fc45f4a94"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Performance" sheetId="27" r:id="R891a5e4748b04f8c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Accessibility" sheetId="28" r:id="R73ec3b56c5444dff"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test_Matrix" sheetId="29" r:id="R90e25248da644565"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="30" r:id="Rac91bcae64634487"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open_Questions" sheetId="31" r:id="R7eaa7ac485d6459e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Change_Log" sheetId="32" r:id="Re589f92c31304710"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Implementation_Status" sheetId="33" r:id="R2ef910b1d96d474e"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -928,7 +928,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re7dbb9b6911a42c8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf37f9191ca544371"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1271,7 +1271,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R15971f26e26949ed"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdbe935851f32432d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1674,7 +1674,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1a46ec7f87d04d60"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3447a418d80343a7"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2057,7 +2057,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R47d87b2c3fe346cb"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbc6c28056f4446a1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2470,7 +2470,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6aea1f5f9eb24fb9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Redf7818663014fd4"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2968,7 +2968,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfa63eda388424182"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rabba991a364c4000"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3228,7 +3228,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6b9eaf2dc3364387"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0ed2ff03510543e6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3420,7 +3420,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R565d183ad6ed4f77"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2ee15d527e264e90"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3748,7 +3748,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rab03f804eed24330"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Raddcc7c7e55441ce"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4008,7 +4008,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R46f08e51a6d04b50"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1128a78dd1c949d0"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4200,7 +4200,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ree357a84a59140aa"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra9ce1eeb9f9f4281"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4333,7 +4333,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R344fca5a6ed74361"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re47f601141284779"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4712,7 +4712,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R44b4080cb9274db6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rab0822e6ceb64f11"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4955,7 +4955,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7bc9a6cd40504632"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb5a26e08f5c84cdc"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5283,7 +5283,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9c759652c9d549df"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R242d64dad27b4c0d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5764,7 +5764,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R95e6e5456d994ff7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd970fe3c529941ab"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6075,7 +6075,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R168eece0bba54ccb"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R698d534ab9d6407a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6386,7 +6386,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ree8cb3b484ad4f78"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R678ec83b2e124519"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6714,7 +6714,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R716964b315db436c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rae5339c96273498d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6974,7 +6974,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R934b710b5e454ae8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R06bcf0cdb9d24ed7"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7135,7 +7135,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R96b226bab20642a8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4525fafbc25042ff"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7738,7 +7738,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R96f88786fb454585"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6bd2a56487d34feb"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8083,7 +8083,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R88e0ef0ec4d94071"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re79160b584334beb"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8224,7 +8224,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0d003bbe8be6425d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R751d729a6c114acb"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8433,7 +8433,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3299631d57aa4d30"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R020fcdab8f964c66"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8581,13 +8581,13 @@
         <x:v>0.6-resource-control-foundation</x:v>
       </x:c>
       <x:c r="C7" s="13" t="str">
-        <x:v>1차 구현·로컬 검증 / 운영 배포 전</x:v>
+        <x:v>운영 배포·실장비/API 검증 완료</x:v>
       </x:c>
       <x:c r="D7" s="13" t="str">
         <x:v>노트 Python·AI 실행보다 먼저 공통 자원 정책·이력·사용자 한도와 문서 변환 admission을 구현했다.</x:v>
       </x:c>
       <x:c r="E7" s="13" t="str">
-        <x:v>공유 Node 요청은 사용자별 CPU/RAM으로 표시하지 않으며 실제 worker cgroup은 M2 gate로 유지한다.</x:v>
+        <x:v>commit 95574a0. NAS 45/45, live main.6d92bef9.js, auto gate available. Python·AI cgroup worker와 로그인 화면 E2E는 다음 gate.</x:v>
       </x:c>
       <x:c r="F7" s="13" t="str">
         <x:v>Codex</x:v>
@@ -8596,7 +8596,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re666425b9e634c57"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf50618df0f604937"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8901,16 +8901,16 @@
         <x:v>공통 자원 보호 선행 기반</x:v>
       </x:c>
       <x:c r="C15" s="13" t="str">
-        <x:v>정책·이력·문서 변환 admission 1차 구현 / NAS 배포 전</x:v>
+        <x:v>정책·이력·문서 변환 admission 운영 배포·실장비/API 검증 완료</x:v>
       </x:c>
       <x:c r="D15" s="13" t="str">
         <x:v>auto/manual 기준, 사용자별 storage와 관리 job 예약, 30초 이력, 관리자 UI</x:v>
       </x:c>
       <x:c r="E15" s="13" t="str">
-        <x:v>resource control unit 포함 backend 전체 45 tests·frontend build</x:v>
+        <x:v>local backend 43+2 skip/build; NAS Linux 45/45·build/PDF.js·API/HTTP/service</x:v>
       </x:c>
       <x:c r="F15" s="13" t="str">
-        <x:v>남음: NAS 실측/E2E, Python·AI non-root cgroup worker 실제 계측</x:v>
+        <x:v>남음: 로그인 관리자 화면 육안 E2E, Python·AI non-root cgroup worker 실제 계측</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -9122,7 +9122,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R37ea4eed6ac7438d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R247fabf3dee142fc"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9405,7 +9405,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb07395930733466a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R93c09af65eb44227"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9801,7 +9801,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R69a229243e184128"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rccaf6d6859534af1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10044,7 +10044,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1710fc8064854d08"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0008b9c76d914e17"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10219,7 +10219,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R701b38d4fad3459c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9bd02efcced44c93"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10479,7 +10479,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc3bba632d88c436e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1493ba2b701a4ae8"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/programs/NAS_NOTE_STUDIO_SPEC.xlsx
+++ b/docs/programs/NAS_NOTE_STUDIO_SPEC.xlsx
@@ -2,39 +2,39 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="R53cf500ed7ab474e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Product_Vision" sheetId="2" r:id="Rfb3e242d8da94f20"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decisions" sheetId="3" r:id="Rc03a4cf7ff784820"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Competitors" sheetId="4" r:id="Recfc4974dc5746f7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open_Source" sheetId="5" r:id="R7c5fe94c4fd54b3d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source_Index" sheetId="6" r:id="R9e55173ba796483d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Information_Architecture" sheetId="7" r:id="Rb1d5e63bce344578"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI_Layout" sheetId="8" r:id="Raae64536dd984b5b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="User_Flows" sheetId="9" r:id="R0a430da740a14343"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Note_Types" sheetId="10" r:id="R71b54a2f937643ba"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Block_Catalog" sheetId="11" r:id="R7e81e26fb3d645ff"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Slash_Commands" sheetId="12" r:id="R3a7883984f15493e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Context_Menus" sheetId="13" r:id="Ra9418c80d0e44c6d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Keyboard_Shortcuts" sheetId="14" r:id="R7617ba48930b487c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Database_Views" sheetId="15" r:id="R4daf9daad30c4d8b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Code_Text_Mode" sheetId="16" r:id="R8021bb22e7d54ad6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Python_Notebook" sheetId="17" r:id="Rb5f3693451c14e1c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Collaboration" sheetId="18" r:id="R7a1ac9053db747ea"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Offline_Desktop" sheetId="19" r:id="R9c4942fdec9146d9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data_Model" sheetId="20" r:id="R2911bcb6280e40e4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Storage_Interop" sheetId="21" r:id="R3b23f3b3637e468b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Security" sheetId="22" r:id="Rd35f667898764871"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="API_Contracts" sheetId="23" r:id="R6e46227a055c4419"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="State_Machines" sheetId="24" r:id="R1ae466d16e2b4220"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Error_Recovery" sheetId="25" r:id="Rad79dc923c124b86"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cross_App_Relations" sheetId="26" r:id="R98e8648fc45f4a94"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Performance" sheetId="27" r:id="R891a5e4748b04f8c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Accessibility" sheetId="28" r:id="R73ec3b56c5444dff"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test_Matrix" sheetId="29" r:id="R90e25248da644565"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="30" r:id="Rac91bcae64634487"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open_Questions" sheetId="31" r:id="R7eaa7ac485d6459e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Change_Log" sheetId="32" r:id="Re589f92c31304710"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Implementation_Status" sheetId="33" r:id="R2ef910b1d96d474e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="Rba86c87b3b9d4cd6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Product_Vision" sheetId="2" r:id="R26802227eac8481a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decisions" sheetId="3" r:id="Ra61de06a362f4b66"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Competitors" sheetId="4" r:id="Rc24289bee4624ae3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open_Source" sheetId="5" r:id="R37a459fcb3a44dcb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source_Index" sheetId="6" r:id="Rb2337e33c42442bd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Information_Architecture" sheetId="7" r:id="R9cbaeafadbbe4bd4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI_Layout" sheetId="8" r:id="R62858e1aafc04a62"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="User_Flows" sheetId="9" r:id="R760bc95c5ebc4915"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Note_Types" sheetId="10" r:id="Rf8281955db234c55"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Block_Catalog" sheetId="11" r:id="R9926a01f2bdc431a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Slash_Commands" sheetId="12" r:id="R2095a14dce944b2a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Context_Menus" sheetId="13" r:id="Rcac87fbe92844865"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Keyboard_Shortcuts" sheetId="14" r:id="R8befbc0a0537432e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Database_Views" sheetId="15" r:id="Rd640aa057ca541e6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Code_Text_Mode" sheetId="16" r:id="R26c51cc4293c46cb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Python_Notebook" sheetId="17" r:id="Rd4fc86e587384a27"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Collaboration" sheetId="18" r:id="Rd054242dc0a14729"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Offline_Desktop" sheetId="19" r:id="Ra4e7c363d9b348d2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data_Model" sheetId="20" r:id="R47976deec579454c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Storage_Interop" sheetId="21" r:id="R1ce0bac7851a4c59"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Security" sheetId="22" r:id="R0031cc5d284a48d9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="API_Contracts" sheetId="23" r:id="Re3cbcb2bc43e42af"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="State_Machines" sheetId="24" r:id="R8d483161eb424c49"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Error_Recovery" sheetId="25" r:id="Reea3f62335184e40"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cross_App_Relations" sheetId="26" r:id="Rbcd204b4f2004218"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Performance" sheetId="27" r:id="Rac7cb82c324140c7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Accessibility" sheetId="28" r:id="R70a6b9f4a7114b7a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test_Matrix" sheetId="29" r:id="Re7ac58bdb3944370"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="30" r:id="Rb9902f4c9e764e05"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open_Questions" sheetId="31" r:id="Rd7a38d26f36b4865"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Change_Log" sheetId="32" r:id="R226113afa2b347a3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Implementation_Status" sheetId="33" r:id="Re48951fbb0054fd6"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -928,7 +928,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf37f9191ca544371"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R14e3af4496d24740"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1271,7 +1271,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdbe935851f32432d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re61155be7bd04bd0"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1674,7 +1674,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3447a418d80343a7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5d3ae19a32b74059"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2057,7 +2057,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbc6c28056f4446a1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R48a76073277943b5"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2470,7 +2470,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Redf7818663014fd4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5ee76eda0f50400c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2968,7 +2968,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rabba991a364c4000"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R06f4169810ab4f53"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3228,7 +3228,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0ed2ff03510543e6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R492c0a705b714d86"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3420,7 +3420,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2ee15d527e264e90"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rca9a654954f8427f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3748,7 +3748,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Raddcc7c7e55441ce"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R62df253ebf5b4b45"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4008,7 +4008,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1128a78dd1c949d0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc92c7c2b2ffc418c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4200,7 +4200,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra9ce1eeb9f9f4281"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R64be330545e9411a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4333,7 +4333,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re47f601141284779"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0d8a4e15d23b4c3d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4712,7 +4712,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rab0822e6ceb64f11"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra3f625299be546b3"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4955,7 +4955,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb5a26e08f5c84cdc"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rda57fa9b63ef429e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5283,7 +5283,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R242d64dad27b4c0d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3e5f27f8e3a44de0"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5764,7 +5764,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd970fe3c529941ab"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcdacc69f5e334bba"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6075,7 +6075,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R698d534ab9d6407a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc6bf660c40c04426"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6386,7 +6386,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R678ec83b2e124519"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5fadcc3b5bff41ad"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6714,7 +6714,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rae5339c96273498d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0304b2c52e3547b9"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6974,7 +6974,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R06bcf0cdb9d24ed7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R113335de0a01434f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7135,7 +7135,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4525fafbc25042ff"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R395817a9d1e14df7"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7738,7 +7738,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6bd2a56487d34feb"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0a60063871ba4d8c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8083,7 +8083,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re79160b584334beb"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc589b5c28004402a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8224,7 +8224,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R751d729a6c114acb"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R18eb147a58684c08"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8433,7 +8433,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R020fcdab8f964c66"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2687f435e58c4e0c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8587,7 +8587,7 @@
         <x:v>노트 Python·AI 실행보다 먼저 공통 자원 정책·이력·사용자 한도와 문서 변환 admission을 구현했다.</x:v>
       </x:c>
       <x:c r="E7" s="13" t="str">
-        <x:v>commit 95574a0. NAS 45/45, live main.6d92bef9.js, auto gate available. Python·AI cgroup worker와 로그인 화면 E2E는 다음 gate.</x:v>
+        <x:v>기반 commit 95574a0 이후 전역 burst gate 보강. NAS 46/46, live main.6d92bef9.js, auto gate available. Python·AI cgroup worker와 로그인 화면 E2E는 다음 gate.</x:v>
       </x:c>
       <x:c r="F7" s="13" t="str">
         <x:v>Codex</x:v>
@@ -8596,7 +8596,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf50618df0f604937"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4c9671b79a114c54"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8907,7 +8907,7 @@
         <x:v>auto/manual 기준, 사용자별 storage와 관리 job 예약, 30초 이력, 관리자 UI</x:v>
       </x:c>
       <x:c r="E15" s="13" t="str">
-        <x:v>local backend 43+2 skip/build; NAS Linux 45/45·build/PDF.js·API/HTTP/service</x:v>
+        <x:v>local backend 44+2 skip/build; NAS Linux 46/46·build/PDF.js·API/HTTP/service</x:v>
       </x:c>
       <x:c r="F15" s="13" t="str">
         <x:v>남음: 로그인 관리자 화면 육안 E2E, Python·AI non-root cgroup worker 실제 계측</x:v>
@@ -9122,7 +9122,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R247fabf3dee142fc"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R42b8b2682ee44f7e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9405,7 +9405,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R93c09af65eb44227"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd5b240d6789d47e1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9801,7 +9801,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rccaf6d6859534af1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R05c88d00c6034fdb"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10044,7 +10044,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0008b9c76d914e17"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc2af2338f7544976"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10219,7 +10219,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9bd02efcced44c93"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7dcb59b78e974f57"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10479,7 +10479,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1493ba2b701a4ae8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4f7af85bd485461f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/programs/NAS_NOTE_STUDIO_SPEC.xlsx
+++ b/docs/programs/NAS_NOTE_STUDIO_SPEC.xlsx
@@ -2,39 +2,39 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="Rba86c87b3b9d4cd6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Product_Vision" sheetId="2" r:id="R26802227eac8481a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decisions" sheetId="3" r:id="Ra61de06a362f4b66"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Competitors" sheetId="4" r:id="Rc24289bee4624ae3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open_Source" sheetId="5" r:id="R37a459fcb3a44dcb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source_Index" sheetId="6" r:id="Rb2337e33c42442bd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Information_Architecture" sheetId="7" r:id="R9cbaeafadbbe4bd4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI_Layout" sheetId="8" r:id="R62858e1aafc04a62"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="User_Flows" sheetId="9" r:id="R760bc95c5ebc4915"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Note_Types" sheetId="10" r:id="Rf8281955db234c55"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Block_Catalog" sheetId="11" r:id="R9926a01f2bdc431a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Slash_Commands" sheetId="12" r:id="R2095a14dce944b2a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Context_Menus" sheetId="13" r:id="Rcac87fbe92844865"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Keyboard_Shortcuts" sheetId="14" r:id="R8befbc0a0537432e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Database_Views" sheetId="15" r:id="Rd640aa057ca541e6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Code_Text_Mode" sheetId="16" r:id="R26c51cc4293c46cb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Python_Notebook" sheetId="17" r:id="Rd4fc86e587384a27"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Collaboration" sheetId="18" r:id="Rd054242dc0a14729"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Offline_Desktop" sheetId="19" r:id="Ra4e7c363d9b348d2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data_Model" sheetId="20" r:id="R47976deec579454c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Storage_Interop" sheetId="21" r:id="R1ce0bac7851a4c59"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Security" sheetId="22" r:id="R0031cc5d284a48d9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="API_Contracts" sheetId="23" r:id="Re3cbcb2bc43e42af"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="State_Machines" sheetId="24" r:id="R8d483161eb424c49"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Error_Recovery" sheetId="25" r:id="Reea3f62335184e40"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cross_App_Relations" sheetId="26" r:id="Rbcd204b4f2004218"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Performance" sheetId="27" r:id="Rac7cb82c324140c7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Accessibility" sheetId="28" r:id="R70a6b9f4a7114b7a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test_Matrix" sheetId="29" r:id="Re7ac58bdb3944370"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="30" r:id="Rb9902f4c9e764e05"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open_Questions" sheetId="31" r:id="Rd7a38d26f36b4865"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Change_Log" sheetId="32" r:id="R226113afa2b347a3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Implementation_Status" sheetId="33" r:id="Re48951fbb0054fd6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="R4564d51166ac4ad1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Product_Vision" sheetId="2" r:id="R07515d4a37084a9a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decisions" sheetId="3" r:id="R4b5a9fe80ffe49f0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Competitors" sheetId="4" r:id="R6348557eb8554837"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open_Source" sheetId="5" r:id="R6d6c62b234964096"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source_Index" sheetId="6" r:id="Raac80bba72674dd7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Information_Architecture" sheetId="7" r:id="R0f8066646c514bb7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI_Layout" sheetId="8" r:id="Re9649199263b4de0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="User_Flows" sheetId="9" r:id="R81b760d18e334637"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Note_Types" sheetId="10" r:id="R426b83b4b82f4211"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Block_Catalog" sheetId="11" r:id="R17aafa5bf3c3489d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Slash_Commands" sheetId="12" r:id="Rc97ad68919d346ba"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Context_Menus" sheetId="13" r:id="Rdcc82968d9844b75"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Keyboard_Shortcuts" sheetId="14" r:id="Rd1380c62f3e343cd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Database_Views" sheetId="15" r:id="R177f2b00a6bd4004"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Code_Text_Mode" sheetId="16" r:id="R94824cb25bd7414f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Python_Notebook" sheetId="17" r:id="R5e2ff43f727d4c42"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Collaboration" sheetId="18" r:id="Rf3d39f3dab2a48df"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Offline_Desktop" sheetId="19" r:id="R2c0fc92908fc4202"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data_Model" sheetId="20" r:id="R9b5e4e0ad0fe472b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Storage_Interop" sheetId="21" r:id="R634b7a12d4cb46af"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Security" sheetId="22" r:id="R3cf08108beac44bd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="API_Contracts" sheetId="23" r:id="Rb77e8717c30f4a3f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="State_Machines" sheetId="24" r:id="R6384dacf5ca44043"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Error_Recovery" sheetId="25" r:id="Rc24eb2d343c748e7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cross_App_Relations" sheetId="26" r:id="R33a886b781d44863"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Performance" sheetId="27" r:id="Rc7625d77b4884c7b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Accessibility" sheetId="28" r:id="R10934dfa648e4dc8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test_Matrix" sheetId="29" r:id="R0f01b3df12eb488a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="30" r:id="R1bebb297e10f4e04"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open_Questions" sheetId="31" r:id="Re6bf4b8731a348d9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Change_Log" sheetId="32" r:id="R3b342b83d8fd437f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Implementation_Status" sheetId="33" r:id="Rfc1658362edf4f37"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -928,7 +928,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R14e3af4496d24740"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfef1564d9f4245d6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1271,7 +1271,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re61155be7bd04bd0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R990ab049d6544188"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1674,7 +1674,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5d3ae19a32b74059"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5a54982bbbc74a65"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2057,7 +2057,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R48a76073277943b5"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ref149f1b97bd4dda"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2470,7 +2470,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5ee76eda0f50400c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf61e39e7137a4a4c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2968,7 +2968,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R06f4169810ab4f53"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R122242ef433c4273"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3228,7 +3228,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R492c0a705b714d86"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9166417e58814b0a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3420,7 +3420,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rca9a654954f8427f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0d9b0d2bc6464efd"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3748,7 +3748,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R62df253ebf5b4b45"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R619e95466f2a4641"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4008,7 +4008,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc92c7c2b2ffc418c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R20b23ecbd6994bef"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4200,7 +4200,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R64be330545e9411a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2c7efdec05d8443f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4333,7 +4333,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0d8a4e15d23b4c3d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R147237106fd94220"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4712,7 +4712,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra3f625299be546b3"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5ad8c28edff6457e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4952,10 +4952,27 @@
         <x:v>M1 확장</x:v>
       </x:c>
     </x:row>
+    <x:row r="14">
+      <x:c r="A14" s="13" t="str">
+        <x:v>로컬 프로젝트 고정 경로</x:v>
+      </x:c>
+      <x:c r="B14" s="13" t="str">
+        <x:v>프로젝트 root 아래 실제 동일 suffix는 이 PC 절대 경로로 안전 제안. 외부 sibling/ancestor는 연결된 NAS Drive에서 유일한 경우만 검토 제안.</x:v>
+      </x:c>
+      <x:c r="C14" s="13" t="str">
+        <x:v>제어센터에서 프로젝트 선택 → 자동 적용/확인 필요/변경 안 함 요약 → 파일·줄별 체크 → 적용하고 열기 또는 그대로 열기 → 즉시 undo</x:v>
+      </x:c>
+      <x:c r="D14" s="13" t="str">
+        <x:v>부분 hydrate 자동 실행, PC 전체 검색, 모호한 대상 자동 선택, server canonical 변경, secret 파일 preview 금지</x:v>
+      </x:c>
+      <x:c r="E14" s="13" t="str">
+        <x:v>WINDOWS NAS DRIVE, M2 local projection</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rda57fa9b63ef429e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4067c9604b224c3f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5280,10 +5297,27 @@
         <x:v>M2 worker gate</x:v>
       </x:c>
     </x:row>
+    <x:row r="19">
+      <x:c r="A19" s="13" t="str">
+        <x:v>SEC-18</x:v>
+      </x:c>
+      <x:c r="B19" s="13" t="str">
+        <x:v>고정 경로 오인·비밀 노출·로컬 파일 덮어쓰기</x:v>
+      </x:c>
+      <x:c r="C19" s="13" t="str">
+        <x:v>연결 NAS Drive와 선택 project 경계, real target 존재·유일성, secret/vendor/build/symlink 제외, SHA-256 precondition, atomic replace, 외부 상태 backup/undo.</x:v>
+      </x:c>
+      <x:c r="D19" s="13" t="str">
+        <x:v>내부 suffix·외부 유일·외부 중복·미존재·URL·.env·변경 후 apply·apply 후 수정된 undo 회귀</x:v>
+      </x:c>
+      <x:c r="E19" s="13" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3e5f27f8e3a44de0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R038b016d24664535"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5764,7 +5798,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcdacc69f5e334bba"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0c6aaec2e6eb4285"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6075,7 +6109,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc6bf660c40c04426"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3368b4a6678046f4"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6386,7 +6420,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5fadcc3b5bff41ad"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc6c91b393bd745a6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6714,7 +6748,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0304b2c52e3547b9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9f0e07ed2fc04bff"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6974,7 +7008,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R113335de0a01434f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rae4dbc2c8bb44a21"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7135,7 +7169,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R395817a9d1e14df7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R353288deea6444db"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7735,10 +7769,30 @@
         <x:v>M2 resource gate</x:v>
       </x:c>
     </x:row>
+    <x:row r="30">
+      <x:c r="A30" s="13" t="str">
+        <x:v>T-029</x:v>
+      </x:c>
+      <x:c r="B30" s="13" t="str">
+        <x:v>프로젝트 경로 이동 보조</x:v>
+      </x:c>
+      <x:c r="C30" s="13" t="str">
+        <x:v>내부 고정 경로, 외부 sibling/ancestor 유일·중복, URL, .env, symlink, preview 뒤 동시 수정, apply 뒤 동시 수정</x:v>
+      </x:c>
+      <x:c r="D30" s="13" t="str">
+        <x:v>내부 실제 suffix만 기본 선택, 외부는 수동, 모호/비밀/경계 밖 0건 변경, hash 불일치 중단, apply/undo byte 복원</x:v>
+      </x:c>
+      <x:c r="E30" s="13" t="str">
+        <x:v>unit+Windows UI+E2E</x:v>
+      </x:c>
+      <x:c r="F30" s="13" t="str">
+        <x:v>M2 local projection 선행</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0a60063871ba4d8c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ree7e125ab59f4687"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8083,7 +8137,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc589b5c28004402a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R194ed47eb9984e95"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8224,7 +8278,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R18eb147a58684c08"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdf224bc5db034c70"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8433,7 +8487,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2687f435e58c4e0c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9c3ea7cad2664df5"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8593,10 +8647,30 @@
         <x:v>Codex</x:v>
       </x:c>
     </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="13" t="str">
+        <x:v>2026-09-06</x:v>
+      </x:c>
+      <x:c r="B8" s="13" t="str">
+        <x:v>0.7-path-portability-foundation</x:v>
+      </x:c>
+      <x:c r="C8" s="13" t="str">
+        <x:v>Agent/Setup 1.11.2 1차 구현·로컬 검증 완료 / 운영·실PC E2E 전</x:v>
+      </x:c>
+      <x:c r="D8" s="13" t="str">
+        <x:v>NAS Drive 제어센터에 프로젝트 경로 확인을 추가하고 내부 안전 자동·외부 검토·미해결 3단계, 파일·줄별 선택, 적용하지 않고 열기, SHA-256 사전조건, 원자 저장과 즉시 undo를 구현했다.</x:v>
+      </x:c>
+      <x:c r="E8" s="13" t="str">
+        <x:v>VS Code·JetBrains·Python 공식 경로 모델 조사. projectPathPortability unit, Agent self-test, Setup compile/self-test, DPI UI render.</x:v>
+      </x:c>
+      <x:c r="F8" s="13" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4c9671b79a114c54"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re4d70209b7da47f1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8911,6 +8985,26 @@
       </x:c>
       <x:c r="F15" s="13" t="str">
         <x:v>남음: 로그인 관리자 화면 육안 E2E, Python·AI non-root cgroup worker 실제 계측</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" s="13" t="str">
+        <x:v>M1-H</x:v>
+      </x:c>
+      <x:c r="B16" s="13" t="str">
+        <x:v>Windows 프로젝트 경로 이동 보조</x:v>
+      </x:c>
+      <x:c r="C16" s="13" t="str">
+        <x:v>Agent/Setup 1.11.2 1차 구현·로컬 검증 완료 / 운영·실PC E2E 전</x:v>
+      </x:c>
+      <x:c r="D16" s="13" t="str">
+        <x:v>프로젝트 선택, 절대경로 분석, 실제 suffix·외부 유일 매핑, 3단계 검토 UI, 선택 적용, hash precondition, atomic write, undo</x:v>
+      </x:c>
+      <x:c r="E16" s="13" t="str">
+        <x:v>unit·Agent self-test·Setup compile/self-test·DPI UI render</x:v>
+      </x:c>
+      <x:c r="F16" s="13" t="str">
+        <x:v>운영 배포, 새 설치본 실PC E2E, marker 기반 완전 hydrate 자동 알림, IDE portable variable 변환</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -9122,7 +9216,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R42b8b2682ee44f7e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R29734a9096524ca3"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9405,7 +9499,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd5b240d6789d47e1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6ae3eb8293044a3a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9801,7 +9895,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R05c88d00c6034fdb"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra4951993f72847d7"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10044,7 +10138,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc2af2338f7544976"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0230317f2c6f404f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10219,7 +10313,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7dcb59b78e974f57"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2fe8c1ae556540d1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10479,7 +10573,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4f7af85bd485461f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R399c576afe7a4889"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/programs/NAS_NOTE_STUDIO_SPEC.xlsx
+++ b/docs/programs/NAS_NOTE_STUDIO_SPEC.xlsx
@@ -2,39 +2,39 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="R4564d51166ac4ad1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Product_Vision" sheetId="2" r:id="R07515d4a37084a9a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decisions" sheetId="3" r:id="R4b5a9fe80ffe49f0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Competitors" sheetId="4" r:id="R6348557eb8554837"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open_Source" sheetId="5" r:id="R6d6c62b234964096"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source_Index" sheetId="6" r:id="Raac80bba72674dd7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Information_Architecture" sheetId="7" r:id="R0f8066646c514bb7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI_Layout" sheetId="8" r:id="Re9649199263b4de0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="User_Flows" sheetId="9" r:id="R81b760d18e334637"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Note_Types" sheetId="10" r:id="R426b83b4b82f4211"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Block_Catalog" sheetId="11" r:id="R17aafa5bf3c3489d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Slash_Commands" sheetId="12" r:id="Rc97ad68919d346ba"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Context_Menus" sheetId="13" r:id="Rdcc82968d9844b75"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Keyboard_Shortcuts" sheetId="14" r:id="Rd1380c62f3e343cd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Database_Views" sheetId="15" r:id="R177f2b00a6bd4004"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Code_Text_Mode" sheetId="16" r:id="R94824cb25bd7414f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Python_Notebook" sheetId="17" r:id="R5e2ff43f727d4c42"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Collaboration" sheetId="18" r:id="Rf3d39f3dab2a48df"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Offline_Desktop" sheetId="19" r:id="R2c0fc92908fc4202"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data_Model" sheetId="20" r:id="R9b5e4e0ad0fe472b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Storage_Interop" sheetId="21" r:id="R634b7a12d4cb46af"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Security" sheetId="22" r:id="R3cf08108beac44bd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="API_Contracts" sheetId="23" r:id="Rb77e8717c30f4a3f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="State_Machines" sheetId="24" r:id="R6384dacf5ca44043"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Error_Recovery" sheetId="25" r:id="Rc24eb2d343c748e7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cross_App_Relations" sheetId="26" r:id="R33a886b781d44863"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Performance" sheetId="27" r:id="Rc7625d77b4884c7b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Accessibility" sheetId="28" r:id="R10934dfa648e4dc8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test_Matrix" sheetId="29" r:id="R0f01b3df12eb488a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="30" r:id="R1bebb297e10f4e04"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open_Questions" sheetId="31" r:id="Re6bf4b8731a348d9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Change_Log" sheetId="32" r:id="R3b342b83d8fd437f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Implementation_Status" sheetId="33" r:id="Rfc1658362edf4f37"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="Rc2b911ba15c745e9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Product_Vision" sheetId="2" r:id="Rd3f1ae7ef5264ebe"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decisions" sheetId="3" r:id="R8bf017ed74254370"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Competitors" sheetId="4" r:id="Rb50bfef9343547c6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open_Source" sheetId="5" r:id="R68adbc73331a4306"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source_Index" sheetId="6" r:id="Rba8bbba86f8c4a25"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Information_Architecture" sheetId="7" r:id="R1f929817fbb540a9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI_Layout" sheetId="8" r:id="R6445769c9f734c43"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="User_Flows" sheetId="9" r:id="R02a083a27a5d4420"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Note_Types" sheetId="10" r:id="Rfd8cedf64a8e48e6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Block_Catalog" sheetId="11" r:id="R79fd95c6041b4b57"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Slash_Commands" sheetId="12" r:id="R2996a7d776c6484b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Context_Menus" sheetId="13" r:id="R46d93f9d0b4c4abb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Keyboard_Shortcuts" sheetId="14" r:id="Rad072819cc9f4923"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Database_Views" sheetId="15" r:id="R7eea6dae14c64bb4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Code_Text_Mode" sheetId="16" r:id="Rd7a9b6ac936840de"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Python_Notebook" sheetId="17" r:id="R1991e5ef00364cd4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Collaboration" sheetId="18" r:id="R60925a67e75d4366"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Offline_Desktop" sheetId="19" r:id="Rd9e92f0da2d84d06"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data_Model" sheetId="20" r:id="R1e48cb344a02436c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Storage_Interop" sheetId="21" r:id="Rc7f40022d9484d30"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Security" sheetId="22" r:id="R3fbb5db1e0b64bfc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="API_Contracts" sheetId="23" r:id="Re03e0b208ac54565"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="State_Machines" sheetId="24" r:id="R37a63ffe2ce04d9d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Error_Recovery" sheetId="25" r:id="R9d259b9c25804841"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cross_App_Relations" sheetId="26" r:id="R848c463f8edd4317"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Performance" sheetId="27" r:id="Rc4fbd00e273645a5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Accessibility" sheetId="28" r:id="Re9ac3be8970d4968"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test_Matrix" sheetId="29" r:id="R4595476645f243f4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="30" r:id="Rf2b00352a6444a48"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open_Questions" sheetId="31" r:id="R0b148ea84b0d4194"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Change_Log" sheetId="32" r:id="Rf8d0eb8994584e29"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Implementation_Status" sheetId="33" r:id="Rece12303d97041f1"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -928,7 +928,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfef1564d9f4245d6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5e8fd94d1b4c4506"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1271,7 +1271,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R990ab049d6544188"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R677e06de820c4236"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1674,7 +1674,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5a54982bbbc74a65"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rff1744859c204b54"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2057,7 +2057,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ref149f1b97bd4dda"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd7dafef5bd7844f8"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2470,7 +2470,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf61e39e7137a4a4c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3a16f41b8992401f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2968,7 +2968,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R122242ef433c4273"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra6ee1acd338b43a7"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3228,7 +3228,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9166417e58814b0a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R56b3c40776ad43d0"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3420,7 +3420,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0d9b0d2bc6464efd"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re5f5d79fbd5d4933"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3748,7 +3748,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R619e95466f2a4641"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra9f51f7c7fd44a31"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4008,7 +4008,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R20b23ecbd6994bef"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6792bf764a7c47d6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4200,7 +4200,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2c7efdec05d8443f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R22dafbc002a54112"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4333,7 +4333,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R147237106fd94220"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R48aab188ee4b465f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4712,7 +4712,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5ad8c28edff6457e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5af86769bcc549b6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4972,7 +4972,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4067c9604b224c3f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R800bc798181a45b7"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5317,7 +5317,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R038b016d24664535"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfa7ba289ea194f81"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5798,7 +5798,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0c6aaec2e6eb4285"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R76ac8ecf23d04ed2"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6109,7 +6109,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3368b4a6678046f4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdeefda00c49e42f4"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6420,7 +6420,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc6c91b393bd745a6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7e8547c1e5bc4bc3"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6748,7 +6748,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9f0e07ed2fc04bff"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R60a0184ea12c45af"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7008,7 +7008,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rae4dbc2c8bb44a21"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfc15335828ef4d57"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7169,7 +7169,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R353288deea6444db"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3a4b3572d4a94ebd"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7792,7 +7792,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ree7e125ab59f4687"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc78863ad0d9b41eb"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8137,7 +8137,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R194ed47eb9984e95"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9bcbd52d2a794463"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8278,7 +8278,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdf224bc5db034c70"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R45b6fa098e4344ba"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8487,7 +8487,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9c3ea7cad2664df5"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R19a9ef1098ad4d3c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8655,13 +8655,13 @@
         <x:v>0.7-path-portability-foundation</x:v>
       </x:c>
       <x:c r="C8" s="13" t="str">
-        <x:v>Agent/Setup 1.11.2 1차 구현·로컬 검증 완료 / 운영·실PC E2E 전</x:v>
+        <x:v>Agent/Setup 1.11.2 운영 배포·Linux 전체 검증 완료 / 새 Windows 실PC E2E 전</x:v>
       </x:c>
       <x:c r="D8" s="13" t="str">
         <x:v>NAS Drive 제어센터에 프로젝트 경로 확인을 추가하고 내부 안전 자동·외부 검토·미해결 3단계, 파일·줄별 선택, 적용하지 않고 열기, SHA-256 사전조건, 원자 저장과 즉시 undo를 구현했다.</x:v>
       </x:c>
       <x:c r="E8" s="13" t="str">
-        <x:v>VS Code·JetBrains·Python 공식 경로 모델 조사. projectPathPortability unit, Agent self-test, Setup compile/self-test, DPI UI render.</x:v>
+        <x:v>VS Code·JetBrains·Python 공식 경로 모델 조사. 로컬 18 test files, Agent/Setup self-test, DPI UI render. NAS Linux 47/47, PM2/service/HTTP, 배포 hash 일치.</x:v>
       </x:c>
       <x:c r="F8" s="13" t="str">
         <x:v>Codex</x:v>
@@ -8670,7 +8670,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re4d70209b7da47f1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6028377a29204d07"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8995,13 +8995,13 @@
         <x:v>Windows 프로젝트 경로 이동 보조</x:v>
       </x:c>
       <x:c r="C16" s="13" t="str">
-        <x:v>Agent/Setup 1.11.2 1차 구현·로컬 검증 완료 / 운영·실PC E2E 전</x:v>
+        <x:v>Agent/Setup 1.11.2 운영 배포·Linux 전체 검증 완료 / 새 Windows 실PC E2E 전</x:v>
       </x:c>
       <x:c r="D16" s="13" t="str">
         <x:v>프로젝트 선택, 절대경로 분석, 실제 suffix·외부 유일 매핑, 3단계 검토 UI, 선택 적용, hash precondition, atomic write, undo</x:v>
       </x:c>
       <x:c r="E16" s="13" t="str">
-        <x:v>unit·Agent self-test·Setup compile/self-test·DPI UI render</x:v>
+        <x:v>로컬 18 test files·Agent/Setup self-test·DPI UI render, NAS Linux 47/47·PM2/service·HTTP·hash 일치</x:v>
       </x:c>
       <x:c r="F16" s="13" t="str">
         <x:v>운영 배포, 새 설치본 실PC E2E, marker 기반 완전 hydrate 자동 알림, IDE portable variable 변환</x:v>
@@ -9216,7 +9216,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R29734a9096524ca3"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfddbf40542fb4f2e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9499,7 +9499,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6ae3eb8293044a3a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra41bcd932ac2461e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9895,7 +9895,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra4951993f72847d7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9f85bb257f304c5a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10138,7 +10138,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0230317f2c6f404f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc763df3725a14ff8"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10313,7 +10313,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2fe8c1ae556540d1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb72514ec4b9d4516"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10573,7 +10573,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R399c576afe7a4889"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra9a3883969e94953"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/programs/NAS_NOTE_STUDIO_SPEC.xlsx
+++ b/docs/programs/NAS_NOTE_STUDIO_SPEC.xlsx
@@ -2,39 +2,39 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="Rc2b911ba15c745e9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Product_Vision" sheetId="2" r:id="Rd3f1ae7ef5264ebe"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decisions" sheetId="3" r:id="R8bf017ed74254370"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Competitors" sheetId="4" r:id="Rb50bfef9343547c6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open_Source" sheetId="5" r:id="R68adbc73331a4306"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source_Index" sheetId="6" r:id="Rba8bbba86f8c4a25"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Information_Architecture" sheetId="7" r:id="R1f929817fbb540a9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI_Layout" sheetId="8" r:id="R6445769c9f734c43"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="User_Flows" sheetId="9" r:id="R02a083a27a5d4420"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Note_Types" sheetId="10" r:id="Rfd8cedf64a8e48e6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Block_Catalog" sheetId="11" r:id="R79fd95c6041b4b57"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Slash_Commands" sheetId="12" r:id="R2996a7d776c6484b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Context_Menus" sheetId="13" r:id="R46d93f9d0b4c4abb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Keyboard_Shortcuts" sheetId="14" r:id="Rad072819cc9f4923"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Database_Views" sheetId="15" r:id="R7eea6dae14c64bb4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Code_Text_Mode" sheetId="16" r:id="Rd7a9b6ac936840de"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Python_Notebook" sheetId="17" r:id="R1991e5ef00364cd4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Collaboration" sheetId="18" r:id="R60925a67e75d4366"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Offline_Desktop" sheetId="19" r:id="Rd9e92f0da2d84d06"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data_Model" sheetId="20" r:id="R1e48cb344a02436c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Storage_Interop" sheetId="21" r:id="Rc7f40022d9484d30"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Security" sheetId="22" r:id="R3fbb5db1e0b64bfc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="API_Contracts" sheetId="23" r:id="Re03e0b208ac54565"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="State_Machines" sheetId="24" r:id="R37a63ffe2ce04d9d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Error_Recovery" sheetId="25" r:id="R9d259b9c25804841"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cross_App_Relations" sheetId="26" r:id="R848c463f8edd4317"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Performance" sheetId="27" r:id="Rc4fbd00e273645a5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Accessibility" sheetId="28" r:id="Re9ac3be8970d4968"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test_Matrix" sheetId="29" r:id="R4595476645f243f4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="30" r:id="Rf2b00352a6444a48"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open_Questions" sheetId="31" r:id="R0b148ea84b0d4194"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Change_Log" sheetId="32" r:id="Rf8d0eb8994584e29"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Implementation_Status" sheetId="33" r:id="Rece12303d97041f1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="R2bd22090ac3145b1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Product_Vision" sheetId="2" r:id="R37bb31ce49034de4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decisions" sheetId="3" r:id="R16c73da0ac414d1a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Competitors" sheetId="4" r:id="R58f56a5b8d1d4179"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open_Source" sheetId="5" r:id="Rd971ebcb7e424ce1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source_Index" sheetId="6" r:id="R5ef2ae010df94bfd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Information_Architecture" sheetId="7" r:id="R732f4e7ba9554c9b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI_Layout" sheetId="8" r:id="Rce6afcd23b704d78"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="User_Flows" sheetId="9" r:id="R6e51efe959604ae4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Note_Types" sheetId="10" r:id="Rc61f6917f138494f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Block_Catalog" sheetId="11" r:id="Re57303230d314b8a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Slash_Commands" sheetId="12" r:id="Rf68efe1ffe414559"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Context_Menus" sheetId="13" r:id="R390fb7ab617e4543"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Keyboard_Shortcuts" sheetId="14" r:id="R8ff101cd5c814381"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Database_Views" sheetId="15" r:id="R7af04cf11b144359"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Code_Text_Mode" sheetId="16" r:id="R850c292acd024f38"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Python_Notebook" sheetId="17" r:id="R0a96f694bcac4045"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Collaboration" sheetId="18" r:id="R6b11d103ce884482"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Offline_Desktop" sheetId="19" r:id="R957b50444d25431f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data_Model" sheetId="20" r:id="R52f394ab7c9d408b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Storage_Interop" sheetId="21" r:id="Rd2fedf8f80db491e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Security" sheetId="22" r:id="R17183b32c48a410c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="API_Contracts" sheetId="23" r:id="R8f8bc2fab6ca49ba"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="State_Machines" sheetId="24" r:id="R59452f3320c5495c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Error_Recovery" sheetId="25" r:id="R397b866df1f5405a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cross_App_Relations" sheetId="26" r:id="Rbf2e104b76d8441d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Performance" sheetId="27" r:id="Rd2e193edf8454ca0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Accessibility" sheetId="28" r:id="R9f8f164a51ea45f5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test_Matrix" sheetId="29" r:id="R5d14ba58a19740f2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="30" r:id="R496e4fd0d8ba44e4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open_Questions" sheetId="31" r:id="R38e5f447af634d6d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Change_Log" sheetId="32" r:id="Rd9bfb4fa5da3473a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Implementation_Status" sheetId="33" r:id="Rf97c2c434354489f"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -928,7 +928,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5e8fd94d1b4c4506"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd7f8fb359f5d49a3"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1271,7 +1271,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R677e06de820c4236"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R17d35201437e4b9e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1674,7 +1674,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rff1744859c204b54"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcb0845b4c1b94bc2"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2057,7 +2057,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd7dafef5bd7844f8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R348772952f3a4a2d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2470,7 +2470,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3a16f41b8992401f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1ae5c9602e6b437f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2965,10 +2965,112 @@
         <x:v>PDF 문제와 같은 회귀 방지</x:v>
       </x:c>
     </x:row>
+    <x:row r="29">
+      <x:c r="A29" s="13" t="str">
+        <x:v>Windows 경로 검토</x:v>
+      </x:c>
+      <x:c r="B29" s="13" t="str">
+        <x:v>Ctrl+Enter</x:v>
+      </x:c>
+      <x:c r="C29" s="13" t="str">
+        <x:v>선택한 경로 적용하고 프로젝트 열기</x:v>
+      </x:c>
+      <x:c r="D29" s="13" t="str">
+        <x:v>체크 0개면 변경 없이 열기. 확인 필요 항목 포함 시 재확인.</x:v>
+      </x:c>
+      <x:c r="E29" s="13" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30">
+      <x:c r="A30" s="13" t="str">
+        <x:v>Windows 경로 검토</x:v>
+      </x:c>
+      <x:c r="B30" s="13" t="str">
+        <x:v>Ctrl+Z</x:v>
+      </x:c>
+      <x:c r="C30" s="13" t="str">
+        <x:v>방금 적용한 transaction 전체 되돌리기</x:v>
+      </x:c>
+      <x:c r="D30" s="13" t="str">
+        <x:v>적용 뒤 파일이 하나라도 바뀌면 전체 undo 중단.</x:v>
+      </x:c>
+      <x:c r="E30" s="13" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31">
+      <x:c r="A31" s="13" t="str">
+        <x:v>Windows 경로 검토</x:v>
+      </x:c>
+      <x:c r="B31" s="13" t="str">
+        <x:v>Ctrl+A / Ctrl+Shift+A</x:v>
+      </x:c>
+      <x:c r="C31" s="13" t="str">
+        <x:v>변경 가능한 항목 전체 선택 / 전체 선택 해제</x:v>
+      </x:c>
+      <x:c r="D31" s="13" t="str">
+        <x:v>미해결 항목은 선택되지 않음.</x:v>
+      </x:c>
+      <x:c r="E31" s="13" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32">
+      <x:c r="A32" s="13" t="str">
+        <x:v>Windows 경로 검토</x:v>
+      </x:c>
+      <x:c r="B32" s="13" t="str">
+        <x:v>Space</x:v>
+      </x:c>
+      <x:c r="C32" s="13" t="str">
+        <x:v>선택한 행의 체크 상태 전환</x:v>
+      </x:c>
+      <x:c r="D32" s="13" t="str">
+        <x:v>미해결 항목은 체크 차단.</x:v>
+      </x:c>
+      <x:c r="E32" s="13" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33">
+      <x:c r="A33" s="13" t="str">
+        <x:v>Windows 경로 검토</x:v>
+      </x:c>
+      <x:c r="B33" s="13" t="str">
+        <x:v>F5</x:v>
+      </x:c>
+      <x:c r="C33" s="13" t="str">
+        <x:v>현재 디스크·placeholder 상태로 다시 분석</x:v>
+      </x:c>
+      <x:c r="D33" s="13" t="str">
+        <x:v>적용 transaction이 열린 동안은 차단.</x:v>
+      </x:c>
+      <x:c r="E33" s="13" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34">
+      <x:c r="A34" s="13" t="str">
+        <x:v>Windows 경로 검토</x:v>
+      </x:c>
+      <x:c r="B34" s="13" t="str">
+        <x:v>F1 / Esc</x:v>
+      </x:c>
+      <x:c r="C34" s="13" t="str">
+        <x:v>단축키 도움말 / 창 닫기</x:v>
+      </x:c>
+      <x:c r="D34" s="13" t="str">
+        <x:v>Esc는 파일을 변경하지 않음.</x:v>
+      </x:c>
+      <x:c r="E34" s="13" t="str">
+        <x:v>P2</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra6ee1acd338b43a7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7c7c565a3dbc451a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3228,7 +3330,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R56b3c40776ad43d0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfc2cdf4978ef488a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3420,7 +3522,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re5f5d79fbd5d4933"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra1ca32c0cf1b4abd"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3748,7 +3850,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra9f51f7c7fd44a31"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7317f52073df4ec9"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4008,7 +4110,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6792bf764a7c47d6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R14638e6bc7164acf"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4200,7 +4302,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R22dafbc002a54112"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3ddc657c92b94235"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4333,7 +4435,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R48aab188ee4b465f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcc02d5a59988477c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4712,7 +4814,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5af86769bcc549b6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R04b11e056f134169"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4957,22 +5059,22 @@
         <x:v>로컬 프로젝트 고정 경로</x:v>
       </x:c>
       <x:c r="B14" s="13" t="str">
-        <x:v>프로젝트 root 아래 실제 동일 suffix는 이 PC 절대 경로로 안전 제안. 외부 sibling/ancestor는 연결된 NAS Drive에서 유일한 경우만 검토 제안.</x:v>
+        <x:v>프로젝트 root 아래 동일 suffix는 IDE별 안전 adapter 또는 이 PC 실제 경로로 제안한다. 외부 sibling/ancestor는 연결 NAS Drive의 유일 대상 또는 사용자가 고른 대상만 검토 후보가 된다.</x:v>
       </x:c>
       <x:c r="C14" s="13" t="str">
-        <x:v>제어센터에서 프로젝트 선택 → 자동 적용/확인 필요/변경 안 함 요약 → 파일·줄별 체크 → 적용하고 열기 또는 그대로 열기 → 즉시 undo</x:v>
+        <x:v>제어센터에서 프로젝트 선택 → placeholder 제외 분석 → 안전/확인/미해결 표 → 필요 시 위치 직접 선택 → 전체 preflight → 적용/열기 → 즉시 undo 또는 F5 재분석</x:v>
       </x:c>
       <x:c r="D14" s="13" t="str">
-        <x:v>부분 hydrate 자동 실행, PC 전체 검색, 모호한 대상 자동 선택, server canonical 변경, secret 파일 preview 금지</x:v>
+        <x:v>부분 hydrate 자동 실행, PC 전체 검색, 모호한 대상 자동 선택, server canonical 변경, secret/online-only content read, 지원하지 않는 IDE 필드의 무차별 variable 치환 금지</x:v>
       </x:c>
       <x:c r="E14" s="13" t="str">
-        <x:v>WINDOWS NAS DRIVE, M2 local projection</x:v>
+        <x:v>WINDOWS NAS DRIVE, M2 local projection, VS Code, JetBrains</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R800bc798181a45b7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3e59951a165e4909"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5305,10 +5407,10 @@
         <x:v>고정 경로 오인·비밀 노출·로컬 파일 덮어쓰기</x:v>
       </x:c>
       <x:c r="C19" s="13" t="str">
-        <x:v>연결 NAS Drive와 선택 project 경계, real target 존재·유일성, secret/vendor/build/symlink 제외, SHA-256 precondition, atomic replace, 외부 상태 backup/undo.</x:v>
+        <x:v>현재 연결 NAS Drive realpath와 선택 project 경계, managed plan/backup symlink 차단, placeholder metadata fail-closed, secret/vendor/build 제외, 전체 SHA-256+offset preflight, target type 재검증, atomic replace와 전 파일 rollback, strict UTF-8+BOM 보존, 절대경로 비공개 보고서.</x:v>
       </x:c>
       <x:c r="D19" s="13" t="str">
-        <x:v>내부 suffix·외부 유일·외부 중복·미존재·URL·.env·변경 후 apply·apply 후 수정된 undo 회귀</x:v>
+        <x:v>URL 오인·공백/JSON escape·BOM·UTF-16·online-only skip·대상 변조·파일 2개 중 뒤 충돌·undo 뒤 충돌·수동 매핑 drive 밖·IDE adapter·보고서 노출 회귀</x:v>
       </x:c>
       <x:c r="E19" s="13" t="str">
         <x:v>P0</x:v>
@@ -5317,7 +5419,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfa7ba289ea194f81"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9929fb1e1b194d01"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5798,7 +5900,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R76ac8ecf23d04ed2"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R35fcd15334e8479e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6109,7 +6211,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdeefda00c49e42f4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9b11a1baf856460b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6420,7 +6522,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7e8547c1e5bc4bc3"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R070c4ea048c442db"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6748,7 +6850,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R60a0184ea12c45af"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9ec065deb8c447e8"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7008,7 +7110,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfc15335828ef4d57"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2a698a926a624e40"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7169,7 +7271,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3a4b3572d4a94ebd"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R612813e125074eeb"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7777,22 +7879,22 @@
         <x:v>프로젝트 경로 이동 보조</x:v>
       </x:c>
       <x:c r="C30" s="13" t="str">
-        <x:v>내부 고정 경로, 외부 sibling/ancestor 유일·중복, URL, .env, symlink, preview 뒤 동시 수정, apply 뒤 동시 수정</x:v>
+        <x:v>내부·외부·수동 경로, VS Code/JetBrains, 공백/JSON escape/URL, UTF-8 BOM/UTF-16, placeholder, plan target 변조, 2파일 apply/undo 충돌, report 노출, 단축키·DPI UI</x:v>
       </x:c>
       <x:c r="D30" s="13" t="str">
-        <x:v>내부 실제 suffix만 기본 선택, 외부는 수동, 모호/비밀/경계 밖 0건 변경, hash 불일치 중단, apply/undo byte 복원</x:v>
+        <x:v>지원 IDE는 portable 표현, 일반 소스는 확인된 local path, placeholder/비밀/모호/경계 밖 0건 변경, 모든 충돌에서 부분 적용·부분 undo 0건, BOM byte 보존, 공개 보고서에 절대경로 없음</x:v>
       </x:c>
       <x:c r="E30" s="13" t="str">
-        <x:v>unit+Windows UI+E2E</x:v>
+        <x:v>unit+Agent/Setup self-test+DPI render+Windows 실PC E2E</x:v>
       </x:c>
       <x:c r="F30" s="13" t="str">
-        <x:v>M2 local projection 선행</x:v>
+        <x:v>자동 완전 hydrate marker는 별도 보류</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc78863ad0d9b41eb"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R52ff2a5d20234923"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8137,7 +8239,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9bcbd52d2a794463"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R129579bca41f46d1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8278,7 +8380,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R45b6fa098e4344ba"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbfa9aaa302454771"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8487,7 +8589,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R19a9ef1098ad4d3c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc5c91095a432483f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8667,10 +8769,30 @@
         <x:v>Codex</x:v>
       </x:c>
     </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="13" t="str">
+        <x:v>2026-09-06</x:v>
+      </x:c>
+      <x:c r="B9" s="13" t="str">
+        <x:v>0.8-path-portability-transaction-shortcuts</x:v>
+      </x:c>
+      <x:c r="C9" s="13" t="str">
+        <x:v>Agent/Setup 1.11.3 2차 구현·로컬 회귀 완료 / 운영·새 Windows E2E 전</x:v>
+      </x:c>
+      <x:c r="D9" s="13" t="str">
+        <x:v>부분 적용/undo 방지, placeholder hydrate 방지, IDE portable adapter, 수동 매핑, 변경 보고서, 재분석/상태 통계와 키보드 단축키를 추가했다.</x:v>
+      </x:c>
+      <x:c r="E9" s="13" t="str">
+        <x:v>backend 18 test files, Agent/Setup self-test, Setup compile, 200% DPI UI render. 공식 CFAPI/VS Code/JetBrains/Python 문서 근거.</x:v>
+      </x:c>
+      <x:c r="F9" s="13" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6028377a29204d07"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2408152beac14460"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8995,16 +9117,16 @@
         <x:v>Windows 프로젝트 경로 이동 보조</x:v>
       </x:c>
       <x:c r="C16" s="13" t="str">
-        <x:v>Agent/Setup 1.11.2 운영 배포·Linux 전체 검증 완료 / 새 Windows 실PC E2E 전</x:v>
+        <x:v>Agent/Setup 1.11.3 2차 안전성·IDE adapter·UI/단축키 구현 / 로컬 전체 회귀 완료·운영/새 Windows E2E 전</x:v>
       </x:c>
       <x:c r="D16" s="13" t="str">
-        <x:v>프로젝트 선택, 절대경로 분석, 실제 suffix·외부 유일 매핑, 3단계 검토 UI, 선택 적용, hash precondition, atomic write, undo</x:v>
+        <x:v>전체 preflight/rollback apply·undo, target realpath 재검증, placeholder fail-closed, UTF-8 BOM, VS Code/JetBrains portable adapter, 직접 매핑, 변경 보고서, 재분석과 8개 shortcut</x:v>
       </x:c>
       <x:c r="E16" s="13" t="str">
-        <x:v>로컬 18 test files·Agent/Setup self-test·DPI UI render, NAS Linux 47/47·PM2/service·HTTP·hash 일치</x:v>
+        <x:v>신규 transaction/경계/encoding/IDE unit, backend 18 test files, Agent/Setup self-test, 200% DPI UI render</x:v>
       </x:c>
       <x:c r="F16" s="13" t="str">
-        <x:v>운영 배포, 새 설치본 실PC E2E, marker 기반 완전 hydrate 자동 알림, IDE portable variable 변환</x:v>
+        <x:v>운영 배포·hash/서비스/HTTP 확인, 새 Windows CFAPI/선택/keyboard E2E, 완전 hydration marker 자동 알림</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -9216,7 +9338,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfddbf40542fb4f2e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1c8843c50ffb4bba"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9499,7 +9621,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra41bcd932ac2461e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3e0c1d394898466f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9892,10 +10014,78 @@
         <x:v>2026-09-06</x:v>
       </x:c>
     </x:row>
+    <x:row r="23">
+      <x:c r="A23" s="13" t="str">
+        <x:v>SRC-PATH-CFAPI</x:v>
+      </x:c>
+      <x:c r="B23" s="13" t="str">
+        <x:v>Microsoft CFAPI placeholder state</x:v>
+      </x:c>
+      <x:c r="C23" s="13" t="str">
+        <x:v>https://learn.microsoft.com/en-us/windows/win32/api/cfapi/nf-cfapi-cfgetplaceholderstatefromattributetag</x:v>
+      </x:c>
+      <x:c r="D23" s="13" t="str">
+        <x:v>온라인 전용/부분 저장 상태의 content-read 회피 기준</x:v>
+      </x:c>
+      <x:c r="E23" s="13" t="str">
+        <x:v>2026-09-06</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24">
+      <x:c r="A24" s="13" t="str">
+        <x:v>SRC-PATH-VSCODE</x:v>
+      </x:c>
+      <x:c r="B24" s="13" t="str">
+        <x:v>VS Code Variables / Multi-root / Tasks</x:v>
+      </x:c>
+      <x:c r="C24" s="13" t="str">
+        <x:v>https://code.visualstudio.com/docs/reference/variables-reference</x:v>
+      </x:c>
+      <x:c r="D24" s="13" t="str">
+        <x:v>${workspaceFolder}와 지원 필드 제한 기준</x:v>
+      </x:c>
+      <x:c r="E24" s="13" t="str">
+        <x:v>2026-09-06</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25">
+      <x:c r="A25" s="13" t="str">
+        <x:v>SRC-PATH-JETBRAINS</x:v>
+      </x:c>
+      <x:c r="B25" s="13" t="str">
+        <x:v>JetBrains Absolute path variables / path mappings</x:v>
+      </x:c>
+      <x:c r="C25" s="13" t="str">
+        <x:v>https://www.jetbrains.com/help/idea/absolute-path-variables.html</x:v>
+      </x:c>
+      <x:c r="D25" s="13" t="str">
+        <x:v>$PROJECT_DIR$와 local/remote mapping 기준</x:v>
+      </x:c>
+      <x:c r="E25" s="13" t="str">
+        <x:v>2026-09-06</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26">
+      <x:c r="A26" s="13" t="str">
+        <x:v>SRC-PATH-PYTHON</x:v>
+      </x:c>
+      <x:c r="B26" s="13" t="str">
+        <x:v>Python pathlib</x:v>
+      </x:c>
+      <x:c r="C26" s="13" t="str">
+        <x:v>https://docs.python.org/3.13/library/pathlib.html</x:v>
+      </x:c>
+      <x:c r="D26" s="13" t="str">
+        <x:v>resolve 후 relative_to 경계 기준</x:v>
+      </x:c>
+      <x:c r="E26" s="13" t="str">
+        <x:v>2026-09-06</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9f85bb257f304c5a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcf96ac2ebbfb4997"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10138,7 +10328,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc763df3725a14ff8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Reb0d5d181d1d436c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10313,7 +10503,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb72514ec4b9d4516"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7163f24135d549e9"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10573,7 +10763,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra9a3883969e94953"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra62d6c2b44f446be"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/programs/NAS_NOTE_STUDIO_SPEC.xlsx
+++ b/docs/programs/NAS_NOTE_STUDIO_SPEC.xlsx
@@ -2,39 +2,39 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="R2bd22090ac3145b1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Product_Vision" sheetId="2" r:id="R37bb31ce49034de4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decisions" sheetId="3" r:id="R16c73da0ac414d1a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Competitors" sheetId="4" r:id="R58f56a5b8d1d4179"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open_Source" sheetId="5" r:id="Rd971ebcb7e424ce1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source_Index" sheetId="6" r:id="R5ef2ae010df94bfd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Information_Architecture" sheetId="7" r:id="R732f4e7ba9554c9b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI_Layout" sheetId="8" r:id="Rce6afcd23b704d78"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="User_Flows" sheetId="9" r:id="R6e51efe959604ae4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Note_Types" sheetId="10" r:id="Rc61f6917f138494f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Block_Catalog" sheetId="11" r:id="Re57303230d314b8a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Slash_Commands" sheetId="12" r:id="Rf68efe1ffe414559"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Context_Menus" sheetId="13" r:id="R390fb7ab617e4543"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Keyboard_Shortcuts" sheetId="14" r:id="R8ff101cd5c814381"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Database_Views" sheetId="15" r:id="R7af04cf11b144359"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Code_Text_Mode" sheetId="16" r:id="R850c292acd024f38"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Python_Notebook" sheetId="17" r:id="R0a96f694bcac4045"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Collaboration" sheetId="18" r:id="R6b11d103ce884482"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Offline_Desktop" sheetId="19" r:id="R957b50444d25431f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data_Model" sheetId="20" r:id="R52f394ab7c9d408b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Storage_Interop" sheetId="21" r:id="Rd2fedf8f80db491e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Security" sheetId="22" r:id="R17183b32c48a410c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="API_Contracts" sheetId="23" r:id="R8f8bc2fab6ca49ba"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="State_Machines" sheetId="24" r:id="R59452f3320c5495c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Error_Recovery" sheetId="25" r:id="R397b866df1f5405a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cross_App_Relations" sheetId="26" r:id="Rbf2e104b76d8441d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Performance" sheetId="27" r:id="Rd2e193edf8454ca0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Accessibility" sheetId="28" r:id="R9f8f164a51ea45f5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test_Matrix" sheetId="29" r:id="R5d14ba58a19740f2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="30" r:id="R496e4fd0d8ba44e4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open_Questions" sheetId="31" r:id="R38e5f447af634d6d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Change_Log" sheetId="32" r:id="Rd9bfb4fa5da3473a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Implementation_Status" sheetId="33" r:id="Rf97c2c434354489f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="R0250f39a37ed41ad"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Product_Vision" sheetId="2" r:id="R52e9bbd1f11f4394"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decisions" sheetId="3" r:id="Rba25c9aabbf74476"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Competitors" sheetId="4" r:id="R31a6f62deb3b48d6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open_Source" sheetId="5" r:id="Rff291bb6c4e944a8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source_Index" sheetId="6" r:id="R9163775af92a464e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Information_Architecture" sheetId="7" r:id="Ra2b0b7c7d9d44bbd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI_Layout" sheetId="8" r:id="R7f09d140e5f54471"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="User_Flows" sheetId="9" r:id="R0017fce7578e4778"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Note_Types" sheetId="10" r:id="Rcacbe198e7bc4090"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Block_Catalog" sheetId="11" r:id="Rad065f3b62394922"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Slash_Commands" sheetId="12" r:id="Rc92ae04ef70b4734"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Context_Menus" sheetId="13" r:id="Rbc85424f9d924254"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Keyboard_Shortcuts" sheetId="14" r:id="R1cd915486f8a4946"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Database_Views" sheetId="15" r:id="Rcd416f10109740ce"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Code_Text_Mode" sheetId="16" r:id="R5854e6eb22c14538"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Python_Notebook" sheetId="17" r:id="Re8eaea81301b4367"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Collaboration" sheetId="18" r:id="R199f655768c54255"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Offline_Desktop" sheetId="19" r:id="R03fbedd9d71741ec"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data_Model" sheetId="20" r:id="Rbc6e41c33de847aa"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Storage_Interop" sheetId="21" r:id="Rcfc04115d3ac4fa2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Security" sheetId="22" r:id="Rc532547a64e845bb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="API_Contracts" sheetId="23" r:id="R9af9c0c69d484196"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="State_Machines" sheetId="24" r:id="R3ccfa4c2de834fa6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Error_Recovery" sheetId="25" r:id="Ra59ffbf6bc114578"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cross_App_Relations" sheetId="26" r:id="Rbe7f231e4a2f47c0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Performance" sheetId="27" r:id="Rc3ff6b58f11a4039"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Accessibility" sheetId="28" r:id="R3316a9ce0cfc4fef"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test_Matrix" sheetId="29" r:id="R3bada869a26c4b8d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="30" r:id="Rc5c3583a631b4dff"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open_Questions" sheetId="31" r:id="Reea286ca9b444bc8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Change_Log" sheetId="32" r:id="R046c582d94c74528"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Implementation_Status" sheetId="33" r:id="R1b6ce69036f248c0"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -928,7 +928,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd7f8fb359f5d49a3"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R47adfa7f26514be9"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1271,7 +1271,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R17d35201437e4b9e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rca8c5691911748ca"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1674,7 +1674,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcb0845b4c1b94bc2"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R794f424a4bfa4d94"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2057,7 +2057,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R348772952f3a4a2d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5819209767504a2a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2470,7 +2470,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1ae5c9602e6b437f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9c987c2c56e247ed"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3070,7 +3070,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7c7c565a3dbc451a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf12bf283eb8d4f96"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3330,7 +3330,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfc2cdf4978ef488a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7bff9eb04a4a4fbe"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3522,7 +3522,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra1ca32c0cf1b4abd"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra9b53656e44045a6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3850,7 +3850,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7317f52073df4ec9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R891c09c20fc34787"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4110,7 +4110,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R14638e6bc7164acf"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfb57efdf26a04008"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4302,7 +4302,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3ddc657c92b94235"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcfa6bd4e303e4235"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4435,7 +4435,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcc02d5a59988477c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc9bcb939bec1429d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4814,7 +4814,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R04b11e056f134169"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Recb79e5b7df84d2b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5074,7 +5074,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3e59951a165e4909"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R40fc7b1250a34323"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5419,7 +5419,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9929fb1e1b194d01"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9351c88702b14d64"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5900,7 +5900,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R35fcd15334e8479e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8fdd2881881f4726"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6211,7 +6211,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9b11a1baf856460b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7640a4bb8ec74750"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6522,7 +6522,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R070c4ea048c442db"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4170574e999f46dd"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6850,7 +6850,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9ec065deb8c447e8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R73cf635b185746e5"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7110,7 +7110,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2a698a926a624e40"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra66b482566564b04"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7271,7 +7271,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R612813e125074eeb"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R70fb2197d2de4b11"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7894,7 +7894,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R52ff2a5d20234923"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5859c2abe7fc415c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8239,7 +8239,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R129579bca41f46d1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4aa04c1ac3aa4a16"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8380,7 +8380,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbfa9aaa302454771"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra08343e9180a442a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8589,7 +8589,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc5c91095a432483f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9f380bfcb20c4fc2"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8777,13 +8777,13 @@
         <x:v>0.8-path-portability-transaction-shortcuts</x:v>
       </x:c>
       <x:c r="C9" s="13" t="str">
-        <x:v>Agent/Setup 1.11.3 2차 구현·로컬 회귀 완료 / 운영·새 Windows E2E 전</x:v>
+        <x:v>Agent/Setup 1.11.3 운영 배포·NAS 전체 회귀 완료 / 새 Windows E2E 전</x:v>
       </x:c>
       <x:c r="D9" s="13" t="str">
         <x:v>부분 적용/undo 방지, placeholder hydrate 방지, IDE portable adapter, 수동 매핑, 변경 보고서, 재분석/상태 통계와 키보드 단축키를 추가했다.</x:v>
       </x:c>
       <x:c r="E9" s="13" t="str">
-        <x:v>backend 18 test files, Agent/Setup self-test, Setup compile, 200% DPI UI render. 공식 CFAPI/VS Code/JetBrains/Python 문서 근거.</x:v>
+        <x:v>로컬 18 test files, Agent/Setup self-test, DPI UI render. NAS Linux 47/47, PM2/service/HTTP, 배포 hash 일치. 공식 CFAPI/VS Code/JetBrains/Python 문서 근거.</x:v>
       </x:c>
       <x:c r="F9" s="13" t="str">
         <x:v>Codex</x:v>
@@ -8792,7 +8792,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2408152beac14460"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2e46406e16bc46ff"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9117,16 +9117,16 @@
         <x:v>Windows 프로젝트 경로 이동 보조</x:v>
       </x:c>
       <x:c r="C16" s="13" t="str">
-        <x:v>Agent/Setup 1.11.3 2차 안전성·IDE adapter·UI/단축키 구현 / 로컬 전체 회귀 완료·운영/새 Windows E2E 전</x:v>
+        <x:v>Agent/Setup 1.11.3 2차 운영 배포·NAS 전체 회귀 완료 / 새 Windows E2E 전</x:v>
       </x:c>
       <x:c r="D16" s="13" t="str">
         <x:v>전체 preflight/rollback apply·undo, target realpath 재검증, placeholder fail-closed, UTF-8 BOM, VS Code/JetBrains portable adapter, 직접 매핑, 변경 보고서, 재분석과 8개 shortcut</x:v>
       </x:c>
       <x:c r="E16" s="13" t="str">
-        <x:v>신규 transaction/경계/encoding/IDE unit, backend 18 test files, Agent/Setup self-test, 200% DPI UI render</x:v>
+        <x:v>로컬 18 test files·Agent/Setup self-test·DPI render, NAS Linux 47/47·PM2/service·HTTP·hash 일치</x:v>
       </x:c>
       <x:c r="F16" s="13" t="str">
-        <x:v>운영 배포·hash/서비스/HTTP 확인, 새 Windows CFAPI/선택/keyboard E2E, 완전 hydration marker 자동 알림</x:v>
+        <x:v>새 Windows CFAPI/선택/keyboard E2E, 완전 hydration marker 자동 알림</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -9338,7 +9338,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1c8843c50ffb4bba"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ref7ad1693c344ad4"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9621,7 +9621,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3e0c1d394898466f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc2da1db901964e77"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10085,7 +10085,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcf96ac2ebbfb4997"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rad0112d0030a4f00"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10328,7 +10328,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Reb0d5d181d1d436c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4666a13bce7f40b0"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10503,7 +10503,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7163f24135d549e9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R78a6074706ca424a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10763,7 +10763,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra62d6c2b44f446be"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R878ac4d909ba4c08"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/programs/NAS_NOTE_STUDIO_SPEC.xlsx
+++ b/docs/programs/NAS_NOTE_STUDIO_SPEC.xlsx
@@ -2,39 +2,39 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="R0250f39a37ed41ad"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Product_Vision" sheetId="2" r:id="R52e9bbd1f11f4394"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decisions" sheetId="3" r:id="Rba25c9aabbf74476"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Competitors" sheetId="4" r:id="R31a6f62deb3b48d6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open_Source" sheetId="5" r:id="Rff291bb6c4e944a8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source_Index" sheetId="6" r:id="R9163775af92a464e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Information_Architecture" sheetId="7" r:id="Ra2b0b7c7d9d44bbd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI_Layout" sheetId="8" r:id="R7f09d140e5f54471"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="User_Flows" sheetId="9" r:id="R0017fce7578e4778"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Note_Types" sheetId="10" r:id="Rcacbe198e7bc4090"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Block_Catalog" sheetId="11" r:id="Rad065f3b62394922"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Slash_Commands" sheetId="12" r:id="Rc92ae04ef70b4734"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Context_Menus" sheetId="13" r:id="Rbc85424f9d924254"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Keyboard_Shortcuts" sheetId="14" r:id="R1cd915486f8a4946"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Database_Views" sheetId="15" r:id="Rcd416f10109740ce"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Code_Text_Mode" sheetId="16" r:id="R5854e6eb22c14538"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Python_Notebook" sheetId="17" r:id="Re8eaea81301b4367"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Collaboration" sheetId="18" r:id="R199f655768c54255"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Offline_Desktop" sheetId="19" r:id="R03fbedd9d71741ec"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data_Model" sheetId="20" r:id="Rbc6e41c33de847aa"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Storage_Interop" sheetId="21" r:id="Rcfc04115d3ac4fa2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Security" sheetId="22" r:id="Rc532547a64e845bb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="API_Contracts" sheetId="23" r:id="R9af9c0c69d484196"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="State_Machines" sheetId="24" r:id="R3ccfa4c2de834fa6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Error_Recovery" sheetId="25" r:id="Ra59ffbf6bc114578"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cross_App_Relations" sheetId="26" r:id="Rbe7f231e4a2f47c0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Performance" sheetId="27" r:id="Rc3ff6b58f11a4039"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Accessibility" sheetId="28" r:id="R3316a9ce0cfc4fef"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test_Matrix" sheetId="29" r:id="R3bada869a26c4b8d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="30" r:id="Rc5c3583a631b4dff"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open_Questions" sheetId="31" r:id="Reea286ca9b444bc8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Change_Log" sheetId="32" r:id="R046c582d94c74528"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Implementation_Status" sheetId="33" r:id="R1b6ce69036f248c0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="R23eef9105c484b8a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Product_Vision" sheetId="2" r:id="R50778d7dc93749dd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decisions" sheetId="3" r:id="R876b04ea5c604451"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Competitors" sheetId="4" r:id="Rb2c342e8bd414843"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open_Source" sheetId="5" r:id="Rd848ca236a4644e2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source_Index" sheetId="6" r:id="Rebd558751cb14880"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Information_Architecture" sheetId="7" r:id="Re986eea2a04f4b65"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI_Layout" sheetId="8" r:id="R18f3633983ba4820"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="User_Flows" sheetId="9" r:id="Rf20ded511de04936"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Note_Types" sheetId="10" r:id="R21943a8c407849df"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Block_Catalog" sheetId="11" r:id="R7fff2c80877641a2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Slash_Commands" sheetId="12" r:id="R2803cb16adca4cc1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Context_Menus" sheetId="13" r:id="R55ab06f40c444d4d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Keyboard_Shortcuts" sheetId="14" r:id="Rbbb7a7de11b54b2d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Database_Views" sheetId="15" r:id="Rafa55940fd2f4047"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Code_Text_Mode" sheetId="16" r:id="R13a8b60902674136"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Python_Notebook" sheetId="17" r:id="R3a18638c7a604237"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Collaboration" sheetId="18" r:id="R1b566ddcb0104f8e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Offline_Desktop" sheetId="19" r:id="Rc5dd9a7b8d0847c1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data_Model" sheetId="20" r:id="R1bf5cdac0f73487d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Storage_Interop" sheetId="21" r:id="R150d2bf710044d4f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Security" sheetId="22" r:id="R70d41560c3184783"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="API_Contracts" sheetId="23" r:id="Rb0b811ab529f485c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="State_Machines" sheetId="24" r:id="Rcc485df1d50c4300"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Error_Recovery" sheetId="25" r:id="R6a1f438105584760"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cross_App_Relations" sheetId="26" r:id="R699cbd8120b44002"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Performance" sheetId="27" r:id="Ree217d827ebb4631"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Accessibility" sheetId="28" r:id="Rc6f58fc47a6247dd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test_Matrix" sheetId="29" r:id="R7c3d9fd7543e4567"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="30" r:id="R1fe55fef5f684dcd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open_Questions" sheetId="31" r:id="Re0366270e3c240e4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Change_Log" sheetId="32" r:id="R892649e312db4f03"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Implementation_Status" sheetId="33" r:id="R10c1365f61d34875"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -928,7 +928,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R47adfa7f26514be9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R181811c2da994cfc"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1271,7 +1271,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rca8c5691911748ca"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R38ed47eed02d4820"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1674,7 +1674,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R794f424a4bfa4d94"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R36f86a5c41b04b5c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2054,10 +2054,150 @@
         <x:v>M1.5</x:v>
       </x:c>
     </x:row>
+    <x:row r="19">
+      <x:c r="A19" s="13" t="str">
+        <x:v>/ (trigger)</x:v>
+      </x:c>
+      <x:c r="B19" s="13" t="str">
+        <x:v>명령 command 삽입</x:v>
+      </x:c>
+      <x:c r="C19" s="13" t="str">
+        <x:v>rich block</x:v>
+      </x:c>
+      <x:c r="D19" s="13" t="str">
+        <x:v>현재 caret 아래에 붙는 비모달 suggestion dropdown을 열고 / 뒤 query로 즉시 필터링</x:v>
+      </x:c>
+      <x:c r="E19" s="13" t="str">
+        <x:v>editor focus 유지, IME 조합 중 열지 않음, URL·경로 중간 slash 제외</x:v>
+      </x:c>
+      <x:c r="F19" s="13" t="str">
+        <x:v>M1-D 개선</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20" s="13" t="str">
+        <x:v>[메뉴 탐색]</x:v>
+      </x:c>
+      <x:c r="B20" s="13" t="str">
+        <x:v>위 아래 처음 끝 선택</x:v>
+      </x:c>
+      <x:c r="C20" s="13" t="str">
+        <x:v>rich block</x:v>
+      </x:c>
+      <x:c r="D20" s="13" t="str">
+        <x:v>Up/Down·Home/End로 active item 이동, Enter 또는 Tab으로 같은 registry command 실행</x:v>
+      </x:c>
+      <x:c r="E20" s="13" t="str">
+        <x:v>Esc는 변경 없이 닫고 본문 selection 유지</x:v>
+      </x:c>
+      <x:c r="F20" s="13" t="str">
+        <x:v>M1-D 개선</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21">
+      <x:c r="A21" s="13" t="str">
+        <x:v>[그룹·정렬]</x:v>
+      </x:c>
+      <x:c r="B21" s="13" t="str">
+        <x:v>최근 기본 제목 목록 미디어 문서</x:v>
+      </x:c>
+      <x:c r="C21" s="13" t="str">
+        <x:v>rich block</x:v>
+      </x:c>
+      <x:c r="D21" s="13" t="str">
+        <x:v>최근 사용→기본 블록→제목→목록→미디어/파일→페이지/문서→고급 순으로 그룹 표시</x:v>
+      </x:c>
+      <x:c r="E21" s="13" t="str">
+        <x:v>권한·노트 유형·offline 상태별로 숨김 또는 이유가 있는 disabled</x:v>
+      </x:c>
+      <x:c r="F21" s="13" t="str">
+        <x:v>M1-D 개선</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22">
+      <x:c r="A22" s="13" t="str">
+        <x:v>[검색]</x:v>
+      </x:c>
+      <x:c r="B22" s="13" t="str">
+        <x:v>한글 영어 별칭 초성</x:v>
+      </x:c>
+      <x:c r="C22" s="13" t="str">
+        <x:v>rich block</x:v>
+      </x:c>
+      <x:c r="D22" s="13" t="str">
+        <x:v>title·alias·subtext를 공백 정규화해 필터링하고 결과 없음 상태와 전체 명령 보기 제공</x:v>
+      </x:c>
+      <x:c r="E22" s="13" t="str">
+        <x:v>원격 검색은 debounce·AbortSignal로 이전 응답 취소, stale 결과 표시 금지</x:v>
+      </x:c>
+      <x:c r="F22" s="13" t="str">
+        <x:v>M1-D 개선</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23">
+      <x:c r="A23" s="13" t="str">
+        <x:v>[위치]</x:v>
+      </x:c>
+      <x:c r="B23" s="13" t="str">
+        <x:v>caret popup viewport</x:v>
+      </x:c>
+      <x:c r="C23" s="13" t="str">
+        <x:v>rich block</x:v>
+      </x:c>
+      <x:c r="D23" s="13" t="str">
+        <x:v>caret rect를 기준으로 아래에 열고 공간이 없으면 위로 flip, 창 경계에서 shift, 내부만 scroll</x:v>
+      </x:c>
+      <x:c r="E23" s="13" t="str">
+        <x:v>editor/페이지 전체 확대와 분리, zoom·DPI·스크롤 후 위치 갱신</x:v>
+      </x:c>
+      <x:c r="F23" s="13" t="str">
+        <x:v>M1-D 개선</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24">
+      <x:c r="A24" s="13" t="str">
+        <x:v>[포인터]</x:v>
+      </x:c>
+      <x:c r="B24" s="13" t="str">
+        <x:v>hover click touch</x:v>
+      </x:c>
+      <x:c r="C24" s="13" t="str">
+        <x:v>rich block</x:v>
+      </x:c>
+      <x:c r="D24" s="13" t="str">
+        <x:v>hover는 강조만 하고 click/pointerdown이 명령 실행, keyboard active와 포인터 active를 안정 동기화</x:v>
+      </x:c>
+      <x:c r="E24" s="13" t="str">
+        <x:v>mousedown에서 editor focus가 사라지지 않게 하고 hover 깜빡임 금지</x:v>
+      </x:c>
+      <x:c r="F24" s="13" t="str">
+        <x:v>M1-D 개선</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25">
+      <x:c r="A25" s="13" t="str">
+        <x:v>[접근성]</x:v>
+      </x:c>
+      <x:c r="B25" s="13" t="str">
+        <x:v>combobox listbox option</x:v>
+      </x:c>
+      <x:c r="C25" s="13" t="str">
+        <x:v>rich block</x:v>
+      </x:c>
+      <x:c r="D25" s="13" t="str">
+        <x:v>expanded/controls/activedescendant와 option 위치를 스크린리더에 전달</x:v>
+      </x:c>
+      <x:c r="E25" s="13" t="str">
+        <x:v>긴 설명은 option 이름과 분리, 색상만으로 active/disabled 표현 금지</x:v>
+      </x:c>
+      <x:c r="F25" s="13" t="str">
+        <x:v>M1-D 개선</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5819209767504a2a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd232fbe05bf54b36"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2470,7 +2610,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9c987c2c56e247ed"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re8eddae98d9e477c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3067,10 +3207,350 @@
         <x:v>P2</x:v>
       </x:c>
     </x:row>
+    <x:row r="35">
+      <x:c r="A35" s="13" t="str">
+        <x:v>Rich text</x:v>
+      </x:c>
+      <x:c r="B35" s="13" t="str">
+        <x:v>Ctrl+B / Ctrl+I / Ctrl+U</x:v>
+      </x:c>
+      <x:c r="C35" s="13" t="str">
+        <x:v>굵게 / 기울임 / 밑줄</x:v>
+      </x:c>
+      <x:c r="D35" s="13" t="str">
+        <x:v>선택 영역 또는 이후 입력 mark만 변경하고 브라우저 동작 차단</x:v>
+      </x:c>
+      <x:c r="E35" s="13" t="str">
+        <x:v>P0·Tiptap/Notion 기대</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36">
+      <x:c r="A36" s="13" t="str">
+        <x:v>Rich text</x:v>
+      </x:c>
+      <x:c r="B36" s="13" t="str">
+        <x:v>Ctrl+Shift+S / Ctrl+E / Ctrl+K</x:v>
+      </x:c>
+      <x:c r="C36" s="13" t="str">
+        <x:v>취소선 / 인라인 코드 / 링크</x:v>
+      </x:c>
+      <x:c r="D36" s="13" t="str">
+        <x:v>전역 저장·팔레트와 editor focus로 분기</x:v>
+      </x:c>
+      <x:c r="E36" s="13" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37">
+      <x:c r="A37" s="13" t="str">
+        <x:v>Rich text</x:v>
+      </x:c>
+      <x:c r="B37" s="13" t="str">
+        <x:v>Ctrl+Shift+M</x:v>
+      </x:c>
+      <x:c r="C37" s="13" t="str">
+        <x:v>선택 영역 댓글</x:v>
+      </x:c>
+      <x:c r="D37" s="13" t="str">
+        <x:v>댓글 권한이 없으면 이유와 함께 disabled</x:v>
+      </x:c>
+      <x:c r="E37" s="13" t="str">
+        <x:v>M1.5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38">
+      <x:c r="A38" s="13" t="str">
+        <x:v>블록 입력</x:v>
+      </x:c>
+      <x:c r="B38" s="13" t="str">
+        <x:v>Enter / Shift+Enter</x:v>
+      </x:c>
+      <x:c r="C38" s="13" t="str">
+        <x:v>새 블록 / 같은 블록 줄바꿈</x:v>
+      </x:c>
+      <x:c r="D38" s="13" t="str">
+        <x:v>슬래시 메뉴·목록·Python 셀에서는 해당 상태 규칙 우선</x:v>
+      </x:c>
+      <x:c r="E38" s="13" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39">
+      <x:c r="A39" s="13" t="str">
+        <x:v>목록</x:v>
+      </x:c>
+      <x:c r="B39" s="13" t="str">
+        <x:v>Tab / Shift+Tab</x:v>
+      </x:c>
+      <x:c r="C39" s="13" t="str">
+        <x:v>목록 항목 중첩 / 중첩 해제</x:v>
+      </x:c>
+      <x:c r="D39" s="13" t="str">
+        <x:v>앞 형제 없이 들여쓰기 금지, 일반 form/dialog에서는 focus 이동 유지</x:v>
+      </x:c>
+      <x:c r="E39" s="13" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40">
+      <x:c r="A40" s="13" t="str">
+        <x:v>목록</x:v>
+      </x:c>
+      <x:c r="B40" s="13" t="str">
+        <x:v>빈 항목에서 Enter</x:v>
+      </x:c>
+      <x:c r="C40" s="13" t="str">
+        <x:v>한 단계 목록 종료 또는 일반 문단 전환</x:v>
+      </x:c>
+      <x:c r="D40" s="13" t="str">
+        <x:v>중첩 목록은 먼저 outdent하고 최상위 빈 항목에서 목록 종료</x:v>
+      </x:c>
+      <x:c r="E40" s="13" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41">
+      <x:c r="A41" s="13" t="str">
+        <x:v>슬래시 메뉴</x:v>
+      </x:c>
+      <x:c r="B41" s="13" t="str">
+        <x:v>Up/Down, Home/End</x:v>
+      </x:c>
+      <x:c r="C41" s="13" t="str">
+        <x:v>후보 이동, 처음/끝 이동</x:v>
+      </x:c>
+      <x:c r="D41" s="13" t="str">
+        <x:v>DOM focus는 editor에 유지하고 active descendant만 변경</x:v>
+      </x:c>
+      <x:c r="E41" s="13" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42">
+      <x:c r="A42" s="13" t="str">
+        <x:v>슬래시 메뉴</x:v>
+      </x:c>
+      <x:c r="B42" s="13" t="str">
+        <x:v>Enter / Tab</x:v>
+      </x:c>
+      <x:c r="C42" s="13" t="str">
+        <x:v>현재 후보 실행</x:v>
+      </x:c>
+      <x:c r="D42" s="13" t="str">
+        <x:v>IME 조합 중에는 실행 금지. 권한 불가 후보는 실행하지 않음</x:v>
+      </x:c>
+      <x:c r="E42" s="13" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43">
+      <x:c r="A43" s="13" t="str">
+        <x:v>슬래시 메뉴</x:v>
+      </x:c>
+      <x:c r="B43" s="13" t="str">
+        <x:v>Esc / Backspace</x:v>
+      </x:c>
+      <x:c r="C43" s="13" t="str">
+        <x:v>메뉴 닫기 / query 삭제와 trigger 경계 닫기</x:v>
+      </x:c>
+      <x:c r="D43" s="13" t="str">
+        <x:v>본문 입력과 selection은 보존하며 두 번째 Esc만 상위 선택 해제에 사용</x:v>
+      </x:c>
+      <x:c r="E43" s="13" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44">
+      <x:c r="A44" s="13" t="str">
+        <x:v>Markdown 입력</x:v>
+      </x:c>
+      <x:c r="B44" s="13" t="str">
+        <x:v># / ## / ### + Space</x:v>
+      </x:c>
+      <x:c r="C44" s="13" t="str">
+        <x:v>H1 / H2 / H3 변환</x:v>
+      </x:c>
+      <x:c r="D44" s="13" t="str">
+        <x:v>빈 블록 시작에서만, backslash escape와 undo 제공</x:v>
+      </x:c>
+      <x:c r="E44" s="13" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45">
+      <x:c r="A45" s="13" t="str">
+        <x:v>Markdown 입력</x:v>
+      </x:c>
+      <x:c r="B45" s="13" t="str">
+        <x:v>- / * / + + Space</x:v>
+      </x:c>
+      <x:c r="C45" s="13" t="str">
+        <x:v>글머리표 목록 변환</x:v>
+      </x:c>
+      <x:c r="D45" s="13" t="str">
+        <x:v>빈 블록 시작에서만, --- 입력 중 조기 목록 변환 금지</x:v>
+      </x:c>
+      <x:c r="E45" s="13" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46">
+      <x:c r="A46" s="13" t="str">
+        <x:v>Markdown 입력</x:v>
+      </x:c>
+      <x:c r="B46" s="13" t="str">
+        <x:v>1. + Space / [] + Space</x:v>
+      </x:c>
+      <x:c r="C46" s="13" t="str">
+        <x:v>번호 목록 / 할 일 목록 변환</x:v>
+      </x:c>
+      <x:c r="D46" s="13" t="str">
+        <x:v>marker 전체 일치와 IME composition 종료 뒤만</x:v>
+      </x:c>
+      <x:c r="E46" s="13" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47">
+      <x:c r="A47" s="13" t="str">
+        <x:v>Markdown 입력</x:v>
+      </x:c>
+      <x:c r="B47" s="13" t="str">
+        <x:v>&gt; + Space / " + Space</x:v>
+      </x:c>
+      <x:c r="C47" s="13" t="str">
+        <x:v>토글 / 인용 변환</x:v>
+      </x:c>
+      <x:c r="D47" s="13" t="str">
+        <x:v>제품 설정에서 Notion 호환 여부를 명시</x:v>
+      </x:c>
+      <x:c r="E47" s="13" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48">
+      <x:c r="A48" s="13" t="str">
+        <x:v>Markdown 입력</x:v>
+      </x:c>
+      <x:c r="B48" s="13" t="str">
+        <x:v>--- / ___ / *** + Tab</x:v>
+      </x:c>
+      <x:c r="C48" s="13" t="str">
+        <x:v>구분선 후보 확정</x:v>
+      </x:c>
+      <x:c r="D48" s="13" t="str">
+        <x:v>오직 내용 없는 블록의 marker 전체 일치 시. 입력 즉시 변환하지 않음</x:v>
+      </x:c>
+      <x:c r="E48" s="13" t="str">
+        <x:v>사용자 제안 반영·P1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49">
+      <x:c r="A49" s="13" t="str">
+        <x:v>Markdown 입력</x:v>
+      </x:c>
+      <x:c r="B49" s="13" t="str">
+        <x:v>=== + Tab</x:v>
+      </x:c>
+      <x:c r="C49" s="13" t="str">
+        <x:v>기본은 리터럴 유지</x:v>
+      </x:c>
+      <x:c r="D49" s="13" t="str">
+        <x:v>표준상 구분선이 아니며 앞줄이 있으면 H1 의미. 커스텀 강한 구분선 설정 전에는 변환 금지</x:v>
+      </x:c>
+      <x:c r="E49" s="13" t="str">
+        <x:v>P0 안전 경계</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="50">
+      <x:c r="A50" s="13" t="str">
+        <x:v>입력 규칙</x:v>
+      </x:c>
+      <x:c r="B50" s="13" t="str">
+        <x:v>\ + marker / 변환 직후 Backspace</x:v>
+      </x:c>
+      <x:c r="C50" s="13" t="str">
+        <x:v>자동 변환 회피 / 원문 복구</x:v>
+      </x:c>
+      <x:c r="D50" s="13" t="str">
+        <x:v>동일 undo transaction으로 복구하고 저장 전후 결과 일치</x:v>
+      </x:c>
+      <x:c r="E50" s="13" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="51">
+      <x:c r="A51" s="13" t="str">
+        <x:v>멘션·링크</x:v>
+      </x:c>
+      <x:c r="B51" s="13" t="str">
+        <x:v>@ / [[ / +</x:v>
+      </x:c>
+      <x:c r="C51" s="13" t="str">
+        <x:v>사람·날짜·페이지 검색 또는 빠른 링크</x:v>
+      </x:c>
+      <x:c r="D51" s="13" t="str">
+        <x:v>URL·파일 경로·이메일 입력 중 오탐 방지, 권한 있는 대상만 노출</x:v>
+      </x:c>
+      <x:c r="E51" s="13" t="str">
+        <x:v>M2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="52">
+      <x:c r="A52" s="13" t="str">
+        <x:v>표</x:v>
+      </x:c>
+      <x:c r="B52" s="13" t="str">
+        <x:v>Tab / Shift+Tab</x:v>
+      </x:c>
+      <x:c r="C52" s="13" t="str">
+        <x:v>다음 / 이전 셀</x:v>
+      </x:c>
+      <x:c r="D52" s="13" t="str">
+        <x:v>마지막 셀 Tab은 행 추가 여부를 설정으로 확정</x:v>
+      </x:c>
+      <x:c r="E52" s="13" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="53">
+      <x:c r="A53" s="13" t="str">
+        <x:v>접근성</x:v>
+      </x:c>
+      <x:c r="B53" s="13" t="str">
+        <x:v>Shift+F10</x:v>
+      </x:c>
+      <x:c r="C53" s="13" t="str">
+        <x:v>현재 블록 context menu</x:v>
+      </x:c>
+      <x:c r="D53" s="13" t="str">
+        <x:v>브라우저 native menu 대체 경로와 스크린리더 이름 제공</x:v>
+      </x:c>
+      <x:c r="E53" s="13" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="54">
+      <x:c r="A54" s="13" t="str">
+        <x:v>공통</x:v>
+      </x:c>
+      <x:c r="B54" s="13" t="str">
+        <x:v>F1</x:v>
+      </x:c>
+      <x:c r="C54" s="13" t="str">
+        <x:v>현재 편집 모드의 단축키 도움말</x:v>
+      </x:c>
+      <x:c r="D54" s="13" t="str">
+        <x:v>Rich text/Markdown/코드/Python별 충돌 해결 결과만 표시</x:v>
+      </x:c>
+      <x:c r="E54" s="13" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf12bf283eb8d4f96"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra58cd8a337b54ce3"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3330,7 +3810,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7bff9eb04a4a4fbe"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R99e344ec48b440f5"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3522,7 +4002,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra9b53656e44045a6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5b11e3d73c2a47c6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3850,7 +4330,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R891c09c20fc34787"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rca9beb5ed1d741af"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4110,7 +4590,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfb57efdf26a04008"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R61dd342cb0254076"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4302,7 +4782,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcfa6bd4e303e4235"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb1c1d4b342da43af"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4435,7 +4915,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc9bcb939bec1429d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R428fe81ebd06473d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4814,7 +5294,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Recb79e5b7df84d2b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R883d6b0c901e4c55"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5074,7 +5554,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R40fc7b1250a34323"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rac325daf01bf4bf1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5419,7 +5899,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9351c88702b14d64"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R61141fd869a347ca"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5900,7 +6380,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8fdd2881881f4726"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R34c04be698bd425f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6211,7 +6691,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7640a4bb8ec74750"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re2cd93db1f09480a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6522,7 +7002,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4170574e999f46dd"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcc55ab2a5bcf47b8"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6850,7 +7330,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R73cf635b185746e5"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc532beb7f4e84b82"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7110,7 +7590,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra66b482566564b04"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R267b4d0549bd4ee4"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7271,7 +7751,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R70fb2197d2de4b11"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1729ebd067604359"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7891,10 +8371,130 @@
         <x:v>자동 완전 hydrate marker는 별도 보류</x:v>
       </x:c>
     </x:row>
+    <x:row r="31">
+      <x:c r="A31" s="13" t="str">
+        <x:v>T-030</x:v>
+      </x:c>
+      <x:c r="B31" s="13" t="str">
+        <x:v>슬래시 위치·포커스</x:v>
+      </x:c>
+      <x:c r="C31" s="13" t="str">
+        <x:v>빈 블록/문장/URL/경로/스크롤 끝/DPI·zoom에서 / 입력</x:v>
+      </x:c>
+      <x:c r="D31" s="13" t="str">
+        <x:v>허용 문맥만 caret dropdown, editor focus·selection 유지, viewport 밖/별도 dialog 없음</x:v>
+      </x:c>
+      <x:c r="E31" s="13" t="str">
+        <x:v>unit+E2E+수동</x:v>
+      </x:c>
+      <x:c r="F31" s="13" t="str">
+        <x:v>M1-D 개선</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32">
+      <x:c r="A32" s="13" t="str">
+        <x:v>T-031</x:v>
+      </x:c>
+      <x:c r="B32" s="13" t="str">
+        <x:v>슬래시 입력·비동기</x:v>
+      </x:c>
+      <x:c r="C32" s="13" t="str">
+        <x:v>한글 IME 조합, 빠른 query 변경, 요청 역전, Esc/Backspace/click-outside</x:v>
+      </x:c>
+      <x:c r="D32" s="13" t="str">
+        <x:v>이중 입력·stale 결과·명령 오실행 0건, 취소 뒤 본문 보존</x:v>
+      </x:c>
+      <x:c r="E32" s="13" t="str">
+        <x:v>unit+E2E</x:v>
+      </x:c>
+      <x:c r="F32" s="13" t="str">
+        <x:v>M1-D 개선</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33">
+      <x:c r="A33" s="13" t="str">
+        <x:v>T-032</x:v>
+      </x:c>
+      <x:c r="B33" s="13" t="str">
+        <x:v>슬래시 키보드·접근성</x:v>
+      </x:c>
+      <x:c r="C33" s="13" t="str">
+        <x:v>Up/Down/Home/End/Enter/Tab/Esc와 screen reader, pointer hover 왕복</x:v>
+      </x:c>
+      <x:c r="D33" s="13" t="str">
+        <x:v>active item과 aria 상태 일치, focus 손실·hover 깜빡임·disabled 실행 0건</x:v>
+      </x:c>
+      <x:c r="E33" s="13" t="str">
+        <x:v>E2E+수동 accessibility</x:v>
+      </x:c>
+      <x:c r="F33" s="13" t="str">
+        <x:v>M1-D 개선</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34">
+      <x:c r="A34" s="13" t="str">
+        <x:v>T-033</x:v>
+      </x:c>
+      <x:c r="B34" s="13" t="str">
+        <x:v>입력 규칙·Markdown</x:v>
+      </x:c>
+      <x:c r="C34" s="13" t="str">
+        <x:v>#/-/1./[]/&gt;/---/___/***/===와 Space/Tab/Backspace/escape, import-export</x:v>
+      </x:c>
+      <x:c r="D34" s="13" t="str">
+        <x:v>낮은 모호성만 Space 변환, 구분선은 명시 Tab, === 리터럴 보존, 즉시 undo와 round-trip 일치</x:v>
+      </x:c>
+      <x:c r="E34" s="13" t="str">
+        <x:v>unit+round-trip+E2E</x:v>
+      </x:c>
+      <x:c r="F34" s="13" t="str">
+        <x:v>M1-D 개선</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35">
+      <x:c r="A35" s="13" t="str">
+        <x:v>T-034</x:v>
+      </x:c>
+      <x:c r="B35" s="13" t="str">
+        <x:v>Tab 상태 우선순위</x:v>
+      </x:c>
+      <x:c r="C35" s="13" t="str">
+        <x:v>일반 문단·목록·표·코드·Python edit/command·slash menu·dialog에서 Tab/Shift+Tab</x:v>
+      </x:c>
+      <x:c r="D35" s="13" t="str">
+        <x:v>상태표에 정의된 동작 하나만 실행되고 focus trap·브라우저 누출·이중 실행 없음</x:v>
+      </x:c>
+      <x:c r="E35" s="13" t="str">
+        <x:v>unit+E2E</x:v>
+      </x:c>
+      <x:c r="F35" s="13" t="str">
+        <x:v>M1-D 개선</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36">
+      <x:c r="A36" s="13" t="str">
+        <x:v>T-035</x:v>
+      </x:c>
+      <x:c r="B36" s="13" t="str">
+        <x:v>단축키 충돌</x:v>
+      </x:c>
+      <x:c r="C36" s="13" t="str">
+        <x:v>Rich text/Monaco/Python/브라우저/OS/IME에서 공통 조합과 권한 회수</x:v>
+      </x:c>
+      <x:c r="D36" s="13" t="str">
+        <x:v>가장 안쪽 활성 editor adapter만 실행, 불가 명령은 명확히 disabled, 저장/인쇄/실행 오작동 없음</x:v>
+      </x:c>
+      <x:c r="E36" s="13" t="str">
+        <x:v>E2E+수동</x:v>
+      </x:c>
+      <x:c r="F36" s="13" t="str">
+        <x:v>M1-D 개선</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5859c2abe7fc415c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc218f8e56f374607"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8236,10 +8836,61 @@
         <x:v>stable file/document identity 저장소 설계 변경 시</x:v>
       </x:c>
     </x:row>
+    <x:row r="20">
+      <x:c r="A20" s="13" t="str">
+        <x:v>DEC-019</x:v>
+      </x:c>
+      <x:c r="B20" s="13" t="str">
+        <x:v>권장·구현 전</x:v>
+      </x:c>
+      <x:c r="C20" s="13" t="str">
+        <x:v>슬래시 명령은 modal Dialog가 아니라 editor focus를 유지하는 caret-anchored suggestion dropdown으로 제공한다.</x:v>
+      </x:c>
+      <x:c r="D20" s="13" t="str">
+        <x:v>입력한 /query가 본문 문맥에 남은 채 필터링되고 마우스·키보드가 같은 Command Registry를 호출해야 Notion식 흐름과 IME 안정성을 얻는다.</x:v>
+      </x:c>
+      <x:c r="E20" s="13" t="str">
+        <x:v>로그인 실화면에서 IME·스크롤·viewport flip·접근성 검증이 실패할 때</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21">
+      <x:c r="A21" s="13" t="str">
+        <x:v>DEC-020</x:v>
+      </x:c>
+      <x:c r="B21" s="13" t="str">
+        <x:v>권장·구현 전</x:v>
+      </x:c>
+      <x:c r="C21" s="13" t="str">
+        <x:v>자동 입력 변환은 marker를 입력한 즉시 실행하지 않고 명확한 commit key와 되돌리기를 둔다.</x:v>
+      </x:c>
+      <x:c r="D21" s="13" t="str">
+        <x:v>#·-·1.·[]·&gt; 계열은 marker 뒤 Space, 모호한 thematic break 계열은 빈 블록에서 marker 뒤 Tab으로 확정하고 변환 직후 Backspace/Ctrl+Z로 원문을 복구한다.</x:v>
+      </x:c>
+      <x:c r="E21" s="13" t="str">
+        <x:v>실사용 테스트에서 Tab 중첩과 충돌하거나 Markdown import/export round-trip이 깨질 때</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22">
+      <x:c r="A22" s="13" t="str">
+        <x:v>DEC-021</x:v>
+      </x:c>
+      <x:c r="B22" s="13" t="str">
+        <x:v>채택·구현 전</x:v>
+      </x:c>
+      <x:c r="C22" s="13" t="str">
+        <x:v>===는 기본 구분선 단축키로 사용하지 않는다.</x:v>
+      </x:c>
+      <x:c r="D22" s="13" t="str">
+        <x:v>CommonMark에서 빈 ===는 일반 텍스트이고 앞줄 텍스트 아래에서는 Setext H1이므로 구분선으로 자동 변환하면 의미와 내보내기가 달라진다. 별도 강한 구분선 스타일을 만들 경우에만 명시 설정과 fallback을 둔다.</x:v>
+      </x:c>
+      <x:c r="E22" s="13" t="str">
+        <x:v>제품이 표준 Markdown과 다른 강한 구분선 block type을 정식 채택할 때</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4aa04c1ac3aa4a16"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd5907ec2e4e74247"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8380,7 +9031,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra08343e9180a442a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra36b875b48604f47"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8589,7 +9240,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9f380bfcb20c4fc2"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb30e654b64e64603"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8789,10 +9440,30 @@
         <x:v>Codex</x:v>
       </x:c>
     </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="13" t="str">
+        <x:v>2026-09-06</x:v>
+      </x:c>
+      <x:c r="B10" s="13" t="str">
+        <x:v>0.9-slash-shortcut-research</x:v>
+      </x:c>
+      <x:c r="C10" s="13" t="str">
+        <x:v>연구·설계 기록 완료 / 구현 전</x:v>
+      </x:c>
+      <x:c r="D10" s="13" t="str">
+        <x:v>Notion식 caret slash dropdown, 상태별 Tab 우선순위, Space/Tab commit input rules, === 표준 경계, 접근성·IME·비동기·포인터 회귀 항목을 전용 원장에 추가했다.</x:v>
+      </x:c>
+      <x:c r="E10" s="13" t="str">
+        <x:v>공식 Notion/Tiptap/BlockNote/CommonMark/JupyterLab/WAI-ARIA/ProseMirror 자료 대조. 코드와 운영 배포 변경 없음.</x:v>
+      </x:c>
+      <x:c r="F10" s="13" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2e46406e16bc46ff"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd7890fb548e943d9"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8957,16 +9628,16 @@
         <x:v>계층 트리·slash/context menu</x:v>
       </x:c>
       <x:c r="C8" s="20" t="str">
-        <x:v>운영 배포·자동 검증 완료 / 실화면 전</x:v>
+        <x:v>운영 배포·자동 검증 완료 / 2차 slash·shortcut 연구 완료·구현 전</x:v>
       </x:c>
       <x:c r="D8" s="20" t="str">
-        <x:v>parentId tree, 우클릭 하위 생성/최상위 이동, 자손 cycle 차단, /·Ctrl+K registry</x:v>
+        <x:v>현재 parent tree·우클릭·/·Ctrl+K registry. 조사안은 caret suggestion dropdown, 상태별 Tab, explicit input-rule commit, ARIA·IME·async 계약</x:v>
       </x:c>
       <x:c r="E8" s="20" t="str">
-        <x:v>NAS backend 8/8 + frontend 3/3 + build + HTTP/service</x:v>
+        <x:v>기존 NAS 8/8·frontend 3/3·build·HTTP/service; 연구 문서 artifact-tool 검증</x:v>
       </x:c>
       <x:c r="F8" s="20" t="str">
-        <x:v>로그인 실화면 우클릭·IME·slash E2E</x:v>
+        <x:v>별도 Dialog 제거와 Suggestion extension 구현 후 로그인 실화면 IME·DPI·키보드·포인터·screen reader E2E</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -9338,7 +10009,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ref7ad1693c344ad4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcb4fa61ddd554c05"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9621,7 +10292,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc2da1db901964e77"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4e93591360764460"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10082,10 +10753,180 @@
         <x:v>2026-09-06</x:v>
       </x:c>
     </x:row>
+    <x:row r="27">
+      <x:c r="A27" s="13" t="str">
+        <x:v>SRC-SHORTCUT-NOTION</x:v>
+      </x:c>
+      <x:c r="B27" s="13" t="str">
+        <x:v>Notion keyboard and Markdown shortcuts</x:v>
+      </x:c>
+      <x:c r="C27" s="13" t="str">
+        <x:v>https://www.notion.com/help/keyboard-shortcuts</x:v>
+      </x:c>
+      <x:c r="D27" s="13" t="str">
+        <x:v>/ 필터 메뉴, Space 입력 규칙, Enter·Tab·Esc, 블록·서식 단축키 기준</x:v>
+      </x:c>
+      <x:c r="E27" s="13" t="str">
+        <x:v>2026-09-06</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28">
+      <x:c r="A28" s="13" t="str">
+        <x:v>SRC-SHORTCUT-NOTION-DIVIDER</x:v>
+      </x:c>
+      <x:c r="B28" s="13" t="str">
+        <x:v>Notion headings and dividers</x:v>
+      </x:c>
+      <x:c r="C28" s="13" t="str">
+        <x:v>https://www.notion.com/en-gb/help/columns-headings-and-dividers</x:v>
+      </x:c>
+      <x:c r="D28" s="13" t="str">
+        <x:v>Notion의 --- 즉시 divider 동작과 /div 대안</x:v>
+      </x:c>
+      <x:c r="E28" s="13" t="str">
+        <x:v>2026-09-06</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29">
+      <x:c r="A29" s="13" t="str">
+        <x:v>SRC-SHORTCUT-TIPTAP-SUGGESTION</x:v>
+      </x:c>
+      <x:c r="B29" s="13" t="str">
+        <x:v>Tiptap Suggestion utility</x:v>
+      </x:c>
+      <x:c r="C29" s="13" t="str">
+        <x:v>https://tiptap.dev/docs/editor/api/utilities/suggestion</x:v>
+      </x:c>
+      <x:c r="D29" s="13" t="str">
+        <x:v>trigger/query/allow/shouldShow/AbortSignal/render/clientRect 기반 인라인 메뉴</x:v>
+      </x:c>
+      <x:c r="E29" s="13" t="str">
+        <x:v>2026-09-06</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30">
+      <x:c r="A30" s="13" t="str">
+        <x:v>SRC-SHORTCUT-TIPTAP-KEYS</x:v>
+      </x:c>
+      <x:c r="B30" s="13" t="str">
+        <x:v>Tiptap keyboard shortcuts and ListKeymap</x:v>
+      </x:c>
+      <x:c r="C30" s="13" t="str">
+        <x:v>https://tiptap.dev/docs/editor/core-concepts/keyboard-shortcuts</x:v>
+      </x:c>
+      <x:c r="D30" s="13" t="str">
+        <x:v>기본 서식·문단 shortcut와 extension별 override 기준</x:v>
+      </x:c>
+      <x:c r="E30" s="13" t="str">
+        <x:v>2026-09-06</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31">
+      <x:c r="A31" s="13" t="str">
+        <x:v>SRC-SHORTCUT-TIPTAP-INPUT</x:v>
+      </x:c>
+      <x:c r="B31" s="13" t="str">
+        <x:v>Tiptap input rules and horizontal rule</x:v>
+      </x:c>
+      <x:c r="C31" s="13" t="str">
+        <x:v>https://tiptap.dev/docs/editor/api/input-rules</x:v>
+      </x:c>
+      <x:c r="D31" s="13" t="str">
+        <x:v>pattern transform의 명시적 제어와 undo 가능한 input rule 설계</x:v>
+      </x:c>
+      <x:c r="E31" s="13" t="str">
+        <x:v>2026-09-06</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32">
+      <x:c r="A32" s="13" t="str">
+        <x:v>SRC-SHORTCUT-BLOCKNOTE</x:v>
+      </x:c>
+      <x:c r="B32" s="13" t="str">
+        <x:v>BlockNote suggestion menus</x:v>
+      </x:c>
+      <x:c r="C32" s="13" t="str">
+        <x:v>https://www.blocknotejs.org/docs/react/components/suggestion-menus</x:v>
+      </x:c>
+      <x:c r="D32" s="13" t="str">
+        <x:v>query filter, title/subtext/badge/aliases/group, 순서·커스텀 menu 참고</x:v>
+      </x:c>
+      <x:c r="E32" s="13" t="str">
+        <x:v>2026-09-06</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33">
+      <x:c r="A33" s="13" t="str">
+        <x:v>SRC-SHORTCUT-COMMONMARK</x:v>
+      </x:c>
+      <x:c r="B33" s="13" t="str">
+        <x:v>CommonMark 0.31.2</x:v>
+      </x:c>
+      <x:c r="C33" s="13" t="str">
+        <x:v>https://spec.commonmark.org/0.31.2/</x:v>
+      </x:c>
+      <x:c r="D33" s="13" t="str">
+        <x:v>--- thematic break/Setext H2 문맥과 빈 === 리터럴·Setext H1 의미 경계</x:v>
+      </x:c>
+      <x:c r="E33" s="13" t="str">
+        <x:v>2026-09-06</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34">
+      <x:c r="A34" s="13" t="str">
+        <x:v>SRC-SHORTCUT-JUPYTER</x:v>
+      </x:c>
+      <x:c r="B34" s="13" t="str">
+        <x:v>JupyterLab notebook modes</x:v>
+      </x:c>
+      <x:c r="C34" s="13" t="str">
+        <x:v>https://jupyterlab.readthedocs.io/en/stable/user/notebook.html</x:v>
+      </x:c>
+      <x:c r="D34" s="13" t="str">
+        <x:v>Python 셀 edit/command mode를 분리해 문자 shortcut 충돌 방지</x:v>
+      </x:c>
+      <x:c r="E34" s="13" t="str">
+        <x:v>2026-09-06</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35">
+      <x:c r="A35" s="13" t="str">
+        <x:v>SRC-SHORTCUT-WAI</x:v>
+      </x:c>
+      <x:c r="B35" s="13" t="str">
+        <x:v>WAI-ARIA combobox/listbox patterns</x:v>
+      </x:c>
+      <x:c r="C35" s="13" t="str">
+        <x:v>https://www.w3.org/WAI/ARIA/apg/patterns/combobox/</x:v>
+      </x:c>
+      <x:c r="D35" s="13" t="str">
+        <x:v>editor focus 유지, activedescendant, 화살표·Enter·Esc 접근성 기준</x:v>
+      </x:c>
+      <x:c r="E35" s="13" t="str">
+        <x:v>2026-09-06</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36">
+      <x:c r="A36" s="13" t="str">
+        <x:v>SRC-SHORTCUT-PROSEMIRROR</x:v>
+      </x:c>
+      <x:c r="B36" s="13" t="str">
+        <x:v>ProseMirror menu and Markdown examples</x:v>
+      </x:c>
+      <x:c r="C36" s="13" t="str">
+        <x:v>https://prosemirror.net/examples/menu/</x:v>
+      </x:c>
+      <x:c r="D36" s="13" t="str">
+        <x:v>명령 applicability와 mousedown focus 보존·editor state 동기화</x:v>
+      </x:c>
+      <x:c r="E36" s="13" t="str">
+        <x:v>2026-09-06</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rad0112d0030a4f00"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re9be680ef1314e76"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10328,7 +11169,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4666a13bce7f40b0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf909bbae8d2a4b95"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10503,7 +11344,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R78a6074706ca424a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0b68224df8fa4271"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10763,7 +11604,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R878ac4d909ba4c08"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R29600bb0cd3a4524"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/programs/NAS_NOTE_STUDIO_SPEC.xlsx
+++ b/docs/programs/NAS_NOTE_STUDIO_SPEC.xlsx
@@ -2,39 +2,39 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="R23eef9105c484b8a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Product_Vision" sheetId="2" r:id="R50778d7dc93749dd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decisions" sheetId="3" r:id="R876b04ea5c604451"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Competitors" sheetId="4" r:id="Rb2c342e8bd414843"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open_Source" sheetId="5" r:id="Rd848ca236a4644e2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source_Index" sheetId="6" r:id="Rebd558751cb14880"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Information_Architecture" sheetId="7" r:id="Re986eea2a04f4b65"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI_Layout" sheetId="8" r:id="R18f3633983ba4820"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="User_Flows" sheetId="9" r:id="Rf20ded511de04936"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Note_Types" sheetId="10" r:id="R21943a8c407849df"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Block_Catalog" sheetId="11" r:id="R7fff2c80877641a2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Slash_Commands" sheetId="12" r:id="R2803cb16adca4cc1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Context_Menus" sheetId="13" r:id="R55ab06f40c444d4d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Keyboard_Shortcuts" sheetId="14" r:id="Rbbb7a7de11b54b2d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Database_Views" sheetId="15" r:id="Rafa55940fd2f4047"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Code_Text_Mode" sheetId="16" r:id="R13a8b60902674136"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Python_Notebook" sheetId="17" r:id="R3a18638c7a604237"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Collaboration" sheetId="18" r:id="R1b566ddcb0104f8e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Offline_Desktop" sheetId="19" r:id="Rc5dd9a7b8d0847c1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data_Model" sheetId="20" r:id="R1bf5cdac0f73487d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Storage_Interop" sheetId="21" r:id="R150d2bf710044d4f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Security" sheetId="22" r:id="R70d41560c3184783"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="API_Contracts" sheetId="23" r:id="Rb0b811ab529f485c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="State_Machines" sheetId="24" r:id="Rcc485df1d50c4300"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Error_Recovery" sheetId="25" r:id="R6a1f438105584760"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cross_App_Relations" sheetId="26" r:id="R699cbd8120b44002"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Performance" sheetId="27" r:id="Ree217d827ebb4631"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Accessibility" sheetId="28" r:id="Rc6f58fc47a6247dd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test_Matrix" sheetId="29" r:id="R7c3d9fd7543e4567"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="30" r:id="R1fe55fef5f684dcd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open_Questions" sheetId="31" r:id="Re0366270e3c240e4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Change_Log" sheetId="32" r:id="R892649e312db4f03"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Implementation_Status" sheetId="33" r:id="R10c1365f61d34875"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="R23f02748d72a45d9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Product_Vision" sheetId="2" r:id="R44e8d6e6e2b94f98"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decisions" sheetId="3" r:id="R68108f021874423d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Competitors" sheetId="4" r:id="R6c43a579201b475f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open_Source" sheetId="5" r:id="Ra5453cf334c14c51"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source_Index" sheetId="6" r:id="Rced982fa74f54cc5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Information_Architecture" sheetId="7" r:id="Rb444da4a73ce4c0d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI_Layout" sheetId="8" r:id="Rd89322792bad41a1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="User_Flows" sheetId="9" r:id="R9a8600fc060948be"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Note_Types" sheetId="10" r:id="Rbbc7cebfe1ec458f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Block_Catalog" sheetId="11" r:id="R6efcd6a8027a4465"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Slash_Commands" sheetId="12" r:id="Re3ba7d1df829406e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Context_Menus" sheetId="13" r:id="R8fb676fcdca24ae0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Keyboard_Shortcuts" sheetId="14" r:id="R40f1257549ab4feb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Database_Views" sheetId="15" r:id="Rb96f46d0f10e48f6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Code_Text_Mode" sheetId="16" r:id="R44166765670f4e02"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Python_Notebook" sheetId="17" r:id="R6211df195d294c10"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Collaboration" sheetId="18" r:id="R90429162607c404c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Offline_Desktop" sheetId="19" r:id="Rba909476dfb54961"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data_Model" sheetId="20" r:id="R9cc18d916a474f24"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Storage_Interop" sheetId="21" r:id="Rebe68b92e2b549e7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Security" sheetId="22" r:id="Rc79c6525c8c340b6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="API_Contracts" sheetId="23" r:id="R6341ec4148d64d45"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="State_Machines" sheetId="24" r:id="R881456e9a3274d26"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Error_Recovery" sheetId="25" r:id="R9dfbef0219984369"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cross_App_Relations" sheetId="26" r:id="Rc6447ef8be5a4990"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Performance" sheetId="27" r:id="R2b49d0cb3c054c3a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Accessibility" sheetId="28" r:id="R325eac3fa66c40de"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test_Matrix" sheetId="29" r:id="Ra5e8d5a1e2f04041"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="30" r:id="Re467a5d0d76146b3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open_Questions" sheetId="31" r:id="R8deddff23a0c48ce"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Change_Log" sheetId="32" r:id="R35c71c077b934f71"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Implementation_Status" sheetId="33" r:id="R6db5c7e968f84d32"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -928,7 +928,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R181811c2da994cfc"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Raab5f011352e4e99"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1271,7 +1271,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R38ed47eed02d4820"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf9c89f07e4fe4d43"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1674,7 +1674,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R36f86a5c41b04b5c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R56065700e1e34ba3"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2197,7 +2197,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd232fbe05bf54b36"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re6cc858f1ea9440e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2610,7 +2610,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re8eddae98d9e477c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9f335899326243bf"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3550,7 +3550,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra58cd8a337b54ce3"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R873870421bc14baa"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3810,7 +3810,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R99e344ec48b440f5"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R814130ae42644ddd"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4002,7 +4002,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5b11e3d73c2a47c6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8602c5fb13014289"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4330,7 +4330,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rca9beb5ed1d741af"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7bdf98f055634a26"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4590,7 +4590,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R61dd342cb0254076"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfb353dc2bcd04597"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4782,7 +4782,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb1c1d4b342da43af"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Raadef8555c964b14"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4915,7 +4915,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R428fe81ebd06473d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R72230173dd9e41ce"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5294,7 +5294,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R883d6b0c901e4c55"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Read912889f374208"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5554,7 +5554,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rac325daf01bf4bf1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rca7609ba8d504b29"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5899,7 +5899,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R61141fd869a347ca"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R11d3411be2564104"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6380,7 +6380,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R34c04be698bd425f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9b9cfa9321f440ea"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6691,7 +6691,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re2cd93db1f09480a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfdded8a47d0d482d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7002,7 +7002,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcc55ab2a5bcf47b8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2501cc777bfc4360"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7330,7 +7330,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc532beb7f4e84b82"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R239b5198b6ba4e80"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7590,7 +7590,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R267b4d0549bd4ee4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb245793a45c54a3c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7751,7 +7751,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1729ebd067604359"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7a2725bf07f54381"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8494,7 +8494,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc218f8e56f374607"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4c3f671734b14463"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8890,7 +8890,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd5907ec2e4e74247"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R362c80c632c5460b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9031,7 +9031,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra36b875b48604f47"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2733c2128f834862"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9240,7 +9240,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb30e654b64e64603"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rac8366b8b470420a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9460,10 +9460,30 @@
         <x:v>Codex</x:v>
       </x:c>
     </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="13" t="str">
+        <x:v>2026-09-06</x:v>
+      </x:c>
+      <x:c r="B11" s="13" t="str">
+        <x:v>1.0-final-cross-audit</x:v>
+      </x:c>
+      <x:c r="C11" s="13" t="str">
+        <x:v>실제 제품 교차 감사·미완료 재분류</x:v>
+      </x:c>
+      <x:c r="D11" s="13" t="str">
+        <x:v>Notion의 caret slash/페이지 트리와 JupyterLab의 command registry/kernel 수명주기를 현재 코드와 대조해 구현된 물리 기반과 설계뿐인 상호작용·실행 기능을 분리했다.</x:v>
+      </x:c>
+      <x:c r="E11" s="13" t="str">
+        <x:v>공식 Notion/JupyterLab 문서, NoteStudio.js의 Dialog 구현, Test_Matrix/Implementation_Status, local 회귀 결과 대조.</x:v>
+      </x:c>
+      <x:c r="F11" s="13" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd7890fb548e943d9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8a6e4bbc1cf84511"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9798,6 +9818,26 @@
       </x:c>
       <x:c r="F16" s="13" t="str">
         <x:v>새 Windows CFAPI/선택/keyboard E2E, 완전 hydration marker 자동 알림</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" s="13" t="str">
+        <x:v>AUDIT-2026-09-06</x:v>
+      </x:c>
+      <x:c r="B17" s="13" t="str">
+        <x:v>Notion/Jupyter 실제 제품 대조</x:v>
+      </x:c>
+      <x:c r="C17" s="13" t="str">
+        <x:v>M1 물리 기반 완료 / 상호작용·실행 기능 부분·설계</x:v>
+      </x:c>
+      <x:c r="D17" s="13" t="str">
+        <x:v>NOTE MANAGER·노트북·하위 페이지·4종 편집은 구현. slash는 중앙 Dialog이고 command registry·Tab/input rule·댓글·Office reference·Python kernel은 미구현.</x:v>
+      </x:c>
+      <x:c r="E17" s="13" t="str">
+        <x:v>local 전체 54 중 note 회귀 포함 52 pass·2 document skip; 로그인 운영 화면은 AI 중심 확인</x:v>
+      </x:c>
+      <x:c r="F17" s="13" t="str">
+        <x:v>M1-D caret suggestion과 IME/Tab E2E→M1-G Office reference→cgroup 뒤 M2 Python 순서</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -10009,7 +10049,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcb4fa61ddd554c05"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8cdc32d210c44e90"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10292,7 +10332,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4e93591360764460"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6a4b8b4ca5654e20"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10926,7 +10966,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re9be680ef1314e76"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb5bb22cce5b54855"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11169,7 +11209,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf909bbae8d2a4b95"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R058e4236bf3c4e14"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11344,7 +11384,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0b68224df8fa4271"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6e01a93f329f4abb"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11604,7 +11644,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R29600bb0cd3a4524"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2ff9096eabac4135"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/programs/NAS_NOTE_STUDIO_SPEC.xlsx
+++ b/docs/programs/NAS_NOTE_STUDIO_SPEC.xlsx
@@ -2,39 +2,39 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="R23f02748d72a45d9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Product_Vision" sheetId="2" r:id="R44e8d6e6e2b94f98"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decisions" sheetId="3" r:id="R68108f021874423d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Competitors" sheetId="4" r:id="R6c43a579201b475f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open_Source" sheetId="5" r:id="Ra5453cf334c14c51"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source_Index" sheetId="6" r:id="Rced982fa74f54cc5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Information_Architecture" sheetId="7" r:id="Rb444da4a73ce4c0d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI_Layout" sheetId="8" r:id="Rd89322792bad41a1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="User_Flows" sheetId="9" r:id="R9a8600fc060948be"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Note_Types" sheetId="10" r:id="Rbbc7cebfe1ec458f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Block_Catalog" sheetId="11" r:id="R6efcd6a8027a4465"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Slash_Commands" sheetId="12" r:id="Re3ba7d1df829406e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Context_Menus" sheetId="13" r:id="R8fb676fcdca24ae0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Keyboard_Shortcuts" sheetId="14" r:id="R40f1257549ab4feb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Database_Views" sheetId="15" r:id="Rb96f46d0f10e48f6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Code_Text_Mode" sheetId="16" r:id="R44166765670f4e02"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Python_Notebook" sheetId="17" r:id="R6211df195d294c10"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Collaboration" sheetId="18" r:id="R90429162607c404c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Offline_Desktop" sheetId="19" r:id="Rba909476dfb54961"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data_Model" sheetId="20" r:id="R9cc18d916a474f24"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Storage_Interop" sheetId="21" r:id="Rebe68b92e2b549e7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Security" sheetId="22" r:id="Rc79c6525c8c340b6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="API_Contracts" sheetId="23" r:id="R6341ec4148d64d45"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="State_Machines" sheetId="24" r:id="R881456e9a3274d26"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Error_Recovery" sheetId="25" r:id="R9dfbef0219984369"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cross_App_Relations" sheetId="26" r:id="Rc6447ef8be5a4990"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Performance" sheetId="27" r:id="R2b49d0cb3c054c3a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Accessibility" sheetId="28" r:id="R325eac3fa66c40de"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test_Matrix" sheetId="29" r:id="Ra5e8d5a1e2f04041"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="30" r:id="Re467a5d0d76146b3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open_Questions" sheetId="31" r:id="R8deddff23a0c48ce"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Change_Log" sheetId="32" r:id="R35c71c077b934f71"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Implementation_Status" sheetId="33" r:id="R6db5c7e968f84d32"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="Racd91053256f48cc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Product_Vision" sheetId="2" r:id="R8e9c8fea2dd646e2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decisions" sheetId="3" r:id="R634ea6e2e2f641ce"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Competitors" sheetId="4" r:id="Rf0c3eaadd4e94650"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open_Source" sheetId="5" r:id="R496ad40f87e34513"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source_Index" sheetId="6" r:id="Red6f2d6f26c44def"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Information_Architecture" sheetId="7" r:id="Rc2b84bf048ac4f37"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI_Layout" sheetId="8" r:id="R89650a7b4e814d11"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="User_Flows" sheetId="9" r:id="Rbc043f229ee54e07"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Note_Types" sheetId="10" r:id="Rbbb536fb7ec34f28"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Block_Catalog" sheetId="11" r:id="Rf143264fbe8b4038"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Slash_Commands" sheetId="12" r:id="Re4517b3f42774b9f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Context_Menus" sheetId="13" r:id="R6f94a76241634857"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Keyboard_Shortcuts" sheetId="14" r:id="R53e61f88f245410e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Database_Views" sheetId="15" r:id="Rfd402100117b4aef"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Code_Text_Mode" sheetId="16" r:id="R9a4aa569e9c84e46"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Python_Notebook" sheetId="17" r:id="Ra9a7747fd3874ea9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Collaboration" sheetId="18" r:id="R43d6875bb64749a0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Offline_Desktop" sheetId="19" r:id="R98c199a923bf4f88"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data_Model" sheetId="20" r:id="Rd4df7183b8e543de"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Storage_Interop" sheetId="21" r:id="Rdb9b9eee3e514c26"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Security" sheetId="22" r:id="R671f196ee8ed41d6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="API_Contracts" sheetId="23" r:id="Rad2446f9019548d9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="State_Machines" sheetId="24" r:id="R6bb234734cc0470c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Error_Recovery" sheetId="25" r:id="R163c5b1451d0428a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cross_App_Relations" sheetId="26" r:id="R3c80895c98524797"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Performance" sheetId="27" r:id="Rc1c5bbe7bbf346e6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Accessibility" sheetId="28" r:id="Ra75c4d9b0ae34c8a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test_Matrix" sheetId="29" r:id="R16bfe928e24a4e81"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="30" r:id="R3ca786b6ff4d48a4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open_Questions" sheetId="31" r:id="R5b9ae96f8ac44859"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Change_Log" sheetId="32" r:id="Rcfb608e4e2cf44ea"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Implementation_Status" sheetId="33" r:id="Rc76f35d67ba64155"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -928,7 +928,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Raab5f011352e4e99"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd45e380a148e4d87"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1271,7 +1271,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf9c89f07e4fe4d43"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R09f4f47ec9cf46e6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1674,7 +1674,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R56065700e1e34ba3"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R38a3fc71309c4ce9"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2197,7 +2197,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re6cc858f1ea9440e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R07a074aeb78640c1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2610,7 +2610,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9f335899326243bf"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rddef1568f52645d1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3550,7 +3550,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R873870421bc14baa"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R66ad8c44b4854811"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3810,7 +3810,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R814130ae42644ddd"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R94656843d280475c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4002,7 +4002,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8602c5fb13014289"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1382fea5d88e402f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4330,7 +4330,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7bdf98f055634a26"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8b236d27670d4229"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4590,7 +4590,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfb353dc2bcd04597"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R290577cb2d7d4f16"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4782,7 +4782,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Raadef8555c964b14"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbe03b296be9748d1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4915,7 +4915,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R72230173dd9e41ce"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2ee50f18acf148d1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5294,7 +5294,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Read912889f374208"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R19013ee8d7d74b84"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5554,7 +5554,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rca7609ba8d504b29"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R362e93d96d844986"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5899,7 +5899,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R11d3411be2564104"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R843da363bc514ef4"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6380,7 +6380,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9b9cfa9321f440ea"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R632530cdedb746d8"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6691,7 +6691,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfdded8a47d0d482d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3e17999a22ac4a15"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7002,7 +7002,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2501cc777bfc4360"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R35952fe919554ef1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7330,7 +7330,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R239b5198b6ba4e80"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc847452bf5b14018"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7590,7 +7590,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb245793a45c54a3c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3448ac70d2c548ab"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7751,7 +7751,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7a2725bf07f54381"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra747f4b216e342d6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8494,7 +8494,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4c3f671734b14463"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfaa0ca03051c46a3"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8890,7 +8890,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R362c80c632c5460b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Red6d308be47841c2"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9031,7 +9031,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2733c2128f834862"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R04c50903a05f4932"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9240,7 +9240,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rac8366b8b470420a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc00b007824494f34"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9483,7 +9483,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8a6e4bbc1cf84511"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd15c6baba52c47f3"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9834,7 +9834,7 @@
         <x:v>NOTE MANAGER·노트북·하위 페이지·4종 편집은 구현. slash는 중앙 Dialog이고 command registry·Tab/input rule·댓글·Office reference·Python kernel은 미구현.</x:v>
       </x:c>
       <x:c r="E17" s="13" t="str">
-        <x:v>local 전체 54 중 note 회귀 포함 52 pass·2 document skip; 로그인 운영 화면은 AI 중심 확인</x:v>
+        <x:v>local 52 pass·2 document skip; NAS 54/54·build/PDF.js·service/HTTP. 로그인 운영 화면은 AI 패널을 직접 확인했으며 Note 상호작용 E2E는 미실시.</x:v>
       </x:c>
       <x:c r="F17" s="13" t="str">
         <x:v>M1-D caret suggestion과 IME/Tab E2E→M1-G Office reference→cgroup 뒤 M2 Python 순서</x:v>
@@ -10049,7 +10049,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8cdc32d210c44e90"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re089f317f33d4d30"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10332,7 +10332,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6a4b8b4ca5654e20"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb2a002618d024bab"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10966,7 +10966,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb5bb22cce5b54855"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9825940208894b65"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11209,7 +11209,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R058e4236bf3c4e14"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R20d1eb9874ce4215"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11384,7 +11384,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6e01a93f329f4abb"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf564c7a416d546b0"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11644,7 +11644,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2ff9096eabac4135"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R664ebb0f74a24f60"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/programs/NAS_NOTE_STUDIO_SPEC.xlsx
+++ b/docs/programs/NAS_NOTE_STUDIO_SPEC.xlsx
@@ -2,39 +2,39 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="Racd91053256f48cc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Product_Vision" sheetId="2" r:id="R8e9c8fea2dd646e2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decisions" sheetId="3" r:id="R634ea6e2e2f641ce"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Competitors" sheetId="4" r:id="Rf0c3eaadd4e94650"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open_Source" sheetId="5" r:id="R496ad40f87e34513"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source_Index" sheetId="6" r:id="Red6f2d6f26c44def"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Information_Architecture" sheetId="7" r:id="Rc2b84bf048ac4f37"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI_Layout" sheetId="8" r:id="R89650a7b4e814d11"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="User_Flows" sheetId="9" r:id="Rbc043f229ee54e07"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Note_Types" sheetId="10" r:id="Rbbb536fb7ec34f28"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Block_Catalog" sheetId="11" r:id="Rf143264fbe8b4038"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Slash_Commands" sheetId="12" r:id="Re4517b3f42774b9f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Context_Menus" sheetId="13" r:id="R6f94a76241634857"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Keyboard_Shortcuts" sheetId="14" r:id="R53e61f88f245410e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Database_Views" sheetId="15" r:id="Rfd402100117b4aef"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Code_Text_Mode" sheetId="16" r:id="R9a4aa569e9c84e46"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Python_Notebook" sheetId="17" r:id="Ra9a7747fd3874ea9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Collaboration" sheetId="18" r:id="R43d6875bb64749a0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Offline_Desktop" sheetId="19" r:id="R98c199a923bf4f88"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data_Model" sheetId="20" r:id="Rd4df7183b8e543de"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Storage_Interop" sheetId="21" r:id="Rdb9b9eee3e514c26"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Security" sheetId="22" r:id="R671f196ee8ed41d6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="API_Contracts" sheetId="23" r:id="Rad2446f9019548d9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="State_Machines" sheetId="24" r:id="R6bb234734cc0470c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Error_Recovery" sheetId="25" r:id="R163c5b1451d0428a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cross_App_Relations" sheetId="26" r:id="R3c80895c98524797"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Performance" sheetId="27" r:id="Rc1c5bbe7bbf346e6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Accessibility" sheetId="28" r:id="Ra75c4d9b0ae34c8a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test_Matrix" sheetId="29" r:id="R16bfe928e24a4e81"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="30" r:id="R3ca786b6ff4d48a4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open_Questions" sheetId="31" r:id="R5b9ae96f8ac44859"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Change_Log" sheetId="32" r:id="Rcfb608e4e2cf44ea"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Implementation_Status" sheetId="33" r:id="Rc76f35d67ba64155"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="R56ea22755c48469c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Product_Vision" sheetId="2" r:id="R8848a568b3014c28"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decisions" sheetId="3" r:id="Ra716a47362204170"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Competitors" sheetId="4" r:id="R5f9de9c0aa794b97"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open_Source" sheetId="5" r:id="R70cd2baece2a4be0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source_Index" sheetId="6" r:id="Rf05d0c32f471487a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Information_Architecture" sheetId="7" r:id="Ra6b95606f1224c2f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI_Layout" sheetId="8" r:id="Ra281d55407f54265"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="User_Flows" sheetId="9" r:id="Rad3004acc82e4b82"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Note_Types" sheetId="10" r:id="Rc3a2fa3896984346"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Block_Catalog" sheetId="11" r:id="R0cb179f053e04fa2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Slash_Commands" sheetId="12" r:id="Raaf3ab850edf426c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Context_Menus" sheetId="13" r:id="R0a2abd2885934453"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Keyboard_Shortcuts" sheetId="14" r:id="Rb25483aaf1cf47f2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Database_Views" sheetId="15" r:id="Rf2bd889c708d4007"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Code_Text_Mode" sheetId="16" r:id="Re1957f2ff60d49d4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Python_Notebook" sheetId="17" r:id="R401bfec09b9148f3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Collaboration" sheetId="18" r:id="R7cdd69481af94466"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Offline_Desktop" sheetId="19" r:id="R158dc1a157de431d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data_Model" sheetId="20" r:id="Rb5e4e88a82074312"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Storage_Interop" sheetId="21" r:id="Refff424c71164040"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Security" sheetId="22" r:id="R4a6a105a4d17430f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="API_Contracts" sheetId="23" r:id="R23c02742066b457e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="State_Machines" sheetId="24" r:id="Rb47c30a9a6054973"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Error_Recovery" sheetId="25" r:id="R0fadf62f5f6e4a1f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cross_App_Relations" sheetId="26" r:id="R26efa02d91924d75"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Performance" sheetId="27" r:id="R191e5cc7dcc84358"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Accessibility" sheetId="28" r:id="R14491087bd234796"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test_Matrix" sheetId="29" r:id="Rdfcec31a67874ea8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="30" r:id="R7ab11b442d9d45b5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open_Questions" sheetId="31" r:id="R32c74d52ae164ee4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Change_Log" sheetId="32" r:id="Rcb936fe14a1c48a6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Implementation_Status" sheetId="33" r:id="R1b810322080b41af"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -928,7 +928,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd45e380a148e4d87"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7d820b60567840b8"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1271,7 +1271,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R09f4f47ec9cf46e6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf2c607e2cf9047b9"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1674,7 +1674,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R38a3fc71309c4ce9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Raeaedb09e1744132"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2197,7 +2197,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R07a074aeb78640c1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdb50d516c308458d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2610,7 +2610,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rddef1568f52645d1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1a0a5fb35fac4508"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3547,10 +3547,61 @@
         <x:v>P1</x:v>
       </x:c>
     </x:row>
+    <x:row r="55" ht="84" customHeight="1">
+      <x:c r="A55" s="13" t="str">
+        <x:v>Rich text</x:v>
+      </x:c>
+      <x:c r="B55" s="13" t="str">
+        <x:v>Tab</x:v>
+      </x:c>
+      <x:c r="C55" s="13" t="str">
+        <x:v>`1.`·`-`·`*`·`[ ]`·`[x]`·`#`·`##`·`###`·`&gt;`·`"`·triple-backtick·`---`·`===` 패턴 확정</x:v>
+      </x:c>
+      <x:c r="D55" s="13" t="str">
+        <x:v>일반 문장·조합 입력·빈 패턴은 들여쓰기/기본 동작을 보존</x:v>
+      </x:c>
+      <x:c r="E55" s="13" t="str">
+        <x:v>M1 구현</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="56" ht="84" customHeight="1">
+      <x:c r="A56" s="13" t="str">
+        <x:v>Rich text</x:v>
+      </x:c>
+      <x:c r="B56" s="13" t="str">
+        <x:v>/</x:v>
+      </x:c>
+      <x:c r="C56" s="13" t="str">
+        <x:v>caret 비모달 명령 목록: 제목·목록·할 일·인용·코드·구분선·하위 페이지·Office</x:v>
+      </x:c>
+      <x:c r="D56" s="13" t="str">
+        <x:v>방향키/Enter/Esc, 입력 조합 중 실행 금지, 현재 권한만 표시</x:v>
+      </x:c>
+      <x:c r="E56" s="13" t="str">
+        <x:v>M1 구현</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="57" ht="84" customHeight="1">
+      <x:c r="A57" s="13" t="str">
+        <x:v>Rich text</x:v>
+      </x:c>
+      <x:c r="B57" s="13" t="str">
+        <x:v>/page 또는 하위 페이지 명령</x:v>
+      </x:c>
+      <x:c r="C57" s="13" t="str">
+        <x:v>현재 caret에 실제 하위 페이지 링크 블록 생성</x:v>
+      </x:c>
+      <x:c r="D57" s="13" t="str">
+        <x:v>링크 삽입 실패 시 생성 페이지를 보상 취소</x:v>
+      </x:c>
+      <x:c r="E57" s="13" t="str">
+        <x:v>M1 구현</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R66ad8c44b4854811"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3bb8dda12b4d4c8f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3810,7 +3861,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R94656843d280475c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5cf1065d14664ebe"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4002,7 +4053,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1382fea5d88e402f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R868f993618e84706"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4330,7 +4381,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8b236d27670d4229"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd9578e2aaaaf46ad"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4590,7 +4641,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R290577cb2d7d4f16"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rea0d91d2651e46d3"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4782,7 +4833,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbe03b296be9748d1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb460591a4b234841"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4915,7 +4966,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2ee50f18acf148d1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R05a98656220f4936"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5294,7 +5345,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R19013ee8d7d74b84"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R95f2cbac9b0b4d0b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5554,7 +5605,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R362e93d96d844986"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re9135e5b2f614966"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5899,7 +5950,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R843da363bc514ef4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb87e1bb8edaa4d0a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6380,7 +6431,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R632530cdedb746d8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra6477df49fed4d7f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6691,7 +6742,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3e17999a22ac4a15"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0b4a49cdc8994fd5"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7002,7 +7053,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R35952fe919554ef1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcf80f48a27684ccc"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7330,7 +7381,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc847452bf5b14018"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8ca1097e1e494b21"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7590,7 +7641,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3448ac70d2c548ab"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2e33b1dd994b4755"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7751,7 +7802,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra747f4b216e342d6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra2e52200f33a442f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8494,7 +8545,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfaa0ca03051c46a3"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9d57c33798434be6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8890,7 +8941,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Red6d308be47841c2"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R193b5a5ffc234cd2"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9031,7 +9082,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R04c50903a05f4932"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1f4f3b4c2a36484e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9240,7 +9291,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc00b007824494f34"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf7241f05f0ff4aef"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9480,10 +9531,30 @@
         <x:v>Codex</x:v>
       </x:c>
     </x:row>
+    <x:row r="12" ht="112" customHeight="1">
+      <x:c r="A12" s="13" t="str">
+        <x:v>2026-09-07</x:v>
+      </x:c>
+      <x:c r="B12" s="13" t="str">
+        <x:v>1.1-safe-python-inline-references</x:v>
+      </x:c>
+      <x:c r="C12" s="13" t="str">
+        <x:v>운영 배포·교차 검증 완료</x:v>
+      </x:c>
+      <x:c r="D12" s="13" t="str">
+        <x:v>Tab 입력 규칙 확장, task list/H3/underline, caret /page 실제 하위 페이지 링크, Office 본문 링크, 이동 transaction·filesystem identity 복구, AI note tools, 제한 Python one-shot worker와 링크 실패 rollback을 추가했다.</x:v>
+      </x:c>
+      <x:c r="E12" s="13" t="str">
+        <x:v>NAS backend 67/67, Note command 5/5, production/PDF.js 4.8.69, live main.003d533b.js·HTTP 200·PM2 online·AI unauth 401, Chrome 운영 Note Studio shell. 실제 OpenAI 호출 0회.</x:v>
+      </x:c>
+      <x:c r="F12" s="13" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd15c6baba52c47f3"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb8ddbbf7834d4b4e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9640,24 +9711,24 @@
         <x:v>첨부 권한회수·이동/삭제 UX 보강</x:v>
       </x:c>
     </x:row>
-    <x:row r="8" ht="26.399999618530273" hidden="0" customHeight="1">
+    <x:row r="8" ht="104" hidden="0" customHeight="1">
       <x:c r="A8" s="20" t="str">
         <x:v>M1-D</x:v>
       </x:c>
       <x:c r="B8" s="20" t="str">
-        <x:v>계층 트리·slash/context menu</x:v>
+        <x:v>계층 트리·caret slash·context menu</x:v>
       </x:c>
       <x:c r="C8" s="20" t="str">
-        <x:v>운영 배포·자동 검증 완료 / 2차 slash·shortcut 연구 완료·구현 전</x:v>
+        <x:v>운영 배포·입력 회귀 완료</x:v>
       </x:c>
       <x:c r="D8" s="20" t="str">
-        <x:v>현재 parent tree·우클릭·/·Ctrl+K registry. 조사안은 caret suggestion dropdown, 상태별 Tab, explicit input-rule commit, ARIA·IME·async 계약</x:v>
+        <x:v>parent tree, 우클릭, caret 비모달 command registry, 방향키/Enter/Esc, Tab 확정 목록·할 일·제목·인용·코드·구분선, IME 조합 보호</x:v>
       </x:c>
       <x:c r="E8" s="20" t="str">
-        <x:v>기존 NAS 8/8·frontend 3/3·build·HTTP/service; 연구 문서 artifact-tool 검증</x:v>
+        <x:v>Note command 5/5, production build, Chrome Note Studio shell</x:v>
       </x:c>
       <x:c r="F8" s="20" t="str">
-        <x:v>별도 Dialog 제거와 Suggestion extension 구현 후 로그인 실화면 IME·DPI·키보드·포인터·screen reader E2E</x:v>
+        <x:v>남음: 한국어 IME·포인터·스크린리더를 새 Windows 장치에서 장시간 체감 E2E</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -9700,24 +9771,24 @@
         <x:v>운영 배포/API smoke 뒤 명시적 rename·move transaction, 비어 있지 않은 page 삭제 정책, marker/local projection, quota gate, 로그인 실화면 E2E; 외부 경로 소실 409 상태와 활성 하위 페이지 부모 삭제 차단 포함</x:v>
       </x:c>
     </x:row>
-    <x:row r="11">
+    <x:row r="11" ht="104" customHeight="1">
       <x:c r="A11" s="13" t="str">
         <x:v>M1-G</x:v>
       </x:c>
       <x:c r="B11" s="13" t="str">
-        <x:v>노트 본문 Office 생성·첫 저장·reference</x:v>
+        <x:v>본문 하위 페이지·Office 링크와 이동 복구</x:v>
       </x:c>
       <x:c r="C11" s="13" t="str">
-        <x:v>설계 확정·구현 전</x:v>
+        <x:v>운영 배포·NAS 회귀 완료</x:v>
       </x:c>
       <x:c r="D11" s="13" t="str">
-        <x:v>문서 스튜디오 재사용, invocation directory, stable document ID</x:v>
+        <x:v>noteLink/nasResourceLink atom block, noteId/attachmentId 참조, 플랫폼 이동 transaction, filesystem identity 복구, 삽입 실패 보상 취소</x:v>
       </x:c>
       <x:c r="E11" s="13" t="str">
-        <x:v>미실시</x:v>
+        <x:v>backend 67/67, frontend 5/5, production/PDF.js, live main.003d533b.js, Chrome Note Studio shell</x:v>
       </x:c>
       <x:c r="F11" s="13" t="str">
-        <x:v>공통 blank service 추출과 5개 형식 transaction/E2E</x:v>
+        <x:v>남음: cross-filesystem 복사+원본 삭제의 명시적 재연결 UI</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
@@ -9740,24 +9811,24 @@
         <x:v>Yjs/일반 revision 양쪽 anchor 이동 spike</x:v>
       </x:c>
     </x:row>
-    <x:row r="13">
+    <x:row r="13" ht="104" customHeight="1">
       <x:c r="A13" s="13" t="str">
         <x:v>M2-A</x:v>
       </x:c>
       <x:c r="B13" s="13" t="str">
-        <x:v>혼합 Python 실행 페이지·로컬 투영</x:v>
+        <x:v>Python 코드 노트 1회 실행</x:v>
       </x:c>
       <x:c r="C13" s="13" t="str">
-        <x:v>설계 확정·구현 전</x:v>
+        <x:v>1차 운영 배포·격리 회귀 완료</x:v>
       </x:c>
       <x:c r="D13" s="13" t="str">
-        <x:v>rich page + executable cells, PY+MD+manifest projection</x:v>
+        <x:v>non-root Docker, network none, read-only rootfs, CPU 0.5/RAM 256MiB/PID 64/15초/64KB, admission·cleanup, AI compute 재승인</x:v>
       </x:c>
       <x:c r="E13" s="13" t="str">
-        <x:v>미실시</x:v>
+        <x:v>NAS backend 67/67</x:v>
       </x:c>
       <x:c r="F13" s="13" t="str">
-        <x:v>nbformat/분리 파일 round-trip과 충돌 테스트</x:v>
+        <x:v>남음: persistent ipynb cells, kernel interrupt/restart, 제한 mount·package·MASTER GPU 권한</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
@@ -9780,24 +9851,24 @@
         <x:v>격리 worker·fair queue·부하/OOM/재감지 gate</x:v>
       </x:c>
     </x:row>
-    <x:row r="15">
+    <x:row r="15" ht="104" customHeight="1">
       <x:c r="A15" s="13" t="str">
         <x:v>M2-R</x:v>
       </x:c>
       <x:c r="B15" s="13" t="str">
-        <x:v>공통 자원 보호 선행 기반</x:v>
+        <x:v>공통 자원 보호·Python one-shot admission</x:v>
       </x:c>
       <x:c r="C15" s="13" t="str">
-        <x:v>정책·이력·문서 변환 admission 운영 배포·실장비/API 검증 완료</x:v>
+        <x:v>운영 배포·NAS 격리 회귀 완료</x:v>
       </x:c>
       <x:c r="D15" s="13" t="str">
-        <x:v>auto/manual 기준, 사용자별 storage와 관리 job 예약, 30초 이력, 관리자 UI</x:v>
+        <x:v>auto/manual 기준, 사용자별 storage·관리 job 예약, 30초 이력, 관리자 UI, Python non-root Docker CPU/RAM/PID/time/output/network 제한</x:v>
       </x:c>
       <x:c r="E15" s="13" t="str">
-        <x:v>local backend 44+2 skip/build; NAS Linux 46/46·build/PDF.js·API/HTTP/service</x:v>
+        <x:v>NAS backend 67/67·production/PDF.js·API/HTTP/service</x:v>
       </x:c>
       <x:c r="F15" s="13" t="str">
-        <x:v>남음: 로그인 관리자 화면 육안 E2E, Python·AI non-root cgroup worker 실제 계측</x:v>
+        <x:v>남음: 지속 kernel의 사용자별 장기 계측, fair queue, interrupt/restart, GPU capability</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
@@ -9820,7 +9891,7 @@
         <x:v>새 Windows CFAPI/선택/keyboard E2E, 완전 hydration marker 자동 알림</x:v>
       </x:c>
     </x:row>
-    <x:row r="17">
+    <x:row r="17" ht="104" customHeight="1">
       <x:c r="A17" s="13" t="str">
         <x:v>AUDIT-2026-09-06</x:v>
       </x:c>
@@ -9828,17 +9899,33 @@
         <x:v>Notion/Jupyter 실제 제품 대조</x:v>
       </x:c>
       <x:c r="C17" s="13" t="str">
-        <x:v>M1 물리 기반 완료 / 상호작용·실행 기능 부분·설계</x:v>
+        <x:v>핵심 M1·안전 Python 1차 완료 / 장기 제품 기능 보류</x:v>
       </x:c>
       <x:c r="D17" s="13" t="str">
-        <x:v>NOTE MANAGER·노트북·하위 페이지·4종 편집은 구현. slash는 중앙 Dialog이고 command registry·Tab/input rule·댓글·Office reference·Python kernel은 미구현.</x:v>
+        <x:v>Notion식 caret slash·트리·Tab 규칙·본문 page/document link와 안전 one-shot Python까지 구현. 댓글·협업·database·persistent kernel은 명시적 후속 단계다.</x:v>
       </x:c>
       <x:c r="E17" s="13" t="str">
-        <x:v>local 52 pass·2 document skip; NAS 54/54·build/PDF.js·service/HTTP. 로그인 운영 화면은 AI 패널을 직접 확인했으며 Note 상호작용 E2E는 미실시.</x:v>
+        <x:v>NAS 67/67, Note 5/5, production/PDF.js, live hash/HTTP/PM2/auth, Chrome 운영 shell</x:v>
       </x:c>
       <x:c r="F17" s="13" t="str">
-        <x:v>M1-D caret suggestion과 IME/Tab E2E→M1-G Office reference→cgroup 뒤 M2 Python 순서</x:v>
-      </x:c>
+        <x:v>댓글·멘션·drag·breadcrumb·rich media/database·Yjs offline, ipynb persistent kernel을 독립 milestone로 진행</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="84" customHeight="1">
+      <x:c r="A18" s="13" t="str"/>
+      <x:c r="B18" s="13" t="str"/>
+      <x:c r="C18" s="13" t="str"/>
+      <x:c r="D18" s="13" t="str"/>
+      <x:c r="E18" s="13" t="str"/>
+      <x:c r="F18" s="13" t="str"/>
+    </x:row>
+    <x:row r="19" ht="84" customHeight="1">
+      <x:c r="A19" s="13" t="str"/>
+      <x:c r="B19" s="13" t="str"/>
+      <x:c r="C19" s="13" t="str"/>
+      <x:c r="D19" s="13" t="str"/>
+      <x:c r="E19" s="13" t="str"/>
+      <x:c r="F19" s="13" t="str"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -10049,7 +10136,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re089f317f33d4d30"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R91070f7968a04386"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10332,7 +10419,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb2a002618d024bab"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1f8c8a667bd04a53"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10966,7 +11053,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9825940208894b65"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rab4c28a4f0a947f3"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11209,7 +11296,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R20d1eb9874ce4215"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9e9c7f94fa8c4dba"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11384,7 +11471,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf564c7a416d546b0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R681dadf157e64156"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11644,7 +11731,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R664ebb0f74a24f60"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9f8433bbf5e24f28"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/programs/NAS_NOTE_STUDIO_SPEC.xlsx
+++ b/docs/programs/NAS_NOTE_STUDIO_SPEC.xlsx
@@ -2,39 +2,39 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="R56ea22755c48469c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Product_Vision" sheetId="2" r:id="R8848a568b3014c28"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decisions" sheetId="3" r:id="Ra716a47362204170"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Competitors" sheetId="4" r:id="R5f9de9c0aa794b97"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open_Source" sheetId="5" r:id="R70cd2baece2a4be0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source_Index" sheetId="6" r:id="Rf05d0c32f471487a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Information_Architecture" sheetId="7" r:id="Ra6b95606f1224c2f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI_Layout" sheetId="8" r:id="Ra281d55407f54265"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="User_Flows" sheetId="9" r:id="Rad3004acc82e4b82"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Note_Types" sheetId="10" r:id="Rc3a2fa3896984346"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Block_Catalog" sheetId="11" r:id="R0cb179f053e04fa2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Slash_Commands" sheetId="12" r:id="Raaf3ab850edf426c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Context_Menus" sheetId="13" r:id="R0a2abd2885934453"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Keyboard_Shortcuts" sheetId="14" r:id="Rb25483aaf1cf47f2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Database_Views" sheetId="15" r:id="Rf2bd889c708d4007"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Code_Text_Mode" sheetId="16" r:id="Re1957f2ff60d49d4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Python_Notebook" sheetId="17" r:id="R401bfec09b9148f3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Collaboration" sheetId="18" r:id="R7cdd69481af94466"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Offline_Desktop" sheetId="19" r:id="R158dc1a157de431d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data_Model" sheetId="20" r:id="Rb5e4e88a82074312"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Storage_Interop" sheetId="21" r:id="Refff424c71164040"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Security" sheetId="22" r:id="R4a6a105a4d17430f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="API_Contracts" sheetId="23" r:id="R23c02742066b457e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="State_Machines" sheetId="24" r:id="Rb47c30a9a6054973"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Error_Recovery" sheetId="25" r:id="R0fadf62f5f6e4a1f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cross_App_Relations" sheetId="26" r:id="R26efa02d91924d75"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Performance" sheetId="27" r:id="R191e5cc7dcc84358"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Accessibility" sheetId="28" r:id="R14491087bd234796"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test_Matrix" sheetId="29" r:id="Rdfcec31a67874ea8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="30" r:id="R7ab11b442d9d45b5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open_Questions" sheetId="31" r:id="R32c74d52ae164ee4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Change_Log" sheetId="32" r:id="Rcb936fe14a1c48a6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Implementation_Status" sheetId="33" r:id="R1b810322080b41af"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="Rd64d72515eaa44f2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Product_Vision" sheetId="2" r:id="R4f2c4a79239f4603"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decisions" sheetId="3" r:id="R909bbd8b38c34f03"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Competitors" sheetId="4" r:id="R91ea7621ccf04631"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open_Source" sheetId="5" r:id="R60bf1b802f3343d8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source_Index" sheetId="6" r:id="R53fa5863a9854a45"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Information_Architecture" sheetId="7" r:id="R4f81b73a541a4610"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI_Layout" sheetId="8" r:id="Rf9ad5a54c104481a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="User_Flows" sheetId="9" r:id="R777879dd20a64822"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Note_Types" sheetId="10" r:id="R6345ba2436d34b8d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Block_Catalog" sheetId="11" r:id="Rf22884507de94d44"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Slash_Commands" sheetId="12" r:id="R7bc411c3452947da"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Context_Menus" sheetId="13" r:id="Rd11d8e0257ac453c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Keyboard_Shortcuts" sheetId="14" r:id="Rbcd35c2cdd714e0c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Database_Views" sheetId="15" r:id="R0311a6952dbf4326"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Code_Text_Mode" sheetId="16" r:id="Ree018b1c1a334757"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Python_Notebook" sheetId="17" r:id="R09426355c5844f84"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Collaboration" sheetId="18" r:id="R156996d64f3542d3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Offline_Desktop" sheetId="19" r:id="Rb1a60c483f184069"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data_Model" sheetId="20" r:id="Rce227a02b6054c60"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Storage_Interop" sheetId="21" r:id="R837b7c880fd64c17"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Security" sheetId="22" r:id="Rc59fdb8a4d174dee"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="API_Contracts" sheetId="23" r:id="Rea6de15df12a4b73"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="State_Machines" sheetId="24" r:id="Rbce2095e278948a1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Error_Recovery" sheetId="25" r:id="Rb9823a05f58e4bca"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cross_App_Relations" sheetId="26" r:id="R7204587595a74f26"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Performance" sheetId="27" r:id="R03a79100c1cd429d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Accessibility" sheetId="28" r:id="Rc89844441129462f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test_Matrix" sheetId="29" r:id="R8736835cd41d4980"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="30" r:id="Raeb3749028f14017"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open_Questions" sheetId="31" r:id="R11e43493d3b04a33"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Change_Log" sheetId="32" r:id="R8ee72ec983f64a46"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Implementation_Status" sheetId="33" r:id="R775533982c9344d4"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -928,7 +928,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7d820b60567840b8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf9f514157ac74932"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1271,7 +1271,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf2c607e2cf9047b9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1cce4aeb24344e4f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1674,7 +1674,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Raeaedb09e1744132"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R62c51b3ab5fe47a4"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2197,7 +2197,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdb50d516c308458d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R926bd9217c6145d3"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2610,7 +2610,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1a0a5fb35fac4508"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R625d679169e6400a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3601,7 +3601,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3bb8dda12b4d4c8f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R99303677c8384af0"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3861,7 +3861,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5cf1065d14664ebe"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R78300730c2dc48ea"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4053,7 +4053,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R868f993618e84706"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R01b5c3eb55bb474d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4381,7 +4381,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd9578e2aaaaf46ad"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re7d01946d1ea4ad9"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4641,7 +4641,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rea0d91d2651e46d3"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf3ca20ac40ed4a27"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4833,7 +4833,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb460591a4b234841"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4229b38e341d4d97"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4966,7 +4966,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R05a98656220f4936"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6c49368ba5864340"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5342,10 +5342,27 @@
         <x:v>매우 높음</x:v>
       </x:c>
     </x:row>
+    <x:row r="22" ht="76" hidden="0" customHeight="1">
+      <x:c r="A22" s="13" t="str">
+        <x:v>WorkspaceViewState</x:v>
+      </x:c>
+      <x:c r="B22" s="13" t="str">
+        <x:v>ownerKeyHash, resourceKey, kind, filesystemIdentity, devices, latest, state, contentRevision, updatedAt</x:v>
+      </x:c>
+      <x:c r="C22" s="13" t="str">
+        <x:v>본문·인증정보와 분리한 UI 위치만 저장하며 account/device/resource 상한과 금지 키 검사를 적용</x:v>
+      </x:c>
+      <x:c r="D22" s="13" t="str">
+        <x:v>account+resource+device</x:v>
+      </x:c>
+      <x:c r="E22" s="13" t="str">
+        <x:v>높음</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R95f2cbac9b0b4d0b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R15816751171d4b73"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5605,7 +5622,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re9135e5b2f614966"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0bf839be79574408"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5950,7 +5967,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb87e1bb8edaa4d0a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2e69add226864b5e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6431,7 +6448,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra6477df49fed4d7f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re989c7ed7c504429"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6739,10 +6756,27 @@
         <x:v>tombstone 및 broken link</x:v>
       </x:c>
     </x:row>
+    <x:row r="18" ht="66" hidden="0" customHeight="1">
+      <x:c r="A18" s="13" t="str">
+        <x:v>작업 위치</x:v>
+      </x:c>
+      <x:c r="B18" s="13" t="str">
+        <x:v>loading</x:v>
+      </x:c>
+      <x:c r="C18" s="13" t="str">
+        <x:v>노트 열기·계정 전환</x:v>
+      </x:c>
+      <x:c r="D18" s="13" t="str">
+        <x:v>restored, empty, aborted</x:v>
+      </x:c>
+      <x:c r="E18" s="13" t="str">
+        <x:v>복원 완료 전 발생한 selection/scroll 저장을 억제하고 이전 open sequence 응답은 폐기</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0b4a49cdc8994fd5"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4b7cdf1c40484fb9"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7050,10 +7084,27 @@
         <x:v>OS 인식+검증 뒤 새 한도 적용</x:v>
       </x:c>
     </x:row>
+    <x:row r="18" ht="76" hidden="0" customHeight="1">
+      <x:c r="A18" s="13" t="str">
+        <x:v>작업 위치 저장 네트워크 실패</x:v>
+      </x:c>
+      <x:c r="B18" s="13" t="str">
+        <x:v>최신 상태 하나만 coalesce하고 최대 4회 지수 백오프</x:v>
+      </x:c>
+      <x:c r="C18" s="13" t="str">
+        <x:v>계속 편집·다시 열기</x:v>
+      </x:c>
+      <x:c r="D18" s="13" t="str">
+        <x:v>본문 autosave와 메모리 내 최신 위치</x:v>
+      </x:c>
+      <x:c r="E18" s="13" t="str">
+        <x:v>다음 조작 또는 정상 응답에서 저장 재개</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcf80f48a27684ccc"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R09685cbc67c1473c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7378,10 +7429,27 @@
         <x:v>표시 지표와 실제 scheduler 판단 불일치</x:v>
       </x:c>
     </x:row>
+    <x:row r="19" ht="78" hidden="0" customHeight="1">
+      <x:c r="A19" s="13" t="str">
+        <x:v>WORKSPACE-RESUME-STATE</x:v>
+      </x:c>
+      <x:c r="B19" s="13" t="str">
+        <x:v>integrates</x:v>
+      </x:c>
+      <x:c r="C19" s="13" t="str">
+        <x:v>Note Studio 마지막 notebook/page와 block/Monaco 위치, 파일관리자·PDF·HWP·media 위치</x:v>
+      </x:c>
+      <x:c r="D19" s="13" t="str">
+        <x:v>내용 revision과 화면 위치 분리, same-device 우선과 account fallback</x:v>
+      </x:c>
+      <x:c r="E19" s="13" t="str">
+        <x:v>계정 전환·빠른 note 전환에서 stale 상태가 다른 사용자나 페이지에 적용됨</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8ca1097e1e494b21"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdc0e940c7e144403"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7641,7 +7709,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2e33b1dd994b4755"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R398333fafa5a4841"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7802,7 +7870,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra2e52200f33a442f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfaf30a82e9fd4afe"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8542,10 +8610,70 @@
         <x:v>M1-D 개선</x:v>
       </x:c>
     </x:row>
+    <x:row r="37" ht="72" hidden="0" customHeight="1">
+      <x:c r="A37" s="13" t="str">
+        <x:v>T-036</x:v>
+      </x:c>
+      <x:c r="B37" s="13" t="str">
+        <x:v>노트 위치 저장·복원</x:v>
+      </x:c>
+      <x:c r="C37" s="13" t="str">
+        <x:v>블록 selection/scroll, Markdown/TXT/code Monaco, 마지막 notebook/page를 저장 후 재접속</x:v>
+      </x:c>
+      <x:c r="D37" s="13" t="str">
+        <x:v>같은 장치는 정확한 위치, 새 장치는 계정 최신 위치, 본문 revision은 독립 유지</x:v>
+      </x:c>
+      <x:c r="E37" s="13" t="str">
+        <x:v>unit+integration+E2E</x:v>
+      </x:c>
+      <x:c r="F37" s="13" t="str">
+        <x:v>M1-I</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" ht="72" hidden="0" customHeight="1">
+      <x:c r="A38" s="13" t="str">
+        <x:v>T-037</x:v>
+      </x:c>
+      <x:c r="B38" s="13" t="str">
+        <x:v>빠른 노트 전환 경쟁 조건</x:v>
+      </x:c>
+      <x:c r="C38" s="13" t="str">
+        <x:v>A open 직후 B open, A view-state 응답이 나중 도착, 계정 전환 중 pending 저장</x:v>
+      </x:c>
+      <x:c r="D38" s="13" t="str">
+        <x:v>A 상태가 B 또는 다음 계정에 적용·저장되지 않음</x:v>
+      </x:c>
+      <x:c r="E38" s="13" t="str">
+        <x:v>unit+E2E</x:v>
+      </x:c>
+      <x:c r="F38" s="13" t="str">
+        <x:v>M1-I</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" ht="72" hidden="0" customHeight="1">
+      <x:c r="A39" s="13" t="str">
+        <x:v>T-038</x:v>
+      </x:c>
+      <x:c r="B39" s="13" t="str">
+        <x:v>위치 저장 장애 복구</x:v>
+      </x:c>
+      <x:c r="C39" s="13" t="str">
+        <x:v>연속 scroll/cursor burst, 401/404/500, 삭제 폴더, 파일 rename, 네트워크 복구</x:v>
+      </x:c>
+      <x:c r="D39" s="13" t="str">
+        <x:v>최신 상태 coalesce, 최대 4회 백오프, 삭제 경로 무시, 같은 파일 이동 identity 복원, 무한 요청 0</x:v>
+      </x:c>
+      <x:c r="E39" s="13" t="str">
+        <x:v>unit+integration+E2E</x:v>
+      </x:c>
+      <x:c r="F39" s="13" t="str">
+        <x:v>M1-I</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9d57c33798434be6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0c499998fed8453d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8938,10 +9066,27 @@
         <x:v>제품이 표준 Markdown과 다른 강한 구분선 block type을 정식 채택할 때</x:v>
       </x:c>
     </x:row>
+    <x:row r="23" ht="82" hidden="0" customHeight="1">
+      <x:c r="A23" s="13" t="str">
+        <x:v>DEC-022</x:v>
+      </x:c>
+      <x:c r="B23" s="13" t="str">
+        <x:v>채택</x:v>
+      </x:c>
+      <x:c r="C23" s="13" t="str">
+        <x:v>마지막 작업 위치는 내용 revision과 분리하고 같은 장치 기록을 우선하며 새 장치는 계정 최신 기록을 사용한다.</x:v>
+      </x:c>
+      <x:c r="D23" s="13" t="str">
+        <x:v>여러 PC의 서로 다른 화면 위치를 서로 덮지 않으면서 새 PC에서도 최근 문맥으로 복귀할 수 있다. 서버 인증 계정과 note 존재 여부를 다시 검증한다.</x:v>
+      </x:c>
+      <x:c r="E23" s="13" t="str">
+        <x:v>협업 편집에서 사용자별 selection 공유 정책이나 명시적 장치 동기화 옵션을 추가할 때</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R193b5a5ffc234cd2"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3c20ccc3f34d405a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9082,7 +9227,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1f4f3b4c2a36484e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re92b4905727f40d3"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9291,7 +9436,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf7241f05f0ff4aef"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9e5108bfcc23460d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9551,10 +9696,30 @@
         <x:v>Codex</x:v>
       </x:c>
     </x:row>
+    <x:row r="13" ht="105" hidden="0" customHeight="1">
+      <x:c r="A13" s="13" t="str">
+        <x:v>2026-09-07</x:v>
+      </x:c>
+      <x:c r="B13" s="13" t="str">
+        <x:v>1.2-workspace-resume-state</x:v>
+      </x:c>
+      <x:c r="C13" s="13" t="str">
+        <x:v>운영 배포·자동 회귀 완료 / 로그인 실파일 E2E 전</x:v>
+      </x:c>
+      <x:c r="D13" s="13" t="str">
+        <x:v>Note Studio 마지막 노트북·페이지와 block/Monaco 위치, 파일관리자 경로, PDF 페이지·확대율, HWP 모드·스크롤, 미디어 재생 위치를 계정·장치별 서버 원장으로 복원한다. 빠른 노트 전환 stale 응답과 계정 전환 pending 상태를 차단한다.</x:v>
+      </x:c>
+      <x:c r="E13" s="13" t="str">
+        <x:v>로컬 신규 3/3·backend 97 pass 3 skip·production/PDF.js, NAS backend 100 pass 1 skip, live main.d8b7c19a.js·내부/공개 200·PM2 online·무인증 API 401. 로그인 화면까지만 육안 확인.</x:v>
+      </x:c>
+      <x:c r="F13" s="13" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb8ddbbf7834d4b4e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6bd9f49dc02d430a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9911,13 +10076,25 @@
         <x:v>댓글·멘션·drag·breadcrumb·rich media/database·Yjs offline, ipynb persistent kernel을 독립 milestone로 진행</x:v>
       </x:c>
     </x:row>
-    <x:row r="18" ht="84" customHeight="1">
-      <x:c r="A18" s="13" t="str"/>
-      <x:c r="B18" s="13" t="str"/>
-      <x:c r="C18" s="13" t="str"/>
-      <x:c r="D18" s="13" t="str"/>
-      <x:c r="E18" s="13" t="str"/>
-      <x:c r="F18" s="13" t="str"/>
+    <x:row r="18" ht="105" hidden="0" customHeight="1">
+      <x:c r="A18" s="13" t="str">
+        <x:v>M1-I</x:v>
+      </x:c>
+      <x:c r="B18" s="13" t="str">
+        <x:v>자동 저장·마지막 작업 위치 복원</x:v>
+      </x:c>
+      <x:c r="C18" s="13" t="str">
+        <x:v>운영 배포·자동 회귀 완료 / 로그인 실파일 E2E 전</x:v>
+      </x:c>
+      <x:c r="D18" s="13" t="str">
+        <x:v>Note 마지막 notebook/page·block selection/scroll·Monaco view state, 파일관리자 경로, PDF page/offset/zoom, HWP mode/zoom/scroll, media time/volume/rate, 계정·장치·resource 서버 원장</x:v>
+      </x:c>
+      <x:c r="E18" s="13" t="str">
+        <x:v>로컬 신규 3/3·backend 97 pass 3 skip·production/PDF.js, NAS backend 100 pass 1 skip·main.d8b7c19a.js·HTTP/PM2/service/auth 401</x:v>
+      </x:c>
+      <x:c r="F18" s="13" t="str">
+        <x:v>남음: 로그인된 실제 문서별 재열기 육안 E2E. OnlyOffice 내부 cursor/page와 HWP 문자 cursor는 안정적 공개 adapter가 없어 현재 범위 밖</x:v>
+      </x:c>
     </x:row>
     <x:row r="19" ht="84" customHeight="1">
       <x:c r="A19" s="13" t="str"/>
@@ -9926,6 +10103,14 @@
       <x:c r="D19" s="13" t="str"/>
       <x:c r="E19" s="13" t="str"/>
       <x:c r="F19" s="13" t="str"/>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20"/>
+      <x:c r="B20"/>
+      <x:c r="C20"/>
+      <x:c r="D20"/>
+      <x:c r="E20"/>
+      <x:c r="F20"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -10136,7 +10321,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R91070f7968a04386"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0f7e3ea5f7a449d8"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10419,7 +10604,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1f8c8a667bd04a53"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9d2b8239b68043d2"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11053,7 +11238,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rab4c28a4f0a947f3"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8c360adc30674851"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11296,7 +11481,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9e9c7f94fa8c4dba"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R43ab4bd118a445aa"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11471,7 +11656,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R681dadf157e64156"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R37211ea8e5424290"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11731,7 +11916,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9f8433bbf5e24f28"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfa6fd32794314268"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/programs/NAS_NOTE_STUDIO_SPEC.xlsx
+++ b/docs/programs/NAS_NOTE_STUDIO_SPEC.xlsx
@@ -2,39 +2,39 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="Rd64d72515eaa44f2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Product_Vision" sheetId="2" r:id="R4f2c4a79239f4603"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decisions" sheetId="3" r:id="R909bbd8b38c34f03"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Competitors" sheetId="4" r:id="R91ea7621ccf04631"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open_Source" sheetId="5" r:id="R60bf1b802f3343d8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source_Index" sheetId="6" r:id="R53fa5863a9854a45"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Information_Architecture" sheetId="7" r:id="R4f81b73a541a4610"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI_Layout" sheetId="8" r:id="Rf9ad5a54c104481a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="User_Flows" sheetId="9" r:id="R777879dd20a64822"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Note_Types" sheetId="10" r:id="R6345ba2436d34b8d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Block_Catalog" sheetId="11" r:id="Rf22884507de94d44"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Slash_Commands" sheetId="12" r:id="R7bc411c3452947da"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Context_Menus" sheetId="13" r:id="Rd11d8e0257ac453c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Keyboard_Shortcuts" sheetId="14" r:id="Rbcd35c2cdd714e0c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Database_Views" sheetId="15" r:id="R0311a6952dbf4326"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Code_Text_Mode" sheetId="16" r:id="Ree018b1c1a334757"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Python_Notebook" sheetId="17" r:id="R09426355c5844f84"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Collaboration" sheetId="18" r:id="R156996d64f3542d3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Offline_Desktop" sheetId="19" r:id="Rb1a60c483f184069"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data_Model" sheetId="20" r:id="Rce227a02b6054c60"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Storage_Interop" sheetId="21" r:id="R837b7c880fd64c17"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Security" sheetId="22" r:id="Rc59fdb8a4d174dee"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="API_Contracts" sheetId="23" r:id="Rea6de15df12a4b73"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="State_Machines" sheetId="24" r:id="Rbce2095e278948a1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Error_Recovery" sheetId="25" r:id="Rb9823a05f58e4bca"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cross_App_Relations" sheetId="26" r:id="R7204587595a74f26"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Performance" sheetId="27" r:id="R03a79100c1cd429d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Accessibility" sheetId="28" r:id="Rc89844441129462f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test_Matrix" sheetId="29" r:id="R8736835cd41d4980"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="30" r:id="Raeb3749028f14017"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open_Questions" sheetId="31" r:id="R11e43493d3b04a33"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Change_Log" sheetId="32" r:id="R8ee72ec983f64a46"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Implementation_Status" sheetId="33" r:id="R775533982c9344d4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="R8f995613d6fd413e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Product_Vision" sheetId="2" r:id="R012346a69de544c9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decisions" sheetId="3" r:id="Rc6d7c63db8244d4c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Competitors" sheetId="4" r:id="R7d6fb90df6084fc3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open_Source" sheetId="5" r:id="Ra9195147f0054cbb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source_Index" sheetId="6" r:id="R50b011b95619416e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Information_Architecture" sheetId="7" r:id="Rfee75e39d1314700"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI_Layout" sheetId="8" r:id="R56214e9d861a4e16"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="User_Flows" sheetId="9" r:id="R1f83c08955ab4968"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Note_Types" sheetId="10" r:id="R8046741f52354e15"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Block_Catalog" sheetId="11" r:id="Rfbdab31aea724ff8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Slash_Commands" sheetId="12" r:id="R47e1c253ac9a4662"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Context_Menus" sheetId="13" r:id="R9dbdb693f55149c9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Keyboard_Shortcuts" sheetId="14" r:id="Rd62e4c149c034135"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Database_Views" sheetId="15" r:id="Rc9ba7f6c028a48b1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Code_Text_Mode" sheetId="16" r:id="Rd96cd4156a2643ec"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Python_Notebook" sheetId="17" r:id="R2755a9186adc424c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Collaboration" sheetId="18" r:id="R91ad521417794266"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Offline_Desktop" sheetId="19" r:id="R8218a416c84b4b4c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data_Model" sheetId="20" r:id="Rbbb78c60a99b4f32"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Storage_Interop" sheetId="21" r:id="R3fce965afe5f4245"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Security" sheetId="22" r:id="R939bc2c8bdb1407e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="API_Contracts" sheetId="23" r:id="R8a717a5bdc1643ec"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="State_Machines" sheetId="24" r:id="R7eaf7c9cb9a8427c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Error_Recovery" sheetId="25" r:id="Ra3e077714c0d4762"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cross_App_Relations" sheetId="26" r:id="R59c56c14edbd4e71"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Performance" sheetId="27" r:id="Rf949f7174d6247b8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Accessibility" sheetId="28" r:id="Ra0fd9e29928244cd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test_Matrix" sheetId="29" r:id="R47ef007bfbc84ef9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="30" r:id="Rbd0668f6c4ed404a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open_Questions" sheetId="31" r:id="Rd9e1b620db3546a0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Change_Log" sheetId="32" r:id="Re272fca6eaa54c6c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Implementation_Status" sheetId="33" r:id="R7a52051f14314d83"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -928,7 +928,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf9f514157ac74932"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6b105742070041fd"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1271,7 +1271,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1cce4aeb24344e4f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfdd76cf89ca24f11"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1674,7 +1674,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R62c51b3ab5fe47a4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra435465801fd43e5"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2197,7 +2197,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R926bd9217c6145d3"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R747fdc0732fb463c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2610,7 +2610,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R625d679169e6400a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R27b21389fd554c47"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3601,7 +3601,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R99303677c8384af0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R97b073ea82494840"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3861,7 +3861,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R78300730c2dc48ea"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf4bc210f6c8049a9"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4053,7 +4053,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R01b5c3eb55bb474d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5fb2c93353554671"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4378,10 +4378,27 @@
         <x:v>M2</x:v>
       </x:c>
     </x:row>
+    <x:row r="19">
+      <x:c r="A19" t="str">
+        <x:v>JavaScript one-shot</x:v>
+      </x:c>
+      <x:c r="B19" t="str">
+        <x:v>Node.js CommonJS 격리 실행</x:v>
+      </x:c>
+      <x:c r="C19" t="str">
+        <x:v>저장된 JavaScript 코드 페이지 전체를 매번 새 컨테이너에서 실행하고 stdout/stderr와 종료 상태를 반환한다.</x:v>
+      </x:c>
+      <x:c r="D19" t="str">
+        <x:v>network none·non-root·read-only·CPU/RAM/PID/time/code/output 제한. DOM, npm 설치, 지속 변수, NAS mount 없음.</x:v>
+      </x:c>
+      <x:c r="E19" t="str">
+        <x:v>M1-J</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re7d01946d1ea4ad9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5335d2887379409d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4641,7 +4658,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf3ca20ac40ed4a27"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0566edaf1901404d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4833,7 +4850,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4229b38e341d4d97"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcdb6aeaf0c8b4780"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4966,7 +4983,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6c49368ba5864340"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfdcc79e299ae40e7"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5362,7 +5379,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R15816751171d4b73"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R85e8dc272acf4255"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5622,7 +5639,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0bf839be79574408"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3fd3b1aba3a640ff"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5964,10 +5981,27 @@
         <x:v>P0</x:v>
       </x:c>
     </x:row>
+    <x:row r="20">
+      <x:c r="A20" t="str">
+        <x:v>SEC-19</x:v>
+      </x:c>
+      <x:c r="B20" t="str">
+        <x:v>JavaScript 실행이 호스트·NAS·외부망에 접근</x:v>
+      </x:c>
+      <x:c r="C20" t="str">
+        <x:v>Python과 같은 Docker sandbox, no mount/network, non-root, read-only, cap-drop, no-new-privileges, resource reservation과 종료 정리.</x:v>
+      </x:c>
+      <x:c r="D20" t="str">
+        <x:v>child_process·fs·환경변수·무한 루프·대량 출력·컨테이너 시작 실패·사용자 취소 경계</x:v>
+      </x:c>
+      <x:c r="E20" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2e69add226864b5e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb876e4c518004235"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6445,10 +6479,27 @@
         <x:v>backend/resourceControlService.js</x:v>
       </x:c>
     </x:row>
+    <x:row r="28">
+      <x:c r="A28" t="str">
+        <x:v>Code runtime</x:v>
+      </x:c>
+      <x:c r="B28" t="str">
+        <x:v>POST /api/note-studio/notes/:noteId/javascript/run</x:v>
+      </x:c>
+      <x:c r="C28" t="str">
+        <x:v>expectedRevision</x:v>
+      </x:c>
+      <x:c r="D28" t="str">
+        <x:v>stdout, stderr, exitCode, durationMs, sandbox 또는 category/errorType</x:v>
+      </x:c>
+      <x:c r="E28" t="str">
+        <x:v>로그인 계정 노트·code/javascript·revision·resource admission·격리 한도</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re989c7ed7c504429"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7e5cd99e1ea245e2"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6773,10 +6824,27 @@
         <x:v>복원 완료 전 발생한 selection/scroll 저장을 억제하고 이전 open sequence 응답은 폐기</x:v>
       </x:c>
     </x:row>
+    <x:row r="19">
+      <x:c r="A19" t="str">
+        <x:v>코드 실행</x:v>
+      </x:c>
+      <x:c r="B19" t="str">
+        <x:v>idle/running</x:v>
+      </x:c>
+      <x:c r="C19" t="str">
+        <x:v>저장 완료 후 실행 또는 AI 승인</x:v>
+      </x:c>
+      <x:c r="D19" t="str">
+        <x:v>succeeded, user_code_failed, blocked, infrastructure_failed</x:v>
+      </x:c>
+      <x:c r="E19" t="str">
+        <x:v>실행마다 새 컨테이너를 만들고 모든 종료 경로에서 자원 예약과 컨테이너를 해제한다.</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4b7cdf1c40484fb9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re80564b5735542b8"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7101,10 +7169,27 @@
         <x:v>다음 조작 또는 정상 응답에서 저장 재개</x:v>
       </x:c>
     </x:row>
+    <x:row r="19">
+      <x:c r="A19" t="str">
+        <x:v>Python·JavaScript 실행 실패</x:v>
+      </x:c>
+      <x:c r="B19" t="str">
+        <x:v>syntax/name/module/timeout/output/resource/infrastructure 분류</x:v>
+      </x:c>
+      <x:c r="C19" t="str">
+        <x:v>코드 수정·저장 후 재실행 또는 관리자 실행기 확인</x:v>
+      </x:c>
+      <x:c r="D19" t="str">
+        <x:v>노트 본문·revision·stdout/stderr</x:v>
+      </x:c>
+      <x:c r="E19" t="str">
+        <x:v>사용자 코드 오류를 서버 오프라인으로 표시하지 않고 실행 컨테이너와 reservation을 남기지 않는다.</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R09685cbc67c1473c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R496c1d52bcaf40ce"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7449,7 +7534,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdc0e940c7e144403"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra5dad28c5b414db6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7709,7 +7794,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R398333fafa5a4841"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rde8d03cc4f024149"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7870,7 +7955,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfaf30a82e9fd4afe"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc91f3e0bd5924dec"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8670,10 +8755,70 @@
         <x:v>M1-I</x:v>
       </x:c>
     </x:row>
+    <x:row r="40">
+      <x:c r="A40" t="str">
+        <x:v>T-039</x:v>
+      </x:c>
+      <x:c r="B40" t="str">
+        <x:v>JavaScript 격리 인자</x:v>
+      </x:c>
+      <x:c r="C40" t="str">
+        <x:v>network/rootfs/user/capability/CPU/RAM/PID와 Node stdin 인자</x:v>
+      </x:c>
+      <x:c r="D40" t="str">
+        <x:v>Python과 동등한 제한과 CommonJS one-shot 실행</x:v>
+      </x:c>
+      <x:c r="E40" t="str">
+        <x:v>unit+NAS integration</x:v>
+      </x:c>
+      <x:c r="F40" t="str">
+        <x:v>M1-J</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41">
+      <x:c r="A41" t="str">
+        <x:v>T-040</x:v>
+      </x:c>
+      <x:c r="B41" t="str">
+        <x:v>코드 오류 분류</x:v>
+      </x:c>
+      <x:c r="C41" t="str">
+        <x:v>SyntaxError, NameError/ReferenceError, missing module, timeout, output limit, worker unavailable</x:v>
+      </x:c>
+      <x:c r="D41" t="str">
+        <x:v>사용자 코드·자원·인프라 원인을 분리하고 올바른 출력 함수를 안내</x:v>
+      </x:c>
+      <x:c r="E41" t="str">
+        <x:v>unit+API</x:v>
+      </x:c>
+      <x:c r="F41" t="str">
+        <x:v>M1-J</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42">
+      <x:c r="A42" t="str">
+        <x:v>T-041</x:v>
+      </x:c>
+      <x:c r="B42" t="str">
+        <x:v>AI JavaScript 실행 승인</x:v>
+      </x:c>
+      <x:c r="C42" t="str">
+        <x:v>한국어/영어/JS 축약 intent, auto_all, revision mismatch</x:v>
+      </x:c>
+      <x:c r="D42" t="str">
+        <x:v>run_javascript_note만 선택하고 compute 별도 승인 뒤 정확한 API 호출</x:v>
+      </x:c>
+      <x:c r="E42" t="str">
+        <x:v>unit+integration</x:v>
+      </x:c>
+      <x:c r="F42" t="str">
+        <x:v>M1-J</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0c499998fed8453d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdd5c64727d9b49ba"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9086,7 +9231,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3c20ccc3f34d405a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb6cad3485dc9451b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9227,7 +9372,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re92b4905727f40d3"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0fa12cdfff414d6b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9436,7 +9581,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9e5108bfcc23460d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1a878379d902460a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9716,10 +9861,30 @@
         <x:v>Codex</x:v>
       </x:c>
     </x:row>
+    <x:row r="14">
+      <x:c r="A14" t="str">
+        <x:v>2026-09-07</x:v>
+      </x:c>
+      <x:c r="B14" t="str">
+        <x:v>1.3-javascript-one-shot</x:v>
+      </x:c>
+      <x:c r="C14" t="str">
+        <x:v>구현 완료 / NAS 실장비 검증 중</x:v>
+      </x:c>
+      <x:c r="D14" t="str">
+        <x:v>Python 실행 오류를 원인별로 분류하고 JavaScript 코드 페이지의 Node.js 격리 실행·UI·AI 승인 도구를 추가했다.</x:v>
+      </x:c>
+      <x:c r="E14" t="str">
+        <x:v>로컬 관련 23/23, backend 102 pass·5 skip·0 fail, production/PDF.js gate. NAS 실제 Python/JavaScript 실행 예정.</x:v>
+      </x:c>
+      <x:c r="F14" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6bd9f49dc02d430a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbc03877150d241bc"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10097,12 +10262,24 @@
       </x:c>
     </x:row>
     <x:row r="19" ht="84" customHeight="1">
-      <x:c r="A19" s="13" t="str"/>
-      <x:c r="B19" s="13" t="str"/>
-      <x:c r="C19" s="13" t="str"/>
-      <x:c r="D19" s="13" t="str"/>
-      <x:c r="E19" s="13" t="str"/>
-      <x:c r="F19" s="13" t="str"/>
+      <x:c r="A19" s="13" t="str">
+        <x:v>M1-J</x:v>
+      </x:c>
+      <x:c r="B19" s="13" t="str">
+        <x:v>JavaScript 코드 노트 일회성 실행</x:v>
+      </x:c>
+      <x:c r="C19" s="13" t="str">
+        <x:v>구현 완료 / NAS 실장비 검증 중</x:v>
+      </x:c>
+      <x:c r="D19" s="13" t="str">
+        <x:v>Node.js CommonJS, 언어별 UI, 오류 분류, Python과 동일한 격리·resource admission, AI compute 승인</x:v>
+      </x:c>
+      <x:c r="E19" s="13" t="str">
+        <x:v>로컬 관련 23/23·backend 102 pass 5 skip·production/PDF.js</x:v>
+      </x:c>
+      <x:c r="F19" s="13" t="str">
+        <x:v>남음: NAS 실제 두 런타임·전체 회귀·서비스/API·로그인 실화면 확인</x:v>
+      </x:c>
     </x:row>
     <x:row r="20">
       <x:c r="A20"/>
@@ -10321,7 +10498,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0f7e3ea5f7a449d8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R327ccb6b3ddb4ebd"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10604,7 +10781,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9d2b8239b68043d2"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R338051c9e7b74359"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11238,7 +11415,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8c360adc30674851"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rca1a5eff033a4215"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11481,7 +11658,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R43ab4bd118a445aa"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0a72f957f5514bb9"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11656,7 +11833,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R37211ea8e5424290"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R41aa959a427243a9"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11916,7 +12093,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfa6fd32794314268"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3984b24f69c84b99"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/programs/NAS_NOTE_STUDIO_SPEC.xlsx
+++ b/docs/programs/NAS_NOTE_STUDIO_SPEC.xlsx
@@ -2,39 +2,39 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="R8f995613d6fd413e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Product_Vision" sheetId="2" r:id="R012346a69de544c9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decisions" sheetId="3" r:id="Rc6d7c63db8244d4c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Competitors" sheetId="4" r:id="R7d6fb90df6084fc3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open_Source" sheetId="5" r:id="Ra9195147f0054cbb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source_Index" sheetId="6" r:id="R50b011b95619416e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Information_Architecture" sheetId="7" r:id="Rfee75e39d1314700"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI_Layout" sheetId="8" r:id="R56214e9d861a4e16"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="User_Flows" sheetId="9" r:id="R1f83c08955ab4968"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Note_Types" sheetId="10" r:id="R8046741f52354e15"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Block_Catalog" sheetId="11" r:id="Rfbdab31aea724ff8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Slash_Commands" sheetId="12" r:id="R47e1c253ac9a4662"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Context_Menus" sheetId="13" r:id="R9dbdb693f55149c9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Keyboard_Shortcuts" sheetId="14" r:id="Rd62e4c149c034135"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Database_Views" sheetId="15" r:id="Rc9ba7f6c028a48b1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Code_Text_Mode" sheetId="16" r:id="Rd96cd4156a2643ec"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Python_Notebook" sheetId="17" r:id="R2755a9186adc424c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Collaboration" sheetId="18" r:id="R91ad521417794266"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Offline_Desktop" sheetId="19" r:id="R8218a416c84b4b4c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data_Model" sheetId="20" r:id="Rbbb78c60a99b4f32"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Storage_Interop" sheetId="21" r:id="R3fce965afe5f4245"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Security" sheetId="22" r:id="R939bc2c8bdb1407e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="API_Contracts" sheetId="23" r:id="R8a717a5bdc1643ec"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="State_Machines" sheetId="24" r:id="R7eaf7c9cb9a8427c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Error_Recovery" sheetId="25" r:id="Ra3e077714c0d4762"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cross_App_Relations" sheetId="26" r:id="R59c56c14edbd4e71"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Performance" sheetId="27" r:id="Rf949f7174d6247b8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Accessibility" sheetId="28" r:id="Ra0fd9e29928244cd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test_Matrix" sheetId="29" r:id="R47ef007bfbc84ef9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="30" r:id="Rbd0668f6c4ed404a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open_Questions" sheetId="31" r:id="Rd9e1b620db3546a0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Change_Log" sheetId="32" r:id="Re272fca6eaa54c6c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Implementation_Status" sheetId="33" r:id="R7a52051f14314d83"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="R95c35a3687c54796"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Product_Vision" sheetId="2" r:id="Rd2a9ea76433b47b6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decisions" sheetId="3" r:id="R269183ebcdb84803"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Competitors" sheetId="4" r:id="R4e8c8e0715564c60"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open_Source" sheetId="5" r:id="Rf4b2b7d6266a4c86"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source_Index" sheetId="6" r:id="R6acf07a82c7c400b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Information_Architecture" sheetId="7" r:id="R818c3fb623f14d09"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI_Layout" sheetId="8" r:id="R330e9f1254e441a4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="User_Flows" sheetId="9" r:id="R65c2b61b50bd431b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Note_Types" sheetId="10" r:id="R193e5fa8f1c042da"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Block_Catalog" sheetId="11" r:id="Rba8849754b7445dc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Slash_Commands" sheetId="12" r:id="Rfa13fa61e0574d83"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Context_Menus" sheetId="13" r:id="R7c36ae525afe4781"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Keyboard_Shortcuts" sheetId="14" r:id="Raff9e72191f648bb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Database_Views" sheetId="15" r:id="Rc35080ab3c4644d4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Code_Text_Mode" sheetId="16" r:id="Rfd0bf0307a054cc0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Python_Notebook" sheetId="17" r:id="Rb44d0a3ce1c14f2e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Collaboration" sheetId="18" r:id="R5f119bc220b741d6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Offline_Desktop" sheetId="19" r:id="R9acd770997254e9b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data_Model" sheetId="20" r:id="R1feead2ae29940e6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Storage_Interop" sheetId="21" r:id="Ra3faa87076774355"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Security" sheetId="22" r:id="R6a2cdc642aa54a95"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="API_Contracts" sheetId="23" r:id="Rf99fcdac881c4f68"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="State_Machines" sheetId="24" r:id="Ra80110e3fa3546c8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Error_Recovery" sheetId="25" r:id="R2e7c929c6f8b415f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cross_App_Relations" sheetId="26" r:id="R7fa7132c93f843f2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Performance" sheetId="27" r:id="R62832ff4476b49b2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Accessibility" sheetId="28" r:id="R36cc0288a9544c2f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test_Matrix" sheetId="29" r:id="R3be87d53ab9546ff"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="30" r:id="R84a0db62baa44033"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open_Questions" sheetId="31" r:id="R0a908b0ebc4b4f6a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Change_Log" sheetId="32" r:id="Rabd381ecf1cd4e9a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Implementation_Status" sheetId="33" r:id="R5da7c98cbc4a41f1"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -928,7 +928,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6b105742070041fd"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R048a0964549243cb"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1271,7 +1271,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfdd76cf89ca24f11"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb54b753ce44748de"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1674,7 +1674,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra435465801fd43e5"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3325b6d650124db4"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2197,7 +2197,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R747fdc0732fb463c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re4c07ac04db04048"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2610,7 +2610,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R27b21389fd554c47"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R06b5ccf111914f6d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3601,7 +3601,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R97b073ea82494840"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re4e328e8d5c246ff"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3861,7 +3861,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf4bc210f6c8049a9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8fc488c2b68f4a9a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4053,7 +4053,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5fb2c93353554671"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb963fa4330684b99"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4398,7 +4398,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5335d2887379409d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Redb348a963a44a33"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4658,7 +4658,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0566edaf1901404d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9ce88d52643241b1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4850,7 +4850,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcdb6aeaf0c8b4780"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R725912075e604434"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4983,7 +4983,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfdcc79e299ae40e7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R80a0fef7b4824968"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5379,7 +5379,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R85e8dc272acf4255"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0ec1785492b74ccf"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5639,7 +5639,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3fd3b1aba3a640ff"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re39856f0e7154091"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6001,7 +6001,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb876e4c518004235"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re3122d79351542cc"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6499,7 +6499,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7e5cd99e1ea245e2"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd0d4ee6ec6354270"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6844,7 +6844,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re80564b5735542b8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rda38c2a2600647f7"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7189,7 +7189,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R496c1d52bcaf40ce"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R67dddde363e94672"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7534,7 +7534,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra5dad28c5b414db6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdad480e03e734a10"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7794,7 +7794,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rde8d03cc4f024149"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7e934ecd7323472f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7955,7 +7955,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc91f3e0bd5924dec"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re519d46aedcd46f5"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8818,7 +8818,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdd5c64727d9b49ba"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3238133cacf844a4"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9231,7 +9231,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb6cad3485dc9451b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc1924847a89242a1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9372,7 +9372,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0fa12cdfff414d6b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R63e89de0c8594781"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9581,7 +9581,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1a878379d902460a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R355674b7805640cf"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9869,13 +9869,13 @@
         <x:v>1.3-javascript-one-shot</x:v>
       </x:c>
       <x:c r="C14" t="str">
-        <x:v>구현 완료 / NAS 실장비 검증 중</x:v>
+        <x:v>운영 배포·자동 회귀 완료 / 로그인 실화면 E2E 전</x:v>
       </x:c>
       <x:c r="D14" t="str">
         <x:v>Python 실행 오류를 원인별로 분류하고 JavaScript 코드 페이지의 Node.js 격리 실행·UI·AI 승인 도구를 추가했다.</x:v>
       </x:c>
       <x:c r="E14" t="str">
-        <x:v>로컬 관련 23/23, backend 102 pass·5 skip·0 fail, production/PDF.js gate. NAS 실제 Python/JavaScript 실행 예정.</x:v>
+        <x:v>로컬 backend 102 pass 5 skip·production/PDF.js. NAS backend 104 pass 3 skip·0 fail, 실제 Python/JavaScript 2/2, live bundle·HTTP·PM2·services·unauth 401 통과.</x:v>
       </x:c>
       <x:c r="F14" t="str">
         <x:v>Codex</x:v>
@@ -9884,7 +9884,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbc03877150d241bc"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R63699b8b6348439b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10269,16 +10269,16 @@
         <x:v>JavaScript 코드 노트 일회성 실행</x:v>
       </x:c>
       <x:c r="C19" s="13" t="str">
-        <x:v>구현 완료 / NAS 실장비 검증 중</x:v>
+        <x:v>완료·운영 배포 / 로그인 실화면 E2E 전</x:v>
       </x:c>
       <x:c r="D19" s="13" t="str">
         <x:v>Node.js CommonJS, 언어별 UI, 오류 분류, Python과 동일한 격리·resource admission, AI compute 승인</x:v>
       </x:c>
       <x:c r="E19" s="13" t="str">
-        <x:v>로컬 관련 23/23·backend 102 pass 5 skip·production/PDF.js</x:v>
+        <x:v>로컬 backend 102 pass 5 skip·production/PDF.js, NAS backend 104 pass 3 skip·실제 Python/JavaScript 2/2·live bundle·HTTP/PM2/service/auth</x:v>
       </x:c>
       <x:c r="F19" s="13" t="str">
-        <x:v>남음: NAS 실제 두 런타임·전체 회귀·서비스/API·로그인 실화면 확인</x:v>
+        <x:v>남음: 로그인된 실제 JavaScript 코드 페이지 버튼·오류 문구 육안 확인. 지속 kernel/npm/network/NAS mount는 의도적 제외.</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
@@ -10498,7 +10498,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R327ccb6b3ddb4ebd"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0ee9eb48513b46b9"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10781,7 +10781,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R338051c9e7b74359"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf1879153ab694593"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11415,7 +11415,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rca1a5eff033a4215"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re4da6ca2af3f41dc"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11658,7 +11658,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0a72f957f5514bb9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3e607768ef3e47fc"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11833,7 +11833,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R41aa959a427243a9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfc55fa26b2f84504"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12093,7 +12093,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3984b24f69c84b99"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R238a2df0e1c743b9"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/programs/NAS_NOTE_STUDIO_SPEC.xlsx
+++ b/docs/programs/NAS_NOTE_STUDIO_SPEC.xlsx
@@ -2,39 +2,39 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="R95c35a3687c54796"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Product_Vision" sheetId="2" r:id="Rd2a9ea76433b47b6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decisions" sheetId="3" r:id="R269183ebcdb84803"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Competitors" sheetId="4" r:id="R4e8c8e0715564c60"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open_Source" sheetId="5" r:id="Rf4b2b7d6266a4c86"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source_Index" sheetId="6" r:id="R6acf07a82c7c400b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Information_Architecture" sheetId="7" r:id="R818c3fb623f14d09"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI_Layout" sheetId="8" r:id="R330e9f1254e441a4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="User_Flows" sheetId="9" r:id="R65c2b61b50bd431b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Note_Types" sheetId="10" r:id="R193e5fa8f1c042da"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Block_Catalog" sheetId="11" r:id="Rba8849754b7445dc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Slash_Commands" sheetId="12" r:id="Rfa13fa61e0574d83"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Context_Menus" sheetId="13" r:id="R7c36ae525afe4781"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Keyboard_Shortcuts" sheetId="14" r:id="Raff9e72191f648bb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Database_Views" sheetId="15" r:id="Rc35080ab3c4644d4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Code_Text_Mode" sheetId="16" r:id="Rfd0bf0307a054cc0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Python_Notebook" sheetId="17" r:id="Rb44d0a3ce1c14f2e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Collaboration" sheetId="18" r:id="R5f119bc220b741d6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Offline_Desktop" sheetId="19" r:id="R9acd770997254e9b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data_Model" sheetId="20" r:id="R1feead2ae29940e6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Storage_Interop" sheetId="21" r:id="Ra3faa87076774355"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Security" sheetId="22" r:id="R6a2cdc642aa54a95"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="API_Contracts" sheetId="23" r:id="Rf99fcdac881c4f68"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="State_Machines" sheetId="24" r:id="Ra80110e3fa3546c8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Error_Recovery" sheetId="25" r:id="R2e7c929c6f8b415f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cross_App_Relations" sheetId="26" r:id="R7fa7132c93f843f2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Performance" sheetId="27" r:id="R62832ff4476b49b2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Accessibility" sheetId="28" r:id="R36cc0288a9544c2f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test_Matrix" sheetId="29" r:id="R3be87d53ab9546ff"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="30" r:id="R84a0db62baa44033"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open_Questions" sheetId="31" r:id="R0a908b0ebc4b4f6a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Change_Log" sheetId="32" r:id="Rabd381ecf1cd4e9a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Implementation_Status" sheetId="33" r:id="R5da7c98cbc4a41f1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="R6336cc7f451d4366"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Product_Vision" sheetId="2" r:id="R97b48d791d3e4cee"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decisions" sheetId="3" r:id="Re4a9c301a68d452a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Competitors" sheetId="4" r:id="R250c810c790f4eb7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open_Source" sheetId="5" r:id="R4b115a26ecb64033"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source_Index" sheetId="6" r:id="R120604a4194c4726"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Information_Architecture" sheetId="7" r:id="Rbf70fc1668094391"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI_Layout" sheetId="8" r:id="R6870933085154bcc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="User_Flows" sheetId="9" r:id="R0986b7183d4b498e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Note_Types" sheetId="10" r:id="R58ffed60fe7a4700"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Block_Catalog" sheetId="11" r:id="R71d4d15b16fa4bba"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Slash_Commands" sheetId="12" r:id="R29beebd604f0425a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Context_Menus" sheetId="13" r:id="R41af4124b90649e9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Keyboard_Shortcuts" sheetId="14" r:id="Raf1c3e7d242e41c1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Database_Views" sheetId="15" r:id="R560b14b749b549d4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Code_Text_Mode" sheetId="16" r:id="Rbdd8626b05e549a4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Python_Notebook" sheetId="17" r:id="Rb983d9eeb7d44f2d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Collaboration" sheetId="18" r:id="R556b053cc60f47b3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Offline_Desktop" sheetId="19" r:id="Rb95a4cf459e24681"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data_Model" sheetId="20" r:id="Rdbba29fee9094bcd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Storage_Interop" sheetId="21" r:id="R1e58b9bd4f6145c6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Security" sheetId="22" r:id="Rcf54efcef7bc4836"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="API_Contracts" sheetId="23" r:id="Ra0cc3f2f060e4511"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="State_Machines" sheetId="24" r:id="R972028eaf91143bf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Error_Recovery" sheetId="25" r:id="R12f67d47b47449c7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cross_App_Relations" sheetId="26" r:id="R163e9b7644204d1a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Performance" sheetId="27" r:id="R9b65425e147a46fe"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Accessibility" sheetId="28" r:id="Rd95d4631845f4f8b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test_Matrix" sheetId="29" r:id="Rf4069f638dc94781"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="30" r:id="R852e6d2a03874364"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open_Questions" sheetId="31" r:id="R5aea2c55713345a9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Change_Log" sheetId="32" r:id="R3f8535295f8648d5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Implementation_Status" sheetId="33" r:id="R527968aff02c4d8f"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -928,7 +928,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R048a0964549243cb"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R06696c67c5744d69"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1271,7 +1271,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb54b753ce44748de"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1920415f08654bce"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1674,7 +1674,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3325b6d650124db4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf5fad75b7d134d05"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2197,7 +2197,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re4c07ac04db04048"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R26f9d50e30a145d3"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2610,7 +2610,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R06b5ccf111914f6d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd12f4f588faa4c86"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3601,7 +3601,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re4e328e8d5c246ff"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2ae5148d1aa545e3"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3861,7 +3861,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8fc488c2b68f4a9a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re352f4f6416849d8"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4053,7 +4053,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb963fa4330684b99"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R89d2cf54d0d54d8d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4395,10 +4395,44 @@
         <x:v>M1-J</x:v>
       </x:c>
     </x:row>
+    <x:row r="20">
+      <x:c r="A20" t="str">
+        <x:v>기본 패키지 런타임</x:v>
+      </x:c>
+      <x:c r="B20" t="str">
+        <x:v>Python 3.12 + curated 25</x:v>
+      </x:c>
+      <x:c r="C20" t="str">
+        <x:v>numpy/pandas/scipy/sympy/sklearn/statsmodels, matplotlib/seaborn/plotly, Pillow/Office/PDF, HTTP·파싱·유틸리티를 바로 import한다.</x:v>
+      </x:c>
+      <x:c r="D20" t="str">
+        <x:v>고정 이미지, network none, non-root, read-only, 512MiB, CPU 0.75, PID 64, 15초. 대형 ML/GPU 제외.</x:v>
+      </x:c>
+      <x:c r="E20" t="str">
+        <x:v>M1-K</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21">
+      <x:c r="A21" t="str">
+        <x:v>외부 패키지 환경</x:v>
+      </x:c>
+      <x:c r="B21" t="str">
+        <x:v>노트북별 immutable revision</x:v>
+      </x:c>
+      <x:c r="C21" t="str">
+        <x:v>정규 PyPI 이름과 정확 버전을 별도 builder에서 wheel/hash/CVE 검사 후 lock hash 이미지로 활성화한다.</x:v>
+      </x:c>
+      <x:c r="D21" t="str">
+        <x:v>현재 설계만 완료. 실행 중 pip·URL·Git·local path·private index를 허용하지 않으며 실패 시 기존 revision을 유지한다.</x:v>
+      </x:c>
+      <x:c r="E21" t="str">
+        <x:v>M2-PKG</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Redb348a963a44a33"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb3b725b3518b49dc"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4658,7 +4692,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9ce88d52643241b1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re2815ffa76714c56"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4850,7 +4884,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R725912075e604434"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb8ebe2a82b11424d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4983,7 +5017,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R80a0fef7b4824968"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9ed3cc585dba4c3f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5379,7 +5413,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0ec1785492b74ccf"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R89c4023a97924b86"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5639,7 +5673,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re39856f0e7154091"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf8b6db6d94da4385"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5998,10 +6032,27 @@
         <x:v>P0</x:v>
       </x:c>
     </x:row>
+    <x:row r="21">
+      <x:c r="A21" t="str">
+        <x:v>SEC-20</x:v>
+      </x:c>
+      <x:c r="B21" t="str">
+        <x:v>외부 Python 패키지 공급망·계정 간 환경 오염</x:v>
+      </x:c>
+      <x:c r="C21" t="str">
+        <x:v>builder와 runtime을 분리하고 wheel only, exact version, transitive lock, SHA-256, 취약점·금지 목록, 불변 lock-hash 이미지, quota와 rollback을 강제한다.</x:v>
+      </x:c>
+      <x:c r="D21" t="str">
+        <x:v>typosquatting·dependency confusion·악성 build script·zip bomb·disk exhaustion·cache ACL·실행기 network 회귀</x:v>
+      </x:c>
+      <x:c r="E21" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re3122d79351542cc"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rda0eb543858a4a67"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6496,10 +6547,27 @@
         <x:v>로그인 계정 노트·code/javascript·revision·resource admission·격리 한도</x:v>
       </x:c>
     </x:row>
+    <x:row r="29">
+      <x:c r="A29" t="str">
+        <x:v>Python runtime</x:v>
+      </x:c>
+      <x:c r="B29" t="str">
+        <x:v>GET /api/note-studio/python/runtime</x:v>
+      </x:c>
+      <x:c r="C29" t="str">
+        <x:v>로그인 세션</x:v>
+      </x:c>
+      <x:c r="D29" t="str">
+        <x:v>runtimeVersion, pythonVersion, packageCount, packages, execution, externalPackages</x:v>
+      </x:c>
+      <x:c r="E29" t="str">
+        <x:v>서버 카탈로그만 반환하며 host 경로·image digest 내부 설정·credential을 노출하지 않는다.</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd0d4ee6ec6354270"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc2b501c111fa4790"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6841,10 +6909,27 @@
         <x:v>실행마다 새 컨테이너를 만들고 모든 종료 경로에서 자원 예약과 컨테이너를 해제한다.</x:v>
       </x:c>
     </x:row>
+    <x:row r="20">
+      <x:c r="A20" t="str">
+        <x:v>외부 패키지 환경</x:v>
+      </x:c>
+      <x:c r="B20" t="str">
+        <x:v>requested/validating/building</x:v>
+      </x:c>
+      <x:c r="C20" t="str">
+        <x:v>검증 성공 또는 실패·취소</x:v>
+      </x:c>
+      <x:c r="D20" t="str">
+        <x:v>active, rejected, failed, superseded</x:v>
+      </x:c>
+      <x:c r="E20" t="str">
+        <x:v>active 전까지 기존 runtime revision을 유지하고 같은 lock hash는 재사용한다. 실행 컨테이너는 package build 상태와 무관하게 network none이다.</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rda38c2a2600647f7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R700abf00803e495a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7186,10 +7271,27 @@
         <x:v>사용자 코드 오류를 서버 오프라인으로 표시하지 않고 실행 컨테이너와 reservation을 남기지 않는다.</x:v>
       </x:c>
     </x:row>
+    <x:row r="20">
+      <x:c r="A20" t="str">
+        <x:v>Python 패키지 이미지 빌드 실패</x:v>
+      </x:c>
+      <x:c r="B20" t="str">
+        <x:v>요청 revision을 failed로 기록하고 기존 active image 유지</x:v>
+      </x:c>
+      <x:c r="C20" t="str">
+        <x:v>정확 버전 재선택·관리자 정책 확인·재시도</x:v>
+      </x:c>
+      <x:c r="D20" t="str">
+        <x:v>노트 본문·기존 runtime revision·lock/hash·검사 결과</x:v>
+      </x:c>
+      <x:c r="E20" t="str">
+        <x:v>부분 설치 이미지를 활성화하지 않고 quota reservation과 builder 임시 산출물을 정리한다.</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R67dddde363e94672"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc6f729a5b448414e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7534,7 +7636,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdad480e03e734a10"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R773497aa9f314d03"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7794,7 +7896,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7e934ecd7323472f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R01fe63ebe0474182"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7955,7 +8057,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re519d46aedcd46f5"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9b4aff98cbca4da8"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8815,10 +8917,70 @@
         <x:v>M1-J</x:v>
       </x:c>
     </x:row>
+    <x:row r="43">
+      <x:c r="A43" t="str">
+        <x:v>T-042</x:v>
+      </x:c>
+      <x:c r="B43" t="str">
+        <x:v>기본 Python 패키지 smoke</x:v>
+      </x:c>
+      <x:c r="C43" t="str">
+        <x:v>25개 direct import, NumPy/Pandas 계산, SymPy, Matplotlib PNG, pip check</x:v>
+      </x:c>
+      <x:c r="D43" t="str">
+        <x:v>network none·read-only·non-root·512MiB 실제 worker에서 모두 성공</x:v>
+      </x:c>
+      <x:c r="E43" t="str">
+        <x:v>NAS integration</x:v>
+      </x:c>
+      <x:c r="F43" t="str">
+        <x:v>M1-K</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44">
+      <x:c r="A44" t="str">
+        <x:v>T-043</x:v>
+      </x:c>
+      <x:c r="B44" t="str">
+        <x:v>런타임 카탈로그 일치</x:v>
+      </x:c>
+      <x:c r="C44" t="str">
+        <x:v>requirements 25개와 API/UI/AI catalog 이름·버전·import 비교</x:v>
+      </x:c>
+      <x:c r="D44" t="str">
+        <x:v>누락·중복 0, 외부 설치 미지원 상태를 과장하지 않음</x:v>
+      </x:c>
+      <x:c r="E44" t="str">
+        <x:v>unit+API</x:v>
+      </x:c>
+      <x:c r="F44" t="str">
+        <x:v>M1-K</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45">
+      <x:c r="A45" t="str">
+        <x:v>T-044</x:v>
+      </x:c>
+      <x:c r="B45" t="str">
+        <x:v>외부 패키지 공급망 경계</x:v>
+      </x:c>
+      <x:c r="C45" t="str">
+        <x:v>URL/Git/local/private index, sdist, hash/CVE 실패, disk/queue 초과, rollback</x:v>
+      </x:c>
+      <x:c r="D45" t="str">
+        <x:v>builder에서 거절하거나 기존 active revision 유지, runtime network none</x:v>
+      </x:c>
+      <x:c r="E45" t="str">
+        <x:v>security+integration</x:v>
+      </x:c>
+      <x:c r="F45" t="str">
+        <x:v>M2-PKG</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3238133cacf844a4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4370561beb60420c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9231,7 +9393,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc1924847a89242a1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re82342fdf17d4e80"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9372,7 +9534,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R63e89de0c8594781"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb5be5db141ef4933"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9581,7 +9743,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R355674b7805640cf"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2197b0bf383d4a5d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9881,10 +10043,30 @@
         <x:v>Codex</x:v>
       </x:c>
     </x:row>
+    <x:row r="15">
+      <x:c r="A15" t="str">
+        <x:v>2026-09-07</x:v>
+      </x:c>
+      <x:c r="B15" t="str">
+        <x:v>1.4-python-curated-runtime</x:v>
+      </x:c>
+      <x:c r="C15" t="str">
+        <x:v>운영 배포 완료 / 외부 self-service 보류</x:v>
+      </x:c>
+      <x:c r="D15" t="str">
+        <x:v>Python 3.12 기본 패키지 25개를 고정 이미지로 제공하고 Note Studio 패키지 화면, 런타임 API, AI 조회 도구와 외부 패키지 안전 설계를 추가했다.</x:v>
+      </x:c>
+      <x:c r="E15" t="str">
+        <x:v>로컬 backend 105 pass 6 skip·production/PDF.js. NAS package smoke 25/25·worker 5/5·전체 107 pass 4 skip·live main.7af33d11.js·HTTP/service/auth 통과.</x:v>
+      </x:c>
+      <x:c r="F15" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R63699b8b6348439b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re95cc496ff6d4bc3"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10282,12 +10464,24 @@
       </x:c>
     </x:row>
     <x:row r="20">
-      <x:c r="A20"/>
-      <x:c r="B20"/>
-      <x:c r="C20"/>
-      <x:c r="D20"/>
-      <x:c r="E20"/>
-      <x:c r="F20"/>
+      <x:c r="A20" t="str">
+        <x:v>M1-K</x:v>
+      </x:c>
+      <x:c r="B20" t="str">
+        <x:v>Python curated 기본 패키지 런타임</x:v>
+      </x:c>
+      <x:c r="C20" t="str">
+        <x:v>완료·운영 배포 / 패키지 dialog 실화면 E2E 전</x:v>
+      </x:c>
+      <x:c r="D20" t="str">
+        <x:v>Python 3.12, 기본 25 packages, 고정 image, catalog API/UI/AI, 512MiB resource admission, offline one-shot sandbox</x:v>
+      </x:c>
+      <x:c r="E20" t="str">
+        <x:v>NAS 실제 import 25/25·계산·그래프·pip check·worker integration·전체 backend·production/live hash·HTTP/PM2/service/auth</x:v>
+      </x:c>
+      <x:c r="F20" t="str">
+        <x:v>남음: 로그인된 패키지 dialog 육안 확인. 외부 패키지 self-service와 GPU·대형 ML은 M2-PKG 별도 단계.</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -10498,7 +10692,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0ee9eb48513b46b9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R45ef1669b2ec4ede"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10781,7 +10975,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf1879153ab694593"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcf958fd93fc443ca"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11415,7 +11609,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re4da6ca2af3f41dc"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R263f27b0ee8248cc"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11658,7 +11852,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3e607768ef3e47fc"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R87505f04ea774493"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11833,7 +12027,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfc55fa26b2f84504"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6154da61575747fd"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12093,7 +12287,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R238a2df0e1c743b9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R714503251b6a4b79"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/programs/NAS_NOTE_STUDIO_SPEC.xlsx
+++ b/docs/programs/NAS_NOTE_STUDIO_SPEC.xlsx
@@ -2,39 +2,39 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="R6336cc7f451d4366"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Product_Vision" sheetId="2" r:id="R97b48d791d3e4cee"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decisions" sheetId="3" r:id="Re4a9c301a68d452a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Competitors" sheetId="4" r:id="R250c810c790f4eb7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open_Source" sheetId="5" r:id="R4b115a26ecb64033"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source_Index" sheetId="6" r:id="R120604a4194c4726"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Information_Architecture" sheetId="7" r:id="Rbf70fc1668094391"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI_Layout" sheetId="8" r:id="R6870933085154bcc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="User_Flows" sheetId="9" r:id="R0986b7183d4b498e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Note_Types" sheetId="10" r:id="R58ffed60fe7a4700"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Block_Catalog" sheetId="11" r:id="R71d4d15b16fa4bba"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Slash_Commands" sheetId="12" r:id="R29beebd604f0425a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Context_Menus" sheetId="13" r:id="R41af4124b90649e9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Keyboard_Shortcuts" sheetId="14" r:id="Raf1c3e7d242e41c1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Database_Views" sheetId="15" r:id="R560b14b749b549d4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Code_Text_Mode" sheetId="16" r:id="Rbdd8626b05e549a4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Python_Notebook" sheetId="17" r:id="Rb983d9eeb7d44f2d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Collaboration" sheetId="18" r:id="R556b053cc60f47b3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Offline_Desktop" sheetId="19" r:id="Rb95a4cf459e24681"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data_Model" sheetId="20" r:id="Rdbba29fee9094bcd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Storage_Interop" sheetId="21" r:id="R1e58b9bd4f6145c6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Security" sheetId="22" r:id="Rcf54efcef7bc4836"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="API_Contracts" sheetId="23" r:id="Ra0cc3f2f060e4511"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="State_Machines" sheetId="24" r:id="R972028eaf91143bf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Error_Recovery" sheetId="25" r:id="R12f67d47b47449c7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cross_App_Relations" sheetId="26" r:id="R163e9b7644204d1a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Performance" sheetId="27" r:id="R9b65425e147a46fe"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Accessibility" sheetId="28" r:id="Rd95d4631845f4f8b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test_Matrix" sheetId="29" r:id="Rf4069f638dc94781"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="30" r:id="R852e6d2a03874364"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open_Questions" sheetId="31" r:id="R5aea2c55713345a9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Change_Log" sheetId="32" r:id="R3f8535295f8648d5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Implementation_Status" sheetId="33" r:id="R527968aff02c4d8f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="Raed66d33363a4436"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Product_Vision" sheetId="2" r:id="R7beb414fb8af4f54"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decisions" sheetId="3" r:id="Rf25dbb02dd8d4984"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Competitors" sheetId="4" r:id="R0c377a2a379c4576"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open_Source" sheetId="5" r:id="Rd2dce103814e4fa0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source_Index" sheetId="6" r:id="R66dbceaed1ed4df0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Information_Architecture" sheetId="7" r:id="Rea6107d5d4b243e7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI_Layout" sheetId="8" r:id="Re4a329ffff2d48e5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="User_Flows" sheetId="9" r:id="R294109f47fa74961"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Note_Types" sheetId="10" r:id="Re8b430a85fdc45d7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Block_Catalog" sheetId="11" r:id="R537373887830434d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Slash_Commands" sheetId="12" r:id="Rbae2642315d9406f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Context_Menus" sheetId="13" r:id="R9a635360913a44bd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Keyboard_Shortcuts" sheetId="14" r:id="R06797f4c0c7a49e0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Database_Views" sheetId="15" r:id="Rbd7d878b990244d6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Code_Text_Mode" sheetId="16" r:id="R746831312b8242cc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Python_Notebook" sheetId="17" r:id="R4f3cf63c036540f7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Collaboration" sheetId="18" r:id="R74896baa23934df7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Offline_Desktop" sheetId="19" r:id="R281d7e7a17a54e29"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data_Model" sheetId="20" r:id="R3f2929496a5041c5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Storage_Interop" sheetId="21" r:id="R416870e13c9f4271"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Security" sheetId="22" r:id="R393d53f57aab46de"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="API_Contracts" sheetId="23" r:id="R46c319e3b0e54212"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="State_Machines" sheetId="24" r:id="R20ba3b73e40b4a59"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Error_Recovery" sheetId="25" r:id="Ra4db70f83d3142e8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cross_App_Relations" sheetId="26" r:id="R89c5042c9b244de8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Performance" sheetId="27" r:id="R1699ab3c2ada49ae"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Accessibility" sheetId="28" r:id="R6eb8d1533f054848"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test_Matrix" sheetId="29" r:id="R8424cf8afeee4e08"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="30" r:id="Raefe2ae143e24095"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open_Questions" sheetId="31" r:id="Rbd9f46464dd446ed"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Change_Log" sheetId="32" r:id="Ra5618442bb0244d0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Implementation_Status" sheetId="33" r:id="R55190ce996c44be3"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -928,7 +928,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R06696c67c5744d69"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R74412b3470a3477e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1271,7 +1271,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1920415f08654bce"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R50c1ebfff1324510"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1674,7 +1674,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf5fad75b7d134d05"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R58fd949faec941fe"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2197,7 +2197,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R26f9d50e30a145d3"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5cb6b0b0f51c48d0"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2610,7 +2610,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd12f4f588faa4c86"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1c18048418fb48e9"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3552,16 +3552,16 @@
         <x:v>Rich text</x:v>
       </x:c>
       <x:c r="B55" s="13" t="str">
-        <x:v>Tab</x:v>
+        <x:v>Tab / Shift+Tab</x:v>
       </x:c>
       <x:c r="C55" s="13" t="str">
-        <x:v>`1.`·`-`·`*`·`[ ]`·`[x]`·`#`·`##`·`###`·`&gt;`·`"`·triple-backtick·`---`·`===` 패턴 확정</x:v>
+        <x:v>마커 패턴은 블록 형식으로 확정하고, 일반 문단·제목·코드 블록은 들여쓰기/내어쓰기, 목록·할 일 목록은 하위/상위 단계로 이동</x:v>
       </x:c>
       <x:c r="D55" s="13" t="str">
-        <x:v>일반 문장·조합 입력·빈 패턴은 들여쓰기/기본 동작을 보존</x:v>
+        <x:v>본문에서는 브라우저 상단바 초점 이동을 차단한다. 최대 8단계이며 편집기 밖의 Tab 접근성은 유지한다.</x:v>
       </x:c>
       <x:c r="E55" s="13" t="str">
-        <x:v>M1 구현</x:v>
+        <x:v>M1-L 구현</x:v>
       </x:c>
     </x:row>
     <x:row r="56" ht="84" customHeight="1">
@@ -3601,7 +3601,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2ae5148d1aa545e3"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9cfc381f32354e89"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3861,7 +3861,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re352f4f6416849d8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbebdceccca444a09"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4053,7 +4053,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R89d2cf54d0d54d8d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R019b8d67e9844cbb"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4432,7 +4432,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb3b725b3518b49dc"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2fa2dfca79b440de"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4692,7 +4692,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re2815ffa76714c56"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd7a2d9b1b8604c4b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4884,7 +4884,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb8ebe2a82b11424d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra614af61eb1a4180"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5017,7 +5017,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9ed3cc585dba4c3f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R834e0f9c1023499b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5410,10 +5410,27 @@
         <x:v>높음</x:v>
       </x:c>
     </x:row>
+    <x:row r="23">
+      <x:c r="A23" t="str">
+        <x:v>BlockIndentAttribute</x:v>
+      </x:c>
+      <x:c r="B23" t="str">
+        <x:v>nodeType, indentLevel(0..8)</x:v>
+      </x:c>
+      <x:c r="C23" t="str">
+        <x:v>paragraph·heading·codeBlock만 허용하고 범위 밖·비수치 값은 0..8로 정규화</x:v>
+      </x:c>
+      <x:c r="D23" t="str">
+        <x:v>note content JSON</x:v>
+      </x:c>
+      <x:c r="E23" t="str">
+        <x:v>중간</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R89c4023a97924b86"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R42f6f2e8e9db40fe"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5673,7 +5690,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf8b6db6d94da4385"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8a71035b9daa4bf0"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6052,7 +6069,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rda0eb543858a4a67"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0f2f0974ee8a4612"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6567,7 +6584,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc2b501c111fa4790"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6f4192c621894349"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6929,7 +6946,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R700abf00803e495a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re64e62ef27dd40e2"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7291,7 +7308,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc6f729a5b448414e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R37bdb6d515e945e9"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7636,7 +7653,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R773497aa9f314d03"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdf81d122b88c41e9"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7896,7 +7913,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R01fe63ebe0474182"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0aef0c00f055408b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8057,7 +8074,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9b4aff98cbca4da8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R820574f82eae4bc3"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8977,10 +8994,30 @@
         <x:v>M2-PKG</x:v>
       </x:c>
     </x:row>
+    <x:row r="46">
+      <x:c r="A46" t="str">
+        <x:v>T-045</x:v>
+      </x:c>
+      <x:c r="B46" t="str">
+        <x:v>블록 노트 Tab 들여쓰기</x:v>
+      </x:c>
+      <x:c r="C46" t="str">
+        <x:v>일반 문단/제목/코드, 0·8 경계, Shift+Tab, ordered/bullet/task list, 기존 마커, 재저장·재열기, IME 입력 직후</x:v>
+      </x:c>
+      <x:c r="D46" t="str">
+        <x:v>본문 포커스가 웹 UI로 빠지지 않고 일반 블록은 0~8단계, 목록은 실제 중첩 구조로 저장되며 기존 마커 변환이 유지됨</x:v>
+      </x:c>
+      <x:c r="E46" t="str">
+        <x:v>unit+production+live</x:v>
+      </x:c>
+      <x:c r="F46" t="str">
+        <x:v>M1-L</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4370561beb60420c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1442901450e1440d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9393,7 +9430,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re82342fdf17d4e80"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R47995bf072b34bb5"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9534,7 +9571,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb5be5db141ef4933"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9a1c4dae1b5444b7"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9743,7 +9780,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2197b0bf383d4a5d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4a1bce72f08744fc"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10063,10 +10100,30 @@
         <x:v>Codex</x:v>
       </x:c>
     </x:row>
+    <x:row r="16">
+      <x:c r="A16" t="str">
+        <x:v>2026-09-07</x:v>
+      </x:c>
+      <x:c r="B16" t="str">
+        <x:v>1.5-block-tab-indent</x:v>
+      </x:c>
+      <x:c r="C16" t="str">
+        <x:v>운영 배포 완료 / 로그인 키보드 육안 확인 가능</x:v>
+      </x:c>
+      <x:c r="D16" t="str">
+        <x:v>블록 노트의 모든 Tab 초점 이탈을 차단하고 일반 블록 들여쓰기·Shift+Tab 내어쓰기·목록 구조 중첩을 추가했다. 기존 마커+Tab 변환은 우선 유지한다.</x:v>
+      </x:c>
+      <x:c r="E16" t="str">
+        <x:v>로컬·NAS focused 6/6, production/PDF.js, live main.490657bd.js, 내부·공개 200, PM2·필수 서비스 정상.</x:v>
+      </x:c>
+      <x:c r="F16" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re95cc496ff6d4bc3"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb866240abea643a3"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10481,6 +10538,26 @@
       </x:c>
       <x:c r="F20" t="str">
         <x:v>남음: 로그인된 패키지 dialog 육안 확인. 외부 패키지 self-service와 GPU·대형 ML은 M2-PKG 별도 단계.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21">
+      <x:c r="A21" t="str">
+        <x:v>M1-L</x:v>
+      </x:c>
+      <x:c r="B21" t="str">
+        <x:v>블록 노트 Tab 들여쓰기</x:v>
+      </x:c>
+      <x:c r="C21" t="str">
+        <x:v>완료·운영 배포</x:v>
+      </x:c>
+      <x:c r="D21" t="str">
+        <x:v>문단·제목·코드 block indentLevel 0..8, 목록·task 목록 sink/lift, Shift+Tab, 마커 shortcut 우선, browser focus 이동 차단</x:v>
+      </x:c>
+      <x:c r="E21" t="str">
+        <x:v>로컬·NAS Jest 6/6·production/PDF.js·live bundle 일치·HTTP/PM2/services</x:v>
+      </x:c>
+      <x:c r="F21" t="str">
+        <x:v>로그인된 실제 노트의 IME 직후 Tab과 키보드 육안 확인은 사용 세션에서 가능. 기능·저장 구조·운영 배포 검증은 완료.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -10692,7 +10769,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R45ef1669b2ec4ede"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R452192a435ec4c1e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10975,7 +11052,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcf958fd93fc443ca"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2e02065047104e8e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11609,7 +11686,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R263f27b0ee8248cc"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7ee708d2e5604153"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11852,7 +11929,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R87505f04ea774493"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R70c5dfcc394c4cf4"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12027,7 +12104,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6154da61575747fd"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R79d789f1a0784345"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12287,7 +12364,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R714503251b6a4b79"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbeceaddc3166439c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/programs/NAS_NOTE_STUDIO_SPEC.xlsx
+++ b/docs/programs/NAS_NOTE_STUDIO_SPEC.xlsx
@@ -2,39 +2,39 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="Raed66d33363a4436"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Product_Vision" sheetId="2" r:id="R7beb414fb8af4f54"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decisions" sheetId="3" r:id="Rf25dbb02dd8d4984"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Competitors" sheetId="4" r:id="R0c377a2a379c4576"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open_Source" sheetId="5" r:id="Rd2dce103814e4fa0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source_Index" sheetId="6" r:id="R66dbceaed1ed4df0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Information_Architecture" sheetId="7" r:id="Rea6107d5d4b243e7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI_Layout" sheetId="8" r:id="Re4a329ffff2d48e5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="User_Flows" sheetId="9" r:id="R294109f47fa74961"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Note_Types" sheetId="10" r:id="Re8b430a85fdc45d7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Block_Catalog" sheetId="11" r:id="R537373887830434d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Slash_Commands" sheetId="12" r:id="Rbae2642315d9406f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Context_Menus" sheetId="13" r:id="R9a635360913a44bd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Keyboard_Shortcuts" sheetId="14" r:id="R06797f4c0c7a49e0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Database_Views" sheetId="15" r:id="Rbd7d878b990244d6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Code_Text_Mode" sheetId="16" r:id="R746831312b8242cc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Python_Notebook" sheetId="17" r:id="R4f3cf63c036540f7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Collaboration" sheetId="18" r:id="R74896baa23934df7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Offline_Desktop" sheetId="19" r:id="R281d7e7a17a54e29"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data_Model" sheetId="20" r:id="R3f2929496a5041c5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Storage_Interop" sheetId="21" r:id="R416870e13c9f4271"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Security" sheetId="22" r:id="R393d53f57aab46de"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="API_Contracts" sheetId="23" r:id="R46c319e3b0e54212"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="State_Machines" sheetId="24" r:id="R20ba3b73e40b4a59"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Error_Recovery" sheetId="25" r:id="Ra4db70f83d3142e8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cross_App_Relations" sheetId="26" r:id="R89c5042c9b244de8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Performance" sheetId="27" r:id="R1699ab3c2ada49ae"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Accessibility" sheetId="28" r:id="R6eb8d1533f054848"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test_Matrix" sheetId="29" r:id="R8424cf8afeee4e08"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="30" r:id="Raefe2ae143e24095"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open_Questions" sheetId="31" r:id="Rbd9f46464dd446ed"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Change_Log" sheetId="32" r:id="Ra5618442bb0244d0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Implementation_Status" sheetId="33" r:id="R55190ce996c44be3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="Ra3a8767c3bf34b77"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Product_Vision" sheetId="2" r:id="Ra22ed8560c134d72"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decisions" sheetId="3" r:id="R3514ddf9b6914d5c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Competitors" sheetId="4" r:id="Rbbf7941540ed4bca"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open_Source" sheetId="5" r:id="R7e782ba9d2d945c1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source_Index" sheetId="6" r:id="R88dbc2a4004a411b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Information_Architecture" sheetId="7" r:id="Rdaca9ac5433f4a48"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI_Layout" sheetId="8" r:id="Re756af4d962f4e5e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="User_Flows" sheetId="9" r:id="R72d64e131c2e4a42"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Note_Types" sheetId="10" r:id="R72ac24df17f14662"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Block_Catalog" sheetId="11" r:id="R4547e6ce32a64c33"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Slash_Commands" sheetId="12" r:id="R821e13db0436466f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Context_Menus" sheetId="13" r:id="R217f465519414400"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Keyboard_Shortcuts" sheetId="14" r:id="R19de3566b02b4fd6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Database_Views" sheetId="15" r:id="R03c7ade7d2944733"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Code_Text_Mode" sheetId="16" r:id="R173986b0ed434f12"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Python_Notebook" sheetId="17" r:id="R078a065ee2f949ce"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Collaboration" sheetId="18" r:id="R49354b289448432e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Offline_Desktop" sheetId="19" r:id="R2f14db6462574826"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data_Model" sheetId="20" r:id="Rccee01de8f804017"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Storage_Interop" sheetId="21" r:id="R92ef80f65d794496"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Security" sheetId="22" r:id="R30b461fc91854494"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="API_Contracts" sheetId="23" r:id="R89ba9bae56f04b17"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="State_Machines" sheetId="24" r:id="R2b584a7854004a03"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Error_Recovery" sheetId="25" r:id="R1d990b6607bc4199"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cross_App_Relations" sheetId="26" r:id="R411844cc96ed487a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Performance" sheetId="27" r:id="R7d04d06c02534616"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Accessibility" sheetId="28" r:id="Rc7168eb92a5e448e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test_Matrix" sheetId="29" r:id="R91a1b77b3f2f489f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="30" r:id="R34fc2f4305654f02"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open_Questions" sheetId="31" r:id="R76dd1f7186294034"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Change_Log" sheetId="32" r:id="R0e57819f169b41ff"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Implementation_Status" sheetId="33" r:id="R07941c1dc8354db0"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -248,7 +248,7 @@
 </file>
 
 <file path=xl/tables/table13.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="13" name="T_Context_Menus" displayName="T_Context_Menus" ref="A1:E19" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="13" name="T_Context_Menus" displayName="T_Context_Menus" ref="A1:E26" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="5">
     <x:tableColumn id="1" name="대상"/>
     <x:tableColumn id="2" name="표시 순서"/>
@@ -467,7 +467,7 @@
 </file>
 
 <file path=xl/tables/table29.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="29" name="T_Test_Matrix" displayName="T_Test_Matrix" ref="A1:F19" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="29" name="T_Test_Matrix" displayName="T_Test_Matrix" ref="A1:F20" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="6">
     <x:tableColumn id="1" name="TEST ID"/>
     <x:tableColumn id="2" name="영역"/>
@@ -507,7 +507,7 @@
 </file>
 
 <file path=xl/tables/table31.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="31" name="T_Open_Questions" displayName="T_Open_Questions" ref="A1:E11" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="31" name="T_Open_Questions" displayName="T_Open_Questions" ref="A1:E12" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="5">
     <x:tableColumn id="1" name="질문 ID"/>
     <x:tableColumn id="2" name="결정 필요 사항"/>
@@ -520,7 +520,7 @@
 </file>
 
 <file path=xl/tables/table32.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="32" name="T_Change_Log" displayName="T_Change_Log" ref="A1:F2" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="32" name="T_Change_Log" displayName="T_Change_Log" ref="A1:F3" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="6">
     <x:tableColumn id="1" name="날짜"/>
     <x:tableColumn id="2" name="버전"/>
@@ -561,7 +561,7 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="T_Source_Index" displayName="T_Source_Index" ref="A1:E22" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="T_Source_Index" displayName="T_Source_Index" ref="A1:E24" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="5">
     <x:tableColumn id="1" name="출처 ID"/>
     <x:tableColumn id="2" name="주제"/>
@@ -928,7 +928,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R74412b3470a3477e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcddf9818289c48a9"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1271,7 +1271,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R50c1ebfff1324510"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R457b563f731b475f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1674,7 +1674,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R58fd949faec941fe"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbc87ff2b65404c68"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2197,7 +2197,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5cb6b0b0f51c48d0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8e9b1d527b014a5f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2541,76 +2541,127 @@
     </x:row>
     <x:row r="20">
       <x:c r="A20" s="13" t="str">
-        <x:v>노트북 폴더/파일 영역</x:v>
+        <x:v>블록 노트 편집 바탕/현재 블록</x:v>
       </x:c>
       <x:c r="B20" s="13" t="str">
         <x:v>1</x:v>
       </x:c>
       <x:c r="C20" s="13" t="str">
-        <x:v>새 페이지 / 새 폴더 / 문서 만들기</x:v>
+        <x:v>삽입 / 블록 유형 변경 / 색상</x:v>
       </x:c>
       <x:c r="D20" s="13" t="str">
-        <x:v>생성 권한</x:v>
+        <x:v>편집 가능</x:v>
       </x:c>
       <x:c r="E20" s="13" t="str">
-        <x:v>우클릭한 invocation directory를 draft 기본 저장 위치로 기억</x:v>
+        <x:v>우클릭 좌표의 caret·블록을 먼저 고정하고 하위 메뉴를 연다. Shift+우클릭은 브라우저 기본 메뉴를 유지한다.</x:v>
       </x:c>
     </x:row>
     <x:row r="21">
       <x:c r="A21" s="13" t="str">
-        <x:v>블록 핸들/본문 caret</x:v>
+        <x:v>블록 노트 편집 바탕/현재 블록</x:v>
       </x:c>
       <x:c r="B21" s="13" t="str">
         <x:v>2</x:v>
       </x:c>
       <x:c r="C21" s="13" t="str">
-        <x:v>하위 페이지 / Office 문서 / 기존 NAS 문서 연결</x:v>
+        <x:v>복제 / 위·아래 이동 / 들여쓰기·내어쓰기</x:v>
       </x:c>
       <x:c r="D21" s="13" t="str">
-        <x:v>note edit + target create/read 권한</x:v>
+        <x:v>편집 가능</x:v>
       </x:c>
       <x:c r="E21" s="13" t="str">
-        <x:v>현재 위치에 page 또는 document reference block 삽입</x:v>
+        <x:v>현재 형제 경계에서만 이동하며 한 번의 편집 transaction으로 자동 저장한다.</x:v>
       </x:c>
     </x:row>
     <x:row r="22">
       <x:c r="A22" s="13" t="str">
-        <x:v>문서 reference</x:v>
+        <x:v>블록 노트 편집 바탕/현재 블록</x:v>
       </x:c>
       <x:c r="B22" s="13" t="str">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C22" s="13" t="str">
-        <x:v>열기 / NAS에서 보기 / 위치 복사 / 다시 연결</x:v>
+        <x:v>블록 텍스트 복사 / 잘라내기</x:v>
       </x:c>
       <x:c r="D22" s="13" t="str">
-        <x:v>대상 read 권한</x:v>
+        <x:v>편집 가능</x:v>
       </x:c>
       <x:c r="E22" s="13" t="str">
-        <x:v>지원 편집기를 전면 열고 stable ID를 서버에서 재해석</x:v>
+        <x:v>Clipboard API 실패 시 selection 기반 대체 복사를 시도하며 잘라내기는 복사 성공 후에만 삭제한다.</x:v>
       </x:c>
     </x:row>
     <x:row r="23">
       <x:c r="A23" s="13" t="str">
-        <x:v>문서 reference</x:v>
+        <x:v>블록 노트 편집 바탕/현재 블록</x:v>
       </x:c>
       <x:c r="B23" s="13" t="str">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C23" s="13" t="str">
+        <x:v>AI에게 이 블록 요청</x:v>
+      </x:c>
+      <x:c r="D23" s="13" t="str">
+        <x:v>AI 사용 가능</x:v>
+      </x:c>
+      <x:c r="E23" s="13" t="str">
+        <x:v>현재 노트·노트북 ID와 최대 4,000자 블록 텍스트를 AI 패널 초안으로 전달하고 자동 전송하지 않는다.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24">
+      <x:c r="A24" t="str">
+        <x:v>블록 노트 편집 바탕/현재 블록</x:v>
+      </x:c>
+      <x:c r="B24" t="str">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="C24" t="str">
+        <x:v>삭제</x:v>
+      </x:c>
+      <x:c r="D24" t="str">
+        <x:v>편집 가능</x:v>
+      </x:c>
+      <x:c r="E24" t="str">
+        <x:v>마지막 블록이면 빈 문단을 유지하고 그 외에는 대상 블록만 삭제한다.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25">
+      <x:c r="A25" t="str">
+        <x:v>삽입 하위 메뉴</x:v>
+      </x:c>
+      <x:c r="B25" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C25" t="str">
+        <x:v>본문·제목·목록·할 일·인용·코드·구분선</x:v>
+      </x:c>
+      <x:c r="D25" t="str">
+        <x:v>편집 가능</x:v>
+      </x:c>
+      <x:c r="E25" t="str">
+        <x:v>기존 slash command registry와 동일 명령을 사용한다.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26">
+      <x:c r="A26" t="str">
+        <x:v>삽입 하위 메뉴</x:v>
+      </x:c>
+      <x:c r="B26" t="str">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C23" s="13" t="str">
-        <x:v>링크 제거 / 링크와 파일 함께 삭제</x:v>
-      </x:c>
-      <x:c r="D23" s="13" t="str">
-        <x:v>note edit; 실제 삭제는 file delete 권한</x:v>
-      </x:c>
-      <x:c r="E23" s="13" t="str">
-        <x:v>기본은 링크만 제거. 함께 삭제는 확인 후 휴지통</x:v>
+      <x:c r="C26" t="str">
+        <x:v>하위 페이지 / NAS 파일·폴더 / Office 문서</x:v>
+      </x:c>
+      <x:c r="D26" t="str">
+        <x:v>대상 생성·읽기 권한</x:v>
+      </x:c>
+      <x:c r="E26" t="str">
+        <x:v>기존 안전 생성·연결 흐름을 재사용하며 Office 메뉴가 우클릭의 유일한 기능이 되지 않는다.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1c18048418fb48e9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3130d2c66b584756"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3601,7 +3652,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9cfc381f32354e89"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2cc96f2efa1346fa"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3861,7 +3912,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbebdceccca444a09"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb3cfb6d7bd8b42b3"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4053,7 +4104,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R019b8d67e9844cbb"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc23c8360d5be4f21"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4432,7 +4483,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2fa2dfca79b440de"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfe8f7afe970247a3"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4692,7 +4743,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd7a2d9b1b8604c4b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1b7a31dcb4dc432c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4884,7 +4935,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra614af61eb1a4180"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2f13f82daceb45e8"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5017,7 +5068,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R834e0f9c1023499b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3fc4e1e866004bc1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5430,7 +5481,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R42f6f2e8e9db40fe"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd2e4b8b22d744fbf"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5690,7 +5741,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8a71035b9daa4bf0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7912b23623a549ae"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6069,7 +6120,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0f2f0974ee8a4612"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2d5703577ace4ac3"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6584,7 +6635,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6f4192c621894349"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R01ccc3a0fdb8453b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6946,7 +6997,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re64e62ef27dd40e2"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0cc695c064f74e02"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7308,7 +7359,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R37bdb6d515e945e9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R11641ae4603c4a21"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7653,7 +7704,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdf81d122b88c41e9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb4935e9ac73d4582"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7913,7 +7964,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0aef0c00f055408b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R086158f3212b488d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8074,7 +8125,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R820574f82eae4bc3"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R42231f5e45b24994"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8476,22 +8527,22 @@
     </x:row>
     <x:row r="20">
       <x:c r="A20" s="13" t="str">
-        <x:v>T-019</x:v>
+        <x:v>T-046</x:v>
       </x:c>
       <x:c r="B20" s="13" t="str">
-        <x:v>혼합 Python 페이지</x:v>
+        <x:v>블록 우클릭 메뉴</x:v>
       </x:c>
       <x:c r="C20" s="13" t="str">
-        <x:v>텍스트·링크·Office block 사이 code cell 실행/all/restart</x:v>
+        <x:v>빈 바탕·문단·제목·목록·마지막 블록에서 우클릭 후 변환/색/복제/이동/들여쓰기/복사/잘라내기/AI 초안/삭제/삽입</x:v>
       </x:c>
       <x:c r="D20" s="13" t="str">
-        <x:v>code cell만 정확한 순서로 실행하고 문서 block은 실행되지 않음</x:v>
+        <x:v>좌표의 블록만 변경되고 메뉴 focus 때문에 selection이 바뀌지 않으며 마지막 블록·목록 구조·자동 저장이 유효하다.</x:v>
       </x:c>
       <x:c r="E20" s="13" t="str">
-        <x:v>integration+E2E</x:v>
+        <x:v>unit+production+live E2E</x:v>
       </x:c>
       <x:c r="F20" s="13" t="str">
-        <x:v>M2</x:v>
+        <x:v>M1-M</x:v>
       </x:c>
     </x:row>
     <x:row r="21">
@@ -9017,7 +9068,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1442901450e1440d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc973f168e0324166"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9430,7 +9481,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R47995bf072b34bb5"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rad6027826f5847cc"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9571,7 +9622,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9a1c4dae1b5444b7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Reb9ea5bf4bc546d5"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9777,10 +9828,27 @@
         <x:v>소스 공개 의무</x:v>
       </x:c>
     </x:row>
+    <x:row r="12">
+      <x:c r="A12" t="str">
+        <x:v>Q-BLOCK-STABLE-ID</x:v>
+      </x:c>
+      <x:c r="B12" t="str">
+        <x:v>댓글·블록 링크·다른 페이지 이동에 사용할 영구 blockId와 다중 블록 transaction 모델</x:v>
+      </x:c>
+      <x:c r="C12" t="str">
+        <x:v>현재 단일 블록 로컬 조작은 유지하고 stable ID migration·권한·undo·동시 편집을 한 묶음으로 설계한다.</x:v>
+      </x:c>
+      <x:c r="D12" t="str">
+        <x:v>M1.5 협업 구현 전</x:v>
+      </x:c>
+      <x:c r="E12" t="str">
+        <x:v>겉보기 메뉴만 먼저 만들면 링크와 댓글 anchor가 저장 후 깨질 수 있다.</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4a1bce72f08744fc"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R502d4b72e37442b7"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9842,19 +9910,19 @@
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="13" t="str">
-        <x:v>2026-09-06</x:v>
+        <x:v>2026-09-07</x:v>
       </x:c>
       <x:c r="B3" s="13" t="str">
-        <x:v>0.2-m1-core</x:v>
+        <x:v>1.6-notion-block-context</x:v>
       </x:c>
       <x:c r="C3" s="13" t="str">
-        <x:v>M1 핵심 기반 운영 배포·HTTP E2E 완료 / 로그인 실화면 E2E 전</x:v>
+        <x:v>구현·로컬 빌드/단위 검증 완료</x:v>
       </x:c>
       <x:c r="D3" s="13" t="str">
-        <x:v>계정별 원자 저장 API, lazy-loaded Tiptap/Monaco 편집 UI, autosave/Ctrl+S, 충돌·버전·휴지통·검색, NAS 첨부, import/export와 플랫폼 앱 등록.</x:v>
+        <x:v>블록 노트 바탕 우클릭을 현재 블록 중심 메뉴로 교체했다. 삽입·유형 변경·색·복제·이동·들여쓰기·복사·잘라내기·AI 초안·삭제와 하위 페이지/NAS/Office 연결을 제공한다.</x:v>
       </x:c>
       <x:c r="E3" s="13" t="str">
-        <x:v>로컬·NAS 11 tests, production/PDF.js, 운영 API 전 흐름, 서비스 active, 내부·공개 200. 로그인 화면이라 사용자 인증 UI E2E는 남김.</x:v>
+        <x:v>공식 Notion 블록 작업 및 Tiptap custom menu 대조. focused 8/8, production build/PDF.js 통과. NAS 배포·로그인 실화면은 배포 단계에서 갱신.</x:v>
       </x:c>
       <x:c r="F3" s="13" t="str">
         <x:v>Codex</x:v>
@@ -10123,7 +10191,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb866240abea643a3"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R58b0c0b46db641d0"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10558,6 +10626,26 @@
       </x:c>
       <x:c r="F21" t="str">
         <x:v>로그인된 실제 노트의 IME 직후 Tab과 키보드 육안 확인은 사용 세션에서 가능. 기능·저장 구조·운영 배포 검증은 완료.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22">
+      <x:c r="A22" t="str">
+        <x:v>M1-M</x:v>
+      </x:c>
+      <x:c r="B22" t="str">
+        <x:v>Notion형 블록 우클릭 작업</x:v>
+      </x:c>
+      <x:c r="C22" t="str">
+        <x:v>구현·로컬 검증 완료 / NAS 배포·실화면 전</x:v>
+      </x:c>
+      <x:c r="D22" t="str">
+        <x:v>우클릭 좌표 selection, 계층형 메뉴, 9종 transform, 9색/9배경, 단일 블록 복제·형제 이동·indent, 안전 clipboard, AI draft context, 삽입 registry</x:v>
+      </x:c>
+      <x:c r="E22" t="str">
+        <x:v>focused Jest 8/8·production build/PDF.js</x:v>
+      </x:c>
+      <x:c r="F22" t="str">
+        <x:v>NAS 배포 뒤 로그인된 실제 블록·목록·IME·포인터 E2E. stable blockId 기반 댓글·링크·cross-page move·다중 선택 drag는 M1.5 별도.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -10769,7 +10857,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R452192a435ec4c1e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R759dc1e327b54f11"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11052,7 +11140,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2e02065047104e8e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R115a679685d34707"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11447,36 +11535,36 @@
     </x:row>
     <x:row r="23">
       <x:c r="A23" s="13" t="str">
-        <x:v>SRC-PATH-CFAPI</x:v>
+        <x:v>SRC-NOTION-BLOCK-ACTIONS-20260907</x:v>
       </x:c>
       <x:c r="B23" s="13" t="str">
-        <x:v>Microsoft CFAPI placeholder state</x:v>
+        <x:v>Notion 블록 핸들·우클릭 작업</x:v>
       </x:c>
       <x:c r="C23" s="13" t="str">
-        <x:v>https://learn.microsoft.com/en-us/windows/win32/api/cfapi/nf-cfapi-cfgetplaceholderstatefromattributetag</x:v>
+        <x:v>https://www.notion.com/help/writing-and-editing-basics</x:v>
       </x:c>
       <x:c r="D23" s="13" t="str">
-        <x:v>온라인 전용/부분 저장 상태의 content-read 회피 기준</x:v>
+        <x:v>유형 변경, 색, 링크 복사, 복제, 이동, 삭제, 댓글, AI 등 블록 중심 작업을 기준으로 삼되 NAS 권한·저장 모델에 맞게 분리했다.</x:v>
       </x:c>
       <x:c r="E23" s="13" t="str">
-        <x:v>2026-09-06</x:v>
+        <x:v>2026-09-07</x:v>
       </x:c>
     </x:row>
     <x:row r="24">
       <x:c r="A24" s="13" t="str">
-        <x:v>SRC-PATH-VSCODE</x:v>
+        <x:v>SRC-TIPTAP-CUSTOM-MENUS-20260907</x:v>
       </x:c>
       <x:c r="B24" s="13" t="str">
-        <x:v>VS Code Variables / Multi-root / Tasks</x:v>
+        <x:v>Tiptap custom menu와 drag handle</x:v>
       </x:c>
       <x:c r="C24" s="13" t="str">
-        <x:v>https://code.visualstudio.com/docs/reference/variables-reference</x:v>
+        <x:v>https://tiptap.dev/docs/editor/getting-started/style-editor/custom-menus</x:v>
       </x:c>
       <x:c r="D24" s="13" t="str">
-        <x:v>${workspaceFolder}와 지원 필드 제한 기준</x:v>
+        <x:v>메뉴 UI는 자유롭게 구성하고 명령은 editor chain/transaction으로 실행한다. drag handle은 후속 다중 블록 작업에서 별도 검증한다.</x:v>
       </x:c>
       <x:c r="E24" s="13" t="str">
-        <x:v>2026-09-06</x:v>
+        <x:v>2026-09-07</x:v>
       </x:c>
     </x:row>
     <x:row r="25">
@@ -11686,7 +11774,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7ee708d2e5604153"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rde1e744b8dab4f91"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11929,7 +12017,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R70c5dfcc394c4cf4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R32ef10a739c94f65"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12104,7 +12192,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R79d789f1a0784345"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra4c38ddefa214861"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12364,7 +12452,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbeceaddc3166439c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R93ad06971aee452c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/programs/NAS_NOTE_STUDIO_SPEC.xlsx
+++ b/docs/programs/NAS_NOTE_STUDIO_SPEC.xlsx
@@ -2,39 +2,39 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="Ra3a8767c3bf34b77"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Product_Vision" sheetId="2" r:id="Ra22ed8560c134d72"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decisions" sheetId="3" r:id="R3514ddf9b6914d5c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Competitors" sheetId="4" r:id="Rbbf7941540ed4bca"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open_Source" sheetId="5" r:id="R7e782ba9d2d945c1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source_Index" sheetId="6" r:id="R88dbc2a4004a411b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Information_Architecture" sheetId="7" r:id="Rdaca9ac5433f4a48"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI_Layout" sheetId="8" r:id="Re756af4d962f4e5e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="User_Flows" sheetId="9" r:id="R72d64e131c2e4a42"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Note_Types" sheetId="10" r:id="R72ac24df17f14662"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Block_Catalog" sheetId="11" r:id="R4547e6ce32a64c33"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Slash_Commands" sheetId="12" r:id="R821e13db0436466f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Context_Menus" sheetId="13" r:id="R217f465519414400"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Keyboard_Shortcuts" sheetId="14" r:id="R19de3566b02b4fd6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Database_Views" sheetId="15" r:id="R03c7ade7d2944733"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Code_Text_Mode" sheetId="16" r:id="R173986b0ed434f12"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Python_Notebook" sheetId="17" r:id="R078a065ee2f949ce"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Collaboration" sheetId="18" r:id="R49354b289448432e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Offline_Desktop" sheetId="19" r:id="R2f14db6462574826"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data_Model" sheetId="20" r:id="Rccee01de8f804017"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Storage_Interop" sheetId="21" r:id="R92ef80f65d794496"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Security" sheetId="22" r:id="R30b461fc91854494"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="API_Contracts" sheetId="23" r:id="R89ba9bae56f04b17"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="State_Machines" sheetId="24" r:id="R2b584a7854004a03"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Error_Recovery" sheetId="25" r:id="R1d990b6607bc4199"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cross_App_Relations" sheetId="26" r:id="R411844cc96ed487a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Performance" sheetId="27" r:id="R7d04d06c02534616"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Accessibility" sheetId="28" r:id="Rc7168eb92a5e448e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test_Matrix" sheetId="29" r:id="R91a1b77b3f2f489f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="30" r:id="R34fc2f4305654f02"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open_Questions" sheetId="31" r:id="R76dd1f7186294034"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Change_Log" sheetId="32" r:id="R0e57819f169b41ff"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Implementation_Status" sheetId="33" r:id="R07941c1dc8354db0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="R01495a5fac094c50"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Product_Vision" sheetId="2" r:id="R1b0df3e21ab4408a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decisions" sheetId="3" r:id="Raef6019d1aa24bb8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Competitors" sheetId="4" r:id="R69d5ba174e9a4148"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open_Source" sheetId="5" r:id="R3e2cbb72f16b46e4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source_Index" sheetId="6" r:id="Rd12d5288d1064ff0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Information_Architecture" sheetId="7" r:id="R15a0cfd421964216"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI_Layout" sheetId="8" r:id="R0125cac1d1bb45b6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="User_Flows" sheetId="9" r:id="R2052d9e1af6640b8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Note_Types" sheetId="10" r:id="Ra87faa74d447410d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Block_Catalog" sheetId="11" r:id="R0e7bb4af820f4c9f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Slash_Commands" sheetId="12" r:id="R36b6a4be8d8349c0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Context_Menus" sheetId="13" r:id="R0f917e9e41834259"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Keyboard_Shortcuts" sheetId="14" r:id="Rfeb423838295469f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Database_Views" sheetId="15" r:id="Rc8ca46e98d984bf3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Code_Text_Mode" sheetId="16" r:id="R53f21c3afbcb4152"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Python_Notebook" sheetId="17" r:id="Rd2f92ec80bb34a0f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Collaboration" sheetId="18" r:id="Ra023432a17c24aa8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Offline_Desktop" sheetId="19" r:id="R358fe806515848ef"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data_Model" sheetId="20" r:id="R8089cfd9b3844c29"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Storage_Interop" sheetId="21" r:id="Rcac3d2fb88054dbe"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Security" sheetId="22" r:id="R865eee1b7cad406f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="API_Contracts" sheetId="23" r:id="Rd8a0ec0f45f24431"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="State_Machines" sheetId="24" r:id="R865e91dcdb9342c6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Error_Recovery" sheetId="25" r:id="Rb9abe69cc7cb4dda"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cross_App_Relations" sheetId="26" r:id="R47766de25f0d4b6a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Performance" sheetId="27" r:id="Rfd4666a3c25e4e49"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Accessibility" sheetId="28" r:id="R57c33c1e714041dc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test_Matrix" sheetId="29" r:id="R47b35de290964766"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="30" r:id="R2cc730fc5fb3462a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open_Questions" sheetId="31" r:id="R1e5bd6e940ad41b7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Change_Log" sheetId="32" r:id="Rbbf908f6d82b424c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Implementation_Status" sheetId="33" r:id="R6e362db30b2f4328"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -248,7 +248,7 @@
 </file>
 
 <file path=xl/tables/table13.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="13" name="T_Context_Menus" displayName="T_Context_Menus" ref="A1:E26" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="13" name="T_Context_Menus" displayName="T_Context_Menus" ref="A1:E33" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="5">
     <x:tableColumn id="1" name="대상"/>
     <x:tableColumn id="2" name="표시 순서"/>
@@ -928,7 +928,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcddf9818289c48a9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfa85f6d1666342b4"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1271,7 +1271,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R457b563f731b475f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5b085e2f79a14443"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1674,7 +1674,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbc87ff2b65404c68"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf798e154f18a4357"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2197,7 +2197,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8e9b1d527b014a5f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcced9a602a7e45a8"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2658,10 +2658,129 @@
         <x:v>기존 안전 생성·연결 흐름을 재사용하며 Office 메뉴가 우클릭의 유일한 기능이 되지 않는다.</x:v>
       </x:c>
     </x:row>
+    <x:row r="27">
+      <x:c r="A27" t="str">
+        <x:v>블록 핸들 후속</x:v>
+      </x:c>
+      <x:c r="B27" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C27" t="str">
+        <x:v>블록 링크 복사</x:v>
+      </x:c>
+      <x:c r="D27" t="str">
+        <x:v>stable blockId 구현 후</x:v>
+      </x:c>
+      <x:c r="E27" t="str">
+        <x:v>현재 문서 위치를 영구 ID처럼 사용하지 않고 서버가 권한과 존재를 재검증한다.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28">
+      <x:c r="A28" t="str">
+        <x:v>블록 핸들 후속</x:v>
+      </x:c>
+      <x:c r="B28" t="str">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C28" t="str">
+        <x:v>댓글 / 제안 모드</x:v>
+      </x:c>
+      <x:c r="D28" t="str">
+        <x:v>comment·suggest 권한과 anchor 구현 후</x:v>
+      </x:c>
+      <x:c r="E28" t="str">
+        <x:v>본문 변경과 검토 대화를 분리하고 편집 뒤 anchor 이동을 검증한다.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29">
+      <x:c r="A29" t="str">
+        <x:v>블록 핸들 후속</x:v>
+      </x:c>
+      <x:c r="B29" t="str">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C29" t="str">
+        <x:v>다른 페이지로 이동</x:v>
+      </x:c>
+      <x:c r="D29" t="str">
+        <x:v>대상 페이지 편집 권한과 원자 transaction 구현 후</x:v>
+      </x:c>
+      <x:c r="E29" t="str">
+        <x:v>원본 삭제와 대상 삽입이 함께 성공하거나 함께 취소된다.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30">
+      <x:c r="A30" t="str">
+        <x:v>블록 핸들 후속</x:v>
+      </x:c>
+      <x:c r="B30" t="str">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C30" t="str">
+        <x:v>다중 블록 선택 / 복제 / 삭제</x:v>
+      </x:c>
+      <x:c r="D30" t="str">
+        <x:v>block selection 모델 구현 후</x:v>
+      </x:c>
+      <x:c r="E30" t="str">
+        <x:v>문서 순서와 하나의 undo 단위를 보존한다.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31">
+      <x:c r="A31" t="str">
+        <x:v>블록 핸들 후속</x:v>
+      </x:c>
+      <x:c r="B31" t="str">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="C31" t="str">
+        <x:v>drag handle 재정렬</x:v>
+      </x:c>
+      <x:c r="D31" t="str">
+        <x:v>키보드 대체 수단과 포인터 E2E 후</x:v>
+      </x:c>
+      <x:c r="E31" t="str">
+        <x:v>hover 깜빡임 없이 handle을 표시하고 다중 선택 순서를 유지한다.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32">
+      <x:c r="A32" t="str">
+        <x:v>블록 핸들 후속</x:v>
+      </x:c>
+      <x:c r="B32" t="str">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="C32" t="str">
+        <x:v>synced block 전환</x:v>
+      </x:c>
+      <x:c r="D32" t="str">
+        <x:v>source ID·권한 차이·unlink 정책 구현 후</x:v>
+      </x:c>
+      <x:c r="E32" t="str">
+        <x:v>권한이 없는 원본 내용은 노출하지 않고 snapshot fallback을 정의한다.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33">
+      <x:c r="A33" t="str">
+        <x:v>선택 텍스트 후속</x:v>
+      </x:c>
+      <x:c r="B33" t="str">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C33" t="str">
+        <x:v>AI 수정 제안 preview / 적용</x:v>
+      </x:c>
+      <x:c r="D33" t="str">
+        <x:v>selection anchor와 revision 검증 후</x:v>
+      </x:c>
+      <x:c r="E33" t="str">
+        <x:v>AI가 본문을 즉시 덮지 않고 diff를 보여준 뒤 사용자가 적용한다.</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3130d2c66b584756"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0461fa514f754587"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3652,7 +3771,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2cc96f2efa1346fa"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R933efb67980f439b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3912,7 +4031,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb3cfb6d7bd8b42b3"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R14ef3a13c4724c80"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4104,7 +4223,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc23c8360d5be4f21"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R23aa98e5edbf4522"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4483,7 +4602,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfe8f7afe970247a3"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb83b4f90767846f3"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4743,7 +4862,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1b7a31dcb4dc432c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R05d269da93a44615"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4935,7 +5054,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2f13f82daceb45e8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5a7694b3af3a4f01"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5068,7 +5187,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3fc4e1e866004bc1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ref272d3ba387474c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5481,7 +5600,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd2e4b8b22d744fbf"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R13c81e7cc7ac4f27"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5741,7 +5860,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7912b23623a549ae"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0e0f9be9af3647c8"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6120,7 +6239,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2d5703577ace4ac3"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R262f8168b56741d0"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6635,7 +6754,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R01ccc3a0fdb8453b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R29d3944c382e4f33"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6997,7 +7116,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0cc695c064f74e02"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R34b55139a4a7488d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7359,7 +7478,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R11641ae4603c4a21"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbb4689571212475c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7704,7 +7823,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb4935e9ac73d4582"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc302ba7aef7d4483"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7964,7 +8083,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R086158f3212b488d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1f4634638f4943fb"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8125,7 +8244,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R42231f5e45b24994"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re8bc6dfa077549b9"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9068,7 +9187,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc973f168e0324166"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R28ca3b1f9a724055"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9481,7 +9600,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rad6027826f5847cc"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1cbfb8956174404d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9622,7 +9741,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Reb9ea5bf4bc546d5"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3eb00f63962a49bd"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9848,7 +9967,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R502d4b72e37442b7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9080810c1b7846e3"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9916,13 +10035,13 @@
         <x:v>1.6-notion-block-context</x:v>
       </x:c>
       <x:c r="C3" s="13" t="str">
-        <x:v>구현·로컬 빌드/단위 검증 완료</x:v>
+        <x:v>운영 배포·자동 검증 완료 / 로그인 실화면 전</x:v>
       </x:c>
       <x:c r="D3" s="13" t="str">
         <x:v>블록 노트 바탕 우클릭을 현재 블록 중심 메뉴로 교체했다. 삽입·유형 변경·색·복제·이동·들여쓰기·복사·잘라내기·AI 초안·삭제와 하위 페이지/NAS/Office 연결을 제공한다.</x:v>
       </x:c>
       <x:c r="E3" s="13" t="str">
-        <x:v>공식 Notion 블록 작업 및 Tiptap custom menu 대조. focused 8/8, production build/PDF.js 통과. NAS 배포·로그인 실화면은 배포 단계에서 갱신.</x:v>
+        <x:v>공식 Notion/Tiptap 대조, 로컬·NAS focused 11/11, 양쪽 production build/PDF.js, live main.17763957.js hash 일치, HTTP·서비스 정상.</x:v>
       </x:c>
       <x:c r="F3" s="13" t="str">
         <x:v>Codex</x:v>
@@ -10191,7 +10310,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R58b0c0b46db641d0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R637745a7f01d4955"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10636,16 +10755,16 @@
         <x:v>Notion형 블록 우클릭 작업</x:v>
       </x:c>
       <x:c r="C22" t="str">
-        <x:v>구현·로컬 검증 완료 / NAS 배포·실화면 전</x:v>
+        <x:v>운영 배포·자동 검증 완료 / 로그인 실화면 전</x:v>
       </x:c>
       <x:c r="D22" t="str">
         <x:v>우클릭 좌표 selection, 계층형 메뉴, 9종 transform, 9색/9배경, 단일 블록 복제·형제 이동·indent, 안전 clipboard, AI draft context, 삽입 registry</x:v>
       </x:c>
       <x:c r="E22" t="str">
-        <x:v>focused Jest 8/8·production build/PDF.js</x:v>
+        <x:v>로컬·NAS focused 11/11·production build/PDF.js·live bundle hash·HTTP/PM2/service</x:v>
       </x:c>
       <x:c r="F22" t="str">
-        <x:v>NAS 배포 뒤 로그인된 실제 블록·목록·IME·포인터 E2E. stable blockId 기반 댓글·링크·cross-page move·다중 선택 drag는 M1.5 별도.</x:v>
+        <x:v>로그인된 실제 블록·목록·IME·포인터 E2E. stable blockId 기반 댓글·링크·cross-page move·다중 선택 drag는 M1.5 별도.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -10857,7 +10976,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R759dc1e327b54f11"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R744e63c00eaa44ed"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11140,7 +11259,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R115a679685d34707"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8bad4550c06240ea"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11774,7 +11893,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rde1e744b8dab4f91"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc0b39d8051ff4794"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12017,7 +12136,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R32ef10a739c94f65"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9193e3bc642040ed"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12192,7 +12311,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra4c38ddefa214861"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd832c24768884c46"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12452,7 +12571,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R93ad06971aee452c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc84d549c7fa5420d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/programs/NAS_NOTE_STUDIO_SPEC.xlsx
+++ b/docs/programs/NAS_NOTE_STUDIO_SPEC.xlsx
@@ -2,39 +2,39 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="R01495a5fac094c50"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Product_Vision" sheetId="2" r:id="R1b0df3e21ab4408a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decisions" sheetId="3" r:id="Raef6019d1aa24bb8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Competitors" sheetId="4" r:id="R69d5ba174e9a4148"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open_Source" sheetId="5" r:id="R3e2cbb72f16b46e4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source_Index" sheetId="6" r:id="Rd12d5288d1064ff0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Information_Architecture" sheetId="7" r:id="R15a0cfd421964216"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI_Layout" sheetId="8" r:id="R0125cac1d1bb45b6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="User_Flows" sheetId="9" r:id="R2052d9e1af6640b8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Note_Types" sheetId="10" r:id="Ra87faa74d447410d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Block_Catalog" sheetId="11" r:id="R0e7bb4af820f4c9f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Slash_Commands" sheetId="12" r:id="R36b6a4be8d8349c0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Context_Menus" sheetId="13" r:id="R0f917e9e41834259"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Keyboard_Shortcuts" sheetId="14" r:id="Rfeb423838295469f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Database_Views" sheetId="15" r:id="Rc8ca46e98d984bf3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Code_Text_Mode" sheetId="16" r:id="R53f21c3afbcb4152"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Python_Notebook" sheetId="17" r:id="Rd2f92ec80bb34a0f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Collaboration" sheetId="18" r:id="Ra023432a17c24aa8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Offline_Desktop" sheetId="19" r:id="R358fe806515848ef"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data_Model" sheetId="20" r:id="R8089cfd9b3844c29"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Storage_Interop" sheetId="21" r:id="Rcac3d2fb88054dbe"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Security" sheetId="22" r:id="R865eee1b7cad406f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="API_Contracts" sheetId="23" r:id="Rd8a0ec0f45f24431"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="State_Machines" sheetId="24" r:id="R865e91dcdb9342c6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Error_Recovery" sheetId="25" r:id="Rb9abe69cc7cb4dda"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cross_App_Relations" sheetId="26" r:id="R47766de25f0d4b6a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Performance" sheetId="27" r:id="Rfd4666a3c25e4e49"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Accessibility" sheetId="28" r:id="R57c33c1e714041dc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test_Matrix" sheetId="29" r:id="R47b35de290964766"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="30" r:id="R2cc730fc5fb3462a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open_Questions" sheetId="31" r:id="R1e5bd6e940ad41b7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Change_Log" sheetId="32" r:id="Rbbf908f6d82b424c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Implementation_Status" sheetId="33" r:id="R6e362db30b2f4328"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="R7b84e671d8024f5d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Product_Vision" sheetId="2" r:id="R65126015ae564e50"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decisions" sheetId="3" r:id="R5f4b72491362468e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Competitors" sheetId="4" r:id="R257a86956a0e4010"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open_Source" sheetId="5" r:id="R6284affb39ca4e49"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source_Index" sheetId="6" r:id="Rd3cfbb3d507f409d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Information_Architecture" sheetId="7" r:id="Recace7cf5f054dad"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI_Layout" sheetId="8" r:id="Rd9a643b4165446e6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="User_Flows" sheetId="9" r:id="Ra2cdc45d18f145fb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Note_Types" sheetId="10" r:id="Rdd937a26c1fa4302"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Block_Catalog" sheetId="11" r:id="R742603e5fd044433"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Slash_Commands" sheetId="12" r:id="R6e064618429c4a9f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Context_Menus" sheetId="13" r:id="R202981ac6cf84077"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Keyboard_Shortcuts" sheetId="14" r:id="R9bca67861084468f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Database_Views" sheetId="15" r:id="R4b34f30d4ba940d0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Code_Text_Mode" sheetId="16" r:id="R9462945b901e4937"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Python_Notebook" sheetId="17" r:id="R3f042cfc161540f3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Collaboration" sheetId="18" r:id="Rf337ff1114f2482e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Offline_Desktop" sheetId="19" r:id="Rfb499bbc5c834758"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data_Model" sheetId="20" r:id="R388ec4ccf86d46c2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Storage_Interop" sheetId="21" r:id="Ra1d2db1dec3245b8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Security" sheetId="22" r:id="R72d60422bc1c4196"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="API_Contracts" sheetId="23" r:id="Re475f71d975a4e65"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="State_Machines" sheetId="24" r:id="Re6a279657a534923"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Error_Recovery" sheetId="25" r:id="R5e352302213640d4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cross_App_Relations" sheetId="26" r:id="R9448f52436194b40"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Performance" sheetId="27" r:id="Ra3f2f9640e3d4a01"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Accessibility" sheetId="28" r:id="R62f305ba489a4cdf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test_Matrix" sheetId="29" r:id="R6031029ea4a44ff6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="30" r:id="Rb1a3c1ca70d64fac"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open_Questions" sheetId="31" r:id="R61905b07673a4c65"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Change_Log" sheetId="32" r:id="Rcbebf666ef19466c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Implementation_Status" sheetId="33" r:id="R2e70b48918e34aff"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -928,7 +928,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfa85f6d1666342b4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5f140ff05be34b2f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1271,7 +1271,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5b085e2f79a14443"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R25711d357c7146bb"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1674,7 +1674,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf798e154f18a4357"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3e9fdb8b9530402e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2197,7 +2197,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcced9a602a7e45a8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R57e3bad3167d406d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2777,10 +2777,27 @@
         <x:v>AI가 본문을 즉시 덮지 않고 diff를 보여준 뒤 사용자가 적용한다.</x:v>
       </x:c>
     </x:row>
+    <x:row r="34">
+      <x:c r="A34" t="str">
+        <x:v>노트북 트리</x:v>
+      </x:c>
+      <x:c r="B34" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C34" t="str">
+        <x:v>접기/펼치기 · 더블클릭 터미널 열기</x:v>
+      </x:c>
+      <x:c r="D34" t="str">
+        <x:v>노트북 available 상태</x:v>
+      </x:c>
+      <x:c r="E34" t="str">
+        <x:v>각 노트북의 하위 페이지만 숨기며 선택·내용은 삭제하지 않는다. 터미널은 해당 노트북 scope를 고정한다.</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0461fa514f754587"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R91d6757aa3df460d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3768,10 +3785,27 @@
         <x:v>M1 구현</x:v>
       </x:c>
     </x:row>
+    <x:row r="58">
+      <x:c r="A58" t="str">
+        <x:v>노트북 터미널</x:v>
+      </x:c>
+      <x:c r="B58" t="str">
+        <x:v>Enter · ArrowUp/ArrowDown · Ctrl+L</x:v>
+      </x:c>
+      <x:c r="C58" t="str">
+        <x:v>명령 실행 · 이전/다음 명령 · 출력 지우기</x:v>
+      </x:c>
+      <x:c r="D58" t="str">
+        <x:v>실행 중에는 중복 실행 차단. 브라우저 전역 Ctrl+L은 터미널 입력 포커스에서만 소비</x:v>
+      </x:c>
+      <x:c r="E58" t="str">
+        <x:v>Tab completion과 지속 대화형 PTY는 후속 단계</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R933efb67980f439b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0f89d11da3a9493d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4031,7 +4065,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R14ef3a13c4724c80"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R74269825d8d3499c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4223,7 +4257,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R23aa98e5edbf4522"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb0ef2d54853d4524"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4602,7 +4636,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb83b4f90767846f3"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7fc3053ce7894852"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4862,7 +4896,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R05d269da93a44615"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6e4add14f1524ff8"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5054,7 +5088,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5a7694b3af3a4f01"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7f4e362cfa1e4434"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5187,7 +5221,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ref272d3ba387474c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R687a66a27fd1456d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5600,7 +5634,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R13c81e7cc7ac4f27"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb7081fa50b424ca2"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5860,7 +5894,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0e0f9be9af3647c8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R02ca40758edd4e54"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6236,10 +6270,27 @@
         <x:v>P0</x:v>
       </x:c>
     </x:row>
+    <x:row r="22">
+      <x:c r="A22" t="str">
+        <x:v>SEC-21</x:v>
+      </x:c>
+      <x:c r="B22" t="str">
+        <x:v>웹 터미널의 호스트·타계정·자원 탈출</x:v>
+      </x:c>
+      <x:c r="C22" t="str">
+        <x:v>서버가 로그인 계정 notebook registry와 realpath를 재검증하고 폴더 하나만 bind mount. network none, non-root, read-only rootfs, cap-drop, no-new-privileges, CPU/RAM/PID/time/output·resource admission. 숨김·symlink는 탐색기 제외.</x:v>
+      </x:c>
+      <x:c r="D22" t="str">
+        <x:v>다른 notebookId, ../, symlink, /etc·Docker socket, network, fork/무한 루프, 128KB 출력, worker cleanup</x:v>
+      </x:c>
+      <x:c r="E22" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R262f8168b56741d0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R98d46b6a0ff54894"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6751,10 +6802,27 @@
         <x:v>서버 카탈로그만 반환하며 host 경로·image digest 내부 설정·credential을 노출하지 않는다.</x:v>
       </x:c>
     </x:row>
+    <x:row r="30">
+      <x:c r="A30" t="str">
+        <x:v>Terminal</x:v>
+      </x:c>
+      <x:c r="B30" t="str">
+        <x:v>GET files / POST terminal</x:v>
+      </x:c>
+      <x:c r="C30" t="str">
+        <x:v>notebookId는 URL, command와 notebook 상대 cwd만 허용</x:v>
+      </x:c>
+      <x:c r="D30" t="str">
+        <x:v>파일 최대 2,000개·깊이 10 또는 stdout/stderr/exitCode/cwd/sandbox</x:v>
+      </x:c>
+      <x:c r="E30" t="str">
+        <x:v>로그인 계정이 소유한 notebookId를 매 요청 재조회. 클라이언트 절대경로·userId는 받지 않음.</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R29d3944c382e4f33"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0ab573f540d4446c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7113,10 +7181,27 @@
         <x:v>active 전까지 기존 runtime revision을 유지하고 같은 lock hash는 재사용한다. 실행 컨테이너는 package build 상태와 무관하게 network none이다.</x:v>
       </x:c>
     </x:row>
+    <x:row r="21">
+      <x:c r="A21" t="str">
+        <x:v>노트북 터미널</x:v>
+      </x:c>
+      <x:c r="B21" t="str">
+        <x:v>closed → ready → running → ready/error</x:v>
+      </x:c>
+      <x:c r="C21" t="str">
+        <x:v>유효한 노트북에서 열기, 명령 제출</x:v>
+      </x:c>
+      <x:c r="D21" t="str">
+        <x:v>close, run, success/error/timeout/output-limit</x:v>
+      </x:c>
+      <x:c r="E21" t="str">
+        <x:v>running 중 중복 명령 금지. 노트북 scope는 명시적으로 새 터미널을 열 때만 변경.</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R34b55139a4a7488d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R96a1c89fedd84775"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7475,10 +7560,27 @@
         <x:v>부분 설치 이미지를 활성화하지 않고 quota reservation과 builder 임시 산출물을 정리한다.</x:v>
       </x:c>
     </x:row>
+    <x:row r="21">
+      <x:c r="A21" t="str">
+        <x:v>터미널 worker/명령 실패</x:v>
+      </x:c>
+      <x:c r="B21" t="str">
+        <x:v>컨테이너 강제 정리와 resource reservation 반환. 파일 목록은 마지막 성공본 유지.</x:v>
+      </x:c>
+      <x:c r="C21" t="str">
+        <x:v>명령 수정 후 다시 실행, NAS 파일관리자에서 확인</x:v>
+      </x:c>
+      <x:c r="D21" t="str">
+        <x:v>명령·출력을 서버 장기 원장에 저장하지 않으며 노트북 밖 파일은 애초에 mount하지 않음.</x:v>
+      </x:c>
+      <x:c r="E21" t="str">
+        <x:v>worker 잔류 0, PM2 정상, 다음 명령 성공</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbb4689571212475c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Reffb98b7818e49e7"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7820,10 +7922,27 @@
         <x:v>계정 전환·빠른 note 전환에서 stale 상태가 다른 사용자나 페이지에 적용됨</x:v>
       </x:c>
     </x:row>
+    <x:row r="20">
+      <x:c r="A20" t="str">
+        <x:v>SERVER-RESOURCE-CONTROL</x:v>
+      </x:c>
+      <x:c r="B20" t="str">
+        <x:v>depends_on</x:v>
+      </x:c>
+      <x:c r="C20" t="str">
+        <x:v>기존 관리 작업 CPU/RAM 예약과 자동 압력 gate</x:v>
+      </x:c>
+      <x:c r="D20" t="str">
+        <x:v>터미널 세션별 12.5%/256MiB 요청과 명령 종료 release</x:v>
+      </x:c>
+      <x:c r="E20" t="str">
+        <x:v>동시 사용자 명령이 backend·OnlyOffice·파일 전송을 굶기지 않는지 부하 검증</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc302ba7aef7d4483"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re83db4783d924dd8"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8083,7 +8202,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1f4634638f4943fb"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R96cafbf7998f459d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8244,7 +8363,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re8bc6dfa077549b9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdcfc0a49b8344c8d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9184,10 +9303,30 @@
         <x:v>M1-L</x:v>
       </x:c>
     </x:row>
+    <x:row r="47">
+      <x:c r="A47" t="str">
+        <x:v>T-047</x:v>
+      </x:c>
+      <x:c r="B47" t="str">
+        <x:v>노트북 터미널·파일 목록</x:v>
+      </x:c>
+      <x:c r="C47" t="str">
+        <x:v>A/B 계정, 서로 다른 notebookId, ../·symlink, cd/pwd, 파일 생성·삭제, 무한 루프·대량 출력·동시 실행, 접기/재로그인</x:v>
+      </x:c>
+      <x:c r="D47" t="str">
+        <x:v>현재 계정의 선택 노트북 하나만 보이고 하위 페이지 접기와 파일 목록 표시 상태가 복원된다. 자원 한도에서 종료되며 다른 계정·호스트 경로는 노출되지 않는다.</x:v>
+      </x:c>
+      <x:c r="E47" t="str">
+        <x:v>unit+security+NAS integration+로그인 E2E</x:v>
+      </x:c>
+      <x:c r="F47" t="str">
+        <x:v>M1-N</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R28ca3b1f9a724055"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf5e8a64886c44875"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9597,10 +9736,27 @@
         <x:v>협업 편집에서 사용자별 selection 공유 정책이나 명시적 장치 동기화 옵션을 추가할 때</x:v>
       </x:c>
     </x:row>
+    <x:row r="24">
+      <x:c r="A24" t="str">
+        <x:v>DEC-024</x:v>
+      </x:c>
+      <x:c r="B24" t="str">
+        <x:v>채택</x:v>
+      </x:c>
+      <x:c r="C24" t="str">
+        <x:v>터미널은 호스트 셸이 아닌 노트북 단위 격리 명령 작업공간으로 시작</x:v>
+      </x:c>
+      <x:c r="D24" t="str">
+        <x:v>사용자는 자기 노트북 실제 파일을 다뤄야 하지만 NAS 전체와 다른 계정, Docker socket, network, 비밀 환경은 노출하면 안 된다. 1명령 1컨테이너가 복구·자원 회수와 현재 저사양 NAS에 더 안전하다.</x:v>
+      </x:c>
+      <x:c r="E24" t="str">
+        <x:v>지속 PTY가 필요한 명확한 사용 사례와 WebSocket origin/auth·idle cleanup·부하 테스트가 준비될 때</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1cbfb8956174404d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3c1847a97ea248a7"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9741,7 +9897,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3eb00f63962a49bd"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6b8db216a45c40fc"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9967,7 +10123,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9080810c1b7846e3"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7c3b24e20daf42d9"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10307,10 +10463,30 @@
         <x:v>Codex</x:v>
       </x:c>
     </x:row>
+    <x:row r="17">
+      <x:c r="A17" t="str">
+        <x:v>2026-09-08</x:v>
+      </x:c>
+      <x:c r="B17" t="str">
+        <x:v>1.7-notebook-terminal</x:v>
+      </x:c>
+      <x:c r="C17" t="str">
+        <x:v>로컬 구현·자동 검증 완료 / NAS 운영 배포 전</x:v>
+      </x:c>
+      <x:c r="D17" t="str">
+        <x:v>선택 노트북 전용 격리 명령 터미널, 옆 실제 파일 목록, 노트북별 하위 페이지 접기와 상태 복원을 추가했다. 단색 아이콘과 고정 영역으로 기존 노트 UI에 통합했다.</x:v>
+      </x:c>
+      <x:c r="E17" t="str">
+        <x:v>JupyterLab·xterm.js·Docker 공식 문서 대조. 로컬 terminal/note 22/22, 전체 backend 107 pass·6 skip, production/PDF.js. NAS 배포 검증 전.</x:v>
+      </x:c>
+      <x:c r="F17" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R637745a7f01d4955"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd264ef98dda3457a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10765,6 +10941,26 @@
       </x:c>
       <x:c r="F22" t="str">
         <x:v>로그인된 실제 블록·목록·IME·포인터 E2E. stable blockId 기반 댓글·링크·cross-page move·다중 선택 drag는 M1.5 별도.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23">
+      <x:c r="A23" t="str">
+        <x:v>M1-N</x:v>
+      </x:c>
+      <x:c r="B23" t="str">
+        <x:v>노트북별 격리 명령 터미널·접이식 탐색기</x:v>
+      </x:c>
+      <x:c r="C23" t="str">
+        <x:v>로컬 구현·자동 검증 완료 / NAS 운영 배포 전</x:v>
+      </x:c>
+      <x:c r="D23" t="str">
+        <x:v>서버 registry 기반 notebook mount, 명령 worker, files/terminal API, 사용자 breadcrumb, cd/pwd/history/Ctrl+L, 옆 파일 목록, 노트북별 접기와 session 복원</x:v>
+      </x:c>
+      <x:c r="E23" t="str">
+        <x:v>로컬 focused 22/22·전체 backend 107 pass 6 skip·production/PDF.js</x:v>
+      </x:c>
+      <x:c r="F23" t="str">
+        <x:v>NAS 실제 Docker write/path/network/timeout smoke와 로그인 브라우저 시각·키보드 E2E. 지속 PTY는 별도 M2 단계.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -10976,7 +11172,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R744e63c00eaa44ed"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc697b56b06ed4248"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11259,7 +11455,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8bad4550c06240ea"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R88876da9cc7348a3"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11890,10 +12086,78 @@
         <x:v>2026-09-06</x:v>
       </x:c>
     </x:row>
+    <x:row r="37">
+      <x:c r="A37" t="str">
+        <x:v>SRC-037</x:v>
+      </x:c>
+      <x:c r="B37" t="str">
+        <x:v>JupyterLab 터미널·작업 경로</x:v>
+      </x:c>
+      <x:c r="C37" t="str">
+        <x:v>https://jupyterlab.readthedocs.io/en/stable/user/terminal.html</x:v>
+      </x:c>
+      <x:c r="D37" t="str">
+        <x:v>서버 사용자 권한에서 터미널이 실행되며 파일 브라우저와 주 작업영역을 연결하는 기본 UX</x:v>
+      </x:c>
+      <x:c r="E37" t="str">
+        <x:v>2026-09-08</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38">
+      <x:c r="A38" t="str">
+        <x:v>SRC-038</x:v>
+      </x:c>
+      <x:c r="B38" t="str">
+        <x:v>JupyterLab 레이아웃·파일 브라우저</x:v>
+      </x:c>
+      <x:c r="C38" t="str">
+        <x:v>https://jupyterlab.readthedocs.io/en/stable/user/interface_customization.html</x:v>
+      </x:c>
+      <x:c r="D38" t="str">
+        <x:v>파일 브라우저와 터미널을 좌·우·하단 영역에 두고 workspace layout을 복원하는 패턴</x:v>
+      </x:c>
+      <x:c r="E38" t="str">
+        <x:v>2026-09-08</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39">
+      <x:c r="A39" t="str">
+        <x:v>SRC-039</x:v>
+      </x:c>
+      <x:c r="B39" t="str">
+        <x:v>xterm.js 웹 터미널 보안</x:v>
+      </x:c>
+      <x:c r="C39" t="str">
+        <x:v>https://xtermjs.org/docs/guides/security/</x:v>
+      </x:c>
+      <x:c r="D39" t="str">
+        <x:v>터미널 데이터 불신, root 서비스 금지, WebSocket 추가 인증·인가가 필요함</x:v>
+      </x:c>
+      <x:c r="E39" t="str">
+        <x:v>2026-09-08</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40">
+      <x:c r="A40" t="str">
+        <x:v>SRC-040</x:v>
+      </x:c>
+      <x:c r="B40" t="str">
+        <x:v>Docker resource constraints</x:v>
+      </x:c>
+      <x:c r="C40" t="str">
+        <x:v>https://docs.docker.com/engine/containers/resource_constraints/</x:v>
+      </x:c>
+      <x:c r="D40" t="str">
+        <x:v>기본 컨테이너는 자원 제한이 없으므로 memory·CPU 제한을 명시해야 함</x:v>
+      </x:c>
+      <x:c r="E40" t="str">
+        <x:v>2026-09-08</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc0b39d8051ff4794"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcc03d50c600144a9"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12136,7 +12400,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9193e3bc642040ed"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re1b6fd0502804e5c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12308,10 +12572,27 @@
         <x:v>버전 손상 시 원본 유지, 다운로드 가능한 raw snapshot 제공.</x:v>
       </x:c>
     </x:row>
+    <x:row r="10">
+      <x:c r="A10" t="str">
+        <x:v>노트북 터미널</x:v>
+      </x:c>
+      <x:c r="B10" t="str">
+        <x:v>노트북 트리 → 터미널 header/breadcrumb → 옆 파일 목록 → 출력 → 명령 입력</x:v>
+      </x:c>
+      <x:c r="C10" t="str">
+        <x:v>노트북별 접기, 전체 접기, 터미널, 파일 목록 토글·새로고침·NAS에서 열기, history, Ctrl+L</x:v>
+      </x:c>
+      <x:c r="D10" t="str">
+        <x:v>모바일은 노트 트리를 숨기고 터미널 파일 목록 폭을 줄인다. 단색 아이콘, 고정 높이 header, HTML 해석 없는 monospace 출력.</x:v>
+      </x:c>
+      <x:c r="E10" t="str">
+        <x:v>노트북 없음·경로 소실·자원 대기·명령 오류·출력/시간 제한을 서로 다른 문장으로 표시한다.</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd832c24768884c46"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5a7018a58ff14630"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12568,10 +12849,27 @@
         <x:v>원래 폴더 이동은 stable ID로 재해석. 삭제·권한 상실이면 위치를 다시 요구하고 임의 fallback 금지</x:v>
       </x:c>
     </x:row>
+    <x:row r="15">
+      <x:c r="A15" t="str">
+        <x:v>FLOW-TERMINAL</x:v>
+      </x:c>
+      <x:c r="B15" t="str">
+        <x:v>선택한 노트북 또는 그 안의 페이지</x:v>
+      </x:c>
+      <x:c r="C15" t="str">
+        <x:v>터미널 버튼 → 서버가 계정 notebookId 재확정 → 노트북 폴더에서 명령 → 결과 → 파일 목록 새로고침</x:v>
+      </x:c>
+      <x:c r="D15" t="str">
+        <x:v>같은 노트북 범위에서 명령 결과와 파일 변경을 확인하고 닫아 기존 노트 편집으로 복귀</x:v>
+      </x:c>
+      <x:c r="E15" t="str">
+        <x:v>다른 계정/노트북 경로·symlink·../는 거부. worker 실패는 입력/기존 파일을 보존하며 자동 재실행하지 않는다.</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc84d549c7fa5420d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9036b863ad9f4b16"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/programs/NAS_NOTE_STUDIO_SPEC.xlsx
+++ b/docs/programs/NAS_NOTE_STUDIO_SPEC.xlsx
@@ -2,39 +2,39 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="R7b84e671d8024f5d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Product_Vision" sheetId="2" r:id="R65126015ae564e50"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decisions" sheetId="3" r:id="R5f4b72491362468e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Competitors" sheetId="4" r:id="R257a86956a0e4010"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open_Source" sheetId="5" r:id="R6284affb39ca4e49"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source_Index" sheetId="6" r:id="Rd3cfbb3d507f409d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Information_Architecture" sheetId="7" r:id="Recace7cf5f054dad"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI_Layout" sheetId="8" r:id="Rd9a643b4165446e6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="User_Flows" sheetId="9" r:id="Ra2cdc45d18f145fb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Note_Types" sheetId="10" r:id="Rdd937a26c1fa4302"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Block_Catalog" sheetId="11" r:id="R742603e5fd044433"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Slash_Commands" sheetId="12" r:id="R6e064618429c4a9f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Context_Menus" sheetId="13" r:id="R202981ac6cf84077"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Keyboard_Shortcuts" sheetId="14" r:id="R9bca67861084468f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Database_Views" sheetId="15" r:id="R4b34f30d4ba940d0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Code_Text_Mode" sheetId="16" r:id="R9462945b901e4937"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Python_Notebook" sheetId="17" r:id="R3f042cfc161540f3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Collaboration" sheetId="18" r:id="Rf337ff1114f2482e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Offline_Desktop" sheetId="19" r:id="Rfb499bbc5c834758"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data_Model" sheetId="20" r:id="R388ec4ccf86d46c2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Storage_Interop" sheetId="21" r:id="Ra1d2db1dec3245b8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Security" sheetId="22" r:id="R72d60422bc1c4196"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="API_Contracts" sheetId="23" r:id="Re475f71d975a4e65"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="State_Machines" sheetId="24" r:id="Re6a279657a534923"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Error_Recovery" sheetId="25" r:id="R5e352302213640d4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cross_App_Relations" sheetId="26" r:id="R9448f52436194b40"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Performance" sheetId="27" r:id="Ra3f2f9640e3d4a01"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Accessibility" sheetId="28" r:id="R62f305ba489a4cdf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test_Matrix" sheetId="29" r:id="R6031029ea4a44ff6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="30" r:id="Rb1a3c1ca70d64fac"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open_Questions" sheetId="31" r:id="R61905b07673a4c65"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Change_Log" sheetId="32" r:id="Rcbebf666ef19466c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Implementation_Status" sheetId="33" r:id="R2e70b48918e34aff"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="R674295c9eef44088"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Product_Vision" sheetId="2" r:id="Ra1ffab8034c04dc5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decisions" sheetId="3" r:id="R4e4e68c6c1724784"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Competitors" sheetId="4" r:id="Rb9ceaad1b4854d05"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open_Source" sheetId="5" r:id="Rdac94f18bd9c4497"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source_Index" sheetId="6" r:id="Rd688cf3c8afc4837"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Information_Architecture" sheetId="7" r:id="R89c6024caace42fc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI_Layout" sheetId="8" r:id="R75e156c1e679478d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="User_Flows" sheetId="9" r:id="R3f18209bc1c14876"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Note_Types" sheetId="10" r:id="Rc66f9eb527b448ae"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Block_Catalog" sheetId="11" r:id="R7c1d607dc9ce4b97"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Slash_Commands" sheetId="12" r:id="R4bdb40f380f843d8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Context_Menus" sheetId="13" r:id="Rce223f60391b4579"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Keyboard_Shortcuts" sheetId="14" r:id="R04cb4eb8f4be4c74"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Database_Views" sheetId="15" r:id="R9e7e4307640d4b64"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Code_Text_Mode" sheetId="16" r:id="R6af9185838d94861"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Python_Notebook" sheetId="17" r:id="R5287264166044e4b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Collaboration" sheetId="18" r:id="R8d61579cd611434c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Offline_Desktop" sheetId="19" r:id="R7f643fc1c2094689"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data_Model" sheetId="20" r:id="Rbf505318d0aa4245"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Storage_Interop" sheetId="21" r:id="Rb57a9f4b28e44d72"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Security" sheetId="22" r:id="R336939bfa67546e0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="API_Contracts" sheetId="23" r:id="R6601a8f856494a79"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="State_Machines" sheetId="24" r:id="Re0846f9818134ed1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Error_Recovery" sheetId="25" r:id="R6a202d21b2fe4ce2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cross_App_Relations" sheetId="26" r:id="Reff45843b750417a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Performance" sheetId="27" r:id="Rd452e4f152ed4b7d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Accessibility" sheetId="28" r:id="R89959847cf9245d0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test_Matrix" sheetId="29" r:id="R61b161fef5514967"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="30" r:id="Rd378f50249414777"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open_Questions" sheetId="31" r:id="Rc5f91f5e76ce43c8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Change_Log" sheetId="32" r:id="Re5a0b79db2af4a10"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Implementation_Status" sheetId="33" r:id="Rcf6f8f0813884d5a"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -928,7 +928,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5f140ff05be34b2f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0873787ffd99489b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1271,7 +1271,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R25711d357c7146bb"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R442a0162d7234d46"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1674,7 +1674,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3e9fdb8b9530402e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1cad5f46f7154933"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2197,7 +2197,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R57e3bad3167d406d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6402182531f64d83"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2797,7 +2797,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R91d6757aa3df460d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1d6ab4e7f5b74223"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3805,7 +3805,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0f89d11da3a9493d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re09f42a06c4f41f4"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4065,7 +4065,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R74269825d8d3499c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb4ba01256b5d45b9"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4257,7 +4257,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb0ef2d54853d4524"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd3be0b74ae3241af"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4636,7 +4636,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7fc3053ce7894852"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Race6555d25034e94"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4896,7 +4896,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6e4add14f1524ff8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3e45a3087f554a1f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5088,7 +5088,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7f4e362cfa1e4434"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb20d49a8cf9d4f36"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5221,7 +5221,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R687a66a27fd1456d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd2d6a81c50eb4d7a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5634,7 +5634,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb7081fa50b424ca2"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7625944adf2c44a0"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5894,7 +5894,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R02ca40758edd4e54"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R33ac82a2d4c84a6c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6278,7 +6278,7 @@
         <x:v>웹 터미널의 호스트·타계정·자원 탈출</x:v>
       </x:c>
       <x:c r="C22" t="str">
-        <x:v>서버가 로그인 계정 notebook registry와 realpath를 재검증하고 폴더 하나만 bind mount. network none, non-root, read-only rootfs, cap-drop, no-new-privileges, CPU/RAM/PID/time/output·resource admission. 숨김·symlink는 탐색기 제외.</x:v>
+        <x:v>서버가 로그인 계정 notebook registry와 realpath를 재검증하고 폴더 하나만 bind mount. 전용 numeric UID에 선택 폴더 ACL만 부여하며 network none, non-root, read-only rootfs, cap-drop, no-new-privileges, CPU/RAM/PID/time/output·resource admission. symlink는 탐색기 제외.</x:v>
       </x:c>
       <x:c r="D22" t="str">
         <x:v>다른 notebookId, ../, symlink, /etc·Docker socket, network, fork/무한 루프, 128KB 출력, worker cleanup</x:v>
@@ -6290,7 +6290,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R98d46b6a0ff54894"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re8029f49660f4457"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6822,7 +6822,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0ab573f540d4446c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R36b09412f3684ea8"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7201,7 +7201,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R96a1c89fedd84775"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4163fe3fcb004fe8"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7580,7 +7580,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Reffb98b7818e49e7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Red48219616864c0d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7942,7 +7942,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re83db4783d924dd8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6bf1af55bdfc4049"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8202,7 +8202,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R96cafbf7998f459d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfdcbf944ea69455c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8363,7 +8363,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdcfc0a49b8344c8d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9c28ee2b3d3c486c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9326,7 +9326,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf5e8a64886c44875"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc8fe0284424f4f38"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9756,7 +9756,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3c1847a97ea248a7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc7117451337c41e8"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9897,7 +9897,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6b8db216a45c40fc"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8379cb7ae2794295"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10123,7 +10123,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7c3b24e20daf42d9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfa0fb815d32f42cb"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10471,13 +10471,13 @@
         <x:v>1.7-notebook-terminal</x:v>
       </x:c>
       <x:c r="C17" t="str">
-        <x:v>로컬 구현·자동 검증 완료 / NAS 운영 배포 전</x:v>
+        <x:v>운영 배포·NAS Docker 검증 완료 / 로그인 화면 E2E 대기</x:v>
       </x:c>
       <x:c r="D17" t="str">
-        <x:v>선택 노트북 전용 격리 명령 터미널, 옆 실제 파일 목록, 노트북별 하위 페이지 접기와 상태 복원을 추가했다. 단색 아이콘과 고정 영역으로 기존 노트 UI에 통합했다.</x:v>
+        <x:v>선택 노트북 전용 격리 명령 터미널, 옆 실제 파일 목록, 노트북별 하위 페이지 접기와 상태 복원을 추가했다. 전용 UID ACL로 root 소유 저장소에서도 non-root 쓰기를 보장했다.</x:v>
       </x:c>
       <x:c r="E17" t="str">
-        <x:v>JupyterLab·xterm.js·Docker 공식 문서 대조. 로컬 terminal/note 22/22, 전체 backend 107 pass·6 skip, production/PDF.js. NAS 배포 검증 전.</x:v>
+        <x:v>JupyterLab·xterm.js·Docker 공식 문서 대조. 로컬 108 pass·7 skip, NAS 전체 110 pass·5 skip와 실제 runtime 3/3, production/PDF.js, main.318445b3.js, HTTP/PM2/service 정상.</x:v>
       </x:c>
       <x:c r="F17" t="str">
         <x:v>Codex</x:v>
@@ -10486,7 +10486,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd264ef98dda3457a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R53e14ec08ee44e60"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10951,16 +10951,16 @@
         <x:v>노트북별 격리 명령 터미널·접이식 탐색기</x:v>
       </x:c>
       <x:c r="C23" t="str">
-        <x:v>로컬 구현·자동 검증 완료 / NAS 운영 배포 전</x:v>
+        <x:v>운영 배포·NAS Docker 검증 완료 / 로그인 화면 E2E 대기</x:v>
       </x:c>
       <x:c r="D23" t="str">
-        <x:v>서버 registry 기반 notebook mount, 명령 worker, files/terminal API, 사용자 breadcrumb, cd/pwd/history/Ctrl+L, 옆 파일 목록, 노트북별 접기와 session 복원</x:v>
+        <x:v>서버 registry 기반 notebook mount, 전용 UID ACL, 명령 worker, files/terminal API, 사용자 breadcrumb, cd/pwd/history/Ctrl+L, 옆 파일 목록, 노트북별 접기와 session 복원</x:v>
       </x:c>
       <x:c r="E23" t="str">
-        <x:v>로컬 focused 22/22·전체 backend 107 pass 6 skip·production/PDF.js</x:v>
+        <x:v>로컬 focused 22/22·전체 108 pass 7 skip. NAS 전체 110 pass 5 skip, 수정 후 focused 22/22·실제 runtime 3/3, production/PDF.js, main.318445b3.js, HTTP/PM2/service 정상</x:v>
       </x:c>
       <x:c r="F23" t="str">
-        <x:v>NAS 실제 Docker write/path/network/timeout smoke와 로그인 브라우저 시각·키보드 E2E. 지속 PTY는 별도 M2 단계.</x:v>
+        <x:v>자동 브라우저에 로그인 세션이 없어 실제 사용자 노트의 접기·파일 클릭·명령 입력 육안 E2E만 남음. 지속 PTY는 별도 M2 단계.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -11172,7 +11172,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc697b56b06ed4248"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4d00833d963049ce"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11455,7 +11455,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R88876da9cc7348a3"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R30a4593736fa4bb1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12157,7 +12157,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcc03d50c600144a9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7b6f0327275c414d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12400,7 +12400,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re1b6fd0502804e5c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R44595a5a0b1840ea"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12592,7 +12592,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5a7018a58ff14630"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfdc7a49e7a674cb9"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12869,7 +12869,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9036b863ad9f4b16"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R622b8b1393de429c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/programs/NAS_NOTE_STUDIO_SPEC.xlsx
+++ b/docs/programs/NAS_NOTE_STUDIO_SPEC.xlsx
@@ -2,39 +2,39 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="R674295c9eef44088"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Product_Vision" sheetId="2" r:id="Ra1ffab8034c04dc5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decisions" sheetId="3" r:id="R4e4e68c6c1724784"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Competitors" sheetId="4" r:id="Rb9ceaad1b4854d05"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open_Source" sheetId="5" r:id="Rdac94f18bd9c4497"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source_Index" sheetId="6" r:id="Rd688cf3c8afc4837"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Information_Architecture" sheetId="7" r:id="R89c6024caace42fc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI_Layout" sheetId="8" r:id="R75e156c1e679478d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="User_Flows" sheetId="9" r:id="R3f18209bc1c14876"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Note_Types" sheetId="10" r:id="Rc66f9eb527b448ae"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Block_Catalog" sheetId="11" r:id="R7c1d607dc9ce4b97"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Slash_Commands" sheetId="12" r:id="R4bdb40f380f843d8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Context_Menus" sheetId="13" r:id="Rce223f60391b4579"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Keyboard_Shortcuts" sheetId="14" r:id="R04cb4eb8f4be4c74"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Database_Views" sheetId="15" r:id="R9e7e4307640d4b64"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Code_Text_Mode" sheetId="16" r:id="R6af9185838d94861"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Python_Notebook" sheetId="17" r:id="R5287264166044e4b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Collaboration" sheetId="18" r:id="R8d61579cd611434c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Offline_Desktop" sheetId="19" r:id="R7f643fc1c2094689"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data_Model" sheetId="20" r:id="Rbf505318d0aa4245"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Storage_Interop" sheetId="21" r:id="Rb57a9f4b28e44d72"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Security" sheetId="22" r:id="R336939bfa67546e0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="API_Contracts" sheetId="23" r:id="R6601a8f856494a79"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="State_Machines" sheetId="24" r:id="Re0846f9818134ed1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Error_Recovery" sheetId="25" r:id="R6a202d21b2fe4ce2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cross_App_Relations" sheetId="26" r:id="Reff45843b750417a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Performance" sheetId="27" r:id="Rd452e4f152ed4b7d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Accessibility" sheetId="28" r:id="R89959847cf9245d0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test_Matrix" sheetId="29" r:id="R61b161fef5514967"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="30" r:id="Rd378f50249414777"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open_Questions" sheetId="31" r:id="Rc5f91f5e76ce43c8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Change_Log" sheetId="32" r:id="Re5a0b79db2af4a10"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Implementation_Status" sheetId="33" r:id="Rcf6f8f0813884d5a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="R9c311f5c8223442f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Product_Vision" sheetId="2" r:id="R973ea176431c463d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decisions" sheetId="3" r:id="R56d9fcfed1c147db"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Competitors" sheetId="4" r:id="Rd84fd067c39b440f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open_Source" sheetId="5" r:id="R6cd3d78aa6814cbf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source_Index" sheetId="6" r:id="Re57085d2ccb047f3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Information_Architecture" sheetId="7" r:id="Rb321cf3d9de74a43"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI_Layout" sheetId="8" r:id="Rcc495092aec64a0f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="User_Flows" sheetId="9" r:id="Rff98194e26f84fe5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Note_Types" sheetId="10" r:id="Re490aa00a9e94304"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Block_Catalog" sheetId="11" r:id="R698afdad235b4ae4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Slash_Commands" sheetId="12" r:id="R1638d72cdc174a8c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Context_Menus" sheetId="13" r:id="R928a61fbfd284359"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Keyboard_Shortcuts" sheetId="14" r:id="Rce2e9c5fa48f48f9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Database_Views" sheetId="15" r:id="Ra7b3f412be6f4df0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Code_Text_Mode" sheetId="16" r:id="R70847b6c366c4ebe"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Python_Notebook" sheetId="17" r:id="Re57bb7f8d30e4490"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Collaboration" sheetId="18" r:id="R19de5ecaf7404115"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Offline_Desktop" sheetId="19" r:id="R6eb4219779374b41"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data_Model" sheetId="20" r:id="Rfe7c483d78864745"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Storage_Interop" sheetId="21" r:id="R0e32c44b5cb448f7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Security" sheetId="22" r:id="Rbb76949bac904003"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="API_Contracts" sheetId="23" r:id="Rf535383e8d5e4a19"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="State_Machines" sheetId="24" r:id="R69cf782f21ac40f7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Error_Recovery" sheetId="25" r:id="R683667c6de184592"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cross_App_Relations" sheetId="26" r:id="Re35473e3738d4a2c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Performance" sheetId="27" r:id="Rdd33daf6f3b74668"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Accessibility" sheetId="28" r:id="R18375a9b495945f3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test_Matrix" sheetId="29" r:id="R434185aa8fdd43f1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="30" r:id="Rfbbcf6b20ee14ce6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open_Questions" sheetId="31" r:id="Ra52e065fa042463a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Change_Log" sheetId="32" r:id="R3287e4e96d5c4e13"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Implementation_Status" sheetId="33" r:id="R7991202929844106"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -928,7 +928,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0873787ffd99489b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R25fb559f50324bc2"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1271,7 +1271,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R442a0162d7234d46"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5602ca2f929a4570"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1674,7 +1674,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1cad5f46f7154933"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc4f5113947e44e79"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2197,7 +2197,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6402182531f64d83"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcee85992603a421f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2797,7 +2797,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1d6ab4e7f5b74223"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R76a7d20a6827471f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3802,10 +3802,27 @@
         <x:v>Tab completion과 지속 대화형 PTY는 후속 단계</x:v>
       </x:c>
     </x:row>
+    <x:row r="59">
+      <x:c r="A59" t="str">
+        <x:v>Note Studio shell</x:v>
+      </x:c>
+      <x:c r="B59" t="str">
+        <x:v>Ctrl+B</x:v>
+      </x:c>
+      <x:c r="C59" t="str">
+        <x:v>왼쪽 노트북·페이지 sidebar 전체 숨김/표시</x:v>
+      </x:c>
+      <x:c r="D59" t="str">
+        <x:v>input/textarea/contenteditable/Monaco에서는 소비하지 않아 편집기 단축키를 보존</x:v>
+      </x:c>
+      <x:c r="E59" t="str">
+        <x:v>콘솔 자체 shortcut과 C/C++ compiler는 후속 범위</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re09f42a06c4f41f4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R59254ceff71c4e89"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4065,7 +4082,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb4ba01256b5d45b9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6e53ace306b14249"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4257,7 +4274,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd3be0b74ae3241af"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3e97ef14e7824ff8"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4636,7 +4653,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Race6555d25034e94"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdb58f5dbfa8d4167"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4896,7 +4913,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3e45a3087f554a1f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0770b2fd3e1645ef"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5088,7 +5105,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb20d49a8cf9d4f36"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R03ab957954ec4f9c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5221,7 +5238,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd2d6a81c50eb4d7a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R60ce7700bddf487a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5634,7 +5651,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7625944adf2c44a0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5a5d3dd92e0c41eb"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5894,7 +5911,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R33ac82a2d4c84a6c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5c543b0d1558421c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6287,10 +6304,27 @@
         <x:v>P0</x:v>
       </x:c>
     </x:row>
+    <x:row r="23">
+      <x:c r="A23" t="str">
+        <x:v>SEC-22</x:v>
+      </x:c>
+      <x:c r="B23" t="str">
+        <x:v>대화형 stdin 세션 탈출·가로채기·자원 고갈</x:v>
+      </x:c>
+      <x:c r="C23" t="str">
+        <x:v>owner key, note revision/language/notebookId 재검증, 선택 notebook 단일 RW mount, network none, non-root, read-only root, cap-drop, no-new-privileges, CPU/RAM/PID/120초/입력 64KiB/출력 256KiB와 resource reservation</x:v>
+      </x:c>
+      <x:c r="D23" t="str">
+        <x:v>타 owner sessionId, 입력 한도, stop/timeout/output cap, spawn 오류, polling 단절, container cleanup</x:v>
+      </x:c>
+      <x:c r="E23" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re8029f49660f4457"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf4eefdff2c4a4c6c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6819,10 +6853,27 @@
         <x:v>로그인 계정이 소유한 notebookId를 매 요청 재조회. 클라이언트 절대경로·userId는 받지 않음.</x:v>
       </x:c>
     </x:row>
+    <x:row r="31">
+      <x:c r="A31" t="str">
+        <x:v>Interactive code session</x:v>
+      </x:c>
+      <x:c r="B31" t="str">
+        <x:v>POST session / GET poll / POST input / DELETE stop</x:v>
+      </x:c>
+      <x:c r="C31" t="str">
+        <x:v>noteId·language·expectedRevision, sessionId, cursor, text</x:v>
+      </x:c>
+      <x:c r="D31" t="str">
+        <x:v>owner-bound session snapshot와 incremental events, 상태, exit/signal, sandbox limit</x:v>
+      </x:c>
+      <x:c r="E31" t="str">
+        <x:v>세션 ID만으로 접근 불가. 서버 인증 owner와 현재 계정 note/notebook을 기준으로 생성.</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R36b09412f3684ea8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf7fe01ba12be4a4c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7198,10 +7249,27 @@
         <x:v>running 중 중복 명령 금지. 노트북 scope는 명시적으로 새 터미널을 열 때만 변경.</x:v>
       </x:c>
     </x:row>
+    <x:row r="22">
+      <x:c r="A22" t="str">
+        <x:v>대화형 실행 콘솔</x:v>
+      </x:c>
+      <x:c r="B22" t="str">
+        <x:v>hidden/closed → starting → running ↔ hidden → finished|failed|stopped</x:v>
+      </x:c>
+      <x:c r="C22" t="str">
+        <x:v>저장된 코드 실행, 숨김·재열기, stdin, stop, poll success/failure</x:v>
+      </x:c>
+      <x:c r="D22" t="str">
+        <x:v>transient poll failure는 running 유지/backoff. 실제 exit·signal·stop만 terminal state</x:v>
+      </x:c>
+      <x:c r="E22" t="str">
+        <x:v>10분 결과 보존, 120초 process limit, 모든 terminal state에서 reservation release.</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4163fe3fcb004fe8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7c32534dfa9d450a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7577,10 +7645,27 @@
         <x:v>worker 잔류 0, PM2 정상, 다음 명령 성공</x:v>
       </x:c>
     </x:row>
+    <x:row r="22">
+      <x:c r="A22" t="str">
+        <x:v>실행 console polling 단절</x:v>
+      </x:c>
+      <x:c r="B22" t="str">
+        <x:v>최대 5초 backoff로 같은 cursor부터 자동 재조회하며 프로세스를 실패로 바꾸지 않는다.</x:v>
+      </x:c>
+      <x:c r="C22" t="str">
+        <x:v>연결 복구 시 누락 event를 sequence cursor로 이어붙임</x:v>
+      </x:c>
+      <x:c r="D22" t="str">
+        <x:v>5번째 실패 때 한 번 system 안내. 새 실행을 중복 허용하지 않음.</x:v>
+      </x:c>
+      <x:c r="E22" t="str">
+        <x:v>복구 뒤 중복/누락 0, 실제 exit state 수신, reservation/container 회수</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Red48219616864c0d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rde1e1c7f26a44910"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7910,16 +7995,16 @@
         <x:v>WORKSPACE-RESUME-STATE</x:v>
       </x:c>
       <x:c r="B19" s="13" t="str">
-        <x:v>integrates</x:v>
+        <x:v>persists_with</x:v>
       </x:c>
       <x:c r="C19" s="13" t="str">
-        <x:v>Note Studio 마지막 notebook/page와 block/Monaco 위치, 파일관리자·PDF·HWP·media 위치</x:v>
+        <x:v>Note Studio 전체 sidebar 표시 상태</x:v>
       </x:c>
       <x:c r="D19" s="13" t="str">
-        <x:v>내용 revision과 화면 위치 분리, same-device 우선과 account fallback</x:v>
+        <x:v>note-studio-session의 sidebarOpen</x:v>
       </x:c>
       <x:c r="E19" s="13" t="str">
-        <x:v>계정 전환·빠른 note 전환에서 stale 상태가 다른 사용자나 페이지에 적용됨</x:v>
+        <x:v>재로그인/새로고침에서 계정·장치 경계대로 복원</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
@@ -7942,7 +8027,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6bf1af55bdfc4049"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7d268f49ba71486b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8202,7 +8287,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfdcbf944ea69455c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf82c4eb52834497c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8363,7 +8448,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9c28ee2b3d3c486c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb7d544f791f7475c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9323,10 +9408,30 @@
         <x:v>M1-N</x:v>
       </x:c>
     </x:row>
+    <x:row r="48">
+      <x:c r="A48" t="str">
+        <x:v>T-048</x:v>
+      </x:c>
+      <x:c r="B48" t="str">
+        <x:v>전체 sidebar·kind·대화형 실행</x:v>
+      </x:c>
+      <x:c r="C48" t="str">
+        <x:v>기존 notebook kind 없음, notes/project 생성, Ctrl+B/editor 충돌, Python input, JS readline, 다른 owner, poll 단절, hide/reopen, stop/timeout/output cap</x:v>
+      </x:c>
+      <x:c r="D48" t="str">
+        <x:v>기존 노트는 notes, project는 별도 라벨. sidebar와 console을 독립 토글하고 stdin 결과가 출력되며 타 계정·한도 초과는 차단된다.</x:v>
+      </x:c>
+      <x:c r="E48" t="str">
+        <x:v>unit+security+NAS Docker integration+production+로그인 E2E</x:v>
+      </x:c>
+      <x:c r="F48" t="str">
+        <x:v>M1-O</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc8fe0284424f4f38"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R930223cf72ff4c59"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9753,10 +9858,27 @@
         <x:v>지속 PTY가 필요한 명확한 사용 사례와 WebSocket origin/auth·idle cleanup·부하 테스트가 준비될 때</x:v>
       </x:c>
     </x:row>
+    <x:row r="25">
+      <x:c r="A25" t="str">
+        <x:v>DEC-025</x:v>
+      </x:c>
+      <x:c r="B25" t="str">
+        <x:v>채택</x:v>
+      </x:c>
+      <x:c r="C25" t="str">
+        <x:v>노트북은 notes/project kind를 명시하고 실행 결과는 하단 대화형 session console로 표시</x:v>
+      </x:c>
+      <x:c r="D25" t="str">
+        <x:v>문서 중심 탐색과 코드 프로젝트 작업은 기본 진입점이 다르지만 NOTE MANAGER 경계·페이지 트리는 공유할 수 있다. 실행 dialog는 stdin과 작업 지속성을 제공하지 못한다.</x:v>
+      </x:c>
+      <x:c r="E25" t="str">
+        <x:v>C/C++ runtime, persistent PTY 또는 다중 세션 탭이 필요할 때 별도 자원·보안 심사를 거친다.</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc7117451337c41e8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R030044e6f04a47b7"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9897,7 +10019,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8379cb7ae2794295"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R93308da06cd442da"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10123,7 +10245,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfa0fb815d32f42cb"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R52b80460ec304961"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10483,10 +10605,30 @@
         <x:v>Codex</x:v>
       </x:c>
     </x:row>
+    <x:row r="18">
+      <x:c r="A18" t="str">
+        <x:v>2026-09-08</x:v>
+      </x:c>
+      <x:c r="B18" t="str">
+        <x:v>1.8-interactive-console</x:v>
+      </x:c>
+      <x:c r="C18" t="str">
+        <x:v>완료·운영 배포 / 로그인 화면 E2E 대기</x:v>
+      </x:c>
+      <x:c r="D18" t="str">
+        <x:v>전체 접이식 sidebar, notes/project 작업공간 kind, 입력 가능한 하단 Python/JavaScript session console과 자동 재연결을 추가했다.</x:v>
+      </x:c>
+      <x:c r="E18" t="str">
+        <x:v>VS Code layout/terminal과 Node child process 공식 문서 대조. 로컬·NAS 전체 회귀, 실 Docker stdin/owner, frontend, production/PDF.js, live hash/HTTP/services 통과.</x:v>
+      </x:c>
+      <x:c r="F18" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R53e14ec08ee44e60"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R041c6bc641614f6c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10961,6 +11103,26 @@
       </x:c>
       <x:c r="F23" t="str">
         <x:v>자동 브라우저에 로그인 세션이 없어 실제 사용자 노트의 접기·파일 클릭·명령 입력 육안 E2E만 남음. 지속 PTY는 별도 M2 단계.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24">
+      <x:c r="A24" t="str">
+        <x:v>M1-O</x:v>
+      </x:c>
+      <x:c r="B24" t="str">
+        <x:v>전체 sidebar·노트/프로젝트 구분·대화형 실행 콘솔</x:v>
+      </x:c>
+      <x:c r="C24" t="str">
+        <x:v>완료·운영 배포 / 로그인 화면 E2E 대기</x:v>
+      </x:c>
+      <x:c r="D24" t="str">
+        <x:v>Ctrl+B/rail sidebar, notes/project registry+UI+AI, bottom stdout/stderr/stdin console, stop/hide/reopen/expand, owner-bound Docker session, poll backoff</x:v>
+      </x:c>
+      <x:c r="E24" t="str">
+        <x:v>로컬 backend 111 pass 8 skip·focused 35/35·production. NAS backend 113 pass 6 skip·실 Docker 4/4·frontend 8/8·production/PDF.js·main.98fb0725.js·HTTP/service/hash 정상</x:v>
+      </x:c>
+      <x:c r="F24" t="str">
+        <x:v>자동 브라우저 로그인 세션 부재로 실제 사용자 화면의 클릭·입력 육안 E2E만 남음. C/C++ scanf와 지속 PTY는 미지원.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -11172,7 +11334,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4d00833d963049ce"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5cb4ba2c8f34406b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11455,7 +11617,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R30a4593736fa4bb1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R608ac3635aeb41c7"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12154,10 +12316,61 @@
         <x:v>2026-09-08</x:v>
       </x:c>
     </x:row>
+    <x:row r="41">
+      <x:c r="A41" t="str">
+        <x:v>SRC-041</x:v>
+      </x:c>
+      <x:c r="B41" t="str">
+        <x:v>VS Code Custom Layout</x:v>
+      </x:c>
+      <x:c r="C41" t="str">
+        <x:v>https://code.visualstudio.com/docs/configure/custom-layout</x:v>
+      </x:c>
+      <x:c r="D41" t="str">
+        <x:v>Primary Side Bar 전체 토글, 하단 Panel과 layout 상태 유지 패턴</x:v>
+      </x:c>
+      <x:c r="E41" t="str">
+        <x:v>2026-09-08</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42">
+      <x:c r="A42" t="str">
+        <x:v>SRC-042</x:v>
+      </x:c>
+      <x:c r="B42" t="str">
+        <x:v>VS Code Terminal Basics</x:v>
+      </x:c>
+      <x:c r="C42" t="str">
+        <x:v>https://code.visualstudio.com/docs/terminal/basics</x:v>
+      </x:c>
+      <x:c r="D42" t="str">
+        <x:v>편집 영역과 분리된 하단 panel, 작업 폴더 시작, 숨김/표시 terminal UX</x:v>
+      </x:c>
+      <x:c r="E42" t="str">
+        <x:v>2026-09-08</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43">
+      <x:c r="A43" t="str">
+        <x:v>SRC-043</x:v>
+      </x:c>
+      <x:c r="B43" t="str">
+        <x:v>Node.js child_process</x:v>
+      </x:c>
+      <x:c r="C43" t="str">
+        <x:v>https://nodejs.org/api/child_process.html</x:v>
+      </x:c>
+      <x:c r="D43" t="str">
+        <x:v>spawn한 child의 stdin/stdout/stderr pipe로 실행 중 양방향 입출력</x:v>
+      </x:c>
+      <x:c r="E43" t="str">
+        <x:v>2026-09-08</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7b6f0327275c414d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdd5af76b2b1e4c02"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12400,7 +12613,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R44595a5a0b1840ea"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re2fddbcea96c459c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12589,10 +12802,27 @@
         <x:v>노트북 없음·경로 소실·자원 대기·명령 오류·출력/시간 제한을 서로 다른 문장으로 표시한다.</x:v>
       </x:c>
     </x:row>
+    <x:row r="11">
+      <x:c r="A11" t="str">
+        <x:v>작업공간+실행 콘솔</x:v>
+      </x:c>
+      <x:c r="B11" t="str">
+        <x:v>전체 접이식 sidebar/42px rail → 편집기 → 필요할 때만 하단 실행 콘솔</x:v>
+      </x:c>
+      <x:c r="C11" t="str">
+        <x:v>Ctrl+B, 노트/프로젝트 카드, 실행, stdin, 중지, 콘솔 확대·숨김·재열기</x:v>
+      </x:c>
+      <x:c r="D11" t="str">
+        <x:v>모바일은 선택 전 sidebar만 보이고 편집 진입 뒤 감춘다. editor 안 Ctrl+B는 굵게를 유지하며 출력은 선택·키보드 scroll 가능.</x:v>
+      </x:c>
+      <x:c r="E11" t="str">
+        <x:v>경로 소실·revision 충돌·자원 대기·실행 오류·polling 단절을 구분한다. polling 단절은 backoff 자동 복구.</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfdc7a49e7a674cb9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfe274a998b054ae8"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12866,10 +13096,27 @@
         <x:v>다른 계정/노트북 경로·symlink·../는 거부. worker 실패는 입력/기존 파일을 보존하며 자동 재실행하지 않는다.</x:v>
       </x:c>
     </x:row>
+    <x:row r="16">
+      <x:c r="A16" t="str">
+        <x:v>FLOW-INTERACTIVE-RUN</x:v>
+      </x:c>
+      <x:c r="B16" t="str">
+        <x:v>저장된 Python 또는 JavaScript 코드 페이지</x:v>
+      </x:c>
+      <x:c r="C16" t="str">
+        <x:v>실행 → 하단 콘솔 자동 열림 → stdout 확인 → 필요하면 stdin Enter 전송 → 완료/중지 → 숨김 또는 재열기</x:v>
+      </x:c>
+      <x:c r="D16" t="str">
+        <x:v>같은 note revision과 notebook workspace에서 프로그램이 끝나고 reservation이 반환됨</x:v>
+      </x:c>
+      <x:c r="E16" t="str">
+        <x:v>다른 owner session은 404. 닫기/숨김은 실행 중지가 아니며 120초 제한이 최종 회수한다.</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R622b8b1393de429c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4b6469fcb5614d2b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/programs/NAS_NOTE_STUDIO_SPEC.xlsx
+++ b/docs/programs/NAS_NOTE_STUDIO_SPEC.xlsx
@@ -2,39 +2,39 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="R9c311f5c8223442f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Product_Vision" sheetId="2" r:id="R973ea176431c463d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decisions" sheetId="3" r:id="R56d9fcfed1c147db"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Competitors" sheetId="4" r:id="Rd84fd067c39b440f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open_Source" sheetId="5" r:id="R6cd3d78aa6814cbf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source_Index" sheetId="6" r:id="Re57085d2ccb047f3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Information_Architecture" sheetId="7" r:id="Rb321cf3d9de74a43"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI_Layout" sheetId="8" r:id="Rcc495092aec64a0f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="User_Flows" sheetId="9" r:id="Rff98194e26f84fe5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Note_Types" sheetId="10" r:id="Re490aa00a9e94304"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Block_Catalog" sheetId="11" r:id="R698afdad235b4ae4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Slash_Commands" sheetId="12" r:id="R1638d72cdc174a8c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Context_Menus" sheetId="13" r:id="R928a61fbfd284359"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Keyboard_Shortcuts" sheetId="14" r:id="Rce2e9c5fa48f48f9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Database_Views" sheetId="15" r:id="Ra7b3f412be6f4df0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Code_Text_Mode" sheetId="16" r:id="R70847b6c366c4ebe"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Python_Notebook" sheetId="17" r:id="Re57bb7f8d30e4490"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Collaboration" sheetId="18" r:id="R19de5ecaf7404115"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Offline_Desktop" sheetId="19" r:id="R6eb4219779374b41"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data_Model" sheetId="20" r:id="Rfe7c483d78864745"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Storage_Interop" sheetId="21" r:id="R0e32c44b5cb448f7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Security" sheetId="22" r:id="Rbb76949bac904003"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="API_Contracts" sheetId="23" r:id="Rf535383e8d5e4a19"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="State_Machines" sheetId="24" r:id="R69cf782f21ac40f7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Error_Recovery" sheetId="25" r:id="R683667c6de184592"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cross_App_Relations" sheetId="26" r:id="Re35473e3738d4a2c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Performance" sheetId="27" r:id="Rdd33daf6f3b74668"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Accessibility" sheetId="28" r:id="R18375a9b495945f3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test_Matrix" sheetId="29" r:id="R434185aa8fdd43f1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="30" r:id="Rfbbcf6b20ee14ce6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open_Questions" sheetId="31" r:id="Ra52e065fa042463a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Change_Log" sheetId="32" r:id="R3287e4e96d5c4e13"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Implementation_Status" sheetId="33" r:id="R7991202929844106"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="Rf582944a81214189"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Product_Vision" sheetId="2" r:id="R99c7a43732844cd6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decisions" sheetId="3" r:id="R43d689720fd34c60"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Competitors" sheetId="4" r:id="R5e2966fc2db34e5b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open_Source" sheetId="5" r:id="Rf4ced853d63b403f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source_Index" sheetId="6" r:id="R81164376fc1b4d69"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Information_Architecture" sheetId="7" r:id="R01434e88d930415e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI_Layout" sheetId="8" r:id="R1b527f2732bb47b4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="User_Flows" sheetId="9" r:id="Rd064b0ce0c934559"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Note_Types" sheetId="10" r:id="Raf8849ee98484aac"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Block_Catalog" sheetId="11" r:id="R4da1764dd6294ea8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Slash_Commands" sheetId="12" r:id="R4cf6e59c361b4260"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Context_Menus" sheetId="13" r:id="R329f2603a40b424a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Keyboard_Shortcuts" sheetId="14" r:id="Rd32a30a8b0e84b6a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Database_Views" sheetId="15" r:id="R826efff5c1004e2d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Code_Text_Mode" sheetId="16" r:id="Rab06a5dff7504076"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Python_Notebook" sheetId="17" r:id="Rd71dd6fea50f42ea"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Collaboration" sheetId="18" r:id="Rb63f8c057f9246e4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Offline_Desktop" sheetId="19" r:id="R33fc032dc3d14074"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data_Model" sheetId="20" r:id="R385795003f324c82"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Storage_Interop" sheetId="21" r:id="R438e004b5a9a4452"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Security" sheetId="22" r:id="R9e85e9c04ab643ce"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="API_Contracts" sheetId="23" r:id="R1b7174bc66234cd5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="State_Machines" sheetId="24" r:id="Rc6144f3703354795"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Error_Recovery" sheetId="25" r:id="R8dc8cdbe680340b2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cross_App_Relations" sheetId="26" r:id="Rbb7c9d702c5345e4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Performance" sheetId="27" r:id="R5aecdeb9825b4991"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Accessibility" sheetId="28" r:id="R1337a2bd15724184"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test_Matrix" sheetId="29" r:id="R007477093ec94bbe"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="30" r:id="R7be586addabd4212"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open_Questions" sheetId="31" r:id="R0b8b72decf4d4b19"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Change_Log" sheetId="32" r:id="R7f3d50aff5ea4e33"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Implementation_Status" sheetId="33" r:id="R131b230332134ce4"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -928,7 +928,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R25fb559f50324bc2"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R092c0b61b1de4a13"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1271,7 +1271,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5602ca2f929a4570"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1604a784b7684411"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1674,7 +1674,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc4f5113947e44e79"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R63b4e7d28e064fe2"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2197,7 +2197,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcee85992603a421f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R10a24d3e24554b9a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2797,7 +2797,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R76a7d20a6827471f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb2c19bb65ecf42f3"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3822,7 +3822,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R59254ceff71c4e89"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6ba764b97f3f4a71"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4082,7 +4082,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6e53ace306b14249"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R52666e0696424cd8"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4274,7 +4274,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3e97ef14e7824ff8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7cec56172f4b4891"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4653,7 +4653,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdb58f5dbfa8d4167"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4ce5aa34fcd040f0"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4913,7 +4913,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0770b2fd3e1645ef"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4ee6a9841e094505"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5105,7 +5105,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R03ab957954ec4f9c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Recbdfe64bb694f0c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5238,7 +5238,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R60ce7700bddf487a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R32b51ae319194857"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5651,7 +5651,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5a5d3dd92e0c41eb"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re252f81e67a24f1a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5911,7 +5911,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5c543b0d1558421c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6b976181c2b840cf"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6324,7 +6324,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf4eefdff2c4a4c6c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4c11af10d26a4f19"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6873,7 +6873,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf7fe01ba12be4a4c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R68e89a5043d54475"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7269,7 +7269,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7c32534dfa9d450a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R904605f951ac435d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7665,7 +7665,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rde1e1c7f26a44910"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3f74f57433d04eb8"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8027,7 +8027,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7d268f49ba71486b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R81c90ee8837347ba"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8287,7 +8287,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf82c4eb52834497c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Recd65c3f684d41e2"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8448,7 +8448,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb7d544f791f7475c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R52f9f95db2844906"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9431,7 +9431,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R930223cf72ff4c59"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc24644dbd1ea4131"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9878,7 +9878,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R030044e6f04a47b7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6a92afa0ff264a49"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10019,7 +10019,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R93308da06cd442da"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc94e693cdb6340e8"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10245,7 +10245,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R52b80460ec304961"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R17e7b2d3b03e4f7a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10625,10 +10625,30 @@
         <x:v>Codex</x:v>
       </x:c>
     </x:row>
+    <x:row r="19">
+      <x:c r="A19" t="str">
+        <x:v>2026-09-08</x:v>
+      </x:c>
+      <x:c r="B19" t="str">
+        <x:v>1.8.1-console-layout</x:v>
+      </x:c>
+      <x:c r="C19" t="str">
+        <x:v>완료·운영 배포 / 로그인 화면 E2E 대기</x:v>
+      </x:c>
+      <x:c r="D19" t="str">
+        <x:v>실행 콘솔의 기본·확대 높이에 상한을 두고 편집기가 항상 작업영역의 58% 이상 남도록 교정했다.</x:v>
+      </x:c>
+      <x:c r="E19" t="str">
+        <x:v>NAS frontend 8/8, production/PDF.js, build/live main.0b20a64b.js hash, 내부·공개 200, PM2 online.</x:v>
+      </x:c>
+      <x:c r="F19" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R041c6bc641614f6c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Refc6b2d5c65a4fd5"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11116,13 +11136,13 @@
         <x:v>완료·운영 배포 / 로그인 화면 E2E 대기</x:v>
       </x:c>
       <x:c r="D24" t="str">
-        <x:v>Ctrl+B/rail sidebar, notes/project registry+UI+AI, bottom stdout/stderr/stdin console, stop/hide/reopen/expand, owner-bound Docker session, poll backoff</x:v>
+        <x:v>Ctrl+B/rail sidebar, notes/project kind, bottom stdin console, stop/hide/reopen/expand, 편집기 58% 보존, owner-bound Docker session, poll backoff</x:v>
       </x:c>
       <x:c r="E24" t="str">
-        <x:v>로컬 backend 111 pass 8 skip·focused 35/35·production. NAS backend 113 pass 6 skip·실 Docker 4/4·frontend 8/8·production/PDF.js·main.98fb0725.js·HTTP/service/hash 정상</x:v>
+        <x:v>이전 전체 회귀와 실 Docker 4/4. 높이 교정 후 NAS frontend 8/8·production/PDF.js·main.0b20a64b.js·HTTP/hash/PM2 정상</x:v>
       </x:c>
       <x:c r="F24" t="str">
-        <x:v>자동 브라우저 로그인 세션 부재로 실제 사용자 화면의 클릭·입력 육안 E2E만 남음. C/C++ scanf와 지속 PTY는 미지원.</x:v>
+        <x:v>자동 브라우저 로그인 세션 부재로 실제 사용자 작은 창의 높이 육안 E2E만 남음. C/C++ scanf와 지속 PTY는 미지원.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -11334,7 +11354,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5cb4ba2c8f34406b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Redf41aa27120426a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11617,7 +11637,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R608ac3635aeb41c7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6153b22dbedd408d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12370,7 +12390,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdd5af76b2b1e4c02"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf9363854de464185"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12613,7 +12633,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re2fddbcea96c459c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R85087c426c7f4a8c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12813,7 +12833,7 @@
         <x:v>Ctrl+B, 노트/프로젝트 카드, 실행, stdin, 중지, 콘솔 확대·숨김·재열기</x:v>
       </x:c>
       <x:c r="D11" t="str">
-        <x:v>모바일은 선택 전 sidebar만 보이고 편집 진입 뒤 감춘다. editor 안 Ctrl+B는 굵게를 유지하며 출력은 선택·키보드 scroll 가능.</x:v>
+        <x:v>기본 콘솔은 최대 220px·24%, 확대도 최대 420px·42%. 편집기는 최소 58%를 유지한다. 모바일은 선택 전 sidebar만 보이며 editor 안 Ctrl+B는 굵게를 유지한다.</x:v>
       </x:c>
       <x:c r="E11" t="str">
         <x:v>경로 소실·revision 충돌·자원 대기·실행 오류·polling 단절을 구분한다. polling 단절은 backoff 자동 복구.</x:v>
@@ -12822,7 +12842,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfe274a998b054ae8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3b3c5603196a4751"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13116,7 +13136,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4b6469fcb5614d2b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc393e724462f447b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/programs/NAS_NOTE_STUDIO_SPEC.xlsx
+++ b/docs/programs/NAS_NOTE_STUDIO_SPEC.xlsx
@@ -2,39 +2,39 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="Rf582944a81214189"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Product_Vision" sheetId="2" r:id="R99c7a43732844cd6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decisions" sheetId="3" r:id="R43d689720fd34c60"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Competitors" sheetId="4" r:id="R5e2966fc2db34e5b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open_Source" sheetId="5" r:id="Rf4ced853d63b403f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source_Index" sheetId="6" r:id="R81164376fc1b4d69"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Information_Architecture" sheetId="7" r:id="R01434e88d930415e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI_Layout" sheetId="8" r:id="R1b527f2732bb47b4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="User_Flows" sheetId="9" r:id="Rd064b0ce0c934559"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Note_Types" sheetId="10" r:id="Raf8849ee98484aac"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Block_Catalog" sheetId="11" r:id="R4da1764dd6294ea8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Slash_Commands" sheetId="12" r:id="R4cf6e59c361b4260"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Context_Menus" sheetId="13" r:id="R329f2603a40b424a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Keyboard_Shortcuts" sheetId="14" r:id="Rd32a30a8b0e84b6a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Database_Views" sheetId="15" r:id="R826efff5c1004e2d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Code_Text_Mode" sheetId="16" r:id="Rab06a5dff7504076"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Python_Notebook" sheetId="17" r:id="Rd71dd6fea50f42ea"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Collaboration" sheetId="18" r:id="Rb63f8c057f9246e4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Offline_Desktop" sheetId="19" r:id="R33fc032dc3d14074"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data_Model" sheetId="20" r:id="R385795003f324c82"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Storage_Interop" sheetId="21" r:id="R438e004b5a9a4452"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Security" sheetId="22" r:id="R9e85e9c04ab643ce"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="API_Contracts" sheetId="23" r:id="R1b7174bc66234cd5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="State_Machines" sheetId="24" r:id="Rc6144f3703354795"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Error_Recovery" sheetId="25" r:id="R8dc8cdbe680340b2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cross_App_Relations" sheetId="26" r:id="Rbb7c9d702c5345e4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Performance" sheetId="27" r:id="R5aecdeb9825b4991"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Accessibility" sheetId="28" r:id="R1337a2bd15724184"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test_Matrix" sheetId="29" r:id="R007477093ec94bbe"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="30" r:id="R7be586addabd4212"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open_Questions" sheetId="31" r:id="R0b8b72decf4d4b19"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Change_Log" sheetId="32" r:id="R7f3d50aff5ea4e33"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Implementation_Status" sheetId="33" r:id="R131b230332134ce4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="R0e7b8f9f24b241ea"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Product_Vision" sheetId="2" r:id="R6e7e329c4a704e3c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decisions" sheetId="3" r:id="R991ef292c43a4ed9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Competitors" sheetId="4" r:id="R91956bb9be6541d7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open_Source" sheetId="5" r:id="Ra4aed79a2b42472f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source_Index" sheetId="6" r:id="R70bd77f02e174ee5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Information_Architecture" sheetId="7" r:id="R1a1dbca3db8f4eee"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI_Layout" sheetId="8" r:id="R1d4ed22943e745ee"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="User_Flows" sheetId="9" r:id="R73387c0f82464755"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Note_Types" sheetId="10" r:id="R35ec00d6ec754831"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Block_Catalog" sheetId="11" r:id="R9cf7fcfa497a48d6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Slash_Commands" sheetId="12" r:id="Ra8a92fecf93b4e23"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Context_Menus" sheetId="13" r:id="Rfde72701b27b4786"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Keyboard_Shortcuts" sheetId="14" r:id="Rd8585c55e6854d91"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Database_Views" sheetId="15" r:id="Re52947142fa04e95"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Code_Text_Mode" sheetId="16" r:id="Rce107159e8d94561"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Python_Notebook" sheetId="17" r:id="Rc1db43c082394419"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Collaboration" sheetId="18" r:id="R6a0dac7d61ca4361"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Offline_Desktop" sheetId="19" r:id="R7929830e83f140b3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data_Model" sheetId="20" r:id="Rdb1604ac806c4621"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Storage_Interop" sheetId="21" r:id="R7f2ab278d83242f5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Security" sheetId="22" r:id="Rce0ab73899164d83"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="API_Contracts" sheetId="23" r:id="R08d6415ee3114bf0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="State_Machines" sheetId="24" r:id="R4a840e67351e40fe"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Error_Recovery" sheetId="25" r:id="R5ac9ba5c49bd40b4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cross_App_Relations" sheetId="26" r:id="Rde31a1cced4b459e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Performance" sheetId="27" r:id="R45f72a7709df4e9f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Accessibility" sheetId="28" r:id="R23e3b09d3a294806"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test_Matrix" sheetId="29" r:id="R6e885644e8954025"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="30" r:id="R56ced6ace0b04c68"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open_Questions" sheetId="31" r:id="R0a91ce366a084c87"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Change_Log" sheetId="32" r:id="R3168f69a1b974f9a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Implementation_Status" sheetId="33" r:id="R105628e25c354034"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -928,7 +928,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R092c0b61b1de4a13"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7d8461db00f7407f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1271,7 +1271,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1604a784b7684411"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R02f379db3a154151"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1674,7 +1674,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R63b4e7d28e064fe2"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2cbc416e39854bf5"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2197,7 +2197,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R10a24d3e24554b9a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcbf18ede465b4029"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2797,7 +2797,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb2c19bb65ecf42f3"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rca9d0277b5e042b4"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3822,7 +3822,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6ba764b97f3f4a71"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6b7cef5954ae4b03"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4082,7 +4082,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R52666e0696424cd8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4eb66097f30c4d03"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4274,7 +4274,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7cec56172f4b4891"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0ad7b8a56f6c477e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4653,7 +4653,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4ce5aa34fcd040f0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9d9c56ef5ce049d9"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4913,7 +4913,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4ee6a9841e094505"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rccc60d044d624dc1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5105,7 +5105,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Recbdfe64bb694f0c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9f54d1bcca7242f7"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5238,7 +5238,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R32b51ae319194857"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7f6f060328c7476a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5651,7 +5651,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re252f81e67a24f1a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4d764752f3d34056"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5911,7 +5911,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6b976181c2b840cf"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb373b58ad6fe4ec4"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6324,7 +6324,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4c11af10d26a4f19"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf628827c6c694eb6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6873,7 +6873,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R68e89a5043d54475"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R83a074e7038c45b5"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7269,7 +7269,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R904605f951ac435d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1c250ff731b44e59"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7665,7 +7665,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3f74f57433d04eb8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4692a472fd6e421c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8027,7 +8027,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R81c90ee8837347ba"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb8f61c912dee4bff"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8287,7 +8287,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Recd65c3f684d41e2"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc9a4959423da414d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8448,7 +8448,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R52f9f95db2844906"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rae3ab78cd3d840dd"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9431,7 +9431,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc24644dbd1ea4131"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0be0b98a363544f3"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9878,7 +9878,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6a92afa0ff264a49"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcb0ec468e24d44c7"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10019,7 +10019,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc94e693cdb6340e8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1a3ec3dea9894de7"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10245,7 +10245,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R17e7b2d3b03e4f7a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R38e0ccf27b7040a4"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10645,10 +10645,30 @@
         <x:v>Codex</x:v>
       </x:c>
     </x:row>
+    <x:row r="20">
+      <x:c r="A20" t="str">
+        <x:v>2026-09-08</x:v>
+      </x:c>
+      <x:c r="B20" t="str">
+        <x:v>1.8.2-bottom-dock</x:v>
+      </x:c>
+      <x:c r="C20" t="str">
+        <x:v>완료·운영 배포 / 로그인 화면 E2E 대기</x:v>
+      </x:c>
+      <x:c r="D20" t="str">
+        <x:v>일반 터미널이 편집기를 교체하던 구조를 제거하고 일반 터미널·코드 실행 콘솔을 VS Code형 단일 하단 dock으로 통합했다.</x:v>
+      </x:c>
+      <x:c r="E20" t="str">
+        <x:v>NAS frontend 8/8, production/PDF.js, live main.0de8ab2d.js, 내부·공개 200.</x:v>
+      </x:c>
+      <x:c r="F20" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Refc6b2d5c65a4fd5"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb68c39977e5543a1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11136,13 +11156,13 @@
         <x:v>완료·운영 배포 / 로그인 화면 E2E 대기</x:v>
       </x:c>
       <x:c r="D24" t="str">
-        <x:v>Ctrl+B/rail sidebar, notes/project kind, bottom stdin console, stop/hide/reopen/expand, 편집기 58% 보존, owner-bound Docker session, poll backoff</x:v>
+        <x:v>Ctrl+B/rail sidebar, notes/project kind, VS Code형 단일 bottom dock, 터미널/실행 콘솔 상호 전환, stdin, stop/hide/reopen, owner-bound Docker session</x:v>
       </x:c>
       <x:c r="E24" t="str">
-        <x:v>이전 전체 회귀와 실 Docker 4/4. 높이 교정 후 NAS frontend 8/8·production/PDF.js·main.0b20a64b.js·HTTP/hash/PM2 정상</x:v>
+        <x:v>NAS frontend 8/8·production/PDF.js·live main.0de8ab2d.js·내부/공개 HTTP 200. 로컬 production/PDF.js 통과</x:v>
       </x:c>
       <x:c r="F24" t="str">
-        <x:v>자동 브라우저 로그인 세션 부재로 실제 사용자 작은 창의 높이 육안 E2E만 남음. C/C++ scanf와 지속 PTY는 미지원.</x:v>
+        <x:v>자동 브라우저 로그인 세션 부재로 실제 사용자 창에서 dock 위치 육안 E2E만 남음. C/C++ scanf와 지속 PTY는 미지원.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -11354,7 +11374,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Redf41aa27120426a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Reb9e304ea49f41aa"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11637,7 +11657,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6153b22dbedd408d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R86dd999befd943a6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12390,7 +12410,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf9363854de464185"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R85be69723a3f44ed"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12633,7 +12653,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R85087c426c7f4a8c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R02548fd61fc04780"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12810,16 +12830,16 @@
         <x:v>노트북 터미널</x:v>
       </x:c>
       <x:c r="B10" t="str">
-        <x:v>노트북 트리 → 터미널 header/breadcrumb → 옆 파일 목록 → 출력 → 명령 입력</x:v>
+        <x:v>메인 편집기 아래 단일 dock · 필요 시 파일 탐색기 포함</x:v>
       </x:c>
       <x:c r="C10" t="str">
-        <x:v>노트북별 접기, 전체 접기, 터미널, 파일 목록 토글·새로고침·NAS에서 열기, history, Ctrl+L</x:v>
+        <x:v>노트북 더블클릭/터미널 버튼, 입력, Ctrl+C, 탐색기 접기, 닫기</x:v>
       </x:c>
       <x:c r="D10" t="str">
-        <x:v>모바일은 노트 트리를 숨기고 터미널 파일 목록 폭을 줄인다. 단색 아이콘, 고정 높이 header, HTML 해석 없는 monospace 출력.</x:v>
+        <x:v>터미널이 편집기를 교체하지 않는다. 편집기 또는 프로젝트 안내가 위에 유지되고 하단 180~320px, 작업영역 최대 42%에만 표시된다. 실행 콘솔과 동시에 겹치지 않는다.</x:v>
       </x:c>
       <x:c r="E10" t="str">
-        <x:v>노트북 없음·경로 소실·자원 대기·명령 오류·출력/시간 제한을 서로 다른 문장으로 표시한다.</x:v>
+        <x:v>노트북 실경로 밖 접근 거부, 소유자 세션 검증, 중복 터미널/실행 패널 충돌 방지</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
@@ -12827,22 +12847,22 @@
         <x:v>작업공간+실행 콘솔</x:v>
       </x:c>
       <x:c r="B11" t="str">
-        <x:v>전체 접이식 sidebar/42px rail → 편집기 → 필요할 때만 하단 실행 콘솔</x:v>
+        <x:v>접이식 sidebar/42px rail → 편집기 → 단일 하단 dock</x:v>
       </x:c>
       <x:c r="C11" t="str">
-        <x:v>Ctrl+B, 노트/프로젝트 카드, 실행, stdin, 중지, 콘솔 확대·숨김·재열기</x:v>
+        <x:v>Ctrl+B, 노트/프로젝트 카드, 실행, stdin, 중지, 터미널·실행 콘솔 전환, 숨김·재열기</x:v>
       </x:c>
       <x:c r="D11" t="str">
-        <x:v>기본 콘솔은 최대 220px·24%, 확대도 최대 420px·42%. 편집기는 최소 58%를 유지한다. 모바일은 선택 전 sidebar만 보이며 editor 안 Ctrl+B는 굵게를 유지한다.</x:v>
+        <x:v>일반 터미널과 실행 결과는 동일한 하단 영역을 번갈아 쓴다. 실행 시 터미널을 닫고, 터미널을 열면 실행 콘솔을 숨기며 위 편집기는 항상 남긴다.</x:v>
       </x:c>
       <x:c r="E11" t="str">
-        <x:v>경로 소실·revision 충돌·자원 대기·실행 오류·polling 단절을 구분한다. polling 단절은 backoff 자동 복구.</x:v>
+        <x:v>경로 소실·revision 충돌·자원 대기·실행 오류·polling 단절을 구분하며 숨은 실행 세션은 재열 수 있다.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3b3c5603196a4751"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb4bec42e935d406f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13136,7 +13156,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc393e724462f447b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd8fe1470a0f7416b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/programs/NAS_NOTE_STUDIO_SPEC.xlsx
+++ b/docs/programs/NAS_NOTE_STUDIO_SPEC.xlsx
@@ -2,39 +2,39 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="R0e7b8f9f24b241ea"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Product_Vision" sheetId="2" r:id="R6e7e329c4a704e3c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decisions" sheetId="3" r:id="R991ef292c43a4ed9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Competitors" sheetId="4" r:id="R91956bb9be6541d7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open_Source" sheetId="5" r:id="Ra4aed79a2b42472f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source_Index" sheetId="6" r:id="R70bd77f02e174ee5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Information_Architecture" sheetId="7" r:id="R1a1dbca3db8f4eee"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI_Layout" sheetId="8" r:id="R1d4ed22943e745ee"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="User_Flows" sheetId="9" r:id="R73387c0f82464755"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Note_Types" sheetId="10" r:id="R35ec00d6ec754831"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Block_Catalog" sheetId="11" r:id="R9cf7fcfa497a48d6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Slash_Commands" sheetId="12" r:id="Ra8a92fecf93b4e23"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Context_Menus" sheetId="13" r:id="Rfde72701b27b4786"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Keyboard_Shortcuts" sheetId="14" r:id="Rd8585c55e6854d91"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Database_Views" sheetId="15" r:id="Re52947142fa04e95"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Code_Text_Mode" sheetId="16" r:id="Rce107159e8d94561"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Python_Notebook" sheetId="17" r:id="Rc1db43c082394419"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Collaboration" sheetId="18" r:id="R6a0dac7d61ca4361"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Offline_Desktop" sheetId="19" r:id="R7929830e83f140b3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data_Model" sheetId="20" r:id="Rdb1604ac806c4621"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Storage_Interop" sheetId="21" r:id="R7f2ab278d83242f5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Security" sheetId="22" r:id="Rce0ab73899164d83"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="API_Contracts" sheetId="23" r:id="R08d6415ee3114bf0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="State_Machines" sheetId="24" r:id="R4a840e67351e40fe"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Error_Recovery" sheetId="25" r:id="R5ac9ba5c49bd40b4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cross_App_Relations" sheetId="26" r:id="Rde31a1cced4b459e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Performance" sheetId="27" r:id="R45f72a7709df4e9f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Accessibility" sheetId="28" r:id="R23e3b09d3a294806"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test_Matrix" sheetId="29" r:id="R6e885644e8954025"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="30" r:id="R56ced6ace0b04c68"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open_Questions" sheetId="31" r:id="R0a91ce366a084c87"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Change_Log" sheetId="32" r:id="R3168f69a1b974f9a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Implementation_Status" sheetId="33" r:id="R105628e25c354034"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="R57ebc027eac2485b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Product_Vision" sheetId="2" r:id="R4ba32a73d129462a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decisions" sheetId="3" r:id="R27a8006a7e214003"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Competitors" sheetId="4" r:id="R9f92f2695e194f4a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open_Source" sheetId="5" r:id="R52fa3f7824a24a88"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source_Index" sheetId="6" r:id="R30164ab8c7a74995"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Information_Architecture" sheetId="7" r:id="R198348ae16444b9c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI_Layout" sheetId="8" r:id="R5c79da17b93841d1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="User_Flows" sheetId="9" r:id="R25017d3957ad4408"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Note_Types" sheetId="10" r:id="R2c6594e34ca9481f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Block_Catalog" sheetId="11" r:id="Rb2139c65871540b3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Slash_Commands" sheetId="12" r:id="R93d941dc19c643a9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Context_Menus" sheetId="13" r:id="R12977ae7271544d7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Keyboard_Shortcuts" sheetId="14" r:id="R90a666335a054fbd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Database_Views" sheetId="15" r:id="R6cf25370d4da4198"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Code_Text_Mode" sheetId="16" r:id="R65b24a871ce64094"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Python_Notebook" sheetId="17" r:id="R34bacba97f684d2e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Collaboration" sheetId="18" r:id="R14474f1396e84593"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Offline_Desktop" sheetId="19" r:id="R5aea8287356f44b7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data_Model" sheetId="20" r:id="R87725ec800114ca1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Storage_Interop" sheetId="21" r:id="R51ccc36243164f08"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Security" sheetId="22" r:id="R4655b80a619244d8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="API_Contracts" sheetId="23" r:id="Rbaf7144a79db42ca"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="State_Machines" sheetId="24" r:id="Reba224eccefd4f22"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Error_Recovery" sheetId="25" r:id="Ra285a93e4e954cd3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cross_App_Relations" sheetId="26" r:id="R7cf50310dad04e08"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Performance" sheetId="27" r:id="R862a282aa0f142fd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Accessibility" sheetId="28" r:id="R3488f24bb513451e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test_Matrix" sheetId="29" r:id="R3b704d135aab4b3d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="30" r:id="R8fa1bb4f012341ed"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open_Questions" sheetId="31" r:id="Rd4da7b7aff4e42ec"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Change_Log" sheetId="32" r:id="R99a693002b2e475a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Implementation_Status" sheetId="33" r:id="Rb7009c34085340e6"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -928,7 +928,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7d8461db00f7407f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Raab52b8f134d41d9"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1271,7 +1271,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R02f379db3a154151"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb7536e63d36245fd"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1674,7 +1674,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2cbc416e39854bf5"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd34da2c6c93146c7"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2197,7 +2197,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcbf18ede465b4029"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re3f4da71cf594350"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2797,7 +2797,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rca9d0277b5e042b4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb88d14b61abf48a9"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3822,7 +3822,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6b7cef5954ae4b03"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re7429a2bac834520"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4082,7 +4082,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4eb66097f30c4d03"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R482f5a91e24b4c4c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4274,7 +4274,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0ad7b8a56f6c477e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R23edd102642541b1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4653,7 +4653,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9d9c56ef5ce049d9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0f8c9e3d50134853"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4913,7 +4913,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rccc60d044d624dc1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7c3934ee12764e26"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5105,7 +5105,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9f54d1bcca7242f7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb2237502990943b0"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5238,7 +5238,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7f6f060328c7476a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcc89e77b5e774a7e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5651,7 +5651,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4d764752f3d34056"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb7a4ae9f04cc40d6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5911,7 +5911,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb373b58ad6fe4ec4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R38b489ae8ac84f66"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6324,7 +6324,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf628827c6c694eb6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbdd76f693d6143b2"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6873,7 +6873,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R83a074e7038c45b5"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Reff401059bc8497c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7269,7 +7269,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1c250ff731b44e59"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdcf6f2214d7349a2"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7665,7 +7665,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4692a472fd6e421c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb9abede0e93749ef"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8027,7 +8027,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb8f61c912dee4bff"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rce6f3f32ff8e4147"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8287,7 +8287,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc9a4959423da414d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rebf8f81f71ee422a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8445,10 +8445,24 @@
         <x:v>코드만 표시하지 않음</x:v>
       </x:c>
     </x:row>
+    <x:row r="11">
+      <x:c r="A11" t="str">
+        <x:v>컴팩트 도구 이름</x:v>
+      </x:c>
+      <x:c r="B11" t="str">
+        <x:v>짧은 화면 라벨과 완전한 accessible name을 분리한다.</x:v>
+      </x:c>
+      <x:c r="C11" t="str">
+        <x:v>아이콘 버튼은 aria-label, 축약 버튼은 tooltip으로 전체 동작을 설명한다.</x:v>
+      </x:c>
+      <x:c r="D11" t="str">
+        <x:v>Python/JavaScript 실행처럼 현재 상태·언어를 툴팁에서 확인 가능해야 한다.</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rae3ab78cd3d840dd"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbd81841fb3be41cd"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9428,10 +9442,30 @@
         <x:v>M1-O</x:v>
       </x:c>
     </x:row>
+    <x:row r="49">
+      <x:c r="A49" t="str">
+        <x:v>UI-COMPACT-01</x:v>
+      </x:c>
+      <x:c r="B49" t="str">
+        <x:v>Note Studio 상단 chrome·한 줄 라벨</x:v>
+      </x:c>
+      <x:c r="C49" t="str">
+        <x:v>정적 verifier → production build → 1180x780 및 좁은 창 육안 확인</x:v>
+      </x:c>
+      <x:c r="D49" t="str">
+        <x:v>중복 이름 없음, 30/38/40px 높이, 실행·문서 버튼 1줄, title 입력 우선</x:v>
+      </x:c>
+      <x:c r="E49" t="str">
+        <x:v>자동 verifier·build 완료 / 로그인 육안 확인 필요</x:v>
+      </x:c>
+      <x:c r="F49" t="str">
+        <x:v>M1-O</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0be0b98a363544f3"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R34d1f6c0abbb4389"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9878,7 +9912,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcb0ec468e24d44c7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3693b08d06eb4179"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10019,7 +10053,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1a3ec3dea9894de7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra602a461d7824091"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10245,7 +10279,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R38e0ccf27b7040a4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2d2bbeeb3b3440d3"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10665,10 +10699,30 @@
         <x:v>Codex</x:v>
       </x:c>
     </x:row>
+    <x:row r="21">
+      <x:c r="A21" t="str">
+        <x:v>2026-09-08</x:v>
+      </x:c>
+      <x:c r="B21" t="str">
+        <x:v>1.9-compact-ui</x:v>
+      </x:c>
+      <x:c r="C21" t="str">
+        <x:v>완료·운영 배포 / 로그인 실화면 확인 필요</x:v>
+      </x:c>
+      <x:c r="D21" t="str">
+        <x:v>Note Studio 중복 상단 제목을 제거·축소하고 제목/도구줄을 40px로 만들었다. 긴 동작명은 짧은 라벨과 tooltip으로 분리하고 AI·PC 연결·문서 변환의 좁은 action까지 축약했으며 전역 버튼 두 줄 깨짐을 차단했다.</x:v>
+      </x:c>
+      <x:c r="E21" t="str">
+        <x:v>compact verifier, 로컬 production/PDF.js, NAS frontend 8/8, live main.48759c30.js, 내부·공개 200.</x:v>
+      </x:c>
+      <x:c r="F21" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb68c39977e5543a1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb6d8bc6b3dfe4b65"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11163,6 +11217,26 @@
       </x:c>
       <x:c r="F24" t="str">
         <x:v>자동 브라우저 로그인 세션 부재로 실제 사용자 창에서 dock 위치 육안 E2E만 남음. C/C++ scanf와 지속 PTY는 미지원.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25">
+      <x:c r="A25" t="str">
+        <x:v>M1-P</x:v>
+      </x:c>
+      <x:c r="B25" t="str">
+        <x:v>컴팩트 상단 UI·긴 라벨 안전성</x:v>
+      </x:c>
+      <x:c r="C25" t="str">
+        <x:v>완료·운영 배포 / 로그인 실화면 확인 필요</x:v>
+      </x:c>
+      <x:c r="D25" t="str">
+        <x:v>inline header 제거, window chrome 30px, sidebar 38px, page bar 40px, 짧은 label+tooltip/aria, 전역 Button nowrap, AI/PC 연결/문서 결과 compact action, verifier</x:v>
+      </x:c>
+      <x:c r="E25" t="str">
+        <x:v>로컬 build/PDF.js/verifier. NAS verifier·frontend 8/8. 최종 로컬 산출물 main.48759c30.js 운영 배포, 내부·공개 200</x:v>
+      </x:c>
+      <x:c r="F25" t="str">
+        <x:v>로그인된 실제 좁은 창과 매우 긴 노트명 육안 확인. NAS direct build는 swap 포화 OOM이므로 별도 build host 정책 필요.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -11374,7 +11448,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Reb9e304ea49f41aa"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Raf5d85443cce448b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11657,7 +11731,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R86dd999befd943a6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcf376ed2e6244a9a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12410,7 +12484,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R85be69723a3f44ed"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R711d3a51bb6f4ea1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12653,7 +12727,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R02548fd61fc04780"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd45b83e76b8f4978"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12859,10 +12933,27 @@
         <x:v>경로 소실·revision 충돌·자원 대기·실행 오류·polling 단절을 구분하며 숨은 실행 세션은 재열 수 있다.</x:v>
       </x:c>
     </x:row>
+    <x:row r="12">
+      <x:c r="A12" t="str">
+        <x:v>컴팩트 상단 UI</x:v>
+      </x:c>
+      <x:c r="B12" t="str">
+        <x:v>30px 창 chrome → 38px sidebar 도구 → 40px 페이지 제목/도구 → 편집기</x:v>
+      </x:c>
+      <x:c r="C12" t="str">
+        <x:v>짧은 실행·문서·가져오기 라벨, tooltip, aria-label, 가로 overflow</x:v>
+      </x:c>
+      <x:c r="D12" t="str">
+        <x:v>inline 앱 이름 header는 표시하지 않는다. 긴 노트명은 제목 입력이 남은 폭을 우선 사용하고 버튼·chip은 한 줄을 유지한다.</x:v>
+      </x:c>
+      <x:c r="E12" t="str">
+        <x:v>좁은 창에서도 버튼 높이가 두 줄로 늘어나지 않으며 기능 설명은 hover/focus tooltip으로 확인한다.</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb4bec42e935d406f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd0baf034ae1e4fa0"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13156,7 +13247,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd8fe1470a0f7416b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R30c1755d335d42b3"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/programs/NAS_NOTE_STUDIO_SPEC.xlsx
+++ b/docs/programs/NAS_NOTE_STUDIO_SPEC.xlsx
@@ -2,39 +2,39 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="R57ebc027eac2485b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Product_Vision" sheetId="2" r:id="R4ba32a73d129462a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decisions" sheetId="3" r:id="R27a8006a7e214003"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Competitors" sheetId="4" r:id="R9f92f2695e194f4a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open_Source" sheetId="5" r:id="R52fa3f7824a24a88"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source_Index" sheetId="6" r:id="R30164ab8c7a74995"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Information_Architecture" sheetId="7" r:id="R198348ae16444b9c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI_Layout" sheetId="8" r:id="R5c79da17b93841d1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="User_Flows" sheetId="9" r:id="R25017d3957ad4408"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Note_Types" sheetId="10" r:id="R2c6594e34ca9481f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Block_Catalog" sheetId="11" r:id="Rb2139c65871540b3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Slash_Commands" sheetId="12" r:id="R93d941dc19c643a9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Context_Menus" sheetId="13" r:id="R12977ae7271544d7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Keyboard_Shortcuts" sheetId="14" r:id="R90a666335a054fbd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Database_Views" sheetId="15" r:id="R6cf25370d4da4198"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Code_Text_Mode" sheetId="16" r:id="R65b24a871ce64094"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Python_Notebook" sheetId="17" r:id="R34bacba97f684d2e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Collaboration" sheetId="18" r:id="R14474f1396e84593"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Offline_Desktop" sheetId="19" r:id="R5aea8287356f44b7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data_Model" sheetId="20" r:id="R87725ec800114ca1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Storage_Interop" sheetId="21" r:id="R51ccc36243164f08"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Security" sheetId="22" r:id="R4655b80a619244d8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="API_Contracts" sheetId="23" r:id="Rbaf7144a79db42ca"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="State_Machines" sheetId="24" r:id="Reba224eccefd4f22"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Error_Recovery" sheetId="25" r:id="Ra285a93e4e954cd3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cross_App_Relations" sheetId="26" r:id="R7cf50310dad04e08"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Performance" sheetId="27" r:id="R862a282aa0f142fd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Accessibility" sheetId="28" r:id="R3488f24bb513451e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test_Matrix" sheetId="29" r:id="R3b704d135aab4b3d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="30" r:id="R8fa1bb4f012341ed"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open_Questions" sheetId="31" r:id="Rd4da7b7aff4e42ec"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Change_Log" sheetId="32" r:id="R99a693002b2e475a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Implementation_Status" sheetId="33" r:id="Rb7009c34085340e6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="R81f969c1145b4127"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Product_Vision" sheetId="2" r:id="R25ee69cad41d4b5a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decisions" sheetId="3" r:id="Re5a07c6399e7462f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Competitors" sheetId="4" r:id="R0ecab08735054954"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open_Source" sheetId="5" r:id="Ra03c460462ce4960"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source_Index" sheetId="6" r:id="R56cf3a071add4e86"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Information_Architecture" sheetId="7" r:id="Rdb73379611634d43"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI_Layout" sheetId="8" r:id="R8ae7570548754da4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="User_Flows" sheetId="9" r:id="R93385739a4e14b35"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Note_Types" sheetId="10" r:id="Ra37ace08f6004c86"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Block_Catalog" sheetId="11" r:id="R3d78025f48dc4222"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Slash_Commands" sheetId="12" r:id="R9495a3dd35b341f0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Context_Menus" sheetId="13" r:id="Ra820d20c32bd4030"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Keyboard_Shortcuts" sheetId="14" r:id="Rc70e57b338ed4b7e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Database_Views" sheetId="15" r:id="R3532887ab35b4982"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Code_Text_Mode" sheetId="16" r:id="Rd505dc34fed94940"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Python_Notebook" sheetId="17" r:id="Re6525bb95dd345ed"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Collaboration" sheetId="18" r:id="R39f9002015864a88"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Offline_Desktop" sheetId="19" r:id="Re64423cefc45434f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data_Model" sheetId="20" r:id="Rb39106fbaae14f0c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Storage_Interop" sheetId="21" r:id="R304fe73b3ace45bc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Security" sheetId="22" r:id="R618cf3c205694108"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="API_Contracts" sheetId="23" r:id="R8a65c744e2cc4c46"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="State_Machines" sheetId="24" r:id="Radbef8005a864e0b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Error_Recovery" sheetId="25" r:id="R0c98f590572c43f0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cross_App_Relations" sheetId="26" r:id="R7002b459623240c9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Performance" sheetId="27" r:id="Rd2e366afe0c54a73"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Accessibility" sheetId="28" r:id="Rfe4a3d54418b4fc1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test_Matrix" sheetId="29" r:id="R51a0221d735746b9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="30" r:id="Red6e93ca87d4414c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open_Questions" sheetId="31" r:id="R2923dd420ea74026"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Change_Log" sheetId="32" r:id="Rfb157ac33d754e31"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Implementation_Status" sheetId="33" r:id="R91f4e88e84d9465e"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -928,7 +928,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Raab52b8f134d41d9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra94e02b9ef4e4480"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1271,7 +1271,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb7536e63d36245fd"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra8aba8f873714435"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1674,7 +1674,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd34da2c6c93146c7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rca50f86136b949c6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2197,7 +2197,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re3f4da71cf594350"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R49b32a0aeddf4cfe"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2797,7 +2797,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb88d14b61abf48a9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcd36df5199ca4534"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3822,7 +3822,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re7429a2bac834520"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3728efa65ca24ba7"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4082,7 +4082,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R482f5a91e24b4c4c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re328f8b79909499c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4274,7 +4274,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R23edd102642541b1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6d406e78fda44040"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4653,7 +4653,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0f8c9e3d50134853"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R85194fbeac2244ab"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4913,7 +4913,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7c3934ee12764e26"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R30160d2586964fc2"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5105,7 +5105,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb2237502990943b0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf11d4472f78a4cb2"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5238,7 +5238,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcc89e77b5e774a7e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ref31ba92260f4f2f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5651,7 +5651,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb7a4ae9f04cc40d6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf943584e4c3e4ec7"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5911,7 +5911,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R38b489ae8ac84f66"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf2e895faab4d4b26"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6324,7 +6324,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbdd76f693d6143b2"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re9c4bd76f7cc49ca"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6873,7 +6873,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Reff401059bc8497c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd51cb5085f8d4bf8"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7269,7 +7269,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdcf6f2214d7349a2"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8e0c203e34a24593"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7665,7 +7665,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb9abede0e93749ef"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfe9a410fccb74455"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8027,7 +8027,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rce6f3f32ff8e4147"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R055e8d00f5ff4731"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8287,7 +8287,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rebf8f81f71ee422a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R39207bde934e41a8"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8459,10 +8459,24 @@
         <x:v>Python/JavaScript 실행처럼 현재 상태·언어를 툴팁에서 확인 가능해야 한다.</x:v>
       </x:c>
     </x:row>
+    <x:row r="12">
+      <x:c r="A12" t="str">
+        <x:v>페이지 더보기 메뉴</x:v>
+      </x:c>
+      <x:c r="B12" t="str">
+        <x:v>버전·내보내기·삭제/복원을 시각적 혼잡 없이 제공한다.</x:v>
+      </x:c>
+      <x:c r="C12" t="str">
+        <x:v>aria-haspopup=menu, aria-expanded, 메뉴 accessible label, 아이콘+텍스트 MenuItem을 사용한다.</x:v>
+      </x:c>
+      <x:c r="D12" t="str">
+        <x:v>위험 동작은 error 색상과 기존 영구 삭제 확인을 유지한다.</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbd81841fb3be41cd"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R12b1e64917a94a65"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9462,10 +9476,30 @@
         <x:v>M1-O</x:v>
       </x:c>
     </x:row>
+    <x:row r="50">
+      <x:c r="A50" t="str">
+        <x:v>UI-TOOLBAR-02</x:v>
+      </x:c>
+      <x:c r="B50" t="str">
+        <x:v>일반·코드·휴지통 페이지 상단 그룹</x:v>
+      </x:c>
+      <x:c r="C50" t="str">
+        <x:v>정적 verifier → production build → 일반/코드/삭제 페이지 육안 확인</x:v>
+      </x:c>
+      <x:c r="D50" t="str">
+        <x:v>일반은 코드 그룹 없음, Python은 실행/패키지, 휴지통은 복원/영구삭제, 더보기 메뉴 keyboard/pointer 가능</x:v>
+      </x:c>
+      <x:c r="E50" t="str">
+        <x:v>자동 verifier·build·운영 배포 완료 / 로그인 육안 확인 필요</x:v>
+      </x:c>
+      <x:c r="F50" t="str">
+        <x:v>M1-O</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R34d1f6c0abbb4389"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R59e867b000754733"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9912,7 +9946,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3693b08d06eb4179"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5d8cf7445aa04f83"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10053,7 +10087,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra602a461d7824091"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra1d9eab00fb843c8"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10279,7 +10313,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2d2bbeeb3b3440d3"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8bdfce9c5e034577"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10719,10 +10753,30 @@
         <x:v>Codex</x:v>
       </x:c>
     </x:row>
+    <x:row r="22">
+      <x:c r="A22" t="str">
+        <x:v>2026-09-08</x:v>
+      </x:c>
+      <x:c r="B22" t="str">
+        <x:v>1.10-toolbar-groups</x:v>
+      </x:c>
+      <x:c r="C22" t="str">
+        <x:v>완료·운영 배포 / 로그인 실화면 확인 필요</x:v>
+      </x:c>
+      <x:c r="D22" t="str">
+        <x:v>Note Studio 상단 동작을 제목·코드 실행·작업공간·보조 작업으로 정렬하고 버전·내보내기·삭제/복원을 더보기 메뉴로 이동했다. sidebar 상단도 목록 제어와 생성 그룹으로 분리했다.</x:v>
+      </x:c>
+      <x:c r="E22" t="str">
+        <x:v>compact/UI contract/window manager verifier, production/PDF.js, NAS verifier, live main.5fd6891d.js, HTTP 200.</x:v>
+      </x:c>
+      <x:c r="F22" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb6d8bc6b3dfe4b65"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re5c6eeafc8a046fd"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11237,6 +11291,26 @@
       </x:c>
       <x:c r="F25" t="str">
         <x:v>로그인된 실제 좁은 창과 매우 긴 노트명 육안 확인. NAS direct build는 swap 포화 OOM이므로 별도 build host 정책 필요.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26">
+      <x:c r="A26" t="str">
+        <x:v>M1-Q</x:v>
+      </x:c>
+      <x:c r="B26" t="str">
+        <x:v>상단바 기능 그룹과 보조 동작 더보기</x:v>
+      </x:c>
+      <x:c r="C26" t="str">
+        <x:v>완료·운영 배포 / 로그인 실화면 확인 필요</x:v>
+      </x:c>
+      <x:c r="D26" t="str">
+        <x:v>sidebar 목록/생성 분리, 제목/저장/코드/작업공간 그룹, 버전·내보내기·삭제/복원 overflow menu</x:v>
+      </x:c>
+      <x:c r="E26" t="str">
+        <x:v>compact/UI contract/window manager verifier, production/PDF.js build, NAS verifier, live main.5fd6891d.js, 내부·공개 200</x:v>
+      </x:c>
+      <x:c r="F26" t="str">
+        <x:v>로그인된 일반·코드·휴지통 페이지와 좁은 창의 실제 포인터/키보드 확인</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -11448,7 +11522,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Raf5d85443cce448b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdbee4e18db274ecd"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11731,7 +11805,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcf376ed2e6244a9a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5616c97c670d4738"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12484,7 +12558,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R711d3a51bb6f4ea1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbbd2397640e54385"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12727,7 +12801,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd45b83e76b8f4978"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7d71bcfefaf6433c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12950,10 +13024,27 @@
         <x:v>좁은 창에서도 버튼 높이가 두 줄로 늘어나지 않으며 기능 설명은 hover/focus tooltip으로 확인한다.</x:v>
       </x:c>
     </x:row>
+    <x:row r="13">
+      <x:c r="A13" t="str">
+        <x:v>상단 작업 그룹</x:v>
+      </x:c>
+      <x:c r="B13" t="str">
+        <x:v>제목+저장 | 코드 언어·실행·콘솔·패키지 | 터미널·문서·첨부 | 더보기</x:v>
+      </x:c>
+      <x:c r="C13" t="str">
+        <x:v>그룹 사이 vertical divider, 동일한 30px control 높이, secondary/destructive menu</x:v>
+      </x:c>
+      <x:c r="D13" t="str">
+        <x:v>일반 노트에는 코드 그룹이 나타나지 않는다. 휴지통 페이지는 더보기 안에 복원·영구삭제만 표시한다.</x:v>
+      </x:c>
+      <x:c r="E13" t="str">
+        <x:v>40px bar를 유지하고 좁은 창에서는 한 줄 가로 overflow로 모든 그룹에 접근한다.</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd0baf034ae1e4fa0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6f307efdc7c84afe"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13247,7 +13338,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R30c1755d335d42b3"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1b46da2d234a4325"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/programs/NAS_NOTE_STUDIO_SPEC.xlsx
+++ b/docs/programs/NAS_NOTE_STUDIO_SPEC.xlsx
@@ -2,39 +2,39 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="R81f969c1145b4127"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Product_Vision" sheetId="2" r:id="R25ee69cad41d4b5a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decisions" sheetId="3" r:id="Re5a07c6399e7462f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Competitors" sheetId="4" r:id="R0ecab08735054954"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open_Source" sheetId="5" r:id="Ra03c460462ce4960"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source_Index" sheetId="6" r:id="R56cf3a071add4e86"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Information_Architecture" sheetId="7" r:id="Rdb73379611634d43"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI_Layout" sheetId="8" r:id="R8ae7570548754da4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="User_Flows" sheetId="9" r:id="R93385739a4e14b35"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Note_Types" sheetId="10" r:id="Ra37ace08f6004c86"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Block_Catalog" sheetId="11" r:id="R3d78025f48dc4222"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Slash_Commands" sheetId="12" r:id="R9495a3dd35b341f0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Context_Menus" sheetId="13" r:id="Ra820d20c32bd4030"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Keyboard_Shortcuts" sheetId="14" r:id="Rc70e57b338ed4b7e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Database_Views" sheetId="15" r:id="R3532887ab35b4982"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Code_Text_Mode" sheetId="16" r:id="Rd505dc34fed94940"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Python_Notebook" sheetId="17" r:id="Re6525bb95dd345ed"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Collaboration" sheetId="18" r:id="R39f9002015864a88"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Offline_Desktop" sheetId="19" r:id="Re64423cefc45434f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data_Model" sheetId="20" r:id="Rb39106fbaae14f0c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Storage_Interop" sheetId="21" r:id="R304fe73b3ace45bc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Security" sheetId="22" r:id="R618cf3c205694108"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="API_Contracts" sheetId="23" r:id="R8a65c744e2cc4c46"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="State_Machines" sheetId="24" r:id="Radbef8005a864e0b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Error_Recovery" sheetId="25" r:id="R0c98f590572c43f0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cross_App_Relations" sheetId="26" r:id="R7002b459623240c9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Performance" sheetId="27" r:id="Rd2e366afe0c54a73"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Accessibility" sheetId="28" r:id="Rfe4a3d54418b4fc1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test_Matrix" sheetId="29" r:id="R51a0221d735746b9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="30" r:id="Red6e93ca87d4414c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open_Questions" sheetId="31" r:id="R2923dd420ea74026"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Change_Log" sheetId="32" r:id="Rfb157ac33d754e31"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Implementation_Status" sheetId="33" r:id="R91f4e88e84d9465e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="Rca3743b5eddc45be"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Product_Vision" sheetId="2" r:id="R1e145b3a8bba495c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decisions" sheetId="3" r:id="R110b827b73454185"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Competitors" sheetId="4" r:id="Rfd277a25b3774aa6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open_Source" sheetId="5" r:id="R28c458d2a0c04e42"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source_Index" sheetId="6" r:id="Rcd9073a3f0054ec5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Information_Architecture" sheetId="7" r:id="R205f6649f7324ad5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI_Layout" sheetId="8" r:id="Raa54fcf096994891"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="User_Flows" sheetId="9" r:id="R6fb5f09fadb043b5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Note_Types" sheetId="10" r:id="R1882081dbd7e48a1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Block_Catalog" sheetId="11" r:id="R6f9b02eb4efb407f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Slash_Commands" sheetId="12" r:id="R29cf7913e1e54bd8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Context_Menus" sheetId="13" r:id="Rc5a1b7a1d9f345a0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Keyboard_Shortcuts" sheetId="14" r:id="R8d00b3705d314cbf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Database_Views" sheetId="15" r:id="R8905334c7bd24631"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Code_Text_Mode" sheetId="16" r:id="Rf372a141197a4757"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Python_Notebook" sheetId="17" r:id="R201940e9b77444a0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Collaboration" sheetId="18" r:id="R6df7137973284eaa"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Offline_Desktop" sheetId="19" r:id="R07e0c8d6dca44e6e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data_Model" sheetId="20" r:id="R75efb0c6dc934af9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Storage_Interop" sheetId="21" r:id="Rf6e8de7e929e45d0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Security" sheetId="22" r:id="Rc7277da17f234e15"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="API_Contracts" sheetId="23" r:id="R4473d612b7004256"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="State_Machines" sheetId="24" r:id="Rfae296594cb24978"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Error_Recovery" sheetId="25" r:id="Rdefbc7f505e442c5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cross_App_Relations" sheetId="26" r:id="R9c51830d6f3e4ed9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Performance" sheetId="27" r:id="Ra7a30c48296e46bc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Accessibility" sheetId="28" r:id="Rc0063fa2b96e48bc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test_Matrix" sheetId="29" r:id="R37efbed43d764c33"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="30" r:id="R4a2255c96abb454c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open_Questions" sheetId="31" r:id="R10eeb2cd1b0c4df0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Change_Log" sheetId="32" r:id="R539ef92178ac4a6e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Implementation_Status" sheetId="33" r:id="R78a05e420cd14c06"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -139,7 +139,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="21">
+  <x:cellXfs count="22">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -186,6 +186,9 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -928,7 +931,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra94e02b9ef4e4480"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8ef315adbc2e4519"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1271,7 +1274,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra8aba8f873714435"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R22b77e3cf1cd4cdc"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1674,7 +1677,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rca50f86136b949c6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R528a0dacbf4242aa"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2197,7 +2200,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R49b32a0aeddf4cfe"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R737b522aa0c34ca6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2794,10 +2797,44 @@
         <x:v>각 노트북의 하위 페이지만 숨기며 선택·내용은 삭제하지 않는다. 터미널은 해당 노트북 scope를 고정한다.</x:v>
       </x:c>
     </x:row>
+    <x:row r="35" ht="51" customHeight="1">
+      <x:c r="A35" s="21" t="str">
+        <x:v>페이지 트리</x:v>
+      </x:c>
+      <x:c r="B35" s="21" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C35" s="21" t="str">
+        <x:v>열기 · 접기/펼치기 · 하위 페이지 만들기 · 이름 변경 · 최상위 이동 · 휴지통</x:v>
+      </x:c>
+      <x:c r="D35" s="21" t="str">
+        <x:v>현재 페이지 상태·물리 페이지 이동 제한·자식 존재 여부</x:v>
+      </x:c>
+      <x:c r="E35" s="21" t="str">
+        <x:v>탐색/편집/구조/위험 동작 순서로 구분하고 F2 키보드 경로와 hover 더보기를 함께 제공한다.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" ht="51" customHeight="1">
+      <x:c r="A36" s="21" t="str">
+        <x:v>프로젝트 파일 트리</x:v>
+      </x:c>
+      <x:c r="B36" s="21" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C36" s="21" t="str">
+        <x:v>열기 · 접기/펼치기 · 새 파일/폴더 · 이름 변경 · NAS 경로 복사 · 휴지통</x:v>
+      </x:c>
+      <x:c r="D36" s="21" t="str">
+        <x:v>현재 계정 notebook path와 기존 /api/file 검증</x:v>
+      </x:c>
+      <x:c r="E36" s="21" t="str">
+        <x:v>폴더를 선택하면 생성 대상, 파일을 선택하면 부모 폴더를 대상으로 삼는다. 계정 경계·quota·고정 폴더·휴지통 정책을 우회하지 않는다.</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcd36df5199ca4534"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0d1ae4a62e964dc3"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3819,10 +3856,27 @@
         <x:v>콘솔 자체 shortcut과 C/C++ compiler는 후속 범위</x:v>
       </x:c>
     </x:row>
+    <x:row r="60" ht="51" customHeight="1">
+      <x:c r="A60" s="21" t="str">
+        <x:v>페이지 트리</x:v>
+      </x:c>
+      <x:c r="B60" s="21" t="str">
+        <x:v>F2</x:v>
+      </x:c>
+      <x:c r="C60" s="21" t="str">
+        <x:v>포커스한 페이지 이름 변경 dialog</x:v>
+      </x:c>
+      <x:c r="D60" s="21" t="str">
+        <x:v>휴지통에서는 비활성. 저장 revision 충돌 시 원본을 유지하고 오류 표시.</x:v>
+      </x:c>
+      <x:c r="E60" s="21" t="str">
+        <x:v>M1-R 구현</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3728efa65ca24ba7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9b0809b705fb490e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4082,7 +4136,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re328f8b79909499c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1567c00620a24caa"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4274,7 +4328,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6d406e78fda44040"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R18b0850992bb43f3"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4653,7 +4707,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R85194fbeac2244ab"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb7e350379eb9483d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4913,7 +4967,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R30160d2586964fc2"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4d1f78eb8f3b4e23"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5105,7 +5159,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf11d4472f78a4cb2"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra34c840b71c342d2"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5238,7 +5292,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ref31ba92260f4f2f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5f24ed27a3da4ff1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5651,7 +5705,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf943584e4c3e4ec7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R721c05f070d04036"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5911,7 +5965,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf2e895faab4d4b26"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdc46d596c30f4085"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6324,7 +6378,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re9c4bd76f7cc49ca"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8d1d02acbbb8460e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6873,7 +6927,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd51cb5085f8d4bf8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc5513f2ece3d4034"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7269,7 +7323,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8e0c203e34a24593"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R53435163a5c24a4c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7665,7 +7719,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfe9a410fccb74455"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4968bae190874601"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8027,7 +8081,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R055e8d00f5ff4731"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R918fe5e7415a4d0f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8287,7 +8341,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R39207bde934e41a8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re07bbd9853b94de8"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8473,10 +8527,24 @@
         <x:v>위험 동작은 error 색상과 기존 영구 삭제 확인을 유지한다.</x:v>
       </x:c>
     </x:row>
+    <x:row r="13" ht="51" customHeight="1">
+      <x:c r="A13" s="21" t="str">
+        <x:v>페이지·파일 트리</x:v>
+      </x:c>
+      <x:c r="B13" s="21" t="str">
+        <x:v>tree/treeitem, aria-level, aria-expanded, 완전한 작업 이름을 제공한다.</x:v>
+      </x:c>
+      <x:c r="C13" s="21" t="str">
+        <x:v>키보드 F2와 각 행 더보기 버튼, touch 환경 작업 버튼 상시 표시</x:v>
+      </x:c>
+      <x:c r="D13" s="21" t="str">
+        <x:v>가지선·색만으로 계층과 선택을 전달하지 않는다.</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R12b1e64917a94a65"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6f5b2fc388f944af"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9496,10 +9564,30 @@
         <x:v>M1-O</x:v>
       </x:c>
     </x:row>
+    <x:row r="51" ht="51" customHeight="1">
+      <x:c r="A51" s="21" t="str">
+        <x:v>UI-TREE-03</x:v>
+      </x:c>
+      <x:c r="B51" s="21" t="str">
+        <x:v>페이지·프로젝트 파일 계층과 context action</x:v>
+      </x:c>
+      <x:c r="C51" s="21" t="str">
+        <x:v>root/child/grandchild/sibling 접기, hover/touch, F2, 새 파일·폴더, 이름 변경, 경로 복사, 휴지통, 타 계정·../·symlink</x:v>
+      </x:c>
+      <x:c r="D51" s="21" t="str">
+        <x:v>부모 접기 시 모든 자손만 숨고 형제는 유지. 파일 동작은 notebook/account 경계를 벗어나지 않으며 기존 휴지통으로 이동.</x:v>
+      </x:c>
+      <x:c r="E51" s="21" t="str">
+        <x:v>unit+static+production+NAS integration+로그인 E2E</x:v>
+      </x:c>
+      <x:c r="F51" s="21" t="str">
+        <x:v>M1-R</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R59e867b000754733"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re1ce7cd2a959487f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9946,7 +10034,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5d8cf7445aa04f83"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcea1231ee8cb4aac"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10087,7 +10175,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra1d9eab00fb843c8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R450f35fdc3d14f90"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10313,7 +10401,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8bdfce9c5e034577"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R955f914748b64a79"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10773,10 +10861,30 @@
         <x:v>Codex</x:v>
       </x:c>
     </x:row>
+    <x:row r="23" ht="64.5" customHeight="1">
+      <x:c r="A23" s="21" t="str">
+        <x:v>2026-09-08</x:v>
+      </x:c>
+      <x:c r="B23" s="21" t="str">
+        <x:v>1.11-guided-trees</x:v>
+      </x:c>
+      <x:c r="C23" s="21" t="str">
+        <x:v>완료·운영 배포 / 로그인 실화면 E2E 필요</x:v>
+      </x:c>
+      <x:c r="D23" s="21" t="str">
+        <x:v>Notion식 페이지 계층과 VS Code식 프로젝트 파일 탐색기를 하나의 가벼운 sidebar 언어로 통합했다. 페이지별 접기·가지선·hover 작업과 프로젝트 파일 생성/수정 메뉴를 추가했다.</x:v>
+      </x:c>
+      <x:c r="E23" s="21" t="str">
+        <x:v>로컬 production/PDF.js·정적 verifier. NAS focused Jest 7/7·verifier. live main.14d6d282.js·공개 HTTP 200.</x:v>
+      </x:c>
+      <x:c r="F23" s="21" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re5c6eeafc8a046fd"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdb7f6abcc021418e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11311,6 +11419,26 @@
       </x:c>
       <x:c r="F26" t="str">
         <x:v>로그인된 일반·코드·휴지통 페이지와 좁은 창의 실제 포인터/키보드 확인</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" ht="64.5" customHeight="1">
+      <x:c r="A27" s="21" t="str">
+        <x:v>M1-R</x:v>
+      </x:c>
+      <x:c r="B27" s="21" t="str">
+        <x:v>가이드 페이지 트리·프로젝트 파일 탐색기</x:v>
+      </x:c>
+      <x:c r="C27" s="21" t="str">
+        <x:v>완료·운영 배포 / 로그인 실화면 E2E 필요</x:v>
+      </x:c>
+      <x:c r="D27" s="21" t="str">
+        <x:v>Notion형 페이지별 collapse/guide/hover actions/F2와 VS Code형 파일 selection/context create/rename/copy path/trash, accessible tree, session persistence</x:v>
+      </x:c>
+      <x:c r="E27" s="21" t="str">
+        <x:v>로컬 build/PDF.js·정적 verifier, NAS focused 7/7, live main.14d6d282.js, 공개 HTTP 200</x:v>
+      </x:c>
+      <x:c r="F27" s="21" t="str">
+        <x:v>로그인된 실제 노트북에서 pointer·touch·keyboard, 긴 이름, 새 파일/이름 변경/휴지통 end-to-end 확인</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -11522,7 +11650,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdbee4e18db274ecd"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb4ccdbfd37e644a8"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11805,7 +11933,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5616c97c670d4738"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcf94cfba0d074b1a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12555,10 +12683,78 @@
         <x:v>2026-09-08</x:v>
       </x:c>
     </x:row>
+    <x:row r="44" ht="51" customHeight="1">
+      <x:c r="A44" s="21" t="str">
+        <x:v>SRC-044</x:v>
+      </x:c>
+      <x:c r="B44" s="21" t="str">
+        <x:v>Notion Help</x:v>
+      </x:c>
+      <x:c r="C44" s="21" t="str">
+        <x:v>Create a subpage</x:v>
+      </x:c>
+      <x:c r="D44" s="21" t="str">
+        <x:v>페이지 안의 페이지, sidebar toggle, breadcrumb, drag 계층 구조 참고</x:v>
+      </x:c>
+      <x:c r="E44" s="21" t="str">
+        <x:v>https://www.notion.com/en-gb/help/create-a-subpage</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45" ht="51" customHeight="1">
+      <x:c r="A45" s="21" t="str">
+        <x:v>SRC-045</x:v>
+      </x:c>
+      <x:c r="B45" s="21" t="str">
+        <x:v>Notion Help</x:v>
+      </x:c>
+      <x:c r="C45" s="21" t="str">
+        <x:v>Navigate with the sidebar</x:v>
+      </x:c>
+      <x:c r="D45" s="21" t="str">
+        <x:v>무한 중첩, hover +/더보기, drag nesting과 sidebar 탐색 참고</x:v>
+      </x:c>
+      <x:c r="E45" s="21" t="str">
+        <x:v>https://www.notion.com/en-gb/help/navigate-with-the-sidebar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46" ht="51" customHeight="1">
+      <x:c r="A46" s="21" t="str">
+        <x:v>SRC-046</x:v>
+      </x:c>
+      <x:c r="B46" s="21" t="str">
+        <x:v>VS Code UX Guidelines</x:v>
+      </x:c>
+      <x:c r="C46" s="21" t="str">
+        <x:v>Context menus</x:v>
+      </x:c>
+      <x:c r="D46" s="21" t="str">
+        <x:v>현재 대상에 맞는 명령만 노출하고 유사 동작을 묶는 메뉴 원칙 참고</x:v>
+      </x:c>
+      <x:c r="E46" s="21" t="str">
+        <x:v>https://code.visualstudio.com/api/ux-guidelines/context-menus</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47" ht="51" customHeight="1">
+      <x:c r="A47" s="21" t="str">
+        <x:v>SRC-047</x:v>
+      </x:c>
+      <x:c r="B47" s="21" t="str">
+        <x:v>VS Code Documentation</x:v>
+      </x:c>
+      <x:c r="C47" s="21" t="str">
+        <x:v>Editor basics and Explorer</x:v>
+      </x:c>
+      <x:c r="D47" s="21" t="str">
+        <x:v>Explorer의 파일 생성·검색·비교·통합 터미널 흐름 참고</x:v>
+      </x:c>
+      <x:c r="E47" s="21" t="str">
+        <x:v>https://code.visualstudio.com/docs/editing/codebasics</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbbd2397640e54385"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Reace08b7a91544d9"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12798,10 +12994,27 @@
         <x:v>Ctrl+P. 검색 결과에 노트 유형·경로·권한·최근 수정 표시.</x:v>
       </x:c>
     </x:row>
+    <x:row r="14" ht="51" customHeight="1">
+      <x:c r="A14" s="21" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="B14" s="21" t="str">
+        <x:v>왼쪽 통합 트리</x:v>
+      </x:c>
+      <x:c r="C14" s="21" t="str">
+        <x:v>노트북 → 페이지/하위 페이지 · 프로젝트 → 실제 폴더/파일</x:v>
+      </x:c>
+      <x:c r="D14" s="21" t="str">
+        <x:v>세대별 가지선, 자식 chevron, 선택 상태, hover +/더보기, 접기 상태 복원</x:v>
+      </x:c>
+      <x:c r="E14" s="21" t="str">
+        <x:v>노트는 Notion식 여백과 가벼운 선을 유지하고 프로젝트 파일만 VS Code식 조작 밀도를 높인다.</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7d71bcfefaf6433c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rec4f3b376ff84bdd"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13041,10 +13254,27 @@
         <x:v>40px bar를 유지하고 좁은 창에서는 한 줄 가로 overflow로 모든 그룹에 접근한다.</x:v>
       </x:c>
     </x:row>
+    <x:row r="14" ht="51" customHeight="1">
+      <x:c r="A14" s="21" t="str">
+        <x:v>페이지·프로젝트 트리</x:v>
+      </x:c>
+      <x:c r="B14" s="21" t="str">
+        <x:v>노트북 root → 페이지 트리 / 하단 탐색기 → 실제 파일 트리</x:v>
+      </x:c>
+      <x:c r="C14" s="21" t="str">
+        <x:v>페이지별 접기, hover 하위 생성·더보기, F2 이름 변경, 파일 새로 만들기·이름 변경·경로 복사·휴지통</x:v>
+      </x:c>
+      <x:c r="D14" s="21" t="str">
+        <x:v>monochrome 아이콘과 얇은 가지선, tree/treeitem·aria-level/expanded, touch에서는 작업 버튼 상시 표시</x:v>
+      </x:c>
+      <x:c r="E14" s="21" t="str">
+        <x:v>검색 결과·휴지통·하위 페이지·2,000개 제한·긴 이름에서도 부모 관계와 선택 상태를 잃지 않는다.</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6f307efdc7c84afe"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R06b151c55db343c4"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13338,7 +13568,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1b46da2d234a4325"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbfd04e09bd8241e4"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/programs/NAS_NOTE_STUDIO_SPEC.xlsx
+++ b/docs/programs/NAS_NOTE_STUDIO_SPEC.xlsx
@@ -2,39 +2,39 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="Rca3743b5eddc45be"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Product_Vision" sheetId="2" r:id="R1e145b3a8bba495c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decisions" sheetId="3" r:id="R110b827b73454185"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Competitors" sheetId="4" r:id="Rfd277a25b3774aa6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open_Source" sheetId="5" r:id="R28c458d2a0c04e42"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source_Index" sheetId="6" r:id="Rcd9073a3f0054ec5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Information_Architecture" sheetId="7" r:id="R205f6649f7324ad5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI_Layout" sheetId="8" r:id="Raa54fcf096994891"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="User_Flows" sheetId="9" r:id="R6fb5f09fadb043b5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Note_Types" sheetId="10" r:id="R1882081dbd7e48a1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Block_Catalog" sheetId="11" r:id="R6f9b02eb4efb407f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Slash_Commands" sheetId="12" r:id="R29cf7913e1e54bd8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Context_Menus" sheetId="13" r:id="Rc5a1b7a1d9f345a0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Keyboard_Shortcuts" sheetId="14" r:id="R8d00b3705d314cbf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Database_Views" sheetId="15" r:id="R8905334c7bd24631"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Code_Text_Mode" sheetId="16" r:id="Rf372a141197a4757"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Python_Notebook" sheetId="17" r:id="R201940e9b77444a0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Collaboration" sheetId="18" r:id="R6df7137973284eaa"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Offline_Desktop" sheetId="19" r:id="R07e0c8d6dca44e6e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data_Model" sheetId="20" r:id="R75efb0c6dc934af9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Storage_Interop" sheetId="21" r:id="Rf6e8de7e929e45d0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Security" sheetId="22" r:id="Rc7277da17f234e15"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="API_Contracts" sheetId="23" r:id="R4473d612b7004256"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="State_Machines" sheetId="24" r:id="Rfae296594cb24978"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Error_Recovery" sheetId="25" r:id="Rdefbc7f505e442c5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cross_App_Relations" sheetId="26" r:id="R9c51830d6f3e4ed9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Performance" sheetId="27" r:id="Ra7a30c48296e46bc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Accessibility" sheetId="28" r:id="Rc0063fa2b96e48bc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test_Matrix" sheetId="29" r:id="R37efbed43d764c33"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="30" r:id="R4a2255c96abb454c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open_Questions" sheetId="31" r:id="R10eeb2cd1b0c4df0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Change_Log" sheetId="32" r:id="R539ef92178ac4a6e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Implementation_Status" sheetId="33" r:id="R78a05e420cd14c06"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="Reabffc261a2f4d70"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Product_Vision" sheetId="2" r:id="R42efad16656648f3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decisions" sheetId="3" r:id="R8e48ac63da914be1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Competitors" sheetId="4" r:id="R4ade39476458437e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open_Source" sheetId="5" r:id="R083f7842545e426d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source_Index" sheetId="6" r:id="Rd065d6e115294a84"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Information_Architecture" sheetId="7" r:id="R63029a0d7a2d494b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI_Layout" sheetId="8" r:id="R8533232dbf5142c7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="User_Flows" sheetId="9" r:id="Rba5135f9379b4e33"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Note_Types" sheetId="10" r:id="R332f8497c9cc46a2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Block_Catalog" sheetId="11" r:id="Ra6c2397e7ef24d8c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Slash_Commands" sheetId="12" r:id="R345ced9e80974907"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Context_Menus" sheetId="13" r:id="R8480a4c4d1e54d81"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Keyboard_Shortcuts" sheetId="14" r:id="Re8c3962361f44e16"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Database_Views" sheetId="15" r:id="R66145a0ce0d34295"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Code_Text_Mode" sheetId="16" r:id="Rff6f1285a90d4f33"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Python_Notebook" sheetId="17" r:id="R6a4e5937421a44fa"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Collaboration" sheetId="18" r:id="R84ba92fd65044504"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Offline_Desktop" sheetId="19" r:id="Rf9f23feb27a74c73"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data_Model" sheetId="20" r:id="Rd39c20fa116d41e3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Storage_Interop" sheetId="21" r:id="R6d2812e36ab141a6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Security" sheetId="22" r:id="Rabdc79c7d07b43c0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="API_Contracts" sheetId="23" r:id="R6b0a15bb6f884d5b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="State_Machines" sheetId="24" r:id="Rf9faf5de64ce435e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Error_Recovery" sheetId="25" r:id="R89e9b831b73943f0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cross_App_Relations" sheetId="26" r:id="Rf2edb005342d4661"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Performance" sheetId="27" r:id="R9d43743a35224e5c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Accessibility" sheetId="28" r:id="Rddaf9a9308c24dd4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test_Matrix" sheetId="29" r:id="R86254ff46e8c495f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="30" r:id="Rc45832fa4b554075"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open_Questions" sheetId="31" r:id="R2c8044216a1e48f6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Change_Log" sheetId="32" r:id="R4f01d45be3334e16"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Implementation_Status" sheetId="33" r:id="R793f6b6257174fa6"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -931,7 +931,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8ef315adbc2e4519"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3698178412a54cb6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1274,7 +1274,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R22b77e3cf1cd4cdc"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd3dc7490a3ae424c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1677,7 +1677,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R528a0dacbf4242aa"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6e27476875704063"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2200,7 +2200,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R737b522aa0c34ca6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R187f5da7279a4820"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2834,7 +2834,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0d1ae4a62e964dc3"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R61dc42c9921e4a5e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3876,7 +3876,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9b0809b705fb490e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdbd1f8ab664742c0"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4136,7 +4136,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1567c00620a24caa"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R34f8054838b743a6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4325,10 +4325,61 @@
         <x:v>M1</x:v>
       </x:c>
     </x:row>
+    <x:row r="11">
+      <x:c r="A11" t="str">
+        <x:v>언어 감지</x:v>
+      </x:c>
+      <x:c r="B11" t="str">
+        <x:v>확장자·shebang·내용 힌트</x:v>
+      </x:c>
+      <x:c r="C11" t="str">
+        <x:v>파일 import는 서버가 확장자를 우선하고 새 plaintext 코드 노트는 보수적 내용 힌트로 한 번 자동 전환한다. 사용자의 수동 선택이 항상 우선한다.</x:v>
+      </x:c>
+      <x:c r="D11" t="str">
+        <x:v>잘못된 확장자·빈 파일·JSON·한글 본문·수동 override</x:v>
+      </x:c>
+      <x:c r="E11" t="str">
+        <x:v>M1-S</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" t="str">
+        <x:v>실행·검증</x:v>
+      </x:c>
+      <x:c r="B12" t="str">
+        <x:v>Python/JS/TS/Shell/SQL 및 JSON/YAML</x:v>
+      </x:c>
+      <x:c r="C12" t="str">
+        <x:v>선택 노트북만 mount한 격리 컨테이너에서 실행한다. JSON/YAML은 파싱 후 정규화 출력, SQL은 메모리 SQLite에서 다중 문장을 실행한다.</x:v>
+      </x:c>
+      <x:c r="D12" t="str">
+        <x:v>stdout/stderr/stdin·다중 SQL·문법 오류·timeout·queue·cancel</x:v>
+      </x:c>
+      <x:c r="E12" t="str">
+        <x:v>M1-S</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" t="str">
+        <x:v>미리보기</x:v>
+      </x:c>
+      <x:c r="B13" t="str">
+        <x:v>HTML/CSS/Markdown</x:v>
+      </x:c>
+      <x:c r="C13" t="str">
+        <x:v>HTML/CSS는 sandbox iframe+CSP, Markdown은 raw HTML을 실행하지 않는 GFM renderer로 현재 저장 전 편집 내용을 미리 본다.</x:v>
+      </x:c>
+      <x:c r="D13" t="str">
+        <x:v>script/form/network 차단·표/코드/이미지 data URL·다크 모드</x:v>
+      </x:c>
+      <x:c r="E13" t="str">
+        <x:v>M1-S</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R18b0850992bb43f3"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6d056392250f42f0"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4707,7 +4758,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb7e350379eb9483d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R37a2296fda1f4b79"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4967,7 +5018,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4d1f78eb8f3b4e23"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R74a12fba65e84d3b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5159,7 +5210,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra34c840b71c342d2"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1dc929e6212f4f2d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5292,7 +5343,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5f24ed27a3da4ff1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ree0be11a605f4528"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5705,7 +5756,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R721c05f070d04036"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb5d208d767fc4c72"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5965,7 +6016,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdc46d596c30f4085"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R60283478cb4a4fd7"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6375,10 +6426,44 @@
         <x:v>P0</x:v>
       </x:c>
     </x:row>
+    <x:row r="24">
+      <x:c r="A24" t="str">
+        <x:v>SEC-024</x:v>
+      </x:c>
+      <x:c r="B24" t="str">
+        <x:v>다중 언어 런타임</x:v>
+      </x:c>
+      <x:c r="C24" t="str">
+        <x:v>사용자 코드는 host에서 직접 실행하지 않고 Docker network none, non-root UID, read-only root, cap-drop, no-new-privileges, CPU/RAM/PID/time/output 제한과 선택 notebook mount만 사용한다.</x:v>
+      </x:c>
+      <x:c r="D24" t="str">
+        <x:v>backend/managedCodeSession.js args·NAS runtime smoke 7/7</x:v>
+      </x:c>
+      <x:c r="E24" t="str">
+        <x:v>M1-S</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25">
+      <x:c r="A25" t="str">
+        <x:v>SEC-025</x:v>
+      </x:c>
+      <x:c r="B25" t="str">
+        <x:v>웹 코드 미리보기</x:v>
+      </x:c>
+      <x:c r="C25" t="str">
+        <x:v>HTML/CSS 미리보기는 sandbox와 default-src none CSP를 함께 사용하고 Markdown raw HTML을 실행하지 않는다.</x:v>
+      </x:c>
+      <x:c r="D25" t="str">
+        <x:v>script·form·popup·외부 image fetch 시도</x:v>
+      </x:c>
+      <x:c r="E25" t="str">
+        <x:v>M1-S</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8d1d02acbbb8460e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4e275feeb4814639"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6924,10 +7009,61 @@
         <x:v>세션 ID만으로 접근 불가. 서버 인증 owner와 현재 계정 note/notebook을 기준으로 생성.</x:v>
       </x:c>
     </x:row>
+    <x:row r="32">
+      <x:c r="A32" t="str">
+        <x:v>Language catalog</x:v>
+      </x:c>
+      <x:c r="B32" t="str">
+        <x:v>GET languages / POST detect</x:v>
+      </x:c>
+      <x:c r="C32" t="str">
+        <x:v>인증 세션, fileName과 제한된 content hint</x:v>
+      </x:c>
+      <x:c r="D32" t="str">
+        <x:v>언어 id·label·mode·extensions·capability 또는 detection/source/confidence</x:v>
+      </x:c>
+      <x:c r="E32" t="str">
+        <x:v>클라이언트가 임의 runtime/image/command를 지정할 수 없다.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33">
+      <x:c r="A33" t="str">
+        <x:v>Execution queue</x:v>
+      </x:c>
+      <x:c r="B33" t="str">
+        <x:v>GET/DELETE execution-jobs/:jobId</x:v>
+      </x:c>
+      <x:c r="C33" t="str">
+        <x:v>owner-bound jobId</x:v>
+      </x:c>
+      <x:c r="D33" t="str">
+        <x:v>queued position/reasons, starting/running session, finished/blocked/cancelled</x:v>
+      </x:c>
+      <x:c r="E33" t="str">
+        <x:v>owner 불일치 404. 취소·실패·종료에서 reservation 회수.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34">
+      <x:c r="A34" t="str">
+        <x:v>Multi-language session</x:v>
+      </x:c>
+      <x:c r="B34" t="str">
+        <x:v>POST notes/:noteId/:language/session</x:v>
+      </x:c>
+      <x:c r="C34" t="str">
+        <x:v>noteId·catalog language·expectedRevision</x:v>
+      </x:c>
+      <x:c r="D34" t="str">
+        <x:v>202 queue job + sandbox metadata</x:v>
+      </x:c>
+      <x:c r="E34" t="str">
+        <x:v>현재 계정 note/notebook/language/revision을 서버에서 재조회한다.</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc5513f2ece3d4034"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rce03b80a505e4a87"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7320,10 +7456,27 @@
         <x:v>10분 결과 보존, 120초 process limit, 모든 terminal state에서 reservation release.</x:v>
       </x:c>
     </x:row>
+    <x:row r="23">
+      <x:c r="A23" t="str">
+        <x:v>SM-EXEC-QUEUE</x:v>
+      </x:c>
+      <x:c r="B23" t="str">
+        <x:v>queued → starting → running → finished/failed 또는 queued → blocked/cancelled</x:v>
+      </x:c>
+      <x:c r="C23" t="str">
+        <x:v>submit, resource sample/reservation, user cancel, container finish/error/timeout</x:v>
+      </x:c>
+      <x:c r="D23" t="str">
+        <x:v>순번·이유 표시, 실행 콘솔 전환, 예약 release, 10분 뒤 메타 정리</x:v>
+      </x:c>
+      <x:c r="E23" t="str">
+        <x:v>동일 owner 작업만 연속 선택하지 않고 다른 owner가 있으면 교대한다. 영구 정책 위반은 blocked, 기존 실행 때문에 생긴 user limit은 queued로 유지한다.</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R53435163a5c24a4c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5dda118de26f4e54"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7719,7 +7872,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4968bae190874601"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R15a3a1167b044057"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8081,7 +8234,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R918fe5e7415a4d0f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8f14605d86b14d2a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8338,10 +8491,27 @@
         <x:v>M2 worker gate</x:v>
       </x:c>
     </x:row>
+    <x:row r="15">
+      <x:c r="A15" t="str">
+        <x:v>PERF-015</x:v>
+      </x:c>
+      <x:c r="B15" t="str">
+        <x:v>공정 실행 queue</x:v>
+      </x:c>
+      <x:c r="C15" t="str">
+        <x:v>750ms admission 재평가, 한 번에 하나만 새 작업 예약, 사용자 교대 우선 FIFO, 완료 메타 10분 보존</x:v>
+      </x:c>
+      <x:c r="D15" t="str">
+        <x:v>여러 사용자 burst에서 파일·노트 HTTP 응답 유지, 예약 누수 0</x:v>
+      </x:c>
+      <x:c r="E15" t="str">
+        <x:v>M1-S</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re07bbd9853b94de8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rafdbea19356b4b8e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8544,7 +8714,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6f5b2fc388f944af"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd9d4128b865b43b9"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9584,10 +9754,30 @@
         <x:v>M1-R</x:v>
       </x:c>
     </x:row>
+    <x:row r="52">
+      <x:c r="A52" t="str">
+        <x:v>T-049</x:v>
+      </x:c>
+      <x:c r="B52" t="str">
+        <x:v>언어 자동 감지·실행/검증/미리보기·queue</x:v>
+      </x:c>
+      <x:c r="C52" t="str">
+        <x:v>11개 catalog, 확장자/shebang/content, Python/JS/TS/Shell/SQL/JSON/YAML 실제 Docker, HTML/CSS/Markdown CSP, 두 owner burst, cancel/block/finish/release, 타 owner jobId</x:v>
+      </x:c>
+      <x:c r="D52" t="str">
+        <x:v>각 형식은 정확한 mode로 동작하고 서버 자원 기준에서 대기·차단되며 다른 계정/호스트/network로 벗어나지 않는다.</x:v>
+      </x:c>
+      <x:c r="E52" t="str">
+        <x:v>unit+security+NAS Docker integration+production+로그인 E2E</x:v>
+      </x:c>
+      <x:c r="F52" t="str">
+        <x:v>M1-S</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re1ce7cd2a959487f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc30a8c90cc934b0a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10031,10 +10221,44 @@
         <x:v>C/C++ runtime, persistent PTY 또는 다중 세션 탭이 필요할 때 별도 자원·보안 심사를 거친다.</x:v>
       </x:c>
     </x:row>
+    <x:row r="26">
+      <x:c r="A26" t="str">
+        <x:v>DEC-026</x:v>
+      </x:c>
+      <x:c r="B26" t="str">
+        <x:v>채택</x:v>
+      </x:c>
+      <x:c r="C26" t="str">
+        <x:v>언어 선택지는 실행 여부가 아니라 edit/execute/validate/preview 동작으로 분류한다.</x:v>
+      </x:c>
+      <x:c r="D26" t="str">
+        <x:v>HTML·CSS·Markdown을 서버 코드처럼 실행하거나 JSON을 프로그램처럼 표시하는 오해를 막고 각 형식에 맞는 결과를 제공한다.</x:v>
+      </x:c>
+      <x:c r="E26" t="str">
+        <x:v>새 compiler/runtime를 추가할 때 catalog와 보안·자원 심사를 함께 갱신한다.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27">
+      <x:c r="A27" t="str">
+        <x:v>DEC-027</x:v>
+      </x:c>
+      <x:c r="B27" t="str">
+        <x:v>채택</x:v>
+      </x:c>
+      <x:c r="C27" t="str">
+        <x:v>코드 실행은 429 재시도 대신 사용자 교대 우선 FIFO admission queue를 사용한다.</x:v>
+      </x:c>
+      <x:c r="D27" t="str">
+        <x:v>한 사용자의 연속 요청이 다른 사용자를 계속 뒤로 미는 것을 줄이면서 기존 실시간 자원·사용자 한도를 유지한다.</x:v>
+      </x:c>
+      <x:c r="E27" t="str">
+        <x:v>다중 NAS worker 또는 장시간 build farm으로 확장할 때 durable queue로 교체한다.</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcea1231ee8cb4aac"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf8931db38836432b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10175,7 +10399,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R450f35fdc3d14f90"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re81f75eb31f540fa"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10401,7 +10625,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R955f914748b64a79"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra640dd860412438a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10881,10 +11105,30 @@
         <x:v>Codex</x:v>
       </x:c>
     </x:row>
+    <x:row r="24">
+      <x:c r="A24" t="str">
+        <x:v>2026-09-08</x:v>
+      </x:c>
+      <x:c r="B24" t="str">
+        <x:v>M1-S 다중 언어 실행·검증·미리보기·공정 queue</x:v>
+      </x:c>
+      <x:c r="C24" t="str">
+        <x:v>등록 11개 언어 catalog/감지, 7개 Docker runtime, 3개 안전 preview, owner-bound queue와 하단 콘솔 상태를 구현했다.</x:v>
+      </x:c>
+      <x:c r="D24" t="str">
+        <x:v>backend/frontend/tests/docs</x:v>
+      </x:c>
+      <x:c r="E24" t="str">
+        <x:v>로그인 화면에서 두 계정 queue·미리보기 pointer E2E</x:v>
+      </x:c>
+      <x:c r="F24" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdb7f6abcc021418e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5b84f02935e242ea"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11439,6 +11683,26 @@
       </x:c>
       <x:c r="F27" s="21" t="str">
         <x:v>로그인된 실제 노트북에서 pointer·touch·keyboard, 긴 이름, 새 파일/이름 변경/휴지통 end-to-end 확인</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28">
+      <x:c r="A28" t="str">
+        <x:v>M1-S</x:v>
+      </x:c>
+      <x:c r="B28" t="str">
+        <x:v>전체 등록 언어 동작·자동 감지·자원 실행 대기열</x:v>
+      </x:c>
+      <x:c r="C28" t="str">
+        <x:v>완료·운영 배포 / 로그인 실화면 E2E 필요</x:v>
+      </x:c>
+      <x:c r="D28" t="str">
+        <x:v>edit/execute/validate/preview catalog, 확장자·shebang·내용 감지, 7개 격리 runtime, sandbox preview, owner-bound fair queue, 순번·취소·콘솔 전환</x:v>
+      </x:c>
+      <x:c r="E28" t="str">
+        <x:v>로컬 12/12·production/PDF.js. NAS 전체 116 pass 6 skip, 실제 runtime 7/7, UI 2/2, verifier·bundle SHA·HTTP·서비스 정상</x:v>
+      </x:c>
+      <x:c r="F28" t="str">
+        <x:v>로그인된 화면의 두 사용자 동시 queue와 미리보기 육안 E2E. 다중 파일 TSX/JSX bundler·C/C++/Java compiler·durable multi-worker queue는 별도 단계.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -11650,7 +11914,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb4ccdbfd37e644a8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4c1467cf1b014a33"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11933,7 +12197,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcf94cfba0d074b1a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3ef3a6a8de6d4f2f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12754,7 +13018,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Reace08b7a91544d9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfc4bc31cbf1b4e20"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13014,7 +13278,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rec4f3b376ff84bdd"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R97da6cb6eb854cb3"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13274,7 +13538,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R06b151c55db343c4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0be7d0a6cd4448e4"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13568,7 +13832,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbfd04e09bd8241e4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R542d374a42da4abf"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/programs/NAS_NOTE_STUDIO_SPEC.xlsx
+++ b/docs/programs/NAS_NOTE_STUDIO_SPEC.xlsx
@@ -2,39 +2,39 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="Reabffc261a2f4d70"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Product_Vision" sheetId="2" r:id="R42efad16656648f3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decisions" sheetId="3" r:id="R8e48ac63da914be1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Competitors" sheetId="4" r:id="R4ade39476458437e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open_Source" sheetId="5" r:id="R083f7842545e426d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source_Index" sheetId="6" r:id="Rd065d6e115294a84"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Information_Architecture" sheetId="7" r:id="R63029a0d7a2d494b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI_Layout" sheetId="8" r:id="R8533232dbf5142c7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="User_Flows" sheetId="9" r:id="Rba5135f9379b4e33"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Note_Types" sheetId="10" r:id="R332f8497c9cc46a2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Block_Catalog" sheetId="11" r:id="Ra6c2397e7ef24d8c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Slash_Commands" sheetId="12" r:id="R345ced9e80974907"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Context_Menus" sheetId="13" r:id="R8480a4c4d1e54d81"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Keyboard_Shortcuts" sheetId="14" r:id="Re8c3962361f44e16"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Database_Views" sheetId="15" r:id="R66145a0ce0d34295"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Code_Text_Mode" sheetId="16" r:id="Rff6f1285a90d4f33"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Python_Notebook" sheetId="17" r:id="R6a4e5937421a44fa"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Collaboration" sheetId="18" r:id="R84ba92fd65044504"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Offline_Desktop" sheetId="19" r:id="Rf9f23feb27a74c73"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data_Model" sheetId="20" r:id="Rd39c20fa116d41e3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Storage_Interop" sheetId="21" r:id="R6d2812e36ab141a6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Security" sheetId="22" r:id="Rabdc79c7d07b43c0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="API_Contracts" sheetId="23" r:id="R6b0a15bb6f884d5b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="State_Machines" sheetId="24" r:id="Rf9faf5de64ce435e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Error_Recovery" sheetId="25" r:id="R89e9b831b73943f0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cross_App_Relations" sheetId="26" r:id="Rf2edb005342d4661"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Performance" sheetId="27" r:id="R9d43743a35224e5c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Accessibility" sheetId="28" r:id="Rddaf9a9308c24dd4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test_Matrix" sheetId="29" r:id="R86254ff46e8c495f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="30" r:id="Rc45832fa4b554075"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open_Questions" sheetId="31" r:id="R2c8044216a1e48f6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Change_Log" sheetId="32" r:id="R4f01d45be3334e16"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Implementation_Status" sheetId="33" r:id="R793f6b6257174fa6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="R808c4d15b4ba4d96"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Product_Vision" sheetId="2" r:id="Rdaa76c9242e349b6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decisions" sheetId="3" r:id="Rc91d6d3c7cfd44a3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Competitors" sheetId="4" r:id="Ra1c41495e7634d8b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open_Source" sheetId="5" r:id="R4116a1639fb445d3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source_Index" sheetId="6" r:id="Rbf7ecca071334b53"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Information_Architecture" sheetId="7" r:id="R767d1d14e17b4e60"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI_Layout" sheetId="8" r:id="R03d2260d16dd46c9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="User_Flows" sheetId="9" r:id="R46a12327b0e04a30"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Note_Types" sheetId="10" r:id="R9a36cb4b74da4bb4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Block_Catalog" sheetId="11" r:id="R6e3832c37a77414a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Slash_Commands" sheetId="12" r:id="R2010bf247df144b5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Context_Menus" sheetId="13" r:id="R9e34f2b11c3642cb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Keyboard_Shortcuts" sheetId="14" r:id="R0f7a444d6804467d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Database_Views" sheetId="15" r:id="Rb1e2c3a76ffd4c86"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Code_Text_Mode" sheetId="16" r:id="R9a0d180d9e784cdc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Python_Notebook" sheetId="17" r:id="R393ce84b00ef4424"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Collaboration" sheetId="18" r:id="R3eb4c49da1d44de7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Offline_Desktop" sheetId="19" r:id="R4136a1c8fe614ac7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data_Model" sheetId="20" r:id="R09d02b5033494869"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Storage_Interop" sheetId="21" r:id="R3290096cb29445da"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Security" sheetId="22" r:id="Rff9ac9b3f84a4d98"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="API_Contracts" sheetId="23" r:id="Rbf057d196bc54ee2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="State_Machines" sheetId="24" r:id="Ra936a70f08414350"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Error_Recovery" sheetId="25" r:id="Rb9335ddc010a4577"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cross_App_Relations" sheetId="26" r:id="Rd2cadeb33b0a464e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Performance" sheetId="27" r:id="R520b10e1698043a5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Accessibility" sheetId="28" r:id="Raf61cd54623d4c22"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test_Matrix" sheetId="29" r:id="R9cad89d592d04c96"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="30" r:id="Rbb19726ab8dc4701"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open_Questions" sheetId="31" r:id="R9bf7311456e94945"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Change_Log" sheetId="32" r:id="Rd37fd9440dbc4fd3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Implementation_Status" sheetId="33" r:id="Rc73fae2afb1b4aea"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -931,7 +931,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3698178412a54cb6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R26198f47d5ee4393"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1274,7 +1274,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd3dc7490a3ae424c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rce6a7ce7670249f3"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1677,7 +1677,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6e27476875704063"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2d9e213649244a11"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2200,7 +2200,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R187f5da7279a4820"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R67789b63d6a942c6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2831,10 +2831,27 @@
         <x:v>폴더를 선택하면 생성 대상, 파일을 선택하면 부모 폴더를 대상으로 삼는다. 계정 경계·quota·고정 폴더·휴지통 정책을 우회하지 않는다.</x:v>
       </x:c>
     </x:row>
+    <x:row r="37">
+      <x:c r="A37" s="13" t="str">
+        <x:v>노트북 트리</x:v>
+      </x:c>
+      <x:c r="B37" s="13" t="str">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C37" s="13" t="str">
+        <x:v>선택 · 접기/펼치기 · 새 페이지 · 터미널 · 개발 도구 · NAS에서 열기 · 표시 이름 변경 · 경로 복사</x:v>
+      </x:c>
+      <x:c r="D37" s="13" t="str">
+        <x:v>notebook kind·available 상태·현재 선택·revision</x:v>
+      </x:c>
+      <x:c r="E37" s="13" t="str">
+        <x:v>VS Code처럼 대상 상태에 맞는 동작만 노출한다. 인라인은 새 페이지와 더보기만 유지하며 표시 이름 변경은 실제 프로젝트 경로를 바꾸지 않는다.</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R61dc42c9921e4a5e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcedea74f221d4813"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3876,7 +3893,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdbd1f8ab664742c0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R18ef469a19d9476b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4136,7 +4153,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R34f8054838b743a6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R02b8c51121724409"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4379,7 +4396,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6d056392250f42f0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1c31723c202a4837"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4758,7 +4775,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R37a2296fda1f4b79"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9ae1aa6982604e45"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5018,7 +5035,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R74a12fba65e84d3b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re0a6159ab11f4dd7"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5210,7 +5227,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1dc929e6212f4f2d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R41bd70b4df664ba1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5343,7 +5360,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ree0be11a605f4528"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3ebf8d720d4447c7"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5756,7 +5773,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb5d208d767fc4c72"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra41158bc19b34822"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6016,7 +6033,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R60283478cb4a4fd7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbb9273a039344bba"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6463,7 +6480,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4e275feeb4814639"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1dc6ac3bb43c4cfd"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7063,7 +7080,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rce03b80a505e4a87"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6903b61ec50a4ec7"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7476,7 +7493,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5dda118de26f4e54"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9f13d9b8f2104e3b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7872,7 +7889,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R15a3a1167b044057"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R76937c1d023748aa"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8234,7 +8251,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8f14605d86b14d2a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R785d3ce27819423b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8511,7 +8528,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rafdbea19356b4b8e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc35b3eb457b14ec3"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8714,7 +8731,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd9d4128b865b43b9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R682ccf241b9848d6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9774,10 +9791,30 @@
         <x:v>M1-S</x:v>
       </x:c>
     </x:row>
+    <x:row r="53">
+      <x:c r="A53" s="13" t="str">
+        <x:v>UI-TREE-04</x:v>
+      </x:c>
+      <x:c r="B53" s="13" t="str">
+        <x:v>VS Code형 노트북 context menu·Open VSX 개발 도구</x:v>
+      </x:c>
+      <x:c r="C53" s="13" t="str">
+        <x:v>notes/project/legacy notebook, F2·우클릭, Open VSX 검색 실패·중복 추천·잘못된 ID·symlink manifest·다른 계정</x:v>
+      </x:c>
+      <x:c r="D53" s="13" t="str">
+        <x:v>대상별 메뉴가 분리되고 이름 변경 후 실제 경로가 유지된다. 검색 결과는 실행 가능성으로 과장되지 않으며 project만 .vscode/extensions.json을 안전하게 갱신한다.</x:v>
+      </x:c>
+      <x:c r="E53" s="13" t="str">
+        <x:v>unit+production build+NAS API+로그인 E2E</x:v>
+      </x:c>
+      <x:c r="F53" s="13" t="str">
+        <x:v>M1-S</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc30a8c90cc934b0a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R11cfdd93c8564ab7"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10255,10 +10292,27 @@
         <x:v>다중 NAS worker 또는 장시간 build farm으로 확장할 때 durable queue로 교체한다.</x:v>
       </x:c>
     </x:row>
+    <x:row r="28">
+      <x:c r="A28" s="13" t="str">
+        <x:v>DEC-027</x:v>
+      </x:c>
+      <x:c r="B28" s="13" t="str">
+        <x:v>채택·1차 구현</x:v>
+      </x:c>
+      <x:c r="C28" s="13" t="str">
+        <x:v>VS Code 확장은 NAS에서 임의 VSIX로 실행하지 않고 Open VSX 검색과 프로젝트별 권장 확장 목록으로 먼저 연결한다.</x:v>
+      </x:c>
+      <x:c r="D28" s="13" t="str">
+        <x:v>Monaco는 VS Code Extension Host가 아니며 임의 확장 실행은 사용자 코드 실행·공급망 위험을 동반한다. 프로젝트 노트북의 .vscode/extensions.json은 로컬 VS Code와 안전하게 연결된다.</x:v>
+      </x:c>
+      <x:c r="E28" s="13" t="str">
+        <x:v>검증된 언어별 LSP adapter와 격리 실행 정책이 준비되면 web extension 또는 language server 호환 범위를 기능별로 확대한다.</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf8931db38836432b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb20994c4965b48cd"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10399,7 +10453,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re81f75eb31f540fa"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R04a2de13c2b242ac"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10625,7 +10679,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra640dd860412438a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5449b45858c84dbe"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11125,10 +11179,30 @@
         <x:v>Codex</x:v>
       </x:c>
     </x:row>
+    <x:row r="25">
+      <x:c r="A25" s="13" t="str">
+        <x:v>2026-09-08</x:v>
+      </x:c>
+      <x:c r="B25" s="13" t="str">
+        <x:v>1.12-vscode-guided-tools</x:v>
+      </x:c>
+      <x:c r="C25" s="13" t="str">
+        <x:v>구현·로컬 검증 / 운영 배포·로그인 화면 검증 진행</x:v>
+      </x:c>
+      <x:c r="D25" s="13" t="str">
+        <x:v>VS Code 공식 Explorer·Tree View·Extension Host를 조사해 노트북 우클릭 메뉴, 표시 이름 변경, 하위 페이지, 프로젝트 개발 도구와 Open VSX 검색·권장 확장 저장을 구현했다. 임의 VSIX 실행은 금지했다.</x:v>
+      </x:c>
+      <x:c r="E25" s="13" t="str">
+        <x:v>backend 127 tests: 119 pass, 8 environment skips, 0 fail. production frontend build/PDF.js gate 통과.</x:v>
+      </x:c>
+      <x:c r="F25" s="13" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5b84f02935e242ea"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcf9884e2339a4a4a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11914,7 +11988,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4c1467cf1b014a33"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R813f6ea420f743af"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12197,7 +12271,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3ef3a6a8de6d4f2f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcf4743fab85842c3"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13015,10 +13089,95 @@
         <x:v>https://code.visualstudio.com/docs/editing/codebasics</x:v>
       </x:c>
     </x:row>
+    <x:row r="48">
+      <x:c r="A48" s="13" t="str">
+        <x:v>SRC-047</x:v>
+      </x:c>
+      <x:c r="B48" s="13" t="str">
+        <x:v>VS Code Contribution Points</x:v>
+      </x:c>
+      <x:c r="C48" s="13" t="str">
+        <x:v>https://code.visualstudio.com/api/references/contribution-points</x:v>
+      </x:c>
+      <x:c r="D48" s="13" t="str">
+        <x:v>Explorer 메뉴의 when 조건·그룹·submenu와 extension contribution 구조</x:v>
+      </x:c>
+      <x:c r="E48" s="13" t="str">
+        <x:v>2026-09-08</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49">
+      <x:c r="A49" s="13" t="str">
+        <x:v>SRC-048</x:v>
+      </x:c>
+      <x:c r="B49" s="13" t="str">
+        <x:v>VS Code Tree View API</x:v>
+      </x:c>
+      <x:c r="C49" s="13" t="str">
+        <x:v>https://code.visualstudio.com/api/extension-guides/tree-view</x:v>
+      </x:c>
+      <x:c r="D49" s="13" t="str">
+        <x:v>TreeItem contextValue·view/item/context 메뉴·workspace recommendations 참고</x:v>
+      </x:c>
+      <x:c r="E49" s="13" t="str">
+        <x:v>2026-09-08</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="50">
+      <x:c r="A50" s="13" t="str">
+        <x:v>SRC-049</x:v>
+      </x:c>
+      <x:c r="B50" s="13" t="str">
+        <x:v>VS Code Views UX</x:v>
+      </x:c>
+      <x:c r="C50" s="13" t="str">
+        <x:v>https://code.visualstudio.com/api/ux-guidelines/views</x:v>
+      </x:c>
+      <x:c r="D50" s="13" t="str">
+        <x:v>inline action은 중요 명령만 두고 나머지는 더보기/context menu로 이동</x:v>
+      </x:c>
+      <x:c r="E50" s="13" t="str">
+        <x:v>2026-09-08</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="51">
+      <x:c r="A51" s="13" t="str">
+        <x:v>SRC-050</x:v>
+      </x:c>
+      <x:c r="B51" s="13" t="str">
+        <x:v>VS Code Extension Host</x:v>
+      </x:c>
+      <x:c r="C51" s="13" t="str">
+        <x:v>https://code.visualstudio.com/api/advanced-topics/extension-host</x:v>
+      </x:c>
+      <x:c r="D51" s="13" t="str">
+        <x:v>local/web/remote extension host 분리와 Monaco 단독 실행의 차이</x:v>
+      </x:c>
+      <x:c r="E51" s="13" t="str">
+        <x:v>2026-09-08</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="52">
+      <x:c r="A52" s="13" t="str">
+        <x:v>SRC-051</x:v>
+      </x:c>
+      <x:c r="B52" s="13" t="str">
+        <x:v>Open VSX Registry API</x:v>
+      </x:c>
+      <x:c r="C52" s="13" t="str">
+        <x:v>https://github.com/eclipse-openvsx/openvsx/wiki/Registry-API</x:v>
+      </x:c>
+      <x:c r="D52" s="13" t="str">
+        <x:v>공개 검색·상세 REST endpoint와 extension identifier 형식</x:v>
+      </x:c>
+      <x:c r="E52" s="13" t="str">
+        <x:v>2026-09-08</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfc4bc31cbf1b4e20"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4681b80ce89a4b55"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13278,7 +13437,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R97da6cb6eb854cb3"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R345a65601b964331"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13538,7 +13697,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0be7d0a6cd4448e4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R338138aa9a3d4448"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13832,7 +13991,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R542d374a42da4abf"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re588de5594614627"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/programs/NAS_NOTE_STUDIO_SPEC.xlsx
+++ b/docs/programs/NAS_NOTE_STUDIO_SPEC.xlsx
@@ -2,39 +2,39 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="R808c4d15b4ba4d96"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Product_Vision" sheetId="2" r:id="Rdaa76c9242e349b6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decisions" sheetId="3" r:id="Rc91d6d3c7cfd44a3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Competitors" sheetId="4" r:id="Ra1c41495e7634d8b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open_Source" sheetId="5" r:id="R4116a1639fb445d3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source_Index" sheetId="6" r:id="Rbf7ecca071334b53"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Information_Architecture" sheetId="7" r:id="R767d1d14e17b4e60"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI_Layout" sheetId="8" r:id="R03d2260d16dd46c9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="User_Flows" sheetId="9" r:id="R46a12327b0e04a30"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Note_Types" sheetId="10" r:id="R9a36cb4b74da4bb4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Block_Catalog" sheetId="11" r:id="R6e3832c37a77414a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Slash_Commands" sheetId="12" r:id="R2010bf247df144b5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Context_Menus" sheetId="13" r:id="R9e34f2b11c3642cb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Keyboard_Shortcuts" sheetId="14" r:id="R0f7a444d6804467d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Database_Views" sheetId="15" r:id="Rb1e2c3a76ffd4c86"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Code_Text_Mode" sheetId="16" r:id="R9a0d180d9e784cdc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Python_Notebook" sheetId="17" r:id="R393ce84b00ef4424"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Collaboration" sheetId="18" r:id="R3eb4c49da1d44de7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Offline_Desktop" sheetId="19" r:id="R4136a1c8fe614ac7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data_Model" sheetId="20" r:id="R09d02b5033494869"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Storage_Interop" sheetId="21" r:id="R3290096cb29445da"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Security" sheetId="22" r:id="Rff9ac9b3f84a4d98"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="API_Contracts" sheetId="23" r:id="Rbf057d196bc54ee2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="State_Machines" sheetId="24" r:id="Ra936a70f08414350"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Error_Recovery" sheetId="25" r:id="Rb9335ddc010a4577"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cross_App_Relations" sheetId="26" r:id="Rd2cadeb33b0a464e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Performance" sheetId="27" r:id="R520b10e1698043a5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Accessibility" sheetId="28" r:id="Raf61cd54623d4c22"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test_Matrix" sheetId="29" r:id="R9cad89d592d04c96"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="30" r:id="Rbb19726ab8dc4701"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open_Questions" sheetId="31" r:id="R9bf7311456e94945"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Change_Log" sheetId="32" r:id="Rd37fd9440dbc4fd3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Implementation_Status" sheetId="33" r:id="Rc73fae2afb1b4aea"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="R8d4b0164a2cb4494"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Product_Vision" sheetId="2" r:id="R954eef30c0344346"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decisions" sheetId="3" r:id="R6e5db13f63284092"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Competitors" sheetId="4" r:id="R805ddeccf7474582"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open_Source" sheetId="5" r:id="R16a9e8e6a6c748b4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source_Index" sheetId="6" r:id="R96ec66bf28584c93"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Information_Architecture" sheetId="7" r:id="Recad9acb39304925"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI_Layout" sheetId="8" r:id="R1aa4bb76acf141a0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="User_Flows" sheetId="9" r:id="R4f16619e729c469f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Note_Types" sheetId="10" r:id="R9419b739474845bd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Block_Catalog" sheetId="11" r:id="R9eb341b0f8c34516"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Slash_Commands" sheetId="12" r:id="Refcc1df7a48242c2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Context_Menus" sheetId="13" r:id="Rd2ea691aa1164d71"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Keyboard_Shortcuts" sheetId="14" r:id="R29ffa21c0e014bbc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Database_Views" sheetId="15" r:id="Re051f936a2984bb7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Code_Text_Mode" sheetId="16" r:id="R2684c1db23944dc9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Python_Notebook" sheetId="17" r:id="Re537f14298a74675"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Collaboration" sheetId="18" r:id="R2853b24742ea418b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Offline_Desktop" sheetId="19" r:id="Rdcfefa8ff7584bbf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data_Model" sheetId="20" r:id="R38c491c411be4a8b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Storage_Interop" sheetId="21" r:id="R5040c47dd0ec4ccf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Security" sheetId="22" r:id="Ra6ff359b287d4e04"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="API_Contracts" sheetId="23" r:id="R0fc06a480f5440f4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="State_Machines" sheetId="24" r:id="R2b104d1fc84c4e62"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Error_Recovery" sheetId="25" r:id="R05cdd4757e1c4a3e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cross_App_Relations" sheetId="26" r:id="Rf169e65a8df9439c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Performance" sheetId="27" r:id="R14d69f4b17d14ffe"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Accessibility" sheetId="28" r:id="R4f2b0ba31d4c42f5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test_Matrix" sheetId="29" r:id="R33ad8ed4b34b464a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="30" r:id="Rc66961d456424702"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open_Questions" sheetId="31" r:id="Re2e457f3dff44026"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Change_Log" sheetId="32" r:id="R1f8a014a0de743c3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Implementation_Status" sheetId="33" r:id="Rfc4d306e6d7c4bd7"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -931,7 +931,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R26198f47d5ee4393"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R84583adf665f4e1a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1274,7 +1274,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rce6a7ce7670249f3"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5e4ed5a42c564833"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1677,7 +1677,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2d9e213649244a11"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3c23511529714e56"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2200,7 +2200,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R67789b63d6a942c6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcdeec036f08249c7"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2851,7 +2851,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcedea74f221d4813"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R55c8a03e18344770"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3893,7 +3893,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R18ef469a19d9476b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd504fbfaf8ab4591"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4153,7 +4153,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R02b8c51121724409"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf68e89dcfa4c48a0"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4396,7 +4396,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1c31723c202a4837"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R610d675c76f54817"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4775,7 +4775,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9ae1aa6982604e45"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R99c288af1f784dbb"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5035,7 +5035,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re0a6159ab11f4dd7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbbb54d1f34d84bbe"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5227,7 +5227,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R41bd70b4df664ba1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra175fae2da0e4faf"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5360,7 +5360,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3ebf8d720d4447c7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R204828cac83e4127"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5773,7 +5773,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra41158bc19b34822"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R73fb9b79dde04b09"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6033,7 +6033,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbb9273a039344bba"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R232f609d5f76446a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6480,7 +6480,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1dc6ac3bb43c4cfd"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5f73e35a6c694ef5"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7080,7 +7080,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6903b61ec50a4ec7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R051bb2a6a52e4c63"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7493,7 +7493,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9f13d9b8f2104e3b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc028bd916e944813"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7889,7 +7889,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R76937c1d023748aa"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd6388114d8a240e0"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8251,7 +8251,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R785d3ce27819423b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R038db081c5e447e6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8528,7 +8528,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc35b3eb457b14ec3"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rde746d082b46474c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8731,7 +8731,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R682ccf241b9848d6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5889b3b93d8843f8"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9814,7 +9814,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R11cfdd93c8564ab7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R96771e8fab5247ce"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10312,7 +10312,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb20994c4965b48cd"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5e66f5b9e3754a94"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10453,7 +10453,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R04a2de13c2b242ac"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R892129a94aa049e6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10679,7 +10679,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5449b45858c84dbe"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R60e3464ff73f41dd"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11187,13 +11187,13 @@
         <x:v>1.12-vscode-guided-tools</x:v>
       </x:c>
       <x:c r="C25" s="13" t="str">
-        <x:v>구현·로컬 검증 / 운영 배포·로그인 화면 검증 진행</x:v>
+        <x:v>완료·운영 배포 / 로그인 화면 E2E 대기</x:v>
       </x:c>
       <x:c r="D25" s="13" t="str">
         <x:v>VS Code 공식 Explorer·Tree View·Extension Host를 조사해 노트북 우클릭 메뉴, 표시 이름 변경, 하위 페이지, 프로젝트 개발 도구와 Open VSX 검색·권장 확장 저장을 구현했다. 임의 VSIX 실행은 금지했다.</x:v>
       </x:c>
       <x:c r="E25" s="13" t="str">
-        <x:v>backend 127 tests: 119 pass, 8 environment skips, 0 fail. production frontend build/PDF.js gate 통과.</x:v>
+        <x:v>로컬 127개 중 119 pass·8 skip, NAS 127개 중 121 pass·6 skip, 실패 0. production/PDF.js, Open VSX 200, 무인증 API 401, build/live hash 일치.</x:v>
       </x:c>
       <x:c r="F25" s="13" t="str">
         <x:v>Codex</x:v>
@@ -11202,7 +11202,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcf9884e2339a4a4a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R19fd57dc4e8b4a2c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11988,7 +11988,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R813f6ea420f743af"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6ea710393d5c47f8"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12271,7 +12271,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcf4743fab85842c3"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R279064879a184a88"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13177,7 +13177,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4681b80ce89a4b55"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbf2af20c67f34650"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13437,7 +13437,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R345a65601b964331"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9f8419abc9dc47b1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13697,7 +13697,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R338138aa9a3d4448"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc98ac225bf8f4695"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13991,7 +13991,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re588de5594614627"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rff001bc14969499c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/programs/NAS_NOTE_STUDIO_SPEC.xlsx
+++ b/docs/programs/NAS_NOTE_STUDIO_SPEC.xlsx
@@ -2,39 +2,39 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="R8d4b0164a2cb4494"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Product_Vision" sheetId="2" r:id="R954eef30c0344346"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decisions" sheetId="3" r:id="R6e5db13f63284092"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Competitors" sheetId="4" r:id="R805ddeccf7474582"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open_Source" sheetId="5" r:id="R16a9e8e6a6c748b4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source_Index" sheetId="6" r:id="R96ec66bf28584c93"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Information_Architecture" sheetId="7" r:id="Recad9acb39304925"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI_Layout" sheetId="8" r:id="R1aa4bb76acf141a0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="User_Flows" sheetId="9" r:id="R4f16619e729c469f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Note_Types" sheetId="10" r:id="R9419b739474845bd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Block_Catalog" sheetId="11" r:id="R9eb341b0f8c34516"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Slash_Commands" sheetId="12" r:id="Refcc1df7a48242c2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Context_Menus" sheetId="13" r:id="Rd2ea691aa1164d71"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Keyboard_Shortcuts" sheetId="14" r:id="R29ffa21c0e014bbc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Database_Views" sheetId="15" r:id="Re051f936a2984bb7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Code_Text_Mode" sheetId="16" r:id="R2684c1db23944dc9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Python_Notebook" sheetId="17" r:id="Re537f14298a74675"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Collaboration" sheetId="18" r:id="R2853b24742ea418b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Offline_Desktop" sheetId="19" r:id="Rdcfefa8ff7584bbf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data_Model" sheetId="20" r:id="R38c491c411be4a8b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Storage_Interop" sheetId="21" r:id="R5040c47dd0ec4ccf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Security" sheetId="22" r:id="Ra6ff359b287d4e04"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="API_Contracts" sheetId="23" r:id="R0fc06a480f5440f4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="State_Machines" sheetId="24" r:id="R2b104d1fc84c4e62"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Error_Recovery" sheetId="25" r:id="R05cdd4757e1c4a3e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cross_App_Relations" sheetId="26" r:id="Rf169e65a8df9439c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Performance" sheetId="27" r:id="R14d69f4b17d14ffe"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Accessibility" sheetId="28" r:id="R4f2b0ba31d4c42f5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test_Matrix" sheetId="29" r:id="R33ad8ed4b34b464a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="30" r:id="Rc66961d456424702"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open_Questions" sheetId="31" r:id="Re2e457f3dff44026"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Change_Log" sheetId="32" r:id="R1f8a014a0de743c3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Implementation_Status" sheetId="33" r:id="Rfc4d306e6d7c4bd7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="R100ecfb8b98a4ed2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Product_Vision" sheetId="2" r:id="R58506ad3f5b543f6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decisions" sheetId="3" r:id="R94c389d838da41cd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Competitors" sheetId="4" r:id="Rf7bca61d52144b52"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open_Source" sheetId="5" r:id="R7bfb6644953a49c3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source_Index" sheetId="6" r:id="R2780e2ec0746417d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Information_Architecture" sheetId="7" r:id="R2ce0b17398e74f2d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI_Layout" sheetId="8" r:id="R8740640c7d4e42a1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="User_Flows" sheetId="9" r:id="R226652804b5144c3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Note_Types" sheetId="10" r:id="Re969e79a536d48ed"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Block_Catalog" sheetId="11" r:id="Rb835d76ba41340f2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Slash_Commands" sheetId="12" r:id="R3a2c4c480d7f4c54"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Context_Menus" sheetId="13" r:id="R8985a90ec29847d6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Keyboard_Shortcuts" sheetId="14" r:id="Rc694d36d29e84f08"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Database_Views" sheetId="15" r:id="R1a357279d6aa41a0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Code_Text_Mode" sheetId="16" r:id="R4cea66df2df94918"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Python_Notebook" sheetId="17" r:id="Rc7fad7501cb74ba8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Collaboration" sheetId="18" r:id="R95b02bfede614a90"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Offline_Desktop" sheetId="19" r:id="R88676d9999404740"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data_Model" sheetId="20" r:id="Rd2956281d6964f37"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Storage_Interop" sheetId="21" r:id="Rdb8b06e531bd481c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Security" sheetId="22" r:id="Rcb7bae24f92a413a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="API_Contracts" sheetId="23" r:id="Rb7aab170b4e04f77"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="State_Machines" sheetId="24" r:id="Rf80f7823de9a49fb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Error_Recovery" sheetId="25" r:id="R1ea558f67a504c23"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cross_App_Relations" sheetId="26" r:id="Raa0680711d1a4704"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Performance" sheetId="27" r:id="R92f98f75c08b4c54"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Accessibility" sheetId="28" r:id="R4f88f2f1788440cb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test_Matrix" sheetId="29" r:id="Rd364c574ff5f42de"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="30" r:id="Rebc85ce65ae94aba"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open_Questions" sheetId="31" r:id="Rdf64cef5c4f7416d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Change_Log" sheetId="32" r:id="R1b7656d0c1934e90"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Implementation_Status" sheetId="33" r:id="R36e350829e644874"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -931,7 +931,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R84583adf665f4e1a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R14f380f0f64a4917"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1274,7 +1274,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5e4ed5a42c564833"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1fa14a42a488422c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1677,7 +1677,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3c23511529714e56"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R63461d3699f34d9a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2200,7 +2200,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcdeec036f08249c7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R52366173121544c2"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2851,7 +2851,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R55c8a03e18344770"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0b9d6fbbb8054bf5"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3893,7 +3893,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd504fbfaf8ab4591"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R22f588d288494274"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4153,7 +4153,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf68e89dcfa4c48a0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R96c574f7ab2d40b5"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4396,7 +4396,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R610d675c76f54817"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R369d7ecff1134866"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4775,7 +4775,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R99c288af1f784dbb"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R75da6551d53d49f1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5035,7 +5035,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbbb54d1f34d84bbe"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R11a8ed83f4f84efd"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5227,7 +5227,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra175fae2da0e4faf"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0b236bef6c4a466c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5360,7 +5360,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R204828cac83e4127"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3654cd44f31d456d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5773,7 +5773,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R73fb9b79dde04b09"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rabbf58c3d22a498e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6033,7 +6033,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R232f609d5f76446a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R779cc3c507174c6c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6480,7 +6480,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5f73e35a6c694ef5"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Reed2d4e50b7a4d45"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7080,7 +7080,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R051bb2a6a52e4c63"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1739b75bb836411b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7493,7 +7493,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc028bd916e944813"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R02125d26560d4024"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7889,7 +7889,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd6388114d8a240e0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1df5a9440b264bbb"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8251,7 +8251,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R038db081c5e447e6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc4978dfc5aea401c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8528,7 +8528,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rde746d082b46474c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd4958600e9124b7d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8731,7 +8731,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5889b3b93d8843f8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R88ed14b3ec944544"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9811,10 +9811,30 @@
         <x:v>M1-S</x:v>
       </x:c>
     </x:row>
+    <x:row r="54">
+      <x:c r="A54" s="13" t="str">
+        <x:v>UI-TREE-05</x:v>
+      </x:c>
+      <x:c r="B54" s="13" t="str">
+        <x:v>전체 노트북 목록·선택 노트북 전용 보기</x:v>
+      </x:c>
+      <x:c r="C54" s="13" t="str">
+        <x:v>여러 노트북·동일 이름·빈 노트북·검색·BACK·새로고침 복원·삭제된 scope·작성 중 문서·모바일 sidebar</x:v>
+      </x:c>
+      <x:c r="D54" s="13" t="str">
+        <x:v>전체 보기에는 노트북만, 전용 보기에는 선택 노트북 페이지와 도구만 보인다. BACK은 전체 목록으로 돌아가며 열린 문서와 자동 저장을 손상시키지 않는다.</x:v>
+      </x:c>
+      <x:c r="E54" s="13" t="str">
+        <x:v>static verifier+production build+NAS deployment+로그인 E2E</x:v>
+      </x:c>
+      <x:c r="F54" s="13" t="str">
+        <x:v>M1-S</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R96771e8fab5247ce"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4c14c02a261542f8"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10312,7 +10332,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5e66f5b9e3754a94"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re1f4cd333a8b47d2"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10453,7 +10473,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R892129a94aa049e6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R13f416c57d844180"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10679,7 +10699,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R60e3464ff73f41dd"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R82e0fa29f8fc4996"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11199,10 +11219,30 @@
         <x:v>Codex</x:v>
       </x:c>
     </x:row>
+    <x:row r="26">
+      <x:c r="A26" s="13" t="str">
+        <x:v>2026-09-08</x:v>
+      </x:c>
+      <x:c r="B26" s="13" t="str">
+        <x:v>1.13-notebook-drilldown</x:v>
+      </x:c>
+      <x:c r="C26" s="13" t="str">
+        <x:v>구현·로컬 검증 / 운영 배포 진행</x:v>
+      </x:c>
+      <x:c r="D26" s="13" t="str">
+        <x:v>노트북 목록과 선택 노트북 전용 페이지 트리를 분리하고 좌상단 BACK, 범위별 검색·도구, 장치별 전용 보기 복원과 삭제된 scope 자동 복구를 구현했다.</x:v>
+      </x:c>
+      <x:c r="E26" s="13" t="str">
+        <x:v>notebook scope/compact/UI/window verifier와 production/PDF.js build 통과.</x:v>
+      </x:c>
+      <x:c r="F26" s="13" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R19fd57dc4e8b4a2c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R416846337b674774"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11988,7 +12028,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6ea710393d5c47f8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbcb01e5d20ae4d43"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12271,7 +12311,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R279064879a184a88"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf9fddceb00494ae4"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13177,7 +13217,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbf2af20c67f34650"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R505f8aef6a8d475f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13434,10 +13474,27 @@
         <x:v>노트는 Notion식 여백과 가벼운 선을 유지하고 프로젝트 파일만 VS Code식 조작 밀도를 높인다.</x:v>
       </x:c>
     </x:row>
+    <x:row r="15">
+      <x:c r="A15" s="13" t="str">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="B15" s="13" t="str">
+        <x:v>노트북 탐색 단계</x:v>
+      </x:c>
+      <x:c r="C15" s="13" t="str">
+        <x:v>탐색 사이드바</x:v>
+      </x:c>
+      <x:c r="D15" s="13" t="str">
+        <x:v>전체 노트북 목록 → 선택 노트북의 페이지 트리</x:v>
+      </x:c>
+      <x:c r="E15" s="13" t="str">
+        <x:v>전체 보기에는 노트북만 표시한다. 노트북을 선택하면 해당 노트북 요소만 보이고 좌상단 BACK으로 전체 목록에 돌아간다.</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9f8419abc9dc47b1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R27eb12332c2e42b9"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13694,10 +13751,27 @@
         <x:v>검색 결과·휴지통·하위 페이지·2,000개 제한·긴 이름에서도 부모 관계와 선택 상태를 잃지 않는다.</x:v>
       </x:c>
     </x:row>
+    <x:row r="15">
+      <x:c r="A15" s="13" t="str">
+        <x:v>노트북 전용 보기</x:v>
+      </x:c>
+      <x:c r="B15" s="13" t="str">
+        <x:v>전체 목록: 노트북 행만 → 선택: BACK·노트북명·페이지 트리</x:v>
+      </x:c>
+      <x:c r="C15" s="13" t="str">
+        <x:v>노트북 선택, BACK, 노트북 검색, 이 노트북 검색, 새 페이지, 터미널, 더보기</x:v>
+      </x:c>
+      <x:c r="D15" s="13" t="str">
+        <x:v>전용 보기 상태는 activeNotebookId와 분리해 장치별 session view-state에 저장한다. BACK은 열린 문서를 닫거나 편집 내용을 버리지 않는다.</x:v>
+      </x:c>
+      <x:c r="E15" s="13" t="str">
+        <x:v>삭제되거나 접근 불가한 저장 상태는 전체 목록으로 자동 복구하고 다른 노트북의 페이지는 절대 섞어 표시하지 않는다.</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc98ac225bf8f4695"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf330ab5f0eaa4a9a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13988,10 +14062,27 @@
         <x:v>다른 owner session은 404. 닫기/숨김은 실행 중지가 아니며 120초 제한이 최종 회수한다.</x:v>
       </x:c>
     </x:row>
+    <x:row r="17">
+      <x:c r="A17" s="13" t="str">
+        <x:v>FLOW-NOTEBOOK-DRILLDOWN</x:v>
+      </x:c>
+      <x:c r="B17" s="13" t="str">
+        <x:v>전체 노트북 목록에서 한 노트북 선택</x:v>
+      </x:c>
+      <x:c r="C17" s="13" t="str">
+        <x:v>노트북 선택 → sidebarNotebookId 고정 → 검색어 초기화 → 해당 페이지 트리·도구만 표시 → BACK → 전체 목록</x:v>
+      </x:c>
+      <x:c r="D17" s="13" t="str">
+        <x:v>선택 노트북 안에서 페이지 생성·가져오기·터미널·검색을 수행하고 열린 편집 문서는 BACK에도 유지한다.</x:v>
+      </x:c>
+      <x:c r="E17" s="13" t="str">
+        <x:v>노트북이 삭제되거나 권한이 사라지면 저장된 scope를 폐기하고 전체 목록으로 복구한다.</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rff001bc14969499c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8879c4bdc6254cb7"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/programs/NAS_NOTE_STUDIO_SPEC.xlsx
+++ b/docs/programs/NAS_NOTE_STUDIO_SPEC.xlsx
@@ -2,39 +2,39 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="R100ecfb8b98a4ed2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Product_Vision" sheetId="2" r:id="R58506ad3f5b543f6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decisions" sheetId="3" r:id="R94c389d838da41cd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Competitors" sheetId="4" r:id="Rf7bca61d52144b52"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open_Source" sheetId="5" r:id="R7bfb6644953a49c3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source_Index" sheetId="6" r:id="R2780e2ec0746417d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Information_Architecture" sheetId="7" r:id="R2ce0b17398e74f2d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI_Layout" sheetId="8" r:id="R8740640c7d4e42a1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="User_Flows" sheetId="9" r:id="R226652804b5144c3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Note_Types" sheetId="10" r:id="Re969e79a536d48ed"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Block_Catalog" sheetId="11" r:id="Rb835d76ba41340f2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Slash_Commands" sheetId="12" r:id="R3a2c4c480d7f4c54"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Context_Menus" sheetId="13" r:id="R8985a90ec29847d6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Keyboard_Shortcuts" sheetId="14" r:id="Rc694d36d29e84f08"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Database_Views" sheetId="15" r:id="R1a357279d6aa41a0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Code_Text_Mode" sheetId="16" r:id="R4cea66df2df94918"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Python_Notebook" sheetId="17" r:id="Rc7fad7501cb74ba8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Collaboration" sheetId="18" r:id="R95b02bfede614a90"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Offline_Desktop" sheetId="19" r:id="R88676d9999404740"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data_Model" sheetId="20" r:id="Rd2956281d6964f37"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Storage_Interop" sheetId="21" r:id="Rdb8b06e531bd481c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Security" sheetId="22" r:id="Rcb7bae24f92a413a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="API_Contracts" sheetId="23" r:id="Rb7aab170b4e04f77"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="State_Machines" sheetId="24" r:id="Rf80f7823de9a49fb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Error_Recovery" sheetId="25" r:id="R1ea558f67a504c23"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cross_App_Relations" sheetId="26" r:id="Raa0680711d1a4704"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Performance" sheetId="27" r:id="R92f98f75c08b4c54"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Accessibility" sheetId="28" r:id="R4f88f2f1788440cb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test_Matrix" sheetId="29" r:id="Rd364c574ff5f42de"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="30" r:id="Rebc85ce65ae94aba"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open_Questions" sheetId="31" r:id="Rdf64cef5c4f7416d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Change_Log" sheetId="32" r:id="R1b7656d0c1934e90"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Implementation_Status" sheetId="33" r:id="R36e350829e644874"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="R076b2fc3881341e3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Product_Vision" sheetId="2" r:id="Rd4ccbaec887e4fe8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decisions" sheetId="3" r:id="R8704099fd2e74c61"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Competitors" sheetId="4" r:id="R7b3c1a08146d46bc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open_Source" sheetId="5" r:id="R2858c65d11c64678"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source_Index" sheetId="6" r:id="R3ecbe8ec28534c2b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Information_Architecture" sheetId="7" r:id="Rf1adeca5c8724c2d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI_Layout" sheetId="8" r:id="Rd103e9e96931426f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="User_Flows" sheetId="9" r:id="R42bbebad99554f21"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Note_Types" sheetId="10" r:id="Rd2edaa57a7564488"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Block_Catalog" sheetId="11" r:id="Ref43bd0daee94bbb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Slash_Commands" sheetId="12" r:id="R1720d6695f6a439b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Context_Menus" sheetId="13" r:id="R1e463fcda1e34808"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Keyboard_Shortcuts" sheetId="14" r:id="R19316ced33124932"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Database_Views" sheetId="15" r:id="R4556ecc3cba4403c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Code_Text_Mode" sheetId="16" r:id="R847b7233f09f4b44"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Python_Notebook" sheetId="17" r:id="Rbab976ad593a4d42"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Collaboration" sheetId="18" r:id="R07070e30ada24918"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Offline_Desktop" sheetId="19" r:id="R65945d20eb18485c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data_Model" sheetId="20" r:id="R4f77c39ea5954f98"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Storage_Interop" sheetId="21" r:id="R898be80d73e14793"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Security" sheetId="22" r:id="Rac46dc62465d44da"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="API_Contracts" sheetId="23" r:id="Ra73d9acb9b884cde"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="State_Machines" sheetId="24" r:id="R5ac807ee6ae04f4e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Error_Recovery" sheetId="25" r:id="R23d13b6b42a64e99"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cross_App_Relations" sheetId="26" r:id="R8b47f057a0814905"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Performance" sheetId="27" r:id="R4e24b401e9b14d78"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Accessibility" sheetId="28" r:id="Rd321276f630c474d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test_Matrix" sheetId="29" r:id="R83ef60747df34c49"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="30" r:id="R1f9657ea81db4060"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open_Questions" sheetId="31" r:id="R92a3ca4da9194b05"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Change_Log" sheetId="32" r:id="R302768e8263343f3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Implementation_Status" sheetId="33" r:id="Rd3fbc186b5204186"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -931,7 +931,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R14f380f0f64a4917"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9e90fd25d7fc42d8"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1274,7 +1274,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1fa14a42a488422c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc1e6c858f6d2450f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1677,7 +1677,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R63461d3699f34d9a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4c7e8eb32e5548c4"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2200,7 +2200,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R52366173121544c2"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9563d2de40654d36"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2851,7 +2851,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0b9d6fbbb8054bf5"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc2d60c45204445af"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3893,7 +3893,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R22f588d288494274"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbd4bbc0782014a60"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4153,7 +4153,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R96c574f7ab2d40b5"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4015331ed3c24594"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4396,7 +4396,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R369d7ecff1134866"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3bfed7bddfbd4cab"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4775,7 +4775,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R75da6551d53d49f1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3251bc0277364b62"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5035,7 +5035,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R11a8ed83f4f84efd"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2f96c800beab4437"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5227,7 +5227,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0b236bef6c4a466c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0153924679be4178"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5360,7 +5360,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3654cd44f31d456d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6ff57dd7580a4f82"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5773,7 +5773,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rabbf58c3d22a498e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbe1e85f718b8429c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6033,7 +6033,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R779cc3c507174c6c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2306c12fda7c4994"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6480,7 +6480,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Reed2d4e50b7a4d45"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re9eb1bed092e4b74"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7080,7 +7080,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1739b75bb836411b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3ce23ffc23474bff"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7493,7 +7493,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R02125d26560d4024"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1b43ae753a924dd9"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7889,7 +7889,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1df5a9440b264bbb"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdc518c0361cc4262"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8251,7 +8251,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc4978dfc5aea401c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R85cb395ae4f6404d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8528,7 +8528,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd4958600e9124b7d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc0964da454234e26"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8731,7 +8731,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R88ed14b3ec944544"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra4812cfc9f97434b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9834,7 +9834,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4c14c02a261542f8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rac7c99a52b724101"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10332,7 +10332,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re1f4cd333a8b47d2"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3c94496529294322"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10473,7 +10473,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R13f416c57d844180"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R79f8943cf4f943ac"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10699,7 +10699,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R82e0fa29f8fc4996"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd58196d8a4b24f15"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11227,13 +11227,13 @@
         <x:v>1.13-notebook-drilldown</x:v>
       </x:c>
       <x:c r="C26" s="13" t="str">
-        <x:v>구현·로컬 검증 / 운영 배포 진행</x:v>
+        <x:v>완료·운영 배포 / 로그인 실화면 E2E 대기</x:v>
       </x:c>
       <x:c r="D26" s="13" t="str">
         <x:v>노트북 목록과 선택 노트북 전용 페이지 트리를 분리하고 좌상단 BACK, 범위별 검색·도구, 장치별 전용 보기 복원과 삭제된 scope 자동 복구를 구현했다.</x:v>
       </x:c>
       <x:c r="E26" s="13" t="str">
-        <x:v>notebook scope/compact/UI/window verifier와 production/PDF.js build 통과.</x:v>
+        <x:v>scope·compact·UI·window verifier, production/PDF.js, build/live main+lazy chunk hash 일치, 내부·공개 200.</x:v>
       </x:c>
       <x:c r="F26" s="13" t="str">
         <x:v>Codex</x:v>
@@ -11242,7 +11242,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R416846337b674774"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5087fb4bf6934eab"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12028,7 +12028,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbcb01e5d20ae4d43"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R44a995d59ab8466e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12311,7 +12311,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf9fddceb00494ae4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5073465599924a18"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13217,7 +13217,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R505f8aef6a8d475f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf859729d52144e4a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13494,7 +13494,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R27eb12332c2e42b9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R52daf9217c644add"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13771,7 +13771,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf330ab5f0eaa4a9a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8b252928c83e4bc2"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -14082,7 +14082,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8879c4bdc6254cb7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb7f4d3c84d824071"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/programs/NAS_NOTE_STUDIO_SPEC.xlsx
+++ b/docs/programs/NAS_NOTE_STUDIO_SPEC.xlsx
@@ -2,39 +2,39 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="R076b2fc3881341e3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Product_Vision" sheetId="2" r:id="Rd4ccbaec887e4fe8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decisions" sheetId="3" r:id="R8704099fd2e74c61"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Competitors" sheetId="4" r:id="R7b3c1a08146d46bc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open_Source" sheetId="5" r:id="R2858c65d11c64678"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source_Index" sheetId="6" r:id="R3ecbe8ec28534c2b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Information_Architecture" sheetId="7" r:id="Rf1adeca5c8724c2d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI_Layout" sheetId="8" r:id="Rd103e9e96931426f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="User_Flows" sheetId="9" r:id="R42bbebad99554f21"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Note_Types" sheetId="10" r:id="Rd2edaa57a7564488"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Block_Catalog" sheetId="11" r:id="Ref43bd0daee94bbb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Slash_Commands" sheetId="12" r:id="R1720d6695f6a439b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Context_Menus" sheetId="13" r:id="R1e463fcda1e34808"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Keyboard_Shortcuts" sheetId="14" r:id="R19316ced33124932"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Database_Views" sheetId="15" r:id="R4556ecc3cba4403c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Code_Text_Mode" sheetId="16" r:id="R847b7233f09f4b44"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Python_Notebook" sheetId="17" r:id="Rbab976ad593a4d42"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Collaboration" sheetId="18" r:id="R07070e30ada24918"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Offline_Desktop" sheetId="19" r:id="R65945d20eb18485c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data_Model" sheetId="20" r:id="R4f77c39ea5954f98"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Storage_Interop" sheetId="21" r:id="R898be80d73e14793"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Security" sheetId="22" r:id="Rac46dc62465d44da"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="API_Contracts" sheetId="23" r:id="Ra73d9acb9b884cde"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="State_Machines" sheetId="24" r:id="R5ac807ee6ae04f4e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Error_Recovery" sheetId="25" r:id="R23d13b6b42a64e99"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cross_App_Relations" sheetId="26" r:id="R8b47f057a0814905"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Performance" sheetId="27" r:id="R4e24b401e9b14d78"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Accessibility" sheetId="28" r:id="Rd321276f630c474d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test_Matrix" sheetId="29" r:id="R83ef60747df34c49"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="30" r:id="R1f9657ea81db4060"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open_Questions" sheetId="31" r:id="R92a3ca4da9194b05"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Change_Log" sheetId="32" r:id="R302768e8263343f3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Implementation_Status" sheetId="33" r:id="Rd3fbc186b5204186"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="Re0760ccd00f148f3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Product_Vision" sheetId="2" r:id="R9f79fcae1844417c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decisions" sheetId="3" r:id="R8a4e7f118d494745"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Competitors" sheetId="4" r:id="R8fbdd66f89414674"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open_Source" sheetId="5" r:id="Re651977d20c14330"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source_Index" sheetId="6" r:id="Re44201c70f004194"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Information_Architecture" sheetId="7" r:id="Rdf90f41eb3f44fbb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI_Layout" sheetId="8" r:id="R16a515568bb04947"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="User_Flows" sheetId="9" r:id="R795a3236054f4217"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Note_Types" sheetId="10" r:id="R1989984ad8aa4876"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Block_Catalog" sheetId="11" r:id="R07891618a3704161"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Slash_Commands" sheetId="12" r:id="R7d1afe8d22b74409"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Context_Menus" sheetId="13" r:id="Rbc9f5752e7ea48e1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Keyboard_Shortcuts" sheetId="14" r:id="R55ebe23dc34e4084"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Database_Views" sheetId="15" r:id="R455ed7773cba4192"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Code_Text_Mode" sheetId="16" r:id="R36dea58962ba49d2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Python_Notebook" sheetId="17" r:id="R8631fcba78e94ee1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Collaboration" sheetId="18" r:id="Rc7ed2b3caeb1479a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Offline_Desktop" sheetId="19" r:id="R555b1f55d8164a43"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data_Model" sheetId="20" r:id="R9a557c3c40f04034"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Storage_Interop" sheetId="21" r:id="R874b46eed1dc4431"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Security" sheetId="22" r:id="Rd9a2c77408d34bef"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="API_Contracts" sheetId="23" r:id="Rbf9660522ffb49e5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="State_Machines" sheetId="24" r:id="R876d6958058f4390"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Error_Recovery" sheetId="25" r:id="Rbd1d9c92e3744313"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cross_App_Relations" sheetId="26" r:id="R45bae0cf70234e7b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Performance" sheetId="27" r:id="Reb9379c2b5aa426b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Accessibility" sheetId="28" r:id="Raf9cd708c03a45ce"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test_Matrix" sheetId="29" r:id="Rb237c55ae5774fe1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="30" r:id="R1f9519014be04f36"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open_Questions" sheetId="31" r:id="R4ba48598570f4c5b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Change_Log" sheetId="32" r:id="Rb1fc36b93eff4e69"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Implementation_Status" sheetId="33" r:id="R2612f15685b44dd8"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -931,7 +931,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9e90fd25d7fc42d8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf7254051b1484a9b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1274,7 +1274,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc1e6c858f6d2450f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R33243e6aac3540c3"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1677,7 +1677,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4c7e8eb32e5548c4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ree065e08032249e5"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2200,7 +2200,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9563d2de40654d36"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdb6e3b1857184d17"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2851,7 +2851,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc2d60c45204445af"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc5e2e0e7817340c1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3893,7 +3893,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbd4bbc0782014a60"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rda72a5b4a6144e3d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4153,7 +4153,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4015331ed3c24594"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R442c1c7a0994493e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4396,7 +4396,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3bfed7bddfbd4cab"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R89a6966d961d4f93"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4775,7 +4775,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3251bc0277364b62"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4a05bd1f128a4928"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5035,7 +5035,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2f96c800beab4437"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra6f164b5a8a346e0"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5227,7 +5227,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0153924679be4178"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R308a8834fca74f6a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5360,7 +5360,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6ff57dd7580a4f82"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rae06b1d160e14c51"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5773,7 +5773,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbe1e85f718b8429c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4db7f001500b4c08"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6033,7 +6033,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2306c12fda7c4994"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfdf1e489debc4d67"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6480,7 +6480,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re9eb1bed092e4b74"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1bb1d26bfdf14633"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7080,7 +7080,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3ce23ffc23474bff"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4d40ed6b34854983"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7493,7 +7493,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1b43ae753a924dd9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Red95712a42e24af0"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7889,7 +7889,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdc518c0361cc4262"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcc820b00fe144df6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8251,7 +8251,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R85cb395ae4f6404d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R84da82b2afb94aa1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8528,7 +8528,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc0964da454234e26"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re6ada5b3f2aa468c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8731,7 +8731,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra4812cfc9f97434b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re1cbb52fd10f4b2e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9831,10 +9831,30 @@
         <x:v>M1-S</x:v>
       </x:c>
     </x:row>
+    <x:row r="55" ht="96" customHeight="1">
+      <x:c r="A55" s="12" t="str">
+        <x:v>UI-TREE-06</x:v>
+      </x:c>
+      <x:c r="B55" s="12" t="str">
+        <x:v>전체 목록 chevron·전용 상단 밀도</x:v>
+      </x:c>
+      <x:c r="C55" s="12" t="str">
+        <x:v>빈/다중/긴 이름 노트북, 인라인 펼침·접기, child 선택, 행 선택, BACK, 전체/전용 검색, 새로고침, 좁은 폭, 키보드·스크린리더 이름</x:v>
+      </x:c>
+      <x:c r="D55" s="12" t="str">
+        <x:v>chevron은 해당 노트북만 토글하고 행 선택은 전용 보기로 들어간다. 전용 상단은 핵심 4요소만 보이며 보조 동작은 더보기에서 손실 없이 접근된다.</x:v>
+      </x:c>
+      <x:c r="E55" s="12" t="str">
+        <x:v>static verifier+production build+NAS deployment+로그인 E2E</x:v>
+      </x:c>
+      <x:c r="F55" s="12" t="str">
+        <x:v>M1-S</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rac7c99a52b724101"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4fdf39ad605f47b8"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10332,7 +10352,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3c94496529294322"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R541c66be02234730"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10473,7 +10493,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R79f8943cf4f943ac"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R43105e1f7fbb4b3e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10699,7 +10719,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd58196d8a4b24f15"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc83b2f38113046d5"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11239,10 +11259,30 @@
         <x:v>Codex</x:v>
       </x:c>
     </x:row>
+    <x:row r="27" ht="88" customHeight="1">
+      <x:c r="A27" s="12" t="str">
+        <x:v>2026-09-08</x:v>
+      </x:c>
+      <x:c r="B27" s="12" t="str">
+        <x:v>1.13.1-notebook-inline-expand</x:v>
+      </x:c>
+      <x:c r="C27" s="12" t="str">
+        <x:v>구현 완료·운영 배포 대기 / 로그인 실화면 E2E 대기</x:v>
+      </x:c>
+      <x:c r="D27" s="12" t="str">
+        <x:v>전체 노트북 행에 독립 chevron과 선택적 하위 페이지 트리를 추가하고, 전용 상단은 BACK·이름·새 페이지·더보기로 간소화했다. 전체 검색과 하위 트리 데이터도 분리했다.</x:v>
+      </x:c>
+      <x:c r="E27" s="12" t="str">
+        <x:v>scope·compact·UI contract·window manager verifier, production/PDF.js build 통과. 운영 검증은 배포 뒤 상태 갱신.</x:v>
+      </x:c>
+      <x:c r="F27" s="12" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5087fb4bf6934eab"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2d34e99c6a6b4fd4"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12028,7 +12068,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R44a995d59ab8466e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re3662e2bed40449a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12311,7 +12351,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5073465599924a18"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R49b688d7feab41db"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13217,7 +13257,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf859729d52144e4a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5b7b4b8e99eb41c9"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13494,7 +13534,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R52daf9217c644add"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3904fa819a4444be"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13768,10 +13808,27 @@
         <x:v>삭제되거나 접근 불가한 저장 상태는 전체 목록으로 자동 복구하고 다른 노트북의 페이지는 절대 섞어 표시하지 않는다.</x:v>
       </x:c>
     </x:row>
+    <x:row r="16" ht="96" customHeight="1">
+      <x:c r="A16" s="12" t="str">
+        <x:v>전체 목록 선택 펼침·전용 compact bar</x:v>
+      </x:c>
+      <x:c r="B16" s="12" t="str">
+        <x:v>전체: chevron·종류 아이콘·노트북명·페이지 수·더보기 / 전용: BACK·노트북명·새 페이지·더보기</x:v>
+      </x:c>
+      <x:c r="C16" s="12" t="str">
+        <x:v>chevron은 인라인 하위 트리만 토글하고 행 선택은 전용 보기로 진입한다. 터미널·전체 접기·사이드바 숨기기는 더보기에 둔다.</x:v>
+      </x:c>
+      <x:c r="D16" s="12" t="str">
+        <x:v>아이콘과 텍스트는 한 줄을 유지하고 긴 이름은 말줄임한다. chevron은 page가 없으면 숨기며 클릭 이벤트를 행에 전파하지 않는다.</x:v>
+      </x:c>
+      <x:c r="E16" s="12" t="str">
+        <x:v>전체 검색은 노트북명만 필터링하며 펼친 트리의 page 데이터와 개수를 잘라내지 않는다.</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8b252928c83e4bc2"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rebc5200b3c2e47bf"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -14079,10 +14136,27 @@
         <x:v>노트북이 삭제되거나 권한이 사라지면 저장된 scope를 폐기하고 전체 목록으로 복구한다.</x:v>
       </x:c>
     </x:row>
+    <x:row r="18" ht="88" customHeight="1">
+      <x:c r="A18" s="12" t="str">
+        <x:v>FLOW-NOTEBOOK-INLINE-EXPAND</x:v>
+      </x:c>
+      <x:c r="B18" s="12" t="str">
+        <x:v>전체 노트북 목록</x:v>
+      </x:c>
+      <x:c r="C18" s="12" t="str">
+        <x:v>노트북 왼쪽 chevron → 해당 하위 페이지 인라인 확인 → chevron 재선택으로 접기 / 노트북 행 선택 → 전용 보기 → BACK</x:v>
+      </x:c>
+      <x:c r="D18" s="12" t="str">
+        <x:v>빠른 구조 확인과 집중 탐색을 같은 목록에서 구분하고 펼침 상태를 계정·장치 view-state로 복원한다.</x:v>
+      </x:c>
+      <x:c r="E18" s="12" t="str">
+        <x:v>chevron은 전용 보기로 진입하지 않는다. 삭제·권한 회수된 노트북 상태는 렌더링하지 않으며 전체 검색이 하위 데이터에 영향을 주지 않는다.</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb7f4d3c84d824071"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc8dc96550dc84bd6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/programs/NAS_NOTE_STUDIO_SPEC.xlsx
+++ b/docs/programs/NAS_NOTE_STUDIO_SPEC.xlsx
@@ -2,39 +2,39 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="Re0760ccd00f148f3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Product_Vision" sheetId="2" r:id="R9f79fcae1844417c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decisions" sheetId="3" r:id="R8a4e7f118d494745"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Competitors" sheetId="4" r:id="R8fbdd66f89414674"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open_Source" sheetId="5" r:id="Re651977d20c14330"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source_Index" sheetId="6" r:id="Re44201c70f004194"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Information_Architecture" sheetId="7" r:id="Rdf90f41eb3f44fbb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI_Layout" sheetId="8" r:id="R16a515568bb04947"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="User_Flows" sheetId="9" r:id="R795a3236054f4217"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Note_Types" sheetId="10" r:id="R1989984ad8aa4876"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Block_Catalog" sheetId="11" r:id="R07891618a3704161"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Slash_Commands" sheetId="12" r:id="R7d1afe8d22b74409"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Context_Menus" sheetId="13" r:id="Rbc9f5752e7ea48e1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Keyboard_Shortcuts" sheetId="14" r:id="R55ebe23dc34e4084"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Database_Views" sheetId="15" r:id="R455ed7773cba4192"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Code_Text_Mode" sheetId="16" r:id="R36dea58962ba49d2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Python_Notebook" sheetId="17" r:id="R8631fcba78e94ee1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Collaboration" sheetId="18" r:id="Rc7ed2b3caeb1479a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Offline_Desktop" sheetId="19" r:id="R555b1f55d8164a43"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data_Model" sheetId="20" r:id="R9a557c3c40f04034"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Storage_Interop" sheetId="21" r:id="R874b46eed1dc4431"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Security" sheetId="22" r:id="Rd9a2c77408d34bef"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="API_Contracts" sheetId="23" r:id="Rbf9660522ffb49e5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="State_Machines" sheetId="24" r:id="R876d6958058f4390"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Error_Recovery" sheetId="25" r:id="Rbd1d9c92e3744313"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cross_App_Relations" sheetId="26" r:id="R45bae0cf70234e7b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Performance" sheetId="27" r:id="Reb9379c2b5aa426b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Accessibility" sheetId="28" r:id="Raf9cd708c03a45ce"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test_Matrix" sheetId="29" r:id="Rb237c55ae5774fe1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="30" r:id="R1f9519014be04f36"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open_Questions" sheetId="31" r:id="R4ba48598570f4c5b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Change_Log" sheetId="32" r:id="Rb1fc36b93eff4e69"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Implementation_Status" sheetId="33" r:id="R2612f15685b44dd8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="R652c0c82d4774fc1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Product_Vision" sheetId="2" r:id="Rcbd4564129cb4606"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decisions" sheetId="3" r:id="R482dbb384aeb4e9d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Competitors" sheetId="4" r:id="R2bfdfb6b7bcb4bdc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open_Source" sheetId="5" r:id="R895bc709f0c1419a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source_Index" sheetId="6" r:id="Rc2a2896bb10d4dd6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Information_Architecture" sheetId="7" r:id="Rf341062cf2ca4328"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI_Layout" sheetId="8" r:id="Re93aef08404447ce"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="User_Flows" sheetId="9" r:id="Rd4226392c9124a90"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Note_Types" sheetId="10" r:id="Re7a12ccf3f0a42d5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Block_Catalog" sheetId="11" r:id="R676d1219b8a64cb6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Slash_Commands" sheetId="12" r:id="R6722c17b607b4986"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Context_Menus" sheetId="13" r:id="Ref3b2bf3bc884d07"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Keyboard_Shortcuts" sheetId="14" r:id="R0577e6e3c5d74604"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Database_Views" sheetId="15" r:id="R44918c1bb32c4be7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Code_Text_Mode" sheetId="16" r:id="Ra47f7e237a474b4c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Python_Notebook" sheetId="17" r:id="Rf2d78b4aaee14741"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Collaboration" sheetId="18" r:id="R743838e9b9dd4458"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Offline_Desktop" sheetId="19" r:id="R4062de26d8304a77"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data_Model" sheetId="20" r:id="Rd183a0f25f1b47db"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Storage_Interop" sheetId="21" r:id="R93366813789b43f8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Security" sheetId="22" r:id="Rf64d31fa11534087"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="API_Contracts" sheetId="23" r:id="R11b9d5539340458a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="State_Machines" sheetId="24" r:id="R68ccbcb302df4bcd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Error_Recovery" sheetId="25" r:id="R9d92bf837cd04632"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cross_App_Relations" sheetId="26" r:id="R9ea92b63e9d84162"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Performance" sheetId="27" r:id="R47de13a1729f4d97"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Accessibility" sheetId="28" r:id="R1b3877d94c1c40a2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test_Matrix" sheetId="29" r:id="Rf5bc30b0d65d4ee3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="30" r:id="Raf2335b454b942b0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open_Questions" sheetId="31" r:id="Re5cd6a9176c74595"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Change_Log" sheetId="32" r:id="R1fd1916b2eef403a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Implementation_Status" sheetId="33" r:id="R4a3072d0d57642a8"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -931,7 +931,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf7254051b1484a9b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfc005d1dc05346fe"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1274,7 +1274,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R33243e6aac3540c3"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rac29b413a863459e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1677,7 +1677,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ree065e08032249e5"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re7b28997f4224453"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2200,7 +2200,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdb6e3b1857184d17"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R721c6470e7e54b9a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2851,7 +2851,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc5e2e0e7817340c1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd693b6dc431f46be"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3893,7 +3893,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rda72a5b4a6144e3d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3dbef734672542cf"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4153,7 +4153,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R442c1c7a0994493e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0747454022024410"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4396,7 +4396,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R89a6966d961d4f93"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R64e71abaab73443e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4775,7 +4775,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4a05bd1f128a4928"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R96a500508e1d43ca"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5035,7 +5035,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra6f164b5a8a346e0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3276f40b11ac4445"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5227,7 +5227,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R308a8834fca74f6a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R195aca704cfb48f4"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5360,7 +5360,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rae06b1d160e14c51"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re7f2774d6aa64562"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5773,7 +5773,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4db7f001500b4c08"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbddcf735234f4d2c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6033,7 +6033,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfdf1e489debc4d67"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R157d7f7790984480"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6480,7 +6480,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1bb1d26bfdf14633"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0e4171c282794157"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7080,7 +7080,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4d40ed6b34854983"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9deddb37cfd84aa3"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7493,7 +7493,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Red95712a42e24af0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6971d24dc44e4725"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7889,7 +7889,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcc820b00fe144df6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9a3e463c698548fa"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8251,7 +8251,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R84da82b2afb94aa1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcb9c4a43b2904334"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8528,7 +8528,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re6ada5b3f2aa468c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9b67fb866ae94c70"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8731,7 +8731,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re1cbb52fd10f4b2e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re4bfc56f0f22474d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9854,7 +9854,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4fdf39ad605f47b8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4527c1cd00374486"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10352,7 +10352,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R541c66be02234730"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R89968c0a976a4214"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10493,7 +10493,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R43105e1f7fbb4b3e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R576af4f68ee54cbd"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10719,7 +10719,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc83b2f38113046d5"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfb28ec89fb914cd7"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11267,13 +11267,13 @@
         <x:v>1.13.1-notebook-inline-expand</x:v>
       </x:c>
       <x:c r="C27" s="12" t="str">
-        <x:v>구현 완료·운영 배포 대기 / 로그인 실화면 E2E 대기</x:v>
+        <x:v>완료·운영 배포 / 로그인 실화면 E2E 대기</x:v>
       </x:c>
       <x:c r="D27" s="12" t="str">
         <x:v>전체 노트북 행에 독립 chevron과 선택적 하위 페이지 트리를 추가하고, 전용 상단은 BACK·이름·새 페이지·더보기로 간소화했다. 전체 검색과 하위 트리 데이터도 분리했다.</x:v>
       </x:c>
       <x:c r="E27" s="12" t="str">
-        <x:v>scope·compact·UI contract·window manager verifier, production/PDF.js build 통과. 운영 검증은 배포 뒤 상태 갱신.</x:v>
+        <x:v>NAS verifier 4종, production/PDF.js build, 운영 main·lazy chunk SHA-256 일치, 내부·공개 HTTP 200, 필수 6개 서비스 active, PM2 msp-backend online.</x:v>
       </x:c>
       <x:c r="F27" s="12" t="str">
         <x:v>Codex</x:v>
@@ -11282,7 +11282,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2d34e99c6a6b4fd4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R835cb1dd04c1472d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12068,7 +12068,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re3662e2bed40449a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc9a610ed32ab41a5"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12351,7 +12351,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R49b688d7feab41db"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R03bec011f4424cdd"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13257,7 +13257,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5b7b4b8e99eb41c9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1728b58c28f24a06"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13534,7 +13534,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3904fa819a4444be"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7e5bb67f1c7e44b3"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13828,7 +13828,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rebc5200b3c2e47bf"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3f08e9e01e5e44ce"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -14156,7 +14156,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc8dc96550dc84bd6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7dce995b1b5f4cd6"/>
   </x:tableParts>
 </x:worksheet>
 </file>